--- a/docs/tester.xlsx
+++ b/docs/tester.xlsx
@@ -577,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O476"/>
+  <dimension ref="A1:O574"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10" customWidth="1" style="36" min="1" max="1"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="N3" s="25" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O3" s="21" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="N5" s="25" t="inlineStr">
         <is>
-          <t>0.09s</t>
+          <t>0.06s</t>
         </is>
       </c>
       <c r="O5" s="21" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="N7" s="25" t="inlineStr">
         <is>
-          <t>0.08s</t>
+          <t>0.06s</t>
         </is>
       </c>
       <c r="O7" s="21" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="N9" s="25" t="inlineStr">
         <is>
-          <t>0.84s</t>
+          <t>1.04s</t>
         </is>
       </c>
       <c r="O9" s="21" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="N10" s="13" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.03s</t>
         </is>
       </c>
       <c r="O10" s="21" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="N12" s="13" t="inlineStr">
         <is>
-          <t>0.17s</t>
+          <t>0.20s</t>
         </is>
       </c>
       <c r="O12" s="21" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="N14" s="13" t="inlineStr">
         <is>
-          <t>0.32s</t>
+          <t>0.31s</t>
         </is>
       </c>
       <c r="O14" s="21" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="N17" s="25" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O17" s="21" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="N18" s="13" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O18" s="21" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="N19" s="25" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O19" s="21" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="N20" s="13" t="inlineStr">
         <is>
-          <t>0.06s</t>
+          <t>0.05s</t>
         </is>
       </c>
       <c r="O20" s="21" t="inlineStr">
@@ -2395,7 +2395,7 @@
       <c r="G21" s="34" t="inlineStr">
         <is>
           <t>ได้  
-นักศึกษาสามารถเรียนวิชาฐานข้อมูลในปีที่ 4 ได้ เนื่องจากหลักสูตรมีวิชาบังคับก่อนอย่าง 06066300 แนวคิดระบบฐานข้อมูล (ปีที่ 2 ภาคการศึกษาที่ 1) และมีวิชาที่เกี่ยวข้องในปีที่ 4 ได้แก่ 06026246 หัวข้อพิเศษทางวิศวกรรมข้อมูล 1 และ 06026247 หัวข้อพิเศษทางวิศวกรรมข้อมูล 2 ซึ่งจัดอยู่ในกลุ่มวิชาเลือกเฉพาะแขนง โดยมีวิชาบังคับก่อนคือ 06026212 การสร้างคลังข้อมูล และ 06026213 ระบบข้อมูลมหัต ที่เรียนในปีที่ 3 ภาคการศึกษาที่ 1 และ 2 ตามลำดับ</t>
+นักศึกษาสามารถเรียนวิชาฐานข้อมูลในปีที่ 4 ได้ เนื่องจากหลักสูตรมีวิชาบังคับที่เกี่ยวข้องกับฐานข้อมูล เช่น 06026246 ระบบฐานข้อมูลแบบกระจาย (DISTRIBUTED DATABASE SYSTEMS) ซึ่งเป็นวิชาเลือกในกลุ่มวิชาเลือกหรือกลุ่มวิชาชีพเฉพาะด้าน จัดสอนในปีที่ 4 ภาคการศึกษาที่ 2 และไม่มีข้อกำหนดวิชาบังคับก่อนที่ขัดแย้งกับการเรียนในปีนี้ โดยวิชาดังกล่าวมีรหัส 06026246 ชื่อว่า "ระบบฐานข้อมูลแบบกระจาย" จำนวน 3 หน่วยกิต ประเภทวิชาเลือก (กลุ่มวิชาเลือกหรือกลุ่มวิชาชีพเฉพาะด้าน) ภาคการศึกษาที่ 2 ปีที่ 4.</t>
         </is>
       </c>
       <c r="H21" s="34" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="K21" s="19" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L21" s="21" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="N21" s="13" t="inlineStr">
         <is>
-          <t>1.74s</t>
+          <t>2.21s</t>
         </is>
       </c>
       <c r="O21" s="21" t="inlineStr">
@@ -2471,7 +2471,7 @@
       <c r="G22" s="35" t="inlineStr">
         <is>
           <t>ไม่ได้  
-วิชา 06026212 การสร้างคลังข้อมูล เป็นวิชาบังคับในปีที่ 3 ภาคการศึกษาที่ 1 และมีข้อกำหนดให้ต้องผ่านวิชา 06066300 แนวคิดระบบฐานข้อมูล ซึ่งเป็นวิชาบังคับในปีที่ 2 ภาคการศึกษาที่ 1 ก่อนจึงจะสามารถลงทะเบียนได้</t>
+วิชา 06026212 การสร้างคลังข้อมูล เป็นวิชาบังคับที่ต้องเรียนหลังจากผ่านวิชา 06066300 แนวคิดระบบฐานข้อมูล ซึ่งจัดสอนในปีที่ 2 ภาคการศึกษาที่ 1 ดังนั้นจึงไม่สามารถลงวิชานี้ได้ในปีที่ 2 เนื่องจากยังไม่ผ่านวิชาพื้นฐานที่กำหนดไว้</t>
         </is>
       </c>
       <c r="H22" s="35" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="N22" s="25" t="inlineStr">
         <is>
-          <t>1.13s</t>
+          <t>1.56s</t>
         </is>
       </c>
       <c r="O22" s="21" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="N23" s="13" t="inlineStr">
         <is>
-          <t>0.10s</t>
+          <t>0.13s</t>
         </is>
       </c>
       <c r="O23" s="21" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="N24" s="25" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O24" s="21" t="inlineStr">
@@ -2798,11 +2798,20 @@
       </c>
       <c r="G25" s="34" t="inlineStr">
         <is>
-          <t>ใช่ หลักสูตรวิทยาการข้อมูลและการวิเคราะห์เชิงธุรกิจ (DSBA) ปีที่ 3 มีการเลือกแขนง (หรือที่เรียกว่า "กลุ่มวิชา") ได้ โดยมีแขนงให้เลือก 3 แขนง ดังนี้:
-- วิทยาการข้อมูล (Data Science)  
-- การวิเคราะห์เชิงสถิติ (Statistical Analytics)  
-- วิศวกรรมข้อมูล (Data Engineering)  
-[3][4][6]</t>
+          <t>ใช่ หลักสูตรวิทยาการข้อมูลและการวิเคราะห์เชิงธุรกิจ (DSBA) ปีที่ 3 มีการเลือกแขนง (หรือที่เรียกว่า "กลุ่มวิชา") ซึ่งแบ่งออกเป็น 3 กลุ่ม ได้แก่:
+- วิชาเลือกกลุ่มวิทยาการข้อมูล 1 (ELECTIVE IN DATA SCIENCE 1) – รหัส 06026xxx [3]
+- วิชาเลือกกลุ่มการวิเคราะห์เชิงสถิติ 1 (ELECTIVE IN STATISTICAL ANALYSIS 1) – รหัส 06026xxx [3]
+- วิชาเลือกกลุ่มวิศวกรรมข้อมูล 1 (ELECTIVE IN DATA ENGINEERING 1) – รหัส 06026xxx [3]
+ในภาคการศึกษาที่ 2 ปีที่ 3 มีการเลือกต่อในกลุ่มเดียวกัน ได้แก่:
+- วิชาเลือกกลุ่มวิทยาการข้อมูล 3 (ELECTIVE IN DATA SCIENCE 3) – รหัส 06026xxx [4]
+- วิชาเลือกกลุ่มการวิเคราะห์เชิงสถิติ 3 (ELECTIVE IN STATISTICAL ANALYTICS 3) – รหัส 06026xxx [4]
+- วิชาเลือกกลุ่มวิศวกรรมข้อมูล 3 (ELECTIVE IN DATA ENGINEERING 3) – รหัส 06026xxx [4]
+นอกจากนี้ยังมีวิชาเลือกในภาคการศึกษาที่ 1 และ 2 ปีที่ 3 สำหรับกลุ่มที่สอง เช่น:
+- วิชาเลือกกลุ่มวิทยาการข้อมูล 2 (ELECTIVE IN DATA SCIENCE 2) – รหัส 06026xxx [3]
+- วิชาเลือกกลุ่มการวิเคราะห์เชิงสถิติ 2 (ELECTIVE IN STATISTICAL ANALYTICS 2) – รหัส 06026xxx [3]
+- วิชาเลือกกลุ่มวิศวกรรมข้อมูล 2 (ELECTIVE IN DATA ENGINEERING 2) – รหัส 06026xxx [3]
+- วิชาเลือกกลุ่มวิทยาการข้อมูล 4 (ELECTIVE IN DATA SCIENCE 4) – รหัส 06026xxx [4]
+- วิชาเลือกกลุ่มการวิเคราะห์เชิงสถิติ 4 (ELECTIVE IN STATIST</t>
         </is>
       </c>
       <c r="H25" s="34" t="inlineStr">
@@ -2835,12 +2844,12 @@
       </c>
       <c r="N25" s="13" t="inlineStr">
         <is>
-          <t>1.30s</t>
+          <t>5.40s</t>
         </is>
       </c>
       <c r="O25" s="21" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2877,9 +2886,9 @@
       </c>
       <c r="G26" s="34" t="inlineStr">
         <is>
-          <t>1. หลักสูตร IT 2565 มีหน่วยกิตรวม 129 หน่วยกิต ลดลง 1 หน่วยกิตจาก IT 2560 ที่มี 130 หน่วยกิต และเปลี่ยนโครงสร้างแขนงวิชาเป็น "โมดูลอาชีพ" 3 โมดูลแทนการเลือก "แขนงวิชา" 3 แขนง
-2. จากข้อมูลมคอ.2 ฉบับ IT 2560 (หน้า 18) และ IT 2565 (หน้า 6) หน่วยกิตรวมลดลง 1 หน่วยกิต ขณะที่โครงสร้างวิชาเฉพาะเปลี่ยนจาก "แขนงวิชา" (เช่น Software Engineering, Network and System Technology) มาเป็น "โมดูลอาชีพ" 3 โมดูล ได้แก่ M1 (Full-Stack Web Developer), M2 (Network/System Engineer), M3 (Game Developer) ตามหน้า 378 และ 370 ของมคอ.2 IT 2565
-3. ข้อมูลอ้างอิง: หน่วยกิตรวม (IT 2560: 130 หน่วยกิต, IT 2565: 129 หน่วยกิต), โครงสร้างแขนงวิชา (IT 2560: 3 แขนงวิชา, IT 2565: 3 โมดูลอาชีพ), ประเภทวิชา: โครงสร้างหลักสูตร (บังคับ), ภาค/ปีที่เปิดสอน: ปีการศึกษา 2560 (IT 2560), ปีการศึกษา 2565 (IT 2565)</t>
+          <t>1. หลักสูตร IT 2565 มีหน่วยกิตรวมน้อยกว่า IT 2560 อยู่ 1 หน่วยกิต และเปลี่ยนโครงสร้างแขนงวิชาเป็น "โมดูลอาชีพ" 3 โมดูลแทนการเลือกแขนงวิชาเดิม
+2. หลักสูตร IT 2560 มีหน่วยกิตรวม 130 หน่วยกิต แบ่งเป็นกลุ่มวิชาเฉพาะ 94 หน่วยกิต (รวมกลุ่มวิชาบังคับเฉพาะแขนง 30 หน่วยกิต), ขณะที่ IT 2565 มีหน่วยกิตรวม 129 หน่วยกิต โดยลดหน่วยกิตกลุ่มวิชาเฉพาะจาก 94 เป็น 93 หน่วยกิต และเปลี่ยนโครงสร้างกลุ่มวิชาเฉพาะแขนงเป็น "โมดูลอาชีพ" 3 โมดูล (M1-M3) แทนการเลือกแขนงวิชาเดิม
+3. อ้างข้อมูลจาก: หน่วยกิตรวม (มคอ.2 IT 2560 หน้า 18, IT 2565 หน้า 6); โครงสร้างกลุ่มวิชาเฉพาะ (IT 2565 หน้า 376, 378); กลุ่มวิชาบังคับเฉพาะแขนง (IT 2565 หน้า 376); กลุ่มวิชาเลือกทางเทคโนโลยีสารสนเทศ (IT 2565 หน้า 378)</t>
         </is>
       </c>
       <c r="H26" s="34" t="inlineStr">
@@ -2912,7 +2921,7 @@
       </c>
       <c r="N26" s="13" t="inlineStr">
         <is>
-          <t>3.48s</t>
+          <t>3.81s</t>
         </is>
       </c>
       <c r="O26" s="21" t="inlineStr">
@@ -2993,7 +3002,7 @@
       </c>
       <c r="N27" s="25" t="inlineStr">
         <is>
-          <t>0.20s</t>
+          <t>0.31s</t>
         </is>
       </c>
       <c r="O27" s="21" t="inlineStr">
@@ -3064,7 +3073,7 @@
       <c r="M28" s="34" t="n"/>
       <c r="N28" s="13" t="inlineStr">
         <is>
-          <t>0.40s</t>
+          <t>0.29s</t>
         </is>
       </c>
       <c r="O28" s="21" t="inlineStr">
@@ -3140,7 +3149,7 @@
       </c>
       <c r="N29" s="25" t="inlineStr">
         <is>
-          <t>0.17s</t>
+          <t>0.07s</t>
         </is>
       </c>
       <c r="O29" s="21" t="inlineStr">
@@ -3219,7 +3228,7 @@
       </c>
       <c r="N30" s="13" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O30" s="21" t="inlineStr">
@@ -3310,7 +3319,7 @@
       </c>
       <c r="N31" s="25" t="inlineStr">
         <is>
-          <t>0.07s</t>
+          <t>0.04s</t>
         </is>
       </c>
       <c r="O31" s="21" t="inlineStr">
@@ -3401,7 +3410,7 @@
       </c>
       <c r="N32" s="13" t="inlineStr">
         <is>
-          <t>0.03s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O32" s="21" t="inlineStr">
@@ -3481,7 +3490,7 @@
       </c>
       <c r="N33" s="25" t="inlineStr">
         <is>
-          <t>0.32s</t>
+          <t>0.19s</t>
         </is>
       </c>
       <c r="O33" s="21" t="inlineStr">
@@ -3558,7 +3567,7 @@
       </c>
       <c r="N34" s="13" t="inlineStr">
         <is>
-          <t>0.07s</t>
+          <t>0.03s</t>
         </is>
       </c>
       <c r="O34" s="21" t="inlineStr">
@@ -3629,7 +3638,7 @@
       <c r="M35" s="35" t="n"/>
       <c r="N35" s="25" t="inlineStr">
         <is>
-          <t>0.58s</t>
+          <t>0.43s</t>
         </is>
       </c>
       <c r="O35" s="21" t="inlineStr">
@@ -3707,7 +3716,7 @@
       </c>
       <c r="N36" s="13" t="inlineStr">
         <is>
-          <t>0.03s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O36" s="21" t="inlineStr">
@@ -3797,7 +3806,7 @@
       </c>
       <c r="N37" s="25" t="inlineStr">
         <is>
-          <t>0.28s</t>
+          <t>0.24s</t>
         </is>
       </c>
       <c r="O37" s="21" t="inlineStr">
@@ -3909,7 +3918,7 @@
       </c>
       <c r="N38" s="13" t="inlineStr">
         <is>
-          <t>0.35s</t>
+          <t>0.26s</t>
         </is>
       </c>
       <c r="O38" s="21" t="inlineStr">
@@ -4001,7 +4010,7 @@
       </c>
       <c r="N39" s="25" t="inlineStr">
         <is>
-          <t>0.46s</t>
+          <t>0.36s</t>
         </is>
       </c>
       <c r="O39" s="21" t="inlineStr">
@@ -4096,7 +4105,7 @@
       </c>
       <c r="N40" s="13" t="inlineStr">
         <is>
-          <t>0.05s</t>
+          <t>0.08s</t>
         </is>
       </c>
       <c r="O40" s="21" t="inlineStr">
@@ -4266,7 +4275,7 @@
       <c r="M42" s="34" t="n"/>
       <c r="N42" s="13" t="inlineStr">
         <is>
-          <t>0.12s</t>
+          <t>0.13s</t>
         </is>
       </c>
       <c r="O42" s="21" t="inlineStr">
@@ -4414,7 +4423,7 @@
       </c>
       <c r="N44" s="13" t="inlineStr">
         <is>
-          <t>0.18s</t>
+          <t>0.20s</t>
         </is>
       </c>
       <c r="O44" s="21" t="inlineStr">
@@ -4492,7 +4501,7 @@
       </c>
       <c r="N45" s="25" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O45" s="21" t="inlineStr">
@@ -4566,7 +4575,7 @@
       <c r="M46" s="34" t="n"/>
       <c r="N46" s="13" t="inlineStr">
         <is>
-          <t>0.18s</t>
+          <t>0.21s</t>
         </is>
       </c>
       <c r="O46" s="21" t="inlineStr">
@@ -4647,7 +4656,7 @@
       </c>
       <c r="N47" s="25" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O47" s="21" t="inlineStr">
@@ -4735,7 +4744,7 @@
       </c>
       <c r="N48" s="13" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.04s</t>
         </is>
       </c>
       <c r="O48" s="21" t="inlineStr">
@@ -4994,7 +5003,7 @@
       </c>
       <c r="N51" s="25" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O51" s="21" t="inlineStr">
@@ -5181,7 +5190,7 @@
       </c>
       <c r="N53" s="25" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O53" s="21" t="inlineStr">
@@ -5263,7 +5272,7 @@
       <c r="M54" s="34" t="n"/>
       <c r="N54" s="13" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O54" s="21" t="inlineStr">
@@ -5507,7 +5516,7 @@
       <c r="M57" s="35" t="n"/>
       <c r="N57" s="25" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O57" s="21" t="inlineStr">
@@ -5782,7 +5791,7 @@
       </c>
       <c r="N60" s="13" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O60" s="21" t="inlineStr">
@@ -5945,7 +5954,7 @@
       </c>
       <c r="N62" s="13" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O62" s="21" t="inlineStr">
@@ -6033,7 +6042,7 @@
       </c>
       <c r="N63" s="25" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O63" s="21" t="inlineStr">
@@ -6135,7 +6144,7 @@
       </c>
       <c r="N64" s="13" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O64" s="21" t="inlineStr">
@@ -6226,7 +6235,7 @@
       <c r="M65" s="35" t="n"/>
       <c r="N65" s="25" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O65" s="21" t="inlineStr">
@@ -6304,7 +6313,7 @@
       <c r="M66" s="34" t="n"/>
       <c r="N66" s="13" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O66" s="21" t="inlineStr">
@@ -6491,7 +6500,7 @@
       <c r="M68" s="34" t="n"/>
       <c r="N68" s="13" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O68" s="21" t="inlineStr">
@@ -6720,7 +6729,7 @@
       </c>
       <c r="N71" s="25" t="inlineStr">
         <is>
-          <t>0.20s</t>
+          <t>0.22s</t>
         </is>
       </c>
       <c r="O71" s="21" t="inlineStr">
@@ -6798,7 +6807,7 @@
       </c>
       <c r="N72" s="13" t="inlineStr">
         <is>
-          <t>0.20s</t>
+          <t>0.21s</t>
         </is>
       </c>
       <c r="O72" s="21" t="inlineStr">
@@ -6876,7 +6885,7 @@
       </c>
       <c r="N73" s="25" t="inlineStr">
         <is>
-          <t>0.13s</t>
+          <t>0.20s</t>
         </is>
       </c>
       <c r="O73" s="21" t="inlineStr">
@@ -6955,7 +6964,7 @@
       </c>
       <c r="N74" s="13" t="inlineStr">
         <is>
-          <t>0.19s</t>
+          <t>0.35s</t>
         </is>
       </c>
       <c r="O74" s="21" t="inlineStr">
@@ -7033,7 +7042,7 @@
       </c>
       <c r="N75" s="25" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O75" s="21" t="inlineStr">
@@ -7196,7 +7205,7 @@
       </c>
       <c r="N77" s="25" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O77" s="21" t="inlineStr">
@@ -7389,7 +7398,7 @@
       </c>
       <c r="N79" s="25" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O79" s="21" t="inlineStr">
@@ -7545,7 +7554,7 @@
       </c>
       <c r="N81" s="25" t="inlineStr">
         <is>
-          <t>0.07s</t>
+          <t>0.08s</t>
         </is>
       </c>
       <c r="O81" s="21" t="inlineStr">
@@ -7622,7 +7631,7 @@
       </c>
       <c r="N82" s="13" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O82" s="21" t="inlineStr">
@@ -8437,7 +8446,7 @@
       </c>
       <c r="N92" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O92" s="41" t="inlineStr">
@@ -8902,7 +8911,7 @@
       </c>
       <c r="N98" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O98" s="41" t="inlineStr">
@@ -8979,7 +8988,7 @@
       </c>
       <c r="N99" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O99" s="41" t="inlineStr">
@@ -10517,7 +10526,7 @@
       </c>
       <c r="N119" s="39" t="inlineStr">
         <is>
-          <t>0.83s</t>
+          <t>0.82s</t>
         </is>
       </c>
       <c r="O119" s="41" t="inlineStr">
@@ -10671,7 +10680,7 @@
       </c>
       <c r="N121" s="39" t="inlineStr">
         <is>
-          <t>0.03s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O121" s="41" t="inlineStr">
@@ -10748,7 +10757,7 @@
       </c>
       <c r="N122" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O122" s="41" t="inlineStr">
@@ -10825,7 +10834,7 @@
       </c>
       <c r="N123" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O123" s="41" t="inlineStr">
@@ -11072,7 +11081,7 @@
       </c>
       <c r="N126" s="39" t="inlineStr">
         <is>
-          <t>0.03s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O126" s="41" t="inlineStr">
@@ -11155,7 +11164,7 @@
       </c>
       <c r="N127" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.03s</t>
         </is>
       </c>
       <c r="O127" s="41" t="inlineStr">
@@ -11324,7 +11333,7 @@
       </c>
       <c r="N129" s="39" t="inlineStr">
         <is>
-          <t>0.03s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O129" s="41" t="inlineStr">
@@ -11406,7 +11415,7 @@
       </c>
       <c r="N130" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O130" s="41" t="inlineStr">
@@ -11723,7 +11732,7 @@
       </c>
       <c r="N134" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O134" s="41" t="inlineStr">
@@ -11960,7 +11969,7 @@
       </c>
       <c r="N137" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O137" s="41" t="inlineStr">
@@ -12039,7 +12048,7 @@
       </c>
       <c r="N138" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O138" s="41" t="inlineStr">
@@ -12118,7 +12127,7 @@
       </c>
       <c r="N139" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O139" s="41" t="inlineStr">
@@ -12197,7 +12206,7 @@
       </c>
       <c r="N140" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O140" s="41" t="inlineStr">
@@ -12671,7 +12680,7 @@
       </c>
       <c r="N146" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O146" s="41" t="inlineStr">
@@ -12829,7 +12838,7 @@
       </c>
       <c r="N148" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O148" s="41" t="inlineStr">
@@ -12908,7 +12917,7 @@
       </c>
       <c r="N149" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O149" s="41" t="inlineStr">
@@ -13144,7 +13153,7 @@
       </c>
       <c r="N152" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O152" s="41" t="inlineStr">
@@ -13381,7 +13390,7 @@
       </c>
       <c r="N155" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O155" s="41" t="inlineStr">
@@ -13768,7 +13777,7 @@
       </c>
       <c r="N160" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O160" s="41" t="inlineStr">
@@ -13845,7 +13854,7 @@
       </c>
       <c r="N161" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O161" s="41" t="inlineStr">
@@ -14154,7 +14163,7 @@
       </c>
       <c r="N165" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O165" s="41" t="inlineStr">
@@ -15324,7 +15333,7 @@
       </c>
       <c r="N179" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O179" s="41" t="inlineStr">
@@ -15482,7 +15491,7 @@
       </c>
       <c r="N181" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O181" s="41" t="inlineStr">
@@ -15561,7 +15570,7 @@
       </c>
       <c r="N182" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O182" s="41" t="inlineStr">
@@ -15877,7 +15886,7 @@
       </c>
       <c r="N186" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O186" s="41" t="inlineStr">
@@ -16114,7 +16123,7 @@
       </c>
       <c r="N189" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O189" s="41" t="inlineStr">
@@ -16193,7 +16202,7 @@
       </c>
       <c r="N190" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O190" s="41" t="inlineStr">
@@ -16762,7 +16771,7 @@
       </c>
       <c r="N197" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O197" s="41" t="inlineStr">
@@ -16839,7 +16848,7 @@
       </c>
       <c r="N198" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O198" s="41" t="inlineStr">
@@ -16916,7 +16925,7 @@
       </c>
       <c r="N199" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O199" s="41" t="inlineStr">
@@ -17455,7 +17464,7 @@
       </c>
       <c r="N206" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O206" s="41" t="inlineStr">
@@ -17700,7 +17709,7 @@
       </c>
       <c r="N209" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O209" s="41" t="inlineStr">
@@ -18118,7 +18127,7 @@
       </c>
       <c r="N214" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O214" s="41" t="inlineStr">
@@ -18916,7 +18925,7 @@
       </c>
       <c r="N224" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O224" s="41" t="inlineStr">
@@ -19311,7 +19320,7 @@
       </c>
       <c r="N229" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O229" s="41" t="inlineStr">
@@ -19390,7 +19399,7 @@
       </c>
       <c r="N230" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O230" s="41" t="inlineStr">
@@ -19631,7 +19640,7 @@
       </c>
       <c r="N233" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O233" s="41" t="inlineStr">
@@ -19713,7 +19722,7 @@
       </c>
       <c r="N234" s="39" t="inlineStr">
         <is>
-          <t>0.03s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O234" s="41" t="inlineStr">
@@ -19793,7 +19802,7 @@
       </c>
       <c r="N235" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O235" s="41" t="inlineStr">
@@ -19872,7 +19881,7 @@
       </c>
       <c r="N236" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O236" s="41" t="inlineStr">
@@ -19954,7 +19963,7 @@
       </c>
       <c r="N237" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O237" s="41" t="inlineStr">
@@ -20036,7 +20045,7 @@
       </c>
       <c r="N238" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O238" s="41" t="inlineStr">
@@ -21044,7 +21053,7 @@
       </c>
       <c r="N251" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.03s</t>
         </is>
       </c>
       <c r="O251" s="41" t="inlineStr">
@@ -21210,7 +21219,7 @@
       </c>
       <c r="N253" s="39" t="inlineStr">
         <is>
-          <t>0.05s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O253" s="41" t="inlineStr">
@@ -21551,7 +21560,7 @@
       </c>
       <c r="N257" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.03s</t>
         </is>
       </c>
       <c r="O257" s="41" t="inlineStr">
@@ -21708,7 +21717,7 @@
       </c>
       <c r="N259" s="39" t="inlineStr">
         <is>
-          <t>0.17s</t>
+          <t>0.11s</t>
         </is>
       </c>
       <c r="O259" s="41" t="inlineStr">
@@ -21784,7 +21793,7 @@
       </c>
       <c r="N260" s="39" t="inlineStr">
         <is>
-          <t>0.22s</t>
+          <t>0.11s</t>
         </is>
       </c>
       <c r="O260" s="41" t="inlineStr">
@@ -22262,7 +22271,7 @@
       </c>
       <c r="N266" s="39" t="inlineStr">
         <is>
-          <t>0.10s</t>
+          <t>0.05s</t>
         </is>
       </c>
       <c r="O266" s="41" t="inlineStr">
@@ -22338,7 +22347,7 @@
       </c>
       <c r="N267" s="39" t="inlineStr">
         <is>
-          <t>0.15s</t>
+          <t>0.05s</t>
         </is>
       </c>
       <c r="O267" s="41" t="inlineStr">
@@ -22499,7 +22508,7 @@
       </c>
       <c r="N269" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O269" s="41" t="inlineStr">
@@ -22735,7 +22744,7 @@
       </c>
       <c r="N272" s="39" t="inlineStr">
         <is>
-          <t>0.10s</t>
+          <t>0.05s</t>
         </is>
       </c>
       <c r="O272" s="41" t="inlineStr">
@@ -22811,7 +22820,7 @@
       </c>
       <c r="N273" s="39" t="inlineStr">
         <is>
-          <t>0.10s</t>
+          <t>0.05s</t>
         </is>
       </c>
       <c r="O273" s="41" t="inlineStr">
@@ -23208,7 +23217,7 @@
       </c>
       <c r="N278" s="39" t="inlineStr">
         <is>
-          <t>0.13s</t>
+          <t>0.08s</t>
         </is>
       </c>
       <c r="O278" s="41" t="inlineStr">
@@ -23284,7 +23293,7 @@
       </c>
       <c r="N279" s="39" t="inlineStr">
         <is>
-          <t>0.14s</t>
+          <t>0.08s</t>
         </is>
       </c>
       <c r="O279" s="41" t="inlineStr">
@@ -23364,7 +23373,7 @@
       </c>
       <c r="N280" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O280" s="41" t="inlineStr">
@@ -23525,7 +23534,7 @@
       </c>
       <c r="N282" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O282" s="41" t="inlineStr">
@@ -23605,7 +23614,7 @@
       </c>
       <c r="N283" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O283" s="41" t="inlineStr">
@@ -23682,7 +23691,7 @@
       </c>
       <c r="N284" s="39" t="inlineStr">
         <is>
-          <t>0.04s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O284" s="41" t="inlineStr">
@@ -23759,7 +23768,7 @@
       </c>
       <c r="N285" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O285" s="41" t="inlineStr">
@@ -23913,7 +23922,7 @@
       </c>
       <c r="N287" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O287" s="41" t="inlineStr">
@@ -24144,7 +24153,7 @@
       </c>
       <c r="N290" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O290" s="41" t="inlineStr">
@@ -24375,7 +24384,7 @@
       </c>
       <c r="N293" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O293" s="41" t="inlineStr">
@@ -24529,7 +24538,7 @@
       </c>
       <c r="N295" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O295" s="41" t="inlineStr">
@@ -24606,7 +24615,7 @@
       </c>
       <c r="N296" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O296" s="41" t="inlineStr">
@@ -24760,7 +24769,7 @@
       </c>
       <c r="N298" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O298" s="41" t="inlineStr">
@@ -24838,7 +24847,7 @@
       </c>
       <c r="N299" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O299" s="41" t="inlineStr">
@@ -24917,7 +24926,7 @@
       </c>
       <c r="N300" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O300" s="41" t="inlineStr">
@@ -25152,7 +25161,7 @@
       </c>
       <c r="N303" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O303" s="41" t="inlineStr">
@@ -25231,7 +25240,7 @@
       </c>
       <c r="N304" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O304" s="41" t="inlineStr">
@@ -25389,7 +25398,7 @@
       </c>
       <c r="N306" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O306" s="41" t="inlineStr">
@@ -25467,7 +25476,7 @@
       </c>
       <c r="N307" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O307" s="41" t="inlineStr">
@@ -25625,7 +25634,7 @@
       </c>
       <c r="N309" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O309" s="41" t="inlineStr">
@@ -26012,7 +26021,7 @@
       </c>
       <c r="N314" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O314" s="41" t="inlineStr">
@@ -26326,7 +26335,7 @@
       </c>
       <c r="N318" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O318" s="41" t="inlineStr">
@@ -26404,7 +26413,7 @@
       </c>
       <c r="N319" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O319" s="41" t="inlineStr">
@@ -26808,7 +26817,7 @@
       </c>
       <c r="N324" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O324" s="41" t="inlineStr">
@@ -26887,7 +26896,7 @@
       </c>
       <c r="N325" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O325" s="41" t="inlineStr">
@@ -26966,7 +26975,7 @@
       </c>
       <c r="N326" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O326" s="41" t="inlineStr">
@@ -27054,7 +27063,7 @@
       </c>
       <c r="N327" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O327" s="41" t="inlineStr">
@@ -27131,7 +27140,7 @@
       </c>
       <c r="N328" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O328" s="41" t="inlineStr">
@@ -27208,7 +27217,7 @@
       </c>
       <c r="N329" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O329" s="41" t="inlineStr">
@@ -27441,7 +27450,7 @@
       </c>
       <c r="N332" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O332" s="41" t="inlineStr">
@@ -27599,7 +27608,7 @@
       </c>
       <c r="N334" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O334" s="41" t="inlineStr">
@@ -27677,7 +27686,7 @@
       </c>
       <c r="N335" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O335" s="41" t="inlineStr">
@@ -28074,7 +28083,7 @@
       </c>
       <c r="N340" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.03s</t>
         </is>
       </c>
       <c r="O340" s="41" t="inlineStr">
@@ -28232,7 +28241,7 @@
       </c>
       <c r="N342" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O342" s="41" t="inlineStr">
@@ -28938,7 +28947,7 @@
       </c>
       <c r="N351" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.03s</t>
         </is>
       </c>
       <c r="O351" s="41" t="inlineStr">
@@ -29691,7 +29700,7 @@
       <c r="G361" s="39" t="inlineStr">
         <is>
           <t>ได้  
-นักศึกษาชั้นปีสุดท้ายที่เหลือรายวิชาไม่ถึง 9 หน่วยกิต หรือต้องลงเกิน 22 หน่วยกิตเพื่อสำเร็จการศึกษา สามารถลงทะเบียนได้สูงสุดไม่เกิน 27 หน่วยกิต โดยต้องได้รับอนุมัติจากสภาวิชาการ ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 82 ซึ่งระบุว่า นักศึกษาชั้นปีสุดท้ายสามารถลงทะเบียนได้ไม่เกิน 27 หน่วยกิตหากจำเป็นต่อการสำเร็จการศึกษา</t>
+นักศึกษาชั้นปีสุดท้ายที่เหลือรายวิชาไม่ถึง 9 หน่วยกิต หรือต้องลงเกิน 22 หน่วยกิตเพื่อสำเร็จการศึกษา สามารถลงทะเบียนได้สูงสุดไม่เกิน 27 หน่วยกิต โดยต้องได้รับอนุมัติจากสภาวิชาการ ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 82</t>
         </is>
       </c>
       <c r="H361" s="39" t="inlineStr">
@@ -29724,7 +29733,7 @@
       </c>
       <c r="N361" s="39" t="inlineStr">
         <is>
-          <t>1.43s</t>
+          <t>1.61s</t>
         </is>
       </c>
       <c r="O361" s="41" t="inlineStr">
@@ -30129,7 +30138,7 @@
       </c>
       <c r="N366" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O366" s="41" t="inlineStr">
@@ -30251,6 +30260,7 @@
         <is>
           <t>วิชา 96641001 โรงเรียนสร้างเสน่ห์ (CHARM SCHOOL) — 2(1-2-3) หน่วยกิต · หลักสูตร BIT 2565 (ปริญญาตรี)
 (วิชาศึกษาทั่วไปที่ใช้ร่วมกันทุกหลักสูตร — เล่ม AIT 2566 (ปริญญาตรี) ไม่ได้ลงรายละเอียดวิชานี้ จึงใช้ข้อมูลจากเล่ม BIT 2565 (ปริญญาตรี))
+ชื่อวิชาเดียวกันในเล่มอื่น: 90641001 — 2(1-2-3) หน่วยกิต · หลักสูตร DSBA 2565 (ปริญญาตรี), IT 2565 (ปริญญาตรี)
 อยู่ในกลุ่มวิชาพื้นฐาน (หน้า 20)
 เรียนตามแผนการศึกษา:
   - ปีที่ 1 ภาคการศึกษาที่ 1 (ทั้งแผนปกติและแผนสหกิจ, หน้า 26, 31)
@@ -30365,7 +30375,7 @@
       </c>
       <c r="N369" s="39" t="inlineStr">
         <is>
-          <t>0.04s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O369" s="41" t="inlineStr">
@@ -30521,7 +30531,7 @@
       </c>
       <c r="N371" s="39" t="inlineStr">
         <is>
-          <t>0.03s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O371" s="41" t="inlineStr">
@@ -30831,7 +30841,7 @@
       </c>
       <c r="N375" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O375" s="41" t="inlineStr">
@@ -31607,7 +31617,7 @@
       </c>
       <c r="N385" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O385" s="41" t="inlineStr">
@@ -31684,7 +31694,7 @@
       </c>
       <c r="N386" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O386" s="41" t="inlineStr">
@@ -31840,7 +31850,7 @@
       </c>
       <c r="N388" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O388" s="41" t="inlineStr">
@@ -31918,7 +31928,7 @@
       </c>
       <c r="N389" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O389" s="41" t="inlineStr">
@@ -31996,7 +32006,7 @@
       </c>
       <c r="N390" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O390" s="41" t="inlineStr">
@@ -32075,7 +32085,7 @@
       </c>
       <c r="N391" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O391" s="41" t="inlineStr">
@@ -32154,7 +32164,7 @@
       </c>
       <c r="N392" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O392" s="41" t="inlineStr">
@@ -32546,7 +32556,7 @@
       </c>
       <c r="N397" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O397" s="41" t="inlineStr">
@@ -33338,7 +33348,7 @@
       </c>
       <c r="N407" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O407" s="41" t="inlineStr">
@@ -33415,7 +33425,7 @@
       </c>
       <c r="N408" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O408" s="41" t="inlineStr">
@@ -33492,7 +33502,7 @@
       </c>
       <c r="N409" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O409" s="41" t="inlineStr">
@@ -33814,7 +33824,7 @@
       </c>
       <c r="N413" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O413" s="41" t="inlineStr">
@@ -33893,7 +33903,7 @@
       </c>
       <c r="N414" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O414" s="41" t="inlineStr">
@@ -33972,7 +33982,7 @@
       </c>
       <c r="N415" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O415" s="41" t="inlineStr">
@@ -34049,7 +34059,7 @@
       </c>
       <c r="N416" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O416" s="41" t="inlineStr">
@@ -34203,7 +34213,7 @@
       </c>
       <c r="N418" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O418" s="41" t="inlineStr">
@@ -34280,7 +34290,7 @@
       </c>
       <c r="N419" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O419" s="41" t="inlineStr">
@@ -34436,7 +34446,7 @@
       </c>
       <c r="N421" s="39" t="inlineStr">
         <is>
-          <t>0.38s</t>
+          <t>0.23s</t>
         </is>
       </c>
       <c r="O421" s="41" t="inlineStr">
@@ -34514,7 +34524,7 @@
       </c>
       <c r="N422" s="39" t="inlineStr">
         <is>
-          <t>0.22s</t>
+          <t>0.31s</t>
         </is>
       </c>
       <c r="O422" s="41" t="inlineStr">
@@ -34593,7 +34603,7 @@
       </c>
       <c r="N423" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O423" s="41" t="inlineStr">
@@ -34838,7 +34848,7 @@
       </c>
       <c r="N426" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O426" s="41" t="inlineStr">
@@ -35075,7 +35085,7 @@
       </c>
       <c r="N429" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.03s</t>
         </is>
       </c>
       <c r="O429" s="41" t="inlineStr">
@@ -35616,7 +35626,7 @@
       </c>
       <c r="N436" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O436" s="41" t="inlineStr">
@@ -36176,7 +36186,7 @@
       </c>
       <c r="N443" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O443" s="41" t="inlineStr">
@@ -36334,7 +36344,7 @@
       </c>
       <c r="N445" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O445" s="41" t="inlineStr">
@@ -36565,7 +36575,7 @@
       </c>
       <c r="N448" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O448" s="41" t="inlineStr">
@@ -36965,7 +36975,7 @@
       </c>
       <c r="N453" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O453" s="41" t="inlineStr">
@@ -37590,7 +37600,7 @@
       </c>
       <c r="N461" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O461" s="41" t="inlineStr">
@@ -38223,7 +38233,7 @@
       </c>
       <c r="N469" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O469" s="41" t="inlineStr">
@@ -38700,7 +38710,7 @@
       </c>
       <c r="N475" s="39" t="inlineStr">
         <is>
-          <t>0.06s</t>
+          <t>0.08s</t>
         </is>
       </c>
       <c r="O475" s="41" t="inlineStr">
@@ -38787,104 +38797,7863 @@
         </is>
       </c>
     </row>
-    <row r="477" ht="14.25" customHeight="1" s="36"/>
-    <row r="478" ht="14.25" customHeight="1" s="36"/>
-    <row r="479" ht="14.25" customHeight="1" s="36"/>
-    <row r="480" ht="14.25" customHeight="1" s="36"/>
-    <row r="481" ht="14.25" customHeight="1" s="36"/>
-    <row r="482" ht="14.25" customHeight="1" s="36"/>
-    <row r="483" ht="14.25" customHeight="1" s="36"/>
-    <row r="484" ht="14.25" customHeight="1" s="36"/>
-    <row r="485" ht="14.25" customHeight="1" s="36"/>
-    <row r="486" ht="14.25" customHeight="1" s="36"/>
-    <row r="487" ht="14.25" customHeight="1" s="36"/>
-    <row r="488" ht="14.25" customHeight="1" s="36"/>
-    <row r="489" ht="14.25" customHeight="1" s="36"/>
-    <row r="490" ht="14.25" customHeight="1" s="36"/>
-    <row r="491" ht="14.25" customHeight="1" s="36"/>
-    <row r="492" ht="14.25" customHeight="1" s="36"/>
-    <row r="493" ht="14.25" customHeight="1" s="36"/>
-    <row r="494" ht="14.25" customHeight="1" s="36"/>
-    <row r="495" ht="14.25" customHeight="1" s="36"/>
-    <row r="496" ht="14.25" customHeight="1" s="36"/>
-    <row r="497" ht="14.25" customHeight="1" s="36"/>
-    <row r="498" ht="14.25" customHeight="1" s="36"/>
-    <row r="499" ht="14.25" customHeight="1" s="36"/>
-    <row r="500" ht="14.25" customHeight="1" s="36"/>
-    <row r="501" ht="14.25" customHeight="1" s="36"/>
-    <row r="502" ht="14.25" customHeight="1" s="36"/>
-    <row r="503" ht="14.25" customHeight="1" s="36"/>
-    <row r="504" ht="14.25" customHeight="1" s="36"/>
-    <row r="505" ht="14.25" customHeight="1" s="36"/>
-    <row r="506" ht="14.25" customHeight="1" s="36"/>
-    <row r="507" ht="14.25" customHeight="1" s="36"/>
-    <row r="508" ht="14.25" customHeight="1" s="36"/>
-    <row r="509" ht="14.25" customHeight="1" s="36"/>
-    <row r="510" ht="14.25" customHeight="1" s="36"/>
-    <row r="511" ht="14.25" customHeight="1" s="36"/>
-    <row r="512" ht="14.25" customHeight="1" s="36"/>
-    <row r="513" ht="14.25" customHeight="1" s="36"/>
-    <row r="514" ht="14.25" customHeight="1" s="36"/>
-    <row r="515" ht="14.25" customHeight="1" s="36"/>
-    <row r="516" ht="14.25" customHeight="1" s="36"/>
-    <row r="517" ht="14.25" customHeight="1" s="36"/>
-    <row r="518" ht="14.25" customHeight="1" s="36"/>
-    <row r="519" ht="14.25" customHeight="1" s="36"/>
-    <row r="520" ht="14.25" customHeight="1" s="36"/>
-    <row r="521" ht="14.25" customHeight="1" s="36"/>
-    <row r="522" ht="14.25" customHeight="1" s="36"/>
-    <row r="523" ht="14.25" customHeight="1" s="36"/>
-    <row r="524" ht="14.25" customHeight="1" s="36"/>
-    <row r="525" ht="14.25" customHeight="1" s="36"/>
-    <row r="526" ht="14.25" customHeight="1" s="36"/>
-    <row r="527" ht="14.25" customHeight="1" s="36"/>
-    <row r="528" ht="14.25" customHeight="1" s="36"/>
-    <row r="529" ht="14.25" customHeight="1" s="36"/>
-    <row r="530" ht="14.25" customHeight="1" s="36"/>
-    <row r="531" ht="14.25" customHeight="1" s="36"/>
-    <row r="532" ht="14.25" customHeight="1" s="36"/>
-    <row r="533" ht="14.25" customHeight="1" s="36"/>
-    <row r="534" ht="14.25" customHeight="1" s="36"/>
-    <row r="535" ht="14.25" customHeight="1" s="36"/>
-    <row r="536" ht="14.25" customHeight="1" s="36"/>
-    <row r="537" ht="14.25" customHeight="1" s="36"/>
-    <row r="538" ht="14.25" customHeight="1" s="36"/>
-    <row r="539" ht="14.25" customHeight="1" s="36"/>
-    <row r="540" ht="14.25" customHeight="1" s="36"/>
-    <row r="541" ht="14.25" customHeight="1" s="36"/>
-    <row r="542" ht="14.25" customHeight="1" s="36"/>
-    <row r="543" ht="14.25" customHeight="1" s="36"/>
-    <row r="544" ht="14.25" customHeight="1" s="36"/>
-    <row r="545" ht="14.25" customHeight="1" s="36"/>
-    <row r="546" ht="14.25" customHeight="1" s="36"/>
-    <row r="547" ht="14.25" customHeight="1" s="36"/>
-    <row r="548" ht="14.25" customHeight="1" s="36"/>
-    <row r="549" ht="14.25" customHeight="1" s="36"/>
-    <row r="550" ht="14.25" customHeight="1" s="36"/>
-    <row r="551" ht="14.25" customHeight="1" s="36"/>
-    <row r="552" ht="14.25" customHeight="1" s="36"/>
-    <row r="553" ht="14.25" customHeight="1" s="36"/>
-    <row r="554" ht="14.25" customHeight="1" s="36"/>
-    <row r="555" ht="14.25" customHeight="1" s="36"/>
-    <row r="556" ht="14.25" customHeight="1" s="36"/>
-    <row r="557" ht="14.25" customHeight="1" s="36"/>
-    <row r="558" ht="14.25" customHeight="1" s="36"/>
-    <row r="559" ht="14.25" customHeight="1" s="36"/>
-    <row r="560" ht="14.25" customHeight="1" s="36"/>
-    <row r="561" ht="14.25" customHeight="1" s="36"/>
-    <row r="562" ht="14.25" customHeight="1" s="36"/>
-    <row r="563" ht="14.25" customHeight="1" s="36"/>
-    <row r="564" ht="14.25" customHeight="1" s="36"/>
-    <row r="565" ht="14.25" customHeight="1" s="36"/>
-    <row r="566" ht="14.25" customHeight="1" s="36"/>
-    <row r="567" ht="14.25" customHeight="1" s="36"/>
-    <row r="568" ht="14.25" customHeight="1" s="36"/>
-    <row r="569" ht="14.25" customHeight="1" s="36"/>
-    <row r="570" ht="14.25" customHeight="1" s="36"/>
-    <row r="571" ht="14.25" customHeight="1" s="36"/>
-    <row r="572" ht="14.25" customHeight="1" s="36"/>
-    <row r="573" ht="14.25" customHeight="1" s="36"/>
-    <row r="574" ht="14.25" customHeight="1" s="36"/>
+    <row r="477" ht="14.25" customHeight="1" s="36">
+      <c r="A477" s="37" t="inlineStr">
+        <is>
+          <t>UE1</t>
+        </is>
+      </c>
+      <c r="B477" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C477" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D477" s="39" t="inlineStr">
+        <is>
+          <t>อยากทราบหน่วยกิตของวิชาพื้นฐานของระบบสมองกลฝังตัว</t>
+        </is>
+      </c>
+      <c r="E477" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F477" s="39" t="inlineStr">
+        <is>
+          <t>3(3-0-6)</t>
+        </is>
+      </c>
+      <c r="G477" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06046404 พื้นฐานของระบบสมองกลฝังตัว (FUNDAMENTAL OF EMBEDDED SYSTEM) — 3(3-0-6) หน่วยกิต · หลักสูตร AIT 2566 (ปริญญาตรี)
+ตามตารางรายวิชา: ปีที่ 1 ภาคการศึกษาที่ 2
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H477" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 20, 23, 37, 291</t>
+        </is>
+      </c>
+      <c r="I477" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J477" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="K477" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L477" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M477" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N477" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O477" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="478" ht="14.25" customHeight="1" s="36">
+      <c r="A478" s="37" t="inlineStr">
+        <is>
+          <t>UE2</t>
+        </is>
+      </c>
+      <c r="B478" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C478" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D478" s="39" t="inlineStr">
+        <is>
+          <t>อยากทราบหน่วยกิตของวิชาการประมวลผลภาพ</t>
+        </is>
+      </c>
+      <c r="E478" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F478" s="39" t="inlineStr">
+        <is>
+          <t>3(3-0-6)</t>
+        </is>
+      </c>
+      <c r="G478" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06046417 การประมวลผลภาพ (IMAGE PROCESSING) — 3(3-0-6) หน่วยกิต · หลักสูตร AIT 2566 (ปริญญาตรี)
+ไม่ได้กำหนดปี/ภาคไว้ในแผนการศึกษาของเล่ม (เป็นวิชาเลือก)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H478" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 21, 38, 297</t>
+        </is>
+      </c>
+      <c r="I478" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J478" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="K478" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L478" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M478" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N478" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O478" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="479" ht="14.25" customHeight="1" s="36">
+      <c r="A479" s="37" t="inlineStr">
+        <is>
+          <t>UE3</t>
+        </is>
+      </c>
+      <c r="B479" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C479" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D479" s="39" t="inlineStr">
+        <is>
+          <t>คณิตศาสตร์ไม่ต่อเนื่อง เรียนปีอะไร</t>
+        </is>
+      </c>
+      <c r="E479" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F479" s="39" t="inlineStr">
+        <is>
+          <t>ปี 1 ภาค 1</t>
+        </is>
+      </c>
+      <c r="G479" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06066000 คณิตศาสตร์ไม่ต่อเนื่อง (DISCRETE MATHEMATICS) — 3(3-0-6) หน่วยกิต · หลักสูตร AIT 2566 (ปริญญาตรี)
+ตามตารางรายวิชา: ปีที่ 1 ภาคการศึกษาที่ 1
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H479" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 19, 23, 37, 288</t>
+        </is>
+      </c>
+      <c r="I479" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J479" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="K479" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L479" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M479" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N479" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O479" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="480" ht="14.25" customHeight="1" s="36">
+      <c r="A480" s="37" t="inlineStr">
+        <is>
+          <t>UE4</t>
+        </is>
+      </c>
+      <c r="B480" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C480" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D480" s="39" t="inlineStr">
+        <is>
+          <t>พื้นฐานการเรียนรู้เชิงลึก เรียนปีอะไร</t>
+        </is>
+      </c>
+      <c r="E480" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F480" s="39" t="inlineStr">
+        <is>
+          <t>ปี 2 ภาค 1</t>
+        </is>
+      </c>
+      <c r="G480" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06046406 พื้นฐานการเรียนรู้เชิงลึก (FUNDAMENTALS OF DEEP LEARNING) — 3(3-0-6) หน่วยกิต · หลักสูตร AIT 2566 (ปริญญาตรี)
+ตามตารางรายวิชา: ปีที่ 2 ภาคการศึกษาที่ 1
+วิชาบังคับก่อน: 06046401 แคลคูลัส 2, 06046402 พีชคณิตเชิงเส้น</t>
+        </is>
+      </c>
+      <c r="H480" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 20, 24, 37, 292</t>
+        </is>
+      </c>
+      <c r="I480" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J480" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="K480" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L480" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M480" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N480" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O480" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="481" ht="14.25" customHeight="1" s="36">
+      <c r="A481" s="37" t="inlineStr">
+        <is>
+          <t>UM1</t>
+        </is>
+      </c>
+      <c r="B481" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C481" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D481" s="39" t="inlineStr">
+        <is>
+          <t>How many credits is Natural Language Processing With Deep Learning?</t>
+        </is>
+      </c>
+      <c r="E481" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F481" s="39" t="inlineStr">
+        <is>
+          <t>3(3-0-6)</t>
+        </is>
+      </c>
+      <c r="G481" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06046414 การประมวลผลภาษาธรรมชาติด้วยการเรียนรู้เชิงลึก (NATURAL LANGUAGE PROCESSING WITH DEEP LEARNING) — 3(3-0-6) หน่วยกิต · หลักสูตร AIT 2566 (ปริญญาตรี)
+ตามตารางรายวิชา: ปีที่ 3 ภาคการศึกษาที่ 1
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H481" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 20, 25, 38, 295</t>
+        </is>
+      </c>
+      <c r="I481" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J481" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="K481" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L481" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M481" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N481" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O481" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="482" ht="14.25" customHeight="1" s="36">
+      <c r="A482" s="37" t="inlineStr">
+        <is>
+          <t>UM2</t>
+        </is>
+      </c>
+      <c r="B482" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C482" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D482" s="39" t="inlineStr">
+        <is>
+          <t>How many credits is Selected Topics In Artificial Intelligence 2?</t>
+        </is>
+      </c>
+      <c r="E482" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F482" s="39" t="inlineStr">
+        <is>
+          <t>3(3-0-6)</t>
+        </is>
+      </c>
+      <c r="G482" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06046431 หัวข้อคัดสรรด้านปัญญาประดิษฐ์ 2 (SELECTED TOPICS IN ARTIFICIAL INTELLIGENCE 2) — 3(3-0-6) หน่วยกิต · หลักสูตร AIT 2566 (ปริญญาตรี)
+ไม่ได้กำหนดปี/ภาคไว้ในแผนการศึกษาของเล่ม (เป็นวิชาเลือก)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H482" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 21, 39, 301</t>
+        </is>
+      </c>
+      <c r="I482" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J482" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="K482" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L482" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M482" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N482" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O482" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="483" ht="14.25" customHeight="1" s="36">
+      <c r="A483" s="37" t="inlineStr">
+        <is>
+          <t>UM3</t>
+        </is>
+      </c>
+      <c r="B483" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C483" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D483" s="39" t="inlineStr">
+        <is>
+          <t>Which year and semester is Fundamental Of Embedded System taught?</t>
+        </is>
+      </c>
+      <c r="E483" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F483" s="39" t="inlineStr">
+        <is>
+          <t>ปี 1 ภาค 2</t>
+        </is>
+      </c>
+      <c r="G483" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06046404 พื้นฐานของระบบสมองกลฝังตัว (FUNDAMENTAL OF EMBEDDED SYSTEM) — 3(3-0-6) หน่วยกิต · หลักสูตร AIT 2566 (ปริญญาตรี)
+ตามตารางรายวิชา: ปีที่ 1 ภาคการศึกษาที่ 2
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H483" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 20, 23, 37, 291</t>
+        </is>
+      </c>
+      <c r="I483" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J483" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="K483" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L483" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M483" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N483" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O483" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="484" ht="14.25" customHeight="1" s="36">
+      <c r="A484" s="37" t="inlineStr">
+        <is>
+          <t>UM4</t>
+        </is>
+      </c>
+      <c r="B484" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C484" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D484" s="39" t="inlineStr">
+        <is>
+          <t>การเรียนรู้ของเครื่องเชิงความน่าจะเป็น มี prerequisite อะไร</t>
+        </is>
+      </c>
+      <c r="E484" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F484" s="39" t="inlineStr">
+        <is>
+          <t>06066001</t>
+        </is>
+      </c>
+      <c r="G484" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06046405 การเรียนรู้ของเครื่องเชิงความน่าจะเป็น (PROBABILISTIC MACHINE LEARNING) — 3(3-0-6) | ปีที่ 2 ภาคการศึกษาที่ 1
+  ต้องผ่านวิชาบังคับก่อน:
+    • 06066001 ความน่าจะเป็นและสถิติ (PROBABILITY AND STATISTICS) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H484" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 37, 291, 19, 20, 23, 24, 289</t>
+        </is>
+      </c>
+      <c r="I484" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (prerequisite) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J484" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="K484" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L484" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M484" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N484" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O484" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="485" ht="14.25" customHeight="1" s="36">
+      <c r="A485" s="37" t="inlineStr">
+        <is>
+          <t>UM5</t>
+        </is>
+      </c>
+      <c r="B485" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C485" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D485" s="39" t="inlineStr">
+        <is>
+          <t>แคลคูลัส 2 มี prerequisite อะไร</t>
+        </is>
+      </c>
+      <c r="E485" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F485" s="39" t="inlineStr">
+        <is>
+          <t>06046400</t>
+        </is>
+      </c>
+      <c r="G485" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06046401 แคลคูลัส 2 (CALCULUS 2) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 2
+  ต้องผ่านวิชาบังคับก่อน:
+    • 06046400 แคลคูลัส 1 (CALCULUS 1) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H485" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 19, 37, 287, 23, 292</t>
+        </is>
+      </c>
+      <c r="I485" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (prerequisite) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J485" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="K485" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L485" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M485" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N485" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O485" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="486" ht="14.25" customHeight="1" s="36">
+      <c r="A486" s="37" t="inlineStr">
+        <is>
+          <t>UH1</t>
+        </is>
+      </c>
+      <c r="B486" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C486" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D486" s="39" t="inlineStr">
+        <is>
+          <t>เทอม 1 ปี 2 ต้องลงวิชาบังคับอะไรบ้าง</t>
+        </is>
+      </c>
+      <c r="E486" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F486" s="39" t="inlineStr">
+        <is>
+          <t>06066300, 06046405, 06046406, 06046409, 06046413, 90641009</t>
+        </is>
+      </c>
+      <c r="G486" s="39" t="inlineStr">
+        <is>
+          <t>รายวิชาของหลักสูตร AIT 2566 (current) ปีที่ 2 (จัดกลุ่มตามภาคการศึกษา):
+▶ ภาคการศึกษาที่ 1 — วิชาบังคับ (6 วิชา 18 หน่วยกิต):
+  - 06046405 การเรียนรู้ของเครื่องเชิงความน่าจะเป็น (PROBABILISTIC MACHINE LEARNING) — 3(3-0-6)
+  - 06046406 พื้นฐานการเรียนรู้เชิงลึก (FUNDAMENTALS OF DEEP LEARNING) — 3(3-0-6)
+  - 06046409 คอมพิวเตอร์วิทัศน์เบื้องต้น (INTRODUCTION TO COMPUTER VISION) — 3(3-0-6)
+  - 06046413 ปัญญาประดิษฐ์และอินเทอร์เน็ตประสานสรรพสิ่ง (ARTIFICIAL INTELLIGIENCE AND INTERNET OF THING) — 3(3-0-6)
+  - 06066300 แนวคิดระบบฐานข้อมูล (DATABASE SYSTEM CONCEPTS) — 3(2-2-5)
+  - 90641009 ทักษะการสื่อสารภาษาอังกฤษระหว่างวัฒนธรรม 1 (INTERCULTURAL COMMUNICATION SKILLS IN ENGLISH 1) — 3(3-0-6)
+รวมปีที่ 2 (วิชาบังคับ): 6 วิชา 18 หน่วยกิต (ยังไม่รวมวิชาเลือก)</t>
+        </is>
+      </c>
+      <c r="H486" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 24, 20, 37, 38, 19, 119, 120, 145</t>
+        </is>
+      </c>
+      <c r="I486" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ปี/ภาค) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J486" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K486" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L486" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M486" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N486" s="39" t="inlineStr">
+        <is>
+          <t>0.02s</t>
+        </is>
+      </c>
+      <c r="O486" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="487" ht="14.25" customHeight="1" s="36">
+      <c r="A487" s="37" t="inlineStr">
+        <is>
+          <t>UH2</t>
+        </is>
+      </c>
+      <c r="B487" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C487" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D487" s="39" t="inlineStr">
+        <is>
+          <t>เทอม 2 ปี 4 ต้องลงวิชาบังคับอะไรบ้าง</t>
+        </is>
+      </c>
+      <c r="E487" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F487" s="39" t="inlineStr">
+        <is>
+          <t>06046443</t>
+        </is>
+      </c>
+      <c r="G487" s="39" t="inlineStr">
+        <is>
+          <t>รายวิชาของหลักสูตร AIT 2566 (current) ปีที่ 4 (จัดกลุ่มตามภาคการศึกษา):
+▶ ภาคการศึกษาที่ 2 — วิชาบังคับ (2 วิชา 12 หน่วยกิต):
+  - 06046443 สหกิจศึกษาทางเทคโนโลยีปัญญาประดิษฐ์ (COOPERATIVE EDUCATION IN ARTIFICIAL INTELLIGIENCE TECHNOLOGY) — 6(0-45-0)
+  - 06046444 สหกิจศึกษาต่างประเทศทางเทคโนโลยีปัญญาประดิษฐ์ (OVERSEA COOPERATIVE EDUCATION IN ARTIFICIAL INTELLIGIENCE TECHNOLOGY) — 6(0-45-0)
+รวมปีที่ 4 (วิชาบังคับ): 2 วิชา 12 หน่วยกิต (ยังไม่รวมวิชาเลือก)</t>
+        </is>
+      </c>
+      <c r="H487" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 22, 26, 40, 303, 304</t>
+        </is>
+      </c>
+      <c r="I487" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ปี/ภาค) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J487" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="K487" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L487" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M487" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N487" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O487" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="488" ht="14.25" customHeight="1" s="36">
+      <c r="A488" s="37" t="inlineStr">
+        <is>
+          <t>UE5</t>
+        </is>
+      </c>
+      <c r="B488" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C488" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D488" s="39" t="inlineStr">
+        <is>
+          <t>อยากทราบหน่วยกิตของวิชาองค์กรและการจัดการ</t>
+        </is>
+      </c>
+      <c r="E488" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F488" s="39" t="inlineStr">
+        <is>
+          <t>3(3-0-6)</t>
+        </is>
+      </c>
+      <c r="G488" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06036104 องค์กรและการจัดการ (MANAGEMENT AND ORGANIZATIONS) — 3(3-0-6) หน่วยกิต · หลักสูตร BIT 2565 (ปริญญาตรี)
+อยู่ในกลุ่มประเด็นด้านองค์การและระบบสารสนเทศ (ส่วนของกลุ่มวิชาเฉพาะด้าน) (หน้า 22)
+เรียนตามแผนการศึกษา:
+  - ปีที่ 2 ภาคการศึกษาที่ 1 (ทั้งแผนปกติและแผนสหกิจ, หน้า 27, 32)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H488" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 22, 27, 32, 74, 240, 268</t>
+        </is>
+      </c>
+      <c r="I488" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J488" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="K488" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L488" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M488" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N488" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O488" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="489" ht="14.25" customHeight="1" s="36">
+      <c r="A489" s="37" t="inlineStr">
+        <is>
+          <t>UE6</t>
+        </is>
+      </c>
+      <c r="B489" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C489" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D489" s="39" t="inlineStr">
+        <is>
+          <t>อยากทราบหน่วยกิตของวิชาหัวข้อพิเศษทางด้านเทคโนโลยีสารสนเทศทางธุรกิจ 1</t>
+        </is>
+      </c>
+      <c r="E489" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F489" s="39" t="inlineStr">
+        <is>
+          <t>3(3-0-6)</t>
+        </is>
+      </c>
+      <c r="G489" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06036132 หัวข้อพิเศษทางด้านเทคโนโลยีสารสนเทศทางธุรกิจ 1 (SPECIAL TOPICS IN BUSINESS INFORMATION TECHNOLOGY 1) — 3(3-0-6) หน่วยกิต · หลักสูตร BIT 2565 (ปริญญาตรี)
+อยู่ในกลุ่มวิชาเลือกทางเทคโนโลยีสารสนเทศทางธุรกิจหรือกลุ่มวิชา (หน้า 23)
+ไม่ได้กำหนดปี/ภาคไว้ในแผนการศึกษาของเล่ม (เป็นวิชาเลือก)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H489" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 23, 24, 76, 251, 273</t>
+        </is>
+      </c>
+      <c r="I489" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J489" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="K489" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L489" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M489" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N489" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O489" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="490" ht="14.25" customHeight="1" s="36">
+      <c r="A490" s="37" t="inlineStr">
+        <is>
+          <t>UE7</t>
+        </is>
+      </c>
+      <c r="B490" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C490" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D490" s="39" t="inlineStr">
+        <is>
+          <t>ภาษาอังกฤษพื้นฐาน 2 เรียนปีอะไร</t>
+        </is>
+      </c>
+      <c r="E490" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F490" s="39" t="inlineStr">
+        <is>
+          <t>ปี 1 ภาค 2</t>
+        </is>
+      </c>
+      <c r="G490" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 96644008 ภาษาอังกฤษพื้นฐาน 2 (FOUNDATION ENGLISH 2) — 3(3-0-6) หน่วยกิต · หลักสูตร BIT 2565 (ปริญญาตรี)
+อยู่ในกลุ่มวิชาด้านภาษาและการสื่อสาร (หน้า 20)
+เรียนตามแผนการศึกษา:
+  - ปีที่ 1 ภาคการศึกษาที่ 2 (ทั้งแผนปกติและแผนสหกิจ, หน้า 27, 32)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H490" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 20, 27, 32, 267</t>
+        </is>
+      </c>
+      <c r="I490" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J490" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="K490" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L490" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M490" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N490" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O490" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="491" ht="14.25" customHeight="1" s="36">
+      <c r="A491" s="37" t="inlineStr">
+        <is>
+          <t>UE8</t>
+        </is>
+      </c>
+      <c r="B491" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C491" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D491" s="39" t="inlineStr">
+        <is>
+          <t>เทคโนโลยีกลุ่มเมฆ เรียนปีอะไร</t>
+        </is>
+      </c>
+      <c r="E491" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F491" s="39" t="inlineStr">
+        <is>
+          <t>ปี 3 ภาค 1</t>
+        </is>
+      </c>
+      <c r="G491" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06036123 เทคโนโลยีกลุ่มเมฆ (CLOUD TECHNOLOGY) — 3(3-0-6) หน่วยกิต · หลักสูตร BIT 2565 (ปริญญาตรี)
+อยู่ในกลุ่มเทคโนโลยีและวิธีการทางซอฟต์แวร์ (ส่วนของกลุ่มวิชาเฉพาะด้าน) (หน้า 23)
+เรียนตามแผนการศึกษา:
+  - ปีที่ 3 ภาคการศึกษาที่ 1 (ทั้งแผนปกติและแผนสหกิจ, หน้า 28, 33)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H491" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 23, 28, 33, 75, 248, 270, 273</t>
+        </is>
+      </c>
+      <c r="I491" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J491" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="K491" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L491" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M491" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N491" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O491" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="492" ht="14.25" customHeight="1" s="36">
+      <c r="A492" s="37" t="inlineStr">
+        <is>
+          <t>UM6</t>
+        </is>
+      </c>
+      <c r="B492" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C492" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D492" s="39" t="inlineStr">
+        <is>
+          <t>How many credits is Customer Relationship Management?</t>
+        </is>
+      </c>
+      <c r="E492" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F492" s="39" t="inlineStr">
+        <is>
+          <t>3(3-0-6)</t>
+        </is>
+      </c>
+      <c r="G492" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06036139 การบริหารระบบลูกค้าสัมพันธ์ (CUSTOMER RELATIONSHIP MANAGEMENT) — 3(3-0-6) หน่วยกิต · หลักสูตร BIT 2565 (ปริญญาตรี)
+อยู่ในกลุ่มวิชาเลือกทางเทคโนโลยีสารสนเทศทางธุรกิจหรือกลุ่มวิชา (หน้า 23)
+ไม่ได้กำหนดปี/ภาคไว้ในแผนการศึกษาของเล่ม (เป็นวิชาเลือก)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H492" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 23, 24, 76, 253, 271</t>
+        </is>
+      </c>
+      <c r="I492" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J492" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="K492" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L492" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M492" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N492" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O492" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="493" ht="14.25" customHeight="1" s="36">
+      <c r="A493" s="37" t="inlineStr">
+        <is>
+          <t>UM7</t>
+        </is>
+      </c>
+      <c r="B493" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C493" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D493" s="39" t="inlineStr">
+        <is>
+          <t>How many credits is Object Oriented Technology?</t>
+        </is>
+      </c>
+      <c r="E493" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F493" s="39" t="inlineStr">
+        <is>
+          <t>3(3-0-6)</t>
+        </is>
+      </c>
+      <c r="G493" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06036130 เทคโนโลยีเชิงอ็อบเจกต์ (OBJECT ORIENTED TECHNOLOGY) — 3(3-0-6) หน่วยกิต · หลักสูตร BIT 2565 (ปริญญาตรี)
+อยู่ในกลุ่มวิชาเลือกทางเทคโนโลยีสารสนเทศทางธุรกิจหรือกลุ่มวิชา (หน้า 23)
+ไม่ได้กำหนดปี/ภาคไว้ในแผนการศึกษาของเล่ม (เป็นวิชาเลือก)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H493" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 23, 24, 75, 251, 270, 273</t>
+        </is>
+      </c>
+      <c r="I493" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J493" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="K493" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L493" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M493" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N493" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O493" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="494" ht="14.25" customHeight="1" s="36">
+      <c r="A494" s="37" t="inlineStr">
+        <is>
+          <t>UM8</t>
+        </is>
+      </c>
+      <c r="B494" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C494" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D494" s="39" t="inlineStr">
+        <is>
+          <t>Which year and semester is Sports And Recreational Activities taught?</t>
+        </is>
+      </c>
+      <c r="E494" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F494" s="39" t="inlineStr">
+        <is>
+          <t>ปี 1 ภาค 1</t>
+        </is>
+      </c>
+      <c r="G494" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 96641003 กีฬาและนันทนาการ (SPORTS AND RECREATIONAL ACTIVITIES) — 1(0-3-2) หน่วยกิต · หลักสูตร BIT 2565 (ปริญญาตรี)
+อยู่ในกลุ่มวิชาพื้นฐาน (หน้า 20)
+เรียนตามแผนการศึกษา:
+  - ปีที่ 1 ภาคการศึกษาที่ 1 (ทั้งแผนปกติและแผนสหกิจ, หน้า 26, 31)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H494" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 20, 26, 31, 267</t>
+        </is>
+      </c>
+      <c r="I494" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J494" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="K494" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L494" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M494" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N494" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O494" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="495" ht="14.25" customHeight="1" s="36">
+      <c r="A495" s="37" t="inlineStr">
+        <is>
+          <t>UM9</t>
+        </is>
+      </c>
+      <c r="B495" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C495" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D495" s="39" t="inlineStr">
+        <is>
+          <t>ระบบฐานข้อมูลขั้นสูง มี prerequisite อะไร</t>
+        </is>
+      </c>
+      <c r="E495" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F495" s="39" t="inlineStr">
+        <is>
+          <t>06036112</t>
+        </is>
+      </c>
+      <c r="G495" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06036127 ระบบฐานข้อมูลขั้นสูง (ADVANCED DATABASE SYSTEMS) — 3(3-0-6) | ไม่ระบุชั้นปี (วิชาเลือก)
+  ต้องผ่านวิชาบังคับก่อน:
+    • 06036112 แนวคิดระบบฐานข้อมูล (DATABASE SYSTEM CONCEPTS) — 3(2-2-5) | ปีที่ 2 ภาคการศึกษาที่ 2</t>
+        </is>
+      </c>
+      <c r="H495" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 22, 23, 28, 33, 74, 75, 243, 249</t>
+        </is>
+      </c>
+      <c r="I495" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (prerequisite) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J495" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K495" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L495" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M495" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N495" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O495" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="496" ht="14.25" customHeight="1" s="36">
+      <c r="A496" s="37" t="inlineStr">
+        <is>
+          <t>UM10</t>
+        </is>
+      </c>
+      <c r="B496" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C496" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D496" s="39" t="inlineStr">
+        <is>
+          <t>โครงงานทางด้านเทคโนโลยีสารสนเทศเชิงธุรกิจ 2 มี prerequisite อะไร</t>
+        </is>
+      </c>
+      <c r="E496" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F496" s="39" t="inlineStr">
+        <is>
+          <t>06036145</t>
+        </is>
+      </c>
+      <c r="G496" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06036146 โครงงานทางด้านเทคโนโลยีสารสนเทศเชิงธุรกิจ 2 (PROJECT IN BUSINESS INFORMATION TECHNOLOGY 2) — 3(0-9-0) | ปีที่ 4 ภาคการศึกษาที่ 1
+  ต้องผ่านวิชาบังคับก่อน:
+    • 06036145 โครงงานทางด้านเทคโนโลยีสารสนเทศเชิงธุรกิจ 1 (PROJECT IN BUSINESS INFORMATION TECHNOLOGY 1) — 3(0-9-0) | ปีที่ 3 ภาคการศึกษาที่ 2</t>
+        </is>
+      </c>
+      <c r="H496" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 29, 76, 256, 269, 22, 23</t>
+        </is>
+      </c>
+      <c r="I496" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (prerequisite) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J496" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="K496" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L496" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M496" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N496" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O496" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="497" ht="14.25" customHeight="1" s="36">
+      <c r="A497" s="37" t="inlineStr">
+        <is>
+          <t>UH3</t>
+        </is>
+      </c>
+      <c r="B497" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C497" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D497" s="39" t="inlineStr">
+        <is>
+          <t>เทอม 1 ปี 3 ต้องลงวิชาบังคับอะไรบ้าง</t>
+        </is>
+      </c>
+      <c r="E497" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F497" s="39" t="inlineStr">
+        <is>
+          <t>06036107, 06036110, 06036114, 06036121, 06036123</t>
+        </is>
+      </c>
+      <c r="G497" s="39" t="inlineStr">
+        <is>
+          <t>รายวิชาของหลักสูตร BIT 2565 (current) ปีที่ 3 (จัดกลุ่มตามภาคการศึกษา):
+▶ ภาคการศึกษาที่ 1 — วิชาบังคับ (5 วิชา 15 หน่วยกิต):
+  - 06036107 การบริหารโครงการเทคโนโลยีสารสนเทศ (INFORMATION TECHNOLOGY PROJECT MANAGEMENT) — 3(3-0-6)
+  - 06036110 การวางแผนทรัพยากรองค์กร (ENTERPRISE RESOURCE PLANNING) — 3(3-0-6)
+  - 06036114 การพัฒนาเว็บแอปพลิเคชันโดยใช้เฟรมเวิร์ก (WEB APPLICATION DEVELOPMENT USING FRAMEWORKS) — 3(2-2-5)
+  - 06036121 การวิเคราะห์และออกแบบระบบสารสนเทศทางธุรกิจ (BUSINESS INFORMATION SYSTEM ANALYSIS AND DESIGN) — 3(3-0-6)
+  - 06036123 เทคโนโลยีกลุ่มเมฆ (CLOUD TECHNOLOGY) — 3(3-0-6)
+  วิชาเลือกเฉพาะแขนง (เลือก 1 แขนง แล้วลงวิชาในแขนงนั้น) กลุ่มที่มี:
+    • วิชาเลือกด้านภาษาและการสื่อสาร
+รวมปีที่ 3 (วิชาบังคับ): 5 วิชา 15 หน่วยกิต (ยังไม่รวมวิชาเลือก)</t>
+        </is>
+      </c>
+      <c r="H497" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 28, 75, 22, 23, 74, 269, 241, 243</t>
+        </is>
+      </c>
+      <c r="I497" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ปี/ภาค) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J497" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K497" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L497" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M497" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N497" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O497" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="498" ht="14.25" customHeight="1" s="36">
+      <c r="A498" s="37" t="inlineStr">
+        <is>
+          <t>UH4</t>
+        </is>
+      </c>
+      <c r="B498" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C498" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D498" s="39" t="inlineStr">
+        <is>
+          <t>เทอม 2 ปี 2 ต้องลงวิชาบังคับอะไรบ้าง</t>
+        </is>
+      </c>
+      <c r="E498" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F498" s="39" t="inlineStr">
+        <is>
+          <t>06036108, 06036111, 06036112, 06036113, 06036124</t>
+        </is>
+      </c>
+      <c r="G498" s="39" t="inlineStr">
+        <is>
+          <t>รายวิชาของหลักสูตร BIT 2565 (current) ปีที่ 2 (จัดกลุ่มตามภาคการศึกษา):
+▶ ภาคการศึกษาที่ 2 — วิชาบังคับ (5 วิชา 15 หน่วยกิต):
+  - 06036108 เศรษฐศาสตร์เทคโนโลยีสารสนเทศ (ECONOMICS OF INFORMATION TECHNOLOGY) — 3(3-0-6)
+  - 06036111 เทคโนโลยีดิจิทัลสำหรับธุรกิจ (DIGITAL TECHNOLOGY FOR BUSINESS) — 3(3-0-6)
+  - 06036112 แนวคิดระบบฐานข้อมูล (DATABASE SYSTEM CONCEPTS) — 3(2-2-5)
+  - 06036113 การออกแบบส่วนต่อประสานกับมนุษย์ (HUMAN INTERFACE DESIGN) — 3(3-0-6)
+  - 06036124 เครือข่ายคอมพิวเตอร์และความมั่นคงทางไซเบอร์เบื้องต้น (INTRODUCTION TO COMPUTER NETWORK AND CYBERSECURITY) — 3(3-0-6)
+  วิชาเลือกเฉพาะแขนง (เลือก 1 แขนง แล้วลงวิชาในแขนงนั้น) กลุ่มที่มี:
+    • วิชาเลือกหมวดวิชาศึกษาทั่วไป
+รวมปีที่ 2 (วิชาบังคับ): 5 วิชา 15 หน่วยกิต (ยังไม่รวมวิชาเลือก)</t>
+        </is>
+      </c>
+      <c r="H498" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 28, 33, 74, 22, 75, 268, 269, 23</t>
+        </is>
+      </c>
+      <c r="I498" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ปี/ภาค) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J498" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K498" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L498" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M498" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N498" s="39" t="inlineStr">
+        <is>
+          <t>0.02s</t>
+        </is>
+      </c>
+      <c r="O498" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="499" ht="14.25" customHeight="1" s="36">
+      <c r="A499" s="37" t="inlineStr">
+        <is>
+          <t>UE9</t>
+        </is>
+      </c>
+      <c r="B499" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C499" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D499" s="39" t="inlineStr">
+        <is>
+          <t>อยากทราบหน่วยกิตของวิชาพีชคณิตเชิงเส้น</t>
+        </is>
+      </c>
+      <c r="E499" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F499" s="39" t="inlineStr">
+        <is>
+          <t>3(3-0-6)</t>
+        </is>
+      </c>
+      <c r="G499" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06026202 พีชคณิตเชิงเส้น (LINEAR ALGEBRA) — 3(3-0-6) หน่วยกิต · หลักสูตร DSBA 2565 (ปริญญาตรี)
+อยู่ในกลุ่มคณิตศาสตร์และสถิติ (ส่วนของกลุ่มวิชาแกน) (หน้า 17)
+เรียนตามแผนการศึกษา:
+  - ปีที่ 1 ภาคการศึกษาที่ 1 (ทั้งแผนปกติและแผนสหกิจ, หน้า 23, 30)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H499" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 17, 23, 30, 68, 315, 353</t>
+        </is>
+      </c>
+      <c r="I499" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J499" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="K499" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L499" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M499" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N499" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O499" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="500" ht="14.25" customHeight="1" s="36">
+      <c r="A500" s="37" t="inlineStr">
+        <is>
+          <t>UE10</t>
+        </is>
+      </c>
+      <c r="B500" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C500" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D500" s="39" t="inlineStr">
+        <is>
+          <t>อยากทราบหน่วยกิตของวิชาแคลคูลัส 2</t>
+        </is>
+      </c>
+      <c r="E500" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F500" s="39" t="inlineStr">
+        <is>
+          <t>3(3-0-6)</t>
+        </is>
+      </c>
+      <c r="G500" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06026201 แคลคูลัส 2 (CALCULUS 2) — 3(3-0-6) หน่วยกิต · หลักสูตร DSBA 2565 (ปริญญาตรี)
+อยู่ในกลุ่มคณิตศาสตร์และสถิติ (ส่วนของกลุ่มวิชาแกน) (หน้า 17)
+เรียนตามแผนการศึกษา:
+  - ปีที่ 1 ภาคการศึกษาที่ 2 (ทั้งแผนปกติและแผนสหกิจ, หน้า 24, 31)
+วิชาบังคับก่อน: 06026200 แคลคูลัส 1</t>
+        </is>
+      </c>
+      <c r="H500" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 17, 24, 31, 68, 314, 353</t>
+        </is>
+      </c>
+      <c r="I500" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J500" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="K500" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L500" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M500" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N500" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O500" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="501" ht="14.25" customHeight="1" s="36">
+      <c r="A501" s="37" t="inlineStr">
+        <is>
+          <t>UE11</t>
+        </is>
+      </c>
+      <c r="B501" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C501" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D501" s="39" t="inlineStr">
+        <is>
+          <t>การเขียนโปรแกรมเว็บพื้นฐาน เรียนปีอะไร</t>
+        </is>
+      </c>
+      <c r="E501" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F501" s="39" t="inlineStr">
+        <is>
+          <t>ปี 2 ภาค 1</t>
+        </is>
+      </c>
+      <c r="G501" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06066302 การเขียนโปรแกรมเว็บพื้นฐาน (FUNDAMENTAL WEB PROGRAMMING) — 3(2-2-5) หน่วยกิต · หลักสูตร DSBA 2565 (ปริญญาตรี)
+อยู่ในกลุ่มพื้นฐานเทคโนโลยีสารสนเทศ (ส่วนของกลุ่มวิชาแกน) (หน้า 17)
+เรียนตามแผนการศึกษา:
+  - ปีที่ 2 ภาคการศึกษาที่ 1 (ทั้งแผนปกติและแผนสหกิจ, หน้า 25, 32)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H501" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 17, 25, 32, 18, 73, 319, 353</t>
+        </is>
+      </c>
+      <c r="I501" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J501" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="K501" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L501" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M501" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N501" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O501" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="502" ht="14.25" customHeight="1" s="36">
+      <c r="A502" s="37" t="inlineStr">
+        <is>
+          <t>UE12</t>
+        </is>
+      </c>
+      <c r="B502" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C502" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D502" s="39" t="inlineStr">
+        <is>
+          <t>แคลคูลัส 2 เรียนปีอะไร</t>
+        </is>
+      </c>
+      <c r="E502" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F502" s="39" t="inlineStr">
+        <is>
+          <t>ปี 1 ภาค 2</t>
+        </is>
+      </c>
+      <c r="G502" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06026201 แคลคูลัส 2 (CALCULUS 2) — 3(3-0-6) หน่วยกิต · หลักสูตร DSBA 2565 (ปริญญาตรี)
+อยู่ในกลุ่มคณิตศาสตร์และสถิติ (ส่วนของกลุ่มวิชาแกน) (หน้า 17)
+เรียนตามแผนการศึกษา:
+  - ปีที่ 1 ภาคการศึกษาที่ 2 (ทั้งแผนปกติและแผนสหกิจ, หน้า 24, 31)
+วิชาบังคับก่อน: 06026200 แคลคูลัส 1</t>
+        </is>
+      </c>
+      <c r="H502" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 17, 24, 31, 68, 314, 353</t>
+        </is>
+      </c>
+      <c r="I502" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J502" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="K502" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L502" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M502" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N502" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O502" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="503" ht="14.25" customHeight="1" s="36">
+      <c r="A503" s="37" t="inlineStr">
+        <is>
+          <t>UM11</t>
+        </is>
+      </c>
+      <c r="B503" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C503" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D503" s="39" t="inlineStr">
+        <is>
+          <t>How many credits is Oversea Cooperative Education In Data Science And Business Analytics?</t>
+        </is>
+      </c>
+      <c r="E503" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F503" s="39" t="inlineStr">
+        <is>
+          <t>6(0-35-0)</t>
+        </is>
+      </c>
+      <c r="G503" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06026260 สหกิจศึกษาต่างประเทศทางวิทยาการข้อมูลและการ วิเคราะห์เชิงธุรกิจ (OVERSEA COOPERATIVE EDUCATION IN DATA SCIENCE AND BUSINESS ANALYTICS) — 6(0-35-0) หน่วยกิต · หลักสูตร DSBA 2565 (ปริญญาตรี)
+อยู่ในสหกิจศึกษา (ส่วนของกลุ่มวิชาการศึกษาทางเลือก) (หน้า 22)
+เรียนตามแผนการศึกษา:
+  - ปีที่ 4 ภาคการศึกษาที่ 2 (แผนสหกิจ, หน้า 36)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H503" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 22, 36, 72, 341, 356</t>
+        </is>
+      </c>
+      <c r="I503" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J503" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="K503" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L503" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M503" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N503" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O503" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="504" ht="14.25" customHeight="1" s="36">
+      <c r="A504" s="37" t="inlineStr">
+        <is>
+          <t>UM12</t>
+        </is>
+      </c>
+      <c r="B504" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C504" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D504" s="39" t="inlineStr">
+        <is>
+          <t>How many credits is Fundamental Web Programming?</t>
+        </is>
+      </c>
+      <c r="E504" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F504" s="39" t="inlineStr">
+        <is>
+          <t>3(2-2-5)</t>
+        </is>
+      </c>
+      <c r="G504" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06066302 การเขียนโปรแกรมเว็บพื้นฐาน (FUNDAMENTAL WEB PROGRAMMING) — 3(2-2-5) หน่วยกิต · หลักสูตร DSBA 2565 (ปริญญาตรี)
+อยู่ในกลุ่มพื้นฐานเทคโนโลยีสารสนเทศ (ส่วนของกลุ่มวิชาแกน) (หน้า 17)
+เรียนตามแผนการศึกษา:
+  - ปีที่ 2 ภาคการศึกษาที่ 1 (ทั้งแผนปกติและแผนสหกิจ, หน้า 25, 32)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H504" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 17, 25, 32, 18, 73, 319, 353</t>
+        </is>
+      </c>
+      <c r="I504" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J504" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="K504" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L504" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M504" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N504" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O504" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="505" ht="14.25" customHeight="1" s="36">
+      <c r="A505" s="37" t="inlineStr">
+        <is>
+          <t>UM13</t>
+        </is>
+      </c>
+      <c r="B505" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C505" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D505" s="39" t="inlineStr">
+        <is>
+          <t>Which year and semester is Database System Concepts taught?</t>
+        </is>
+      </c>
+      <c r="E505" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F505" s="39" t="inlineStr">
+        <is>
+          <t>ปี 2 ภาค 1</t>
+        </is>
+      </c>
+      <c r="G505" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06066300 แนวคิดระบบฐานข้อมูล (DATABASE SYSTEM CONCEPTS) — 3(2-2-5) หน่วยกิต · หลักสูตร DSBA 2565 (ปริญญาตรี)
+อยู่ในกลุ่มพื้นฐานเทคโนโลยีสารสนเทศ (ส่วนของกลุ่มวิชาแกน) (หน้า 17)
+เรียนตามแผนการศึกษา:
+  - ปีที่ 2 ภาคการศึกษาที่ 1 (ทั้งแผนปกติและแผนสหกิจ, หน้า 25, 32)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H505" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 17, 25, 32, 18, 73, 318, 323, 324</t>
+        </is>
+      </c>
+      <c r="I505" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J505" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K505" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L505" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M505" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N505" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O505" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="506" ht="14.25" customHeight="1" s="36">
+      <c r="A506" s="37" t="inlineStr">
+        <is>
+          <t>UM14</t>
+        </is>
+      </c>
+      <c r="B506" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C506" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D506" s="39" t="inlineStr">
+        <is>
+          <t>ระบบสารสนเทศเพื่อการจัดการ มี prerequisite อะไร</t>
+        </is>
+      </c>
+      <c r="E506" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F506" s="39" t="inlineStr">
+        <is>
+          <t>06066101</t>
+        </is>
+      </c>
+      <c r="G506" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06066102 ระบบสารสนเทศเพื่อการจัดการ (MANAGEMENT INFORMATION SYSTEMS) — 3(3-0-6) | ปีที่ 2 ภาคการศึกษาที่ 2
+  ต้องผ่านวิชาบังคับก่อน:
+    • 06066101 พื้นฐานทางธุรกิจสำหรับเทคโนโลยีสารสนเทศ (BUSINESS FUNDAMENTALS FOR INFORMATION TECHNOLOGY) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H506" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 18, 73, 353, 23, 26, 30, 33, 317</t>
+        </is>
+      </c>
+      <c r="I506" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (prerequisite) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J506" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K506" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L506" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M506" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N506" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O506" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="507" ht="14.25" customHeight="1" s="36">
+      <c r="A507" s="37" t="inlineStr">
+        <is>
+          <t>UM15</t>
+        </is>
+      </c>
+      <c r="B507" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C507" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D507" s="39" t="inlineStr">
+        <is>
+          <t>ระบบข้อมูลมหัต มี prerequisite อะไร</t>
+        </is>
+      </c>
+      <c r="E507" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F507" s="39" t="inlineStr">
+        <is>
+          <t>06066300</t>
+        </is>
+      </c>
+      <c r="G507" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06026213 ระบบข้อมูลมหัต (BIG DATA SYSTEMS) — 3(2-2-5) | ปีที่ 3 ภาคการศึกษาที่ 2
+  ต้องผ่านวิชาบังคับก่อน:
+    • 06066300 แนวคิดระบบฐานข้อมูล (DATABASE SYSTEM CONCEPTS) — 3(2-2-5) | ปีที่ 2 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H507" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 18, 19, 25, 28, 32, 35, 69, 73</t>
+        </is>
+      </c>
+      <c r="I507" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (prerequisite) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J507" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K507" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L507" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M507" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N507" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O507" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="508" ht="14.25" customHeight="1" s="36">
+      <c r="A508" s="37" t="inlineStr">
+        <is>
+          <t>UH5</t>
+        </is>
+      </c>
+      <c r="B508" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C508" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D508" s="39" t="inlineStr">
+        <is>
+          <t>เทอม 2 ปี 1 ต้องลงวิชาบังคับอะไรบ้าง</t>
+        </is>
+      </c>
+      <c r="E508" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F508" s="39" t="inlineStr">
+        <is>
+          <t>06026201, 06026203, 06026205, 06066001, 90641002, 90642033, 90644008</t>
+        </is>
+      </c>
+      <c r="G508" s="39" t="inlineStr">
+        <is>
+          <t>รายวิชาของหลักสูตร DSBA 2565 (current) ปีที่ 1 (จัดกลุ่มตามภาคการศึกษา):
+▶ ภาคการศึกษาที่ 2 — วิชาบังคับ (7 วิชา 21 หน่วยกิต):
+  - 06026201 แคลคูลัส 2 (CALCULUS 2) — 3(3-0-6)
+  - 06026203 การโปรแกรมคอมพิวเตอร์ (COMPUTER PROGRAMMING) — 3(2-2-5)
+  - 06026205 การตลาดเบื้องต้น (INTRODUCTION TO MARKETING) — 3(3-0-6)
+  - 06066001 ความน่าจะเป็นและสถิติ (PROBABILITY AND STATISTICS) — 3(3-0-6)
+  - 90641002 ความฉลาดทางดิจิทัล (DIGITAL INTELLIGENCE QUOTIENT) — 3(3-0-6)
+  - 90642033 กฎหมายสำหรับคนรุ่นใหม่ (LAW FOR NEW GENERATION) — 3(3-0-6)
+  - 90644008 ภาษาอังกฤษพื้นฐาน 2 (FOUNDATION ENGLISH 2) — 3(3-0-6)
+รวมปีที่ 1 (วิชาบังคับ): 7 วิชา 21 หน่วยกิต (ยังไม่รวมวิชาเลือก)</t>
+        </is>
+      </c>
+      <c r="H508" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 24, 31, 68, 353, 16, 17, 352, 18</t>
+        </is>
+      </c>
+      <c r="I508" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ปี/ภาค) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J508" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K508" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L508" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M508" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N508" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O508" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="509" ht="14.25" customHeight="1" s="36">
+      <c r="A509" s="37" t="inlineStr">
+        <is>
+          <t>UE13</t>
+        </is>
+      </c>
+      <c r="B509" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C509" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D509" s="39" t="inlineStr">
+        <is>
+          <t>อยากทราบหน่วยกิตของวิชาปฏิบัติการพิเศษทางด้านเทคโนโลยีสารสนเทศ 2</t>
+        </is>
+      </c>
+      <c r="E509" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F509" s="39" t="inlineStr">
+        <is>
+          <t>3(2-2-5)</t>
+        </is>
+      </c>
+      <c r="G509" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06016478 ปฎิบัติการพิเศษทางด้านเทคโนโลยีสารสนเทศ 2 (SPECIAL WORKSHOP IN INFORMATION TECHNOLOGY 2) — 3(2-2-5) หน่วยกิต · หลักสูตร IT 2565 (ปริญญาตรี)
+อยู่ในกลุ่มวิชาเลือกทางเทคโนโลยีสารสนเทศ (หน้า 26)
+ไม่ได้กำหนดปี/ภาคตายตัวในแผนการศึกษา (เป็นวิชาเลือกของกลุ่ม) ลงเรียนได้ในช่องวิชาเลือกตามแผน:
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกทางเทคโนโลยีสารสนเทศ 1" (หน้า 35, 36)
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกทางเทคโนโลยีสารสนเทศ 2" (หน้า 35, 36)
+  - แผนปกติ ปีที่ 4 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกทางเทคโนโลยีสารสนเทศ 3" (หน้า 37)
+  - แผนสหกิจ ปีที่ 4 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกทางเทคโนโลยีสารสนเทศ 1" (หน้า 43)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H509" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 26, 35, 36, 37, 43, 29, 87, 355</t>
+        </is>
+      </c>
+      <c r="I509" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J509" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K509" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L509" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M509" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N509" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O509" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="510" ht="14.25" customHeight="1" s="36">
+      <c r="A510" s="37" t="inlineStr">
+        <is>
+          <t>UE14</t>
+        </is>
+      </c>
+      <c r="B510" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C510" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D510" s="39" t="inlineStr">
+        <is>
+          <t>อยากทราบหน่วยกิตของวิชาเทคโนโลยีกลุ่มเมฆ</t>
+        </is>
+      </c>
+      <c r="E510" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F510" s="39" t="inlineStr">
+        <is>
+          <t>3(2-2-5)</t>
+        </is>
+      </c>
+      <c r="G510" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06016404 เทคโนโลยีกลุ่มเมฆ (CLOUD COMPUTING) — 3(2-2-5) หน่วยกิต · หลักสูตร IT 2565 (ปริญญาตรี)
+อยู่ในกลุ่มเทคโนโลยีเพื่องานประยุกต์ (ส่วนของกลุ่มวิชาเฉพาะด้าน) (หน้า 23)
+เรียนตามแผนการศึกษา:
+  - ปีที่ 3 ภาคการศึกษาที่ 1 (ทั้งแผนปกติและแผนสหกิจ, หน้า 35, 42)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H510" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 23, 35, 42, 83, 325, 336</t>
+        </is>
+      </c>
+      <c r="I510" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J510" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="K510" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L510" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M510" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N510" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O510" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="511" ht="14.25" customHeight="1" s="36">
+      <c r="A511" s="37" t="inlineStr">
+        <is>
+          <t>UE15</t>
+        </is>
+      </c>
+      <c r="B511" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C511" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D511" s="39" t="inlineStr">
+        <is>
+          <t>ผู้ประกอบการสมัยใหม่ เรียนปีอะไร</t>
+        </is>
+      </c>
+      <c r="E511" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F511" s="39" t="inlineStr">
+        <is>
+          <t>ปี 4 ภาค 1</t>
+        </is>
+      </c>
+      <c r="G511" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 90643021 ผู้ประกอบการสมัยใหม่ (MODERN ENTREPRENEURS) — 3(3-0-6) หน่วยกิต · หลักสูตร IT 2565 (ปริญญาตรี)
+อยู่ในกลุ่มวิชาตามเกณฑ์ของคณะ (หน้า 22)
+เรียนตามแผนการศึกษา:
+  - ปีที่ 4 ภาคการศึกษาที่ 1 (ทั้งแผนปกติและแผนสหกิจ, หน้า 37, 43)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H511" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 22, 37, 43, 268, 373</t>
+        </is>
+      </c>
+      <c r="I511" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J511" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="K511" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L511" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M511" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N511" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O511" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="512" ht="14.25" customHeight="1" s="36">
+      <c r="A512" s="37" t="inlineStr">
+        <is>
+          <t>UE16</t>
+        </is>
+      </c>
+      <c r="B512" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C512" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D512" s="39" t="inlineStr">
+        <is>
+          <t>การออกแบบและพัฒนาเกมเบื้องต้น เรียนปีอะไร</t>
+        </is>
+      </c>
+      <c r="E512" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F512" s="39" t="inlineStr">
+        <is>
+          <t>ปี 3 ภาค 1</t>
+        </is>
+      </c>
+      <c r="G512" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06016427 การออกแบบและพัฒนาเกมเบื้องต้น (INTRODUCTION TO GAME DESIGN AND DEVELOPMENT) — 3(2-2-5) หน่วยกิต · หลักสูตร IT 2565 (ปริญญาตรี)
+อยู่ในกลุ่มวิชาด้านสื่อประสมสำหรับการพัฒนาสื่อเชิงโต้ตอบ เว็บ และเกม (ส่วนของกลุ่มวิชาบังคับเฉพาะสาขา) — ต้องเลือกเรียนกลุ่มใดกลุ่มหนึ่ง (หน้า 25)
+เรียนตามแผนการศึกษา:
+  - ปีที่ 3 ภาคการศึกษาที่ 1 (ทั้งแผนปกติและแผนสหกิจ, หน้า 35, 42)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H512" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 25, 35, 42, 26, 84, 335</t>
+        </is>
+      </c>
+      <c r="I512" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J512" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="K512" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L512" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M512" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N512" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O512" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="513" ht="14.25" customHeight="1" s="36">
+      <c r="A513" s="37" t="inlineStr">
+        <is>
+          <t>UM16</t>
+        </is>
+      </c>
+      <c r="B513" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C513" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D513" s="39" t="inlineStr">
+        <is>
+          <t>How many credits is Supply Chain Management And Logistics?</t>
+        </is>
+      </c>
+      <c r="E513" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F513" s="39" t="inlineStr">
+        <is>
+          <t>3(3-0-6)</t>
+        </is>
+      </c>
+      <c r="G513" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06016452 การจัดการห่วงโซ่อุปทานและโลจิสติกส์ (SUPPLY CHAIN MANAGEMENT AND LOGISTICS) — 3(3-0-6) หน่วยกิต · หลักสูตร IT 2565 (ปริญญาตรี)
+อยู่ในกลุ่มวิชาเลือกทางเทคโนโลยีสารสนเทศ (หน้า 26)
+ไม่ได้กำหนดปี/ภาคตายตัวในแผนการศึกษา (เป็นวิชาเลือกของกลุ่ม) ลงเรียนได้ในช่องวิชาเลือกตามแผน:
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกทางเทคโนโลยีสารสนเทศ 1" (หน้า 35, 36)
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกทางเทคโนโลยีสารสนเทศ 2" (หน้า 35, 36)
+  - แผนปกติ ปีที่ 4 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกทางเทคโนโลยีสารสนเทศ 3" (หน้า 37)
+  - แผนสหกิจ ปีที่ 4 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกทางเทคโนโลยีสารสนเทศ 1" (หน้า 43)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H513" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 26, 35, 36, 37, 43, 27, 86, 344</t>
+        </is>
+      </c>
+      <c r="I513" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J513" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K513" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L513" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M513" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N513" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O513" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="514" ht="14.25" customHeight="1" s="36">
+      <c r="A514" s="37" t="inlineStr">
+        <is>
+          <t>UM17</t>
+        </is>
+      </c>
+      <c r="B514" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C514" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D514" s="39" t="inlineStr">
+        <is>
+          <t>How many credits is Mobile Device Programming?</t>
+        </is>
+      </c>
+      <c r="E514" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F514" s="39" t="inlineStr">
+        <is>
+          <t>3(2-2-5)</t>
+        </is>
+      </c>
+      <c r="G514" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06016431 การโปรแกรมอุปกรณ์เคลื่อนที่ (MOBILE DEVICE PROGRAMMING) — 3(2-2-5) หน่วยกิต · หลักสูตร IT 2565 (ปริญญาตรี)
+อยู่ในกลุ่มวิชาเลือกทางเทคโนโลยีสารสนเทศ (หน้า 26)
+ไม่ได้กำหนดปี/ภาคตายตัวในแผนการศึกษา (เป็นวิชาเลือกของกลุ่ม) ลงเรียนได้ในช่องวิชาเลือกตามแผน:
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกทางเทคโนโลยีสารสนเทศ 1" (หน้า 35, 36)
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกทางเทคโนโลยีสารสนเทศ 2" (หน้า 35, 36)
+  - แผนปกติ ปีที่ 4 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกทางเทคโนโลยีสารสนเทศ 3" (หน้า 37)
+  - แผนสหกิจ ปีที่ 4 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกทางเทคโนโลยีสารสนเทศ 1" (หน้า 43)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H514" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 26, 35, 36, 37, 43, 85, 336, 378</t>
+        </is>
+      </c>
+      <c r="I514" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J514" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K514" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L514" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M514" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N514" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O514" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="515" ht="14.25" customHeight="1" s="36">
+      <c r="A515" s="37" t="inlineStr">
+        <is>
+          <t>UM18</t>
+        </is>
+      </c>
+      <c r="B515" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C515" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D515" s="39" t="inlineStr">
+        <is>
+          <t>Which year and semester is Software Engineering taught?</t>
+        </is>
+      </c>
+      <c r="E515" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F515" s="39" t="inlineStr">
+        <is>
+          <t>ปี 2 ภาค 2</t>
+        </is>
+      </c>
+      <c r="G515" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06016410 วิศวกรรมซอฟต์แวร์ (SOFTWARE ENGINEERING) — 3(3-0-6) หน่วยกิต · หลักสูตร IT 2565 (ปริญญาตรี)
+อยู่ในกลุ่มเทคโนโลยีและวิธีการทางซอฟต์แวร์ (ส่วนของกลุ่มวิชาเฉพาะด้าน) (หน้า 24)
+เรียนตามแผนการศึกษา:
+  - ปีที่ 2 ภาคการศึกษาที่ 2 (ทั้งแผนปกติและแผนสหกิจ, หน้า 34, 41)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H515" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 24, 34, 41, 84, 327</t>
+        </is>
+      </c>
+      <c r="I515" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J515" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="K515" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L515" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M515" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N515" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O515" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="516" ht="14.25" customHeight="1" s="36">
+      <c r="A516" s="37" t="inlineStr">
+        <is>
+          <t>UM19</t>
+        </is>
+      </c>
+      <c r="B516" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C516" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D516" s="39" t="inlineStr">
+        <is>
+          <t>การพัฒนาคลาวด์แอปพลิเคชัน มี prerequisite อะไร</t>
+        </is>
+      </c>
+      <c r="E516" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F516" s="39" t="inlineStr">
+        <is>
+          <t>06016404</t>
+        </is>
+      </c>
+      <c r="G516" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06016430 การพัฒนาคลาวด์แอปพลิเคชัน (CLOUD APPLICATION DEVELOPMENT) — 3(2-2-5) | ไม่ระบุชั้นปี (วิชาเลือก)
+  ต้องผ่านวิชาบังคับก่อน:
+    • 06016404 เทคโนโลยีกลุ่มเมฆ (CLOUD COMPUTING) — 3(2-2-5) | ปีที่ 3 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H516" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 23, 26, 29, 35, 42, 83, 85, 325</t>
+        </is>
+      </c>
+      <c r="I516" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (prerequisite) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J516" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K516" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L516" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M516" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N516" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O516" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="517" ht="14.25" customHeight="1" s="36">
+      <c r="A517" s="37" t="inlineStr">
+        <is>
+          <t>UM20</t>
+        </is>
+      </c>
+      <c r="B517" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C517" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D517" s="39" t="inlineStr">
+        <is>
+          <t>การพัฒนาเว็บฝั่งไคลเอนต์ มี prerequisite อะไร</t>
+        </is>
+      </c>
+      <c r="E517" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F517" s="39" t="inlineStr">
+        <is>
+          <t>06066302</t>
+        </is>
+      </c>
+      <c r="G517" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06016429 การพัฒนาเว็บฝั่งไคลเอนต์ (CLIENT-SIDE WEB DEVELOPMENT) — 3(2-2-5) | ไม่ระบุชั้นปี (วิชาเลือก)
+  ต้องผ่านวิชาบังคับก่อน:
+    • 06066302 การเขียนโปรแกรมเว็บพื้นฐาน (FUNDAMENTAL WEB PROGRAMMING) — 3(2-2-5) | ปีที่ 2 ภาคการศึกษาที่ 2</t>
+        </is>
+      </c>
+      <c r="H517" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 336, 24, 26, 29, 34, 41, 85, 88</t>
+        </is>
+      </c>
+      <c r="I517" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (prerequisite) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J517" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K517" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L517" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M517" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N517" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O517" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="518" ht="14.25" customHeight="1" s="36">
+      <c r="A518" s="37" t="inlineStr">
+        <is>
+          <t>UH6</t>
+        </is>
+      </c>
+      <c r="B518" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C518" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D518" s="39" t="inlineStr">
+        <is>
+          <t>เทอม 1 ปี 4 ต้องลงวิชาบังคับอะไรบ้าง</t>
+        </is>
+      </c>
+      <c r="E518" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F518" s="39" t="inlineStr">
+        <is>
+          <t>06016406, 90643021</t>
+        </is>
+      </c>
+      <c r="G518" s="39" t="inlineStr">
+        <is>
+          <t>รายวิชาของหลักสูตร IT 2565 (current) ปีที่ 4 (จัดกลุ่มตามภาคการศึกษา):
+▶ ภาคการศึกษาที่ 1 — วิชาบังคับ (2 วิชา 6 หน่วยกิต):
+  - 06016406 โครงงาน 1 (PROJECT 1) — 3(0-9-0)
+  - 90643021 ผู้ประกอบการสมัยใหม่ (MODERN ENTREPRENEURS) — 3(3-0-6)
+  วิชาเลือกเฉพาะแขนง (เลือก 1 แขนง แล้วลงวิชาในแขนงนั้น) กลุ่มที่มี:
+    • วิชาเลือกทางเทคโนโลยีสารสนเทศ
+    • วิชาเลือกหมวดศึกษาทั่วไป
+    • วิชาเลือกเสรี
+รวมปีที่ 4 (วิชาบังคับ): 2 วิชา 6 หน่วยกิต (ยังไม่รวมวิชาเลือก)</t>
+        </is>
+      </c>
+      <c r="H518" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 37, 43, 22, 23, 83, 268, 326, 373</t>
+        </is>
+      </c>
+      <c r="I518" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ปี/ภาค) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J518" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K518" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L518" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M518" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N518" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O518" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="519" ht="14.25" customHeight="1" s="36">
+      <c r="A519" s="37" t="inlineStr">
+        <is>
+          <t>UE17</t>
+        </is>
+      </c>
+      <c r="B519" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C519" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D519" s="39" t="inlineStr">
+        <is>
+          <t>วิชาศึกษาทั่วไป การอ่านและการเขียนเชิงวิชาการ กี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E519" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F519" s="39" t="inlineStr">
+        <is>
+          <t>0(4-0-8)</t>
+        </is>
+      </c>
+      <c r="G519" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 90644005 การอ่านและการ์เขียนเซิงวิชาการ — 0(4-0-8) หน่วยกิต · หลักสูตร IT 2565 (ปริญญาตรี)
+(วิชาศึกษาทั่วไปที่ใช้ร่วมกันทุกหลักสูตร — เล่ม AIT 2566 (ปริญญาตรี) ไม่ได้ลงรายละเอียดวิชานี้ จึงใช้ข้อมูลจากเล่ม IT 2565 (ปริญญาตรี))
+ไม่ได้กำหนดปี/ภาคไว้ในแผนการศึกษาของเล่ม (เป็นวิชาเลือก)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H519" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 146</t>
+        </is>
+      </c>
+      <c r="I519" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J519" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K519" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L519" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M519" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/general_education_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N519" s="39" t="inlineStr">
+        <is>
+          <t>0.03s</t>
+        </is>
+      </c>
+      <c r="O519" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="520" ht="14.25" customHeight="1" s="36">
+      <c r="A520" s="37" t="inlineStr">
+        <is>
+          <t>UE18</t>
+        </is>
+      </c>
+      <c r="B520" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C520" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D520" s="39" t="inlineStr">
+        <is>
+          <t>วิชาศึกษาทั่วไป รักบี้ฟุตบอล กี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E520" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F520" s="39" t="inlineStr">
+        <is>
+          <t>3(2-2-5)</t>
+        </is>
+      </c>
+      <c r="G520" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 90642176 รักบี้ฟุตบอล — 3(2-2-5) หน่วยกิต · หลักสูตร AIT 2566 (ปริญญาตรี)
+(วิชาศึกษาทั่วไปที่ใช้ร่วมกันทุกหลักสูตร — เล่ม BIT 2565 (ปริญญาตรี) ไม่ได้ลงรายละเอียดวิชานี้ จึงใช้ข้อมูลจากเล่ม AIT 2566 (ปริญญาตรี))
+ไม่ได้กำหนดปี/ภาคไว้ในแผนการศึกษาของเล่ม (เป็นวิชาเลือก)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H520" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 190, 243</t>
+        </is>
+      </c>
+      <c r="I520" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J520" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K520" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L520" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M520" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก รหัส 90642065 ในเฉลยไม่มีในเล่มใด เล่ม AIT 2566 หน้า 190 มีรักบี้ฟุตบอล 90642176 = 3 (2-2-5) (เฉลยอาจารย์เขียน 2(1-2-3)))</t>
+        </is>
+      </c>
+      <c r="N520" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O520" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="521" ht="14.25" customHeight="1" s="36">
+      <c r="A521" s="37" t="inlineStr">
+        <is>
+          <t>UE19</t>
+        </is>
+      </c>
+      <c r="B521" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C521" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D521" s="39" t="inlineStr">
+        <is>
+          <t>วิชาศึกษาทั่วไป ภาษาอังกฤษเพื่อการท่องเที่ยวและการเดินทาง กี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E521" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F521" s="39" t="inlineStr">
+        <is>
+          <t>3(3-0-6)</t>
+        </is>
+      </c>
+      <c r="G521" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 90964446 ภาษาอังกฤษเพื่อก — 3(3-0-6) หน่วยกิต · หลักสูตร IT 2565 (ปริญญาตรี)
+(วิชาศึกษาทั่วไปที่ใช้ร่วมกันทุกหลักสูตร — เล่ม DSBA 2565 (ปริญญาตรี) ไม่ได้ลงรายละเอียดวิชานี้ จึงใช้ข้อมูลจากเล่ม IT 2565 (ปริญญาตรี))
+ไม่ได้กำหนดปี/ภาคไว้ในแผนการศึกษาของเล่ม (เป็นวิชาเลือก)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H521" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 312</t>
+        </is>
+      </c>
+      <c r="I521" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J521" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K521" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L521" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M521" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/general_education_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N521" s="39" t="inlineStr">
+        <is>
+          <t>0.02s</t>
+        </is>
+      </c>
+      <c r="O521" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="522" ht="14.25" customHeight="1" s="36">
+      <c r="A522" s="37" t="inlineStr">
+        <is>
+          <t>UE20</t>
+        </is>
+      </c>
+      <c r="B522" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C522" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D522" s="39" t="inlineStr">
+        <is>
+          <t>วิชาศึกษาทั่วไป ผู้นำพลังบวก กี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E522" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F522" s="39" t="inlineStr">
+        <is>
+          <t>3(3-0-6)</t>
+        </is>
+      </c>
+      <c r="G522" s="39" t="inlineStr">
+        <is>
+          <t>วิชาที่เกี่ยวข้องกับ "ศึกษาทั่วไป ผู้นำพลังบวก" — หลักสูตร IT
+■ IT 2565 — 12 วิชา รวม 36 หน่วยกิต
+  - 90642091 เอเซียนศึกษา
+      หน่วยกิต 3(3-0-6) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)
+  - 90642092 การศึกษาเพื่อสร้างพลเมือง
+      หน่วยกิต 3(3-0-6) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)
+  - 90642115 เทคโนโลยีสีเขียวและพลังงานทดแท1
+      หน่วยกิต 3(3-0-6) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)
+  - 90642132 ซุมพรศึกษาเพื่อการท่องเที่ยว
+      หน่วยกิต 3(3-0-6) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)
+  - 90642133 รสบรวชุมพรศึกษา
+      หน่วยกิต 3(3-0-6) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)
+  - 90643006 การ์จัดการและผู้นําสมัยใหม่ นร
+      หน่วยกิต 3(3-0-6) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)
+  - 90643007 ภาวะผู้นําสําหรับคนรุ่นใหม่
+      หน่วยกิต 3(3-0-6) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)
+  - 90643030 เศรษฐศาสตร์ทั่วไป และการศึกษาความเป็นไปได้
+      หน่วยกิต 3(3-0-6) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)
+  - 90644015 ภาษาอังกฤษเพื่อการศึกษาต่อ
+      หน่วยกิต 3(3-0-6) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)
+  - 90964211 การพัฒนาทักษะขีวิตเพื่อสุขภาพและสังคม
+      หน่วยกิต 3(3-0-6) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)
+  - 90964231 การจัดการทรัพยากร พลังงานและสิงแวดล้อม
+      หน่วยกิต 3(2-2-5) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)
+  - 90964235 วิทยาศาสตร์เพื่องานเทคนิคพลังงาน
+      หน่วยกิต 3(2-2-5) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)</t>
+        </is>
+      </c>
+      <c r="H522" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 141, 143, 291, 292, 142, 144, 145, 146</t>
+        </is>
+      </c>
+      <c r="I522" s="39" t="inlineStr">
+        <is>
+          <t>Semantic topic search (bge-m3) → จัดรูปคำตอบเอง → Typhoon เรียบเรียง</t>
+        </is>
+      </c>
+      <c r="J522" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K522" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L522" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M522" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/general_education_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N522" s="39" t="inlineStr">
+        <is>
+          <t>0.44s</t>
+        </is>
+      </c>
+      <c r="O522" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="523" ht="14.25" customHeight="1" s="36">
+      <c r="A523" s="37" t="inlineStr">
+        <is>
+          <t>UE21</t>
+        </is>
+      </c>
+      <c r="B523" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C523" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D523" s="39" t="inlineStr">
+        <is>
+          <t>วิชาศึกษาทั่วไป การประพันธ์เพลงเบื้องต้น กี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E523" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F523" s="39" t="inlineStr">
+        <is>
+          <t>3(3-0-6)</t>
+        </is>
+      </c>
+      <c r="G523" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 90642080 การประพันธ์เหลงเบื้องต้น — 3(3-0-6) หน่วยกิต · หลักสูตร IT 2565 (ปริญญาตรี)
+(วิชาศึกษาทั่วไปที่ใช้ร่วมกันทุกหลักสูตร — เล่ม AIT 2566 (ปริญญาตรี) ไม่ได้ลงรายละเอียดวิชานี้ จึงใช้ข้อมูลจากเล่ม IT 2565 (ปริญญาตรี))
+ไม่ได้กำหนดปี/ภาคไว้ในแผนการศึกษาของเล่ม (เป็นวิชาเลือก)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H523" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 185, 271</t>
+        </is>
+      </c>
+      <c r="I523" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J523" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K523" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L523" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M523" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/general_education_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N523" s="39" t="inlineStr">
+        <is>
+          <t>0.02s</t>
+        </is>
+      </c>
+      <c r="O523" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="524" ht="14.25" customHeight="1" s="36">
+      <c r="A524" s="37" t="inlineStr">
+        <is>
+          <t>UE22</t>
+        </is>
+      </c>
+      <c r="B524" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C524" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D524" s="39" t="inlineStr">
+        <is>
+          <t>วิชาศึกษาทั่วไป ภาษาอังกฤษสำหรับวิชาชีพสุขภาพ กี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E524" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F524" s="39" t="inlineStr">
+        <is>
+          <t>3(2-2-5)</t>
+        </is>
+      </c>
+      <c r="G524" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 90644029 ภาษาอังกฤษสําหรับวิชาชีพสุขภาพ — 3(2-2-5) หน่วยกิต · หลักสูตร AIT 2566 (ปริญญาตรี)
+(วิชาศึกษาทั่วไปที่ใช้ร่วมกันทุกหลักสูตร — เล่ม BIT 2565 (ปริญญาตรี) ไม่ได้ลงรายละเอียดวิชานี้ จึงใช้ข้อมูลจากเล่ม AIT 2566 (ปริญญาตรี))
+ไม่ได้กำหนดปี/ภาคไว้ในแผนการศึกษาของเล่ม (เป็นวิชาเลือก)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H524" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 135, 217</t>
+        </is>
+      </c>
+      <c r="I524" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J524" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K524" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L524" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M524" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/general_education_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N524" s="39" t="inlineStr">
+        <is>
+          <t>0.03s</t>
+        </is>
+      </c>
+      <c r="O524" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="525" ht="14.25" customHeight="1" s="36">
+      <c r="A525" s="37" t="inlineStr">
+        <is>
+          <t>UE23</t>
+        </is>
+      </c>
+      <c r="B525" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C525" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D525" s="39" t="inlineStr">
+        <is>
+          <t>วิชาศึกษาทั่วไป ภาษาญี่ปุ่นเพื่อการสื่อสาร กี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E525" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F525" s="39" t="inlineStr">
+        <is>
+          <t>3(3-0-6)</t>
+        </is>
+      </c>
+      <c r="G525" s="39" t="inlineStr">
+        <is>
+          <t>วิชาที่เกี่ยวข้องกับ "ศึกษาทั่วไป ภาษาญี่ปุ่นเพื่อการสื่อสาร" — หลักสูตร DSBA
+■ DSBA 2565 — 5 วิชา รวม 15 หน่วยกิต
+  - 90644007 ภาษาอังกฤษพื้นฐาน 1 (FOUNDATION ENGLISH 1)
+      หน่วยกิต 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 1
+  - 90644008 ภาษาอังกฤษพื้นฐาน 2 (FOUNDATION ENGLISH 2)
+      หน่วยกิต 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 2
+  - 06066102 ระบบสารสนเทศเพื่อการจัดการ (MANAGEMENT INFORMATION SYSTEMS)
+      หน่วยกิต 3(3-0-6) | ปีที่ 2 ภาคการศึกษาที่ 2
+  - 90644042 การสื่อสารและการนำเสนออย่างมืออาชีพ (PROFESSIONAL COMMUNICATION AND PRESENTATION)
+      หน่วยกิต 3(3-0-6) | ปีที่ 3 ภาคการศึกษาที่ 1
+  - 06026219 การประมวลผลภาษาธรรมชาติ (NATURAL LANGUAGE PROCESSING)
+      หน่วยกิต 3(3-0-6) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)</t>
+        </is>
+      </c>
+      <c r="H525" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 354, 19, 24, 31, 69, 70, 72, 355</t>
+        </is>
+      </c>
+      <c r="I525" s="39" t="inlineStr">
+        <is>
+          <t>Semantic topic search (bge-m3) → จัดรูปคำตอบเอง → Typhoon เรียบเรียง</t>
+        </is>
+      </c>
+      <c r="J525" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K525" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L525" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M525" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/general_education_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N525" s="39" t="inlineStr">
+        <is>
+          <t>0.21s</t>
+        </is>
+      </c>
+      <c r="O525" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="526" ht="14.25" customHeight="1" s="36">
+      <c r="A526" s="37" t="inlineStr">
+        <is>
+          <t>UE24</t>
+        </is>
+      </c>
+      <c r="B526" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C526" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D526" s="39" t="inlineStr">
+        <is>
+          <t>วิชาศึกษาทั่วไป วิทยาการทางทหาร กี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E526" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F526" s="39" t="inlineStr">
+        <is>
+          <t>3(3-0-6)</t>
+        </is>
+      </c>
+      <c r="G526" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 90642096 วิทยาการทางทหาร — 3(3-0-6) หน่วยกิต · หลักสูตร AIT 2566 (ปริญญาตรี)
+(วิชาศึกษาทั่วไปที่ใช้ร่วมกันทุกหลักสูตร — เล่ม IT 2565 (ปริญญาตรี) ไม่ได้ลงรายละเอียดวิชานี้ จึงใช้ข้อมูลจากเล่ม AIT 2566 (ปริญญาตรี))
+ไม่ได้กำหนดปี/ภาคไว้ในแผนการศึกษาของเล่ม (เป็นวิชาเลือก)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H526" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 168, 241</t>
+        </is>
+      </c>
+      <c r="I526" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J526" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K526" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L526" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M526" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/general_education_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N526" s="39" t="inlineStr">
+        <is>
+          <t>0.02s</t>
+        </is>
+      </c>
+      <c r="O526" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="527" ht="14.25" customHeight="1" s="36">
+      <c r="A527" s="37" t="inlineStr">
+        <is>
+          <t>UC1</t>
+        </is>
+      </c>
+      <c r="B527" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C527" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D527" s="39" t="inlineStr">
+        <is>
+          <t>ลงทะเบียนต่ำสุดเทอมละกี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E527" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F527" s="39" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G527" s="39" t="inlineStr">
+        <is>
+          <t>การลงทะเบียนเรียน (หน่วยกิตต่อภาค) ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 82
+(ข้อบังคับของสถาบัน ใช้กับทุกหลักสูตรปริญญาตรี)
+- ภาคการศึกษาปกติ: ต้องลงทะเบียนไม่น้อยกว่า 9 หน่วยกิต และไม่เกิน 22 หน่วยกิต
+- ข้อยกเว้น: นักศึกษาชั้นปีสุดท้าย (หรือก่อนปีสุดท้ายที่ต้องไปฝึกสอนในปีสุดท้าย) ที่เหลือรายวิชาน้อยกว่า 9 หน่วยกิต หรือต้องลงมากกว่า 22 หน่วยกิตเพื่อสำเร็จการศึกษา ลงได้แต่ต้องไม่เกิน 27 หน่วยกิต
+- ภาคการศึกษาพิเศษ (ภาคฤดูร้อน): ลงทะเบียนได้ไม่เกิน 9 หน่วยกิต ถ้าลงรายวิชาประเภทฝึกงานในภาคพิเศษ จะลงวิชาอื่นในภาคนั้นไม่ได้
+- การลงทะเบียนที่มีหน่วยกิตต่างจากที่กำหนด ให้สภาวิชาการพิจารณาอนุมัติ</t>
+        </is>
+      </c>
+      <c r="H527" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 82</t>
+        </is>
+      </c>
+      <c r="I527" s="39" t="inlineStr">
+        <is>
+          <t>ข้อบังคับปริญญาตรี (ภาคผนวกเล่ม AIT 2566) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J527" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K527" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L527" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M527" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก AIT 2566 ภาคผนวก หน้า 82)</t>
+        </is>
+      </c>
+      <c r="N527" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O527" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="528" ht="14.25" customHeight="1" s="36">
+      <c r="A528" s="37" t="inlineStr">
+        <is>
+          <t>UC2</t>
+        </is>
+      </c>
+      <c r="B528" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C528" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D528" s="39" t="inlineStr">
+        <is>
+          <t>GPA เท่าไหร่ถึงจะจบได้</t>
+        </is>
+      </c>
+      <c r="E528" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F528" s="39" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G528" s="39" t="inlineStr">
+        <is>
+          <t>เกณฑ์การสำเร็จการศึกษา — ข้อ 34 ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 88
+(ข้อบังคับของสถาบัน ใช้กับทุกหลักสูตรปริญญาตรี)
+- เรียนครบหน่วยกิตและสอบผ่านทุกรายวิชาตามโครงสร้างหลักสูตร โดยค่าระดับคะแนนเฉลี่ยสะสมตามโครงสร้างหลักสูตรไม่ต่ำกว่า 2.00
+- ค่าระดับคะแนนเฉลี่ยสะสมทุกรายวิชาไม่ต่ำกว่า 2.00
+- ผ่านการสอบภาษาอังกฤษ (English Exit exam) ตามประกาศสถาบัน
+- เป็นผู้มีเกียรติและศักดิ์ของนักศึกษา และไม่มีหนี้สินหรือภาระผูกพันกับสถาบัน</t>
+        </is>
+      </c>
+      <c r="H528" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 88</t>
+        </is>
+      </c>
+      <c r="I528" s="39" t="inlineStr">
+        <is>
+          <t>ข้อบังคับปริญญาตรี (ภาคผนวกเล่ม AIT 2566) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J528" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K528" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L528" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M528" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก AIT 2566 ภาคผนวก หน้า 88)</t>
+        </is>
+      </c>
+      <c r="N528" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O528" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="529" ht="14.25" customHeight="1" s="36">
+      <c r="A529" s="37" t="inlineStr">
+        <is>
+          <t>UC3</t>
+        </is>
+      </c>
+      <c r="B529" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C529" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D529" s="39" t="inlineStr">
+        <is>
+          <t>อยากได้เกียรตินิยมอันดับ 1 ต้องได้เกรดเฉลี่ยอย่างน้อยเท่าไหร่</t>
+        </is>
+      </c>
+      <c r="E529" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F529" s="39" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="G529" s="39" t="inlineStr">
+        <is>
+          <t>ปริญญาเกียรตินิยม — ข้อ 36 ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 88, 89
+(ข้อบังคับของสถาบัน ใช้กับทุกหลักสูตรปริญญาตรี)
+- เกียรตินิยมอันดับหนึ่งและเหรียญทอง: ค่าระดับคะแนนเฉลี่ยสะสมตามโครงสร้างหลักสูตรสูงสุดในกลุ่มผู้สำเร็จการศึกษาปีเดียวกันของหลักสูตร และค่าระดับคะแนนเฉลี่ยสะสมไม่ต่ำกว่า 3.75 และต้องไม่เทียบโอนผลการเรียนจากสถาบันอื่น
+- เกียรตินิยมอันดับหนึ่ง: ค่าระดับคะแนนเฉลี่ยสะสมไม่ต่ำกว่า 3.50
+- เกียรตินิยมอันดับสอง: ค่าระดับคะแนนเฉลี่ยสะสมไม่ต่ำกว่า 3.25
+- กรณีโอนผลการเรียนจากสถาบันอื่น ทุกรายวิชาต้องได้ไม่ต่ำกว่า B หรือ S และต้องเรียนในหลักสูตรของสถาบันไม่น้อยกว่า 2 ใน 3 ของหน่วยกิตรวม
+- เงื่อนไขทั่วไป (ข้อ 36.1): เรียนไม่เกินระยะเวลาตามแผนการศึกษา · ไม่มีรายวิชาใดได้ F หรือ U · ไม่เคยเรียนซ้ำเพื่อเปลี่ยนเกรด · ไม่เคยลาพักเพราะไม่ลงทะเบียนตามกำหนด และไม่เคยถูกลงโทษทางวินัย</t>
+        </is>
+      </c>
+      <c r="H529" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 88, 89</t>
+        </is>
+      </c>
+      <c r="I529" s="39" t="inlineStr">
+        <is>
+          <t>ข้อบังคับปริญญาตรี (ภาคผนวกเล่ม AIT 2566) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J529" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K529" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L529" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M529" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก AIT 2566 ภาคผนวก หน้า 89)</t>
+        </is>
+      </c>
+      <c r="N529" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O529" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="530" ht="14.25" customHeight="1" s="36">
+      <c r="A530" s="37" t="inlineStr">
+        <is>
+          <t>UC4</t>
+        </is>
+      </c>
+      <c r="B530" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C530" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D530" s="39" t="inlineStr">
+        <is>
+          <t>เกรด B ได้กี่แต้ม</t>
+        </is>
+      </c>
+      <c r="E530" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F530" s="39" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G530" s="39" t="inlineStr">
+        <is>
+          <t>ระบบค่าระดับคะแนน (เกรด) — ข้อ 27.3 ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 85
+(ข้อบังคับของสถาบัน ใช้กับทุกหลักสูตรปริญญาตรี)
+- A = 4.00 ดีเลิศ (Excellent) · B+ = 3.50 ดีมาก (Very Good) · B = 3.00 ดี (Good)
+- C+ = 2.50 ดีพอใช้ (Fairly Good) · C = 2.00 พอใช้ (Fair) · D+ = 1.50 อ่อน (Poor)
+- D = 1.00 อ่อนมาก (Very Poor) · F = 0 ตก (Failed)
+- I = ไม่สมบูรณ์ (Incomplete) · S = พอใจ (Satisfactory) · U = ไม่พอใจ (Unsatisfactory) · T = รับโอน (Transfer) — ไม่มีแต้ม
+- ค่าระดับคะแนนเฉลี่ยคิดทศนิยม 2 ตำแหน่ง (ปัดตามหลักคณิตศาสตร์) รายวิชาที่ลงซ้ำไม่นำผลครั้งเดิมมาคิด (ข้อ 30.1)</t>
+        </is>
+      </c>
+      <c r="H530" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 85</t>
+        </is>
+      </c>
+      <c r="I530" s="39" t="inlineStr">
+        <is>
+          <t>ข้อบังคับปริญญาตรี (ภาคผนวกเล่ม AIT 2566) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J530" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K530" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L530" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M530" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก AIT 2566 ภาคผนวก หน้า 85)</t>
+        </is>
+      </c>
+      <c r="N530" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O530" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="531" ht="14.25" customHeight="1" s="36">
+      <c r="A531" s="37" t="inlineStr">
+        <is>
+          <t>UC5</t>
+        </is>
+      </c>
+      <c r="B531" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C531" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D531" s="39" t="inlineStr">
+        <is>
+          <t>ปริญญาเอก IT 2566 แบบ 2.1 ต้องเรียนวิชาเลือกกี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E531" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F531" s="39" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G531" s="39" t="inlineStr">
+        <is>
+          <t>IT 2566 (ปริญญาเอก) Type 2.1 (Applicants with Master's Degree): ต้องเรียน 60 หน่วยกิต
+IT 2566 (ปริญญาเอก) — จำนวนหน่วยกิตรวมตลอดหลักสูตร (หน้า 25):
+  - Type 1.1  (Applicants with Master's Degree): 57 หน่วยกิต (Thesis courses 57 หน่วยกิต)
+  - Type 1.2 (Applicants with Bachelor's Degree): 72 หน่วยกิต (Thesis courses 72 หน่วยกิต)
+  - Type 2.1 (Applicants with Master's Degree): 60 หน่วยกิต (Thesis courses 48 หน่วยกิต, Elective courses 12 หน่วยกิต) ◀ แผนที่ถาม</t>
+        </is>
+      </c>
+      <c r="H531" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 25</t>
+        </is>
+      </c>
+      <c r="I531" s="39" t="inlineStr">
+        <is>
+          <t>แผนการศึกษาบัณฑิตศึกษา (หัวข้อ 3.1.1/3.1.2) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J531" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K531" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L531" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M531" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก PhD IT 2566 หน้า 25)</t>
+        </is>
+      </c>
+      <c r="N531" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O531" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="532" ht="14.25" customHeight="1" s="36">
+      <c r="A532" s="37" t="inlineStr">
+        <is>
+          <t>UC6</t>
+        </is>
+      </c>
+      <c r="B532" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C532" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D532" s="39" t="inlineStr">
+        <is>
+          <t>ปริญญาโท IT 2568 แผน 2 แบบวิชาชีพ ต้องทำการค้นคว้าอิสระกี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E532" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F532" s="39" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G532" s="39" t="inlineStr">
+        <is>
+          <t>IT 2568 (ปริญญาโท) แผน 2 แบบวิชาชีพ: ต้องเรียน 36 หน่วยกิต
+IT 2568 (ปริญญาโท) — จำนวนหน่วยกิตรวมตลอดหลักสูตร (หน้า 12):
+  - แผน 1 แบบวิชาการ แบบ 1.1: 36 หน่วยกิต (หมวดวิชาวิทยานิพนธ์ 36 หน่วยกิต)
+  - แผน 1 แบบวิชาการ แบบ 1.2: 36 หน่วยกิต (หมวดวิชาวิทยานิพนธ์ 18 หน่วยกิต, หมวดวิชาบังคับ 3 หน่วยกิต, หมวดวิชาบังคับสาขา 12 หน่วยกิต, หมวดวิชาเลือก 3 หน่วยกิต)
+  - แผน 2 แบบวิชาชีพ: 36 หน่วยกิต (หมวดวิชาการค้นคว้าอิสระ 6 หน่วยกิต, หมวดวิชาบังคับสาขา 12 หน่วยกิต, หมวดวิชาบังคับแขนง 12 หน่วยกิต, หมวดวิชาเลือก 6 หน่วยกิต) ◀ แผนที่ถาม</t>
+        </is>
+      </c>
+      <c r="H532" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 12</t>
+        </is>
+      </c>
+      <c r="I532" s="39" t="inlineStr">
+        <is>
+          <t>แผนการศึกษาบัณฑิตศึกษา (หัวข้อ 3.1.1/3.1.2) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J532" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K532" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L532" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M532" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก M.IT 2568 หน้า 12)</t>
+        </is>
+      </c>
+      <c r="N532" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O532" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="533" ht="14.25" customHeight="1" s="36">
+      <c r="A533" s="37" t="inlineStr">
+        <is>
+          <t>UC7</t>
+        </is>
+      </c>
+      <c r="B533" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C533" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D533" s="39" t="inlineStr">
+        <is>
+          <t>DSBA 2560 กับ 2565 หน่วยกิตรวมตลอดหลักสูตรต่างกันกี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E533" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F533" s="39" t="inlineStr">
+        <is>
+          <t>126 กับ 132</t>
+        </is>
+      </c>
+      <c r="G533" s="39" t="inlineStr">
+        <is>
+          <t>หน่วยกิตรวมตลอดหลักสูตร (จากหน้าโครงสร้างหลักสูตรในเล่ม):
+- DSBA 2560: 126 หน่วยกิต (มคอ.2 DSBA 2560 หน้า 17)
+- DSBA 2565: 132 หน่วยกิต (มคอ.2 DSBA 2565 หน้า 2)
+สรุป: DSBA 2565 มากกว่า DSBA 2560 อยู่ 6 หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="H533" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 351, 349, 352, 17</t>
+        </is>
+      </c>
+      <c r="I533" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (เทียบหน่วยกิตข้ามเวอร์ชัน) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J533" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="K533" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L533" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M533" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก DSBA2560 หน้า 17 / DSBA2565 หน้า 15)</t>
+        </is>
+      </c>
+      <c r="N533" s="39" t="inlineStr">
+        <is>
+          <t>0.10s</t>
+        </is>
+      </c>
+      <c r="O533" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="534" ht="14.25" customHeight="1" s="36">
+      <c r="A534" s="37" t="inlineStr">
+        <is>
+          <t>UC8</t>
+        </is>
+      </c>
+      <c r="B534" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C534" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D534" s="39" t="inlineStr">
+        <is>
+          <t>อาจารย์ศุภมิตร จิตตะยโศธร จบปริญญาเอกที่ไหน ปีอะไร</t>
+        </is>
+      </c>
+      <c r="E534" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 3 — ชุดที่ระบบไม่เคยเห็น รอบ 3</t>
+        </is>
+      </c>
+      <c r="F534" s="39" t="inlineStr">
+        <is>
+          <t>The University of Queensland, 2531</t>
+        </is>
+      </c>
+      <c r="G534" s="39" t="inlineStr">
+        <is>
+          <t>ประวัติการศึกษาของอาจารย์ศุภมิตร จิตตะยโศธร ตามเล่ม AIT 2566 (ปริญญาตรี) (หน้า 42):
+  - วศ.บ. (วิศวกรรมคอมพิวเตอร์) สถาบันเทคโนโลยีพระจอมเกล้า เจ้าคุณทหารลาดกระบัง, 2523
+  - Master of Engineering (Computer) สถาบันเทคโนโลยีแห่งเอเชีย (AIT), 2525
+  - Ph.D. (Computer Science) The University of Queensland, Australia, 2531</t>
+        </is>
+      </c>
+      <c r="H534" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 42</t>
+        </is>
+      </c>
+      <c r="I534" s="39" t="inlineStr">
+        <is>
+          <t>ประวัติอาจารย์ (ตารางหัวข้อ 3.2) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J534" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K534" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L534" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M534" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก AIT 2566 หน้า 42)</t>
+        </is>
+      </c>
+      <c r="N534" s="39" t="inlineStr">
+        <is>
+          <t>0.03s</t>
+        </is>
+      </c>
+      <c r="O534" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="535" ht="14.25" customHeight="1" s="36">
+      <c r="A535" s="37" t="inlineStr">
+        <is>
+          <t>VE1</t>
+        </is>
+      </c>
+      <c r="B535" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C535" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D535" s="39" t="inlineStr">
+        <is>
+          <t>อยากทราบหน่วยกิตของวิชาปัญญาประดิษฐ์และอินเทอร์เน็ตประสานสรรพสิ่ง</t>
+        </is>
+      </c>
+      <c r="E535" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F535" s="39" t="inlineStr">
+        <is>
+          <t>3(3-0-6)</t>
+        </is>
+      </c>
+      <c r="G535" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06046413 ปัญญาประดิษฐ์และอินเทอร์เน็ตประสานสรรพสิ่ง (ARTIFICIAL INTELLIGIENCE AND INTERNET OF THING) — 3(3-0-6) หน่วยกิต · หลักสูตร AIT 2566 (ปริญญาตรี)
+ตามตารางรายวิชา: ปีที่ 2 ภาคการศึกษาที่ 1
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H535" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 20, 24, 38, 295</t>
+        </is>
+      </c>
+      <c r="I535" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J535" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="K535" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L535" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M535" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N535" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O535" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="536" ht="14.25" customHeight="1" s="36">
+      <c r="A536" s="37" t="inlineStr">
+        <is>
+          <t>VE2</t>
+        </is>
+      </c>
+      <c r="B536" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C536" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D536" s="39" t="inlineStr">
+        <is>
+          <t>อยากทราบหน่วยกิตของวิชาโครงงานกลุ่ม 1</t>
+        </is>
+      </c>
+      <c r="E536" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F536" s="39" t="inlineStr">
+        <is>
+          <t>1(0-2-1)</t>
+        </is>
+      </c>
+      <c r="G536" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 90641004 โครงงานกลุ่ม 1 (TEAM-PROJECT 1) — 1(0-2-1) หน่วยกิต · หลักสูตร AIT 2566 (ปริญญาตรี)
+ตามตารางรายวิชา: ปีที่ 1 ภาคการศึกษาที่ 2
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H536" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 18, 23, 118, 119, 120, 144, 233, 234</t>
+        </is>
+      </c>
+      <c r="I536" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J536" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K536" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L536" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M536" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N536" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O536" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="537" ht="14.25" customHeight="1" s="36">
+      <c r="A537" s="37" t="inlineStr">
+        <is>
+          <t>VE3</t>
+        </is>
+      </c>
+      <c r="B537" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C537" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D537" s="39" t="inlineStr">
+        <is>
+          <t>โครงงานกลุ่ม 3 เรียนปีอะไร</t>
+        </is>
+      </c>
+      <c r="E537" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F537" s="39" t="inlineStr">
+        <is>
+          <t>ปี 3 ภาค 2</t>
+        </is>
+      </c>
+      <c r="G537" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 90641006 โครงงานกลุ่ม 3 (TEAM-PROJECT 3) — 1(0-2-1) หน่วยกิต · หลักสูตร AIT 2566 (ปริญญาตรี)
+ตามตารางรายวิชา: ปีที่ 3 ภาคการศึกษาที่ 2
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H537" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 18, 25, 118, 119, 120, 233, 234, 235</t>
+        </is>
+      </c>
+      <c r="I537" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J537" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K537" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L537" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M537" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N537" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O537" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="538" ht="14.25" customHeight="1" s="36">
+      <c r="A538" s="37" t="inlineStr">
+        <is>
+          <t>VE4</t>
+        </is>
+      </c>
+      <c r="B538" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C538" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D538" s="39" t="inlineStr">
+        <is>
+          <t>แนวคิดระบบฐานข้อมูล เรียนปีอะไร</t>
+        </is>
+      </c>
+      <c r="E538" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F538" s="39" t="inlineStr">
+        <is>
+          <t>ปี 2 ภาค 1</t>
+        </is>
+      </c>
+      <c r="G538" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06066300 แนวคิดระบบฐานข้อมูล (DATABASE SYSTEM CONCEPTS) — 3(2-2-5) หน่วยกิต · หลักสูตร AIT 2566 (ปริญญาตรี)
+ตามตารางรายวิชา: ปีที่ 2 ภาคการศึกษาที่ 1
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H538" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 20, 24, 37, 290</t>
+        </is>
+      </c>
+      <c r="I538" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J538" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="K538" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L538" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M538" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N538" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O538" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="539" ht="14.25" customHeight="1" s="36">
+      <c r="A539" s="37" t="inlineStr">
+        <is>
+          <t>VM1</t>
+        </is>
+      </c>
+      <c r="B539" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C539" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D539" s="39" t="inlineStr">
+        <is>
+          <t>How many credits is Project In Artificial Intelligence Technology 1?</t>
+        </is>
+      </c>
+      <c r="E539" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F539" s="39" t="inlineStr">
+        <is>
+          <t>3(0-9-0)</t>
+        </is>
+      </c>
+      <c r="G539" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06046441 โครงงานเทคโนโลยีปัญญาประดิษฐ์ 1 (PROJECT IN ARTIFICIAL INTELLIGENCE TECHNOLOGY 1) — 3(0-9-0) หน่วยกิต · หลักสูตร AIT 2566 (ปริญญาตรี)
+ตามตารางรายวิชา: ปีที่ 3 ภาคการศึกษาที่ 2
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H539" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 22, 25, 40, 303</t>
+        </is>
+      </c>
+      <c r="I539" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J539" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="K539" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L539" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M539" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N539" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O539" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="540" ht="14.25" customHeight="1" s="36">
+      <c r="A540" s="37" t="inlineStr">
+        <is>
+          <t>VM2</t>
+        </is>
+      </c>
+      <c r="B540" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C540" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D540" s="39" t="inlineStr">
+        <is>
+          <t>How many credits is Discrete Mathematics?</t>
+        </is>
+      </c>
+      <c r="E540" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F540" s="39" t="inlineStr">
+        <is>
+          <t>3(3-0-6)</t>
+        </is>
+      </c>
+      <c r="G540" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06066000 คณิตศาสตร์ไม่ต่อเนื่อง (DISCRETE MATHEMATICS) — 3(3-0-6) หน่วยกิต · หลักสูตร AIT 2566 (ปริญญาตรี)
+ตามตารางรายวิชา: ปีที่ 1 ภาคการศึกษาที่ 1
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H540" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 19, 23, 37, 288</t>
+        </is>
+      </c>
+      <c r="I540" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J540" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="K540" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L540" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M540" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N540" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O540" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="541" ht="14.25" customHeight="1" s="36">
+      <c r="A541" s="37" t="inlineStr">
+        <is>
+          <t>VM3</t>
+        </is>
+      </c>
+      <c r="B541" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C541" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D541" s="39" t="inlineStr">
+        <is>
+          <t>Which year and semester is Probabilistic Machine Learning taught?</t>
+        </is>
+      </c>
+      <c r="E541" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F541" s="39" t="inlineStr">
+        <is>
+          <t>ปี 2 ภาค 1</t>
+        </is>
+      </c>
+      <c r="G541" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06046405 การเรียนรู้ของเครื่องเชิงความน่าจะเป็น (PROBABILISTIC MACHINE LEARNING) — 3(3-0-6) หน่วยกิต · หลักสูตร AIT 2566 (ปริญญาตรี)
+ตามตารางรายวิชา: ปีที่ 2 ภาคการศึกษาที่ 1
+วิชาบังคับก่อน: 06066001 ความน่าจะเป็นและสถิติ</t>
+        </is>
+      </c>
+      <c r="H541" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 20, 24, 37, 291</t>
+        </is>
+      </c>
+      <c r="I541" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J541" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="K541" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L541" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M541" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N541" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O541" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="542" ht="14.25" customHeight="1" s="36">
+      <c r="A542" s="37" t="inlineStr">
+        <is>
+          <t>VM4</t>
+        </is>
+      </c>
+      <c r="B542" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C542" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D542" s="39" t="inlineStr">
+        <is>
+          <t>พื้นฐานการเรียนรู้เชิงลึก มี prerequisite อะไร</t>
+        </is>
+      </c>
+      <c r="E542" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F542" s="39" t="inlineStr">
+        <is>
+          <t>06046401, 06046402</t>
+        </is>
+      </c>
+      <c r="G542" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06046406 พื้นฐานการเรียนรู้เชิงลึก (FUNDAMENTALS OF DEEP LEARNING) — 3(3-0-6) | ปีที่ 2 ภาคการศึกษาที่ 1
+  ต้องผ่านวิชาบังคับก่อน:
+    • 06046401 แคลคูลัส 2 (CALCULUS 2) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 2
+      ↳ ต้องผ่าน 06046400 แคลคูลัส 1 (CALCULUS 1) ก่อน
+    • 06046402 พีชคณิตเชิงเส้น (LINEAR ALGEBRA) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H542" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 37, 292, 19, 20, 23, 24, 287, 288</t>
+        </is>
+      </c>
+      <c r="I542" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (prerequisite) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J542" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K542" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L542" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M542" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N542" s="39" t="inlineStr">
+        <is>
+          <t>0.02s</t>
+        </is>
+      </c>
+      <c r="O542" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="543" ht="14.25" customHeight="1" s="36">
+      <c r="A543" s="37" t="inlineStr">
+        <is>
+          <t>VH1</t>
+        </is>
+      </c>
+      <c r="B543" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C543" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D543" s="39" t="inlineStr">
+        <is>
+          <t>เทอม 2 ปี 3 ต้องลงวิชาบังคับอะไรบ้าง</t>
+        </is>
+      </c>
+      <c r="E543" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F543" s="39" t="inlineStr">
+        <is>
+          <t>06046441, 90641006</t>
+        </is>
+      </c>
+      <c r="G543" s="39" t="inlineStr">
+        <is>
+          <t>รายวิชาของหลักสูตร AIT 2566 (current) ปีที่ 3 (จัดกลุ่มตามภาคการศึกษา):
+▶ ภาคการศึกษาที่ 2 — วิชาบังคับ (2 วิชา 4 หน่วยกิต):
+  - 06046441 โครงงานเทคโนโลยีปัญญาประดิษฐ์ 1 (PROJECT IN ARTIFICIAL INTELLIGENCE TECHNOLOGY 1) — 3(0-9-0)
+  - 90641006 โครงงานกลุ่ม 3 (TEAM-PROJECT 3) — 1(0-2-1)
+  วิชาเลือกเฉพาะแขนง (เลือก 1 แขนง แล้วลงวิชาในแขนงนั้น) กลุ่มที่มี:
+    • วิชาเลือกเทคโนโลยีปัญญาประดิษฐ์เฉพาะทาง
+    • วิชาเลือกเสรี
+รวมปีที่ 3 (วิชาบังคับ): 2 วิชา 4 หน่วยกิต (ยังไม่รวมวิชาเลือก)</t>
+        </is>
+      </c>
+      <c r="H543" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 25, 18, 22, 40, 118, 119, 120, 233</t>
+        </is>
+      </c>
+      <c r="I543" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ปี/ภาค) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J543" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K543" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L543" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M543" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N543" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O543" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="544" ht="14.25" customHeight="1" s="36">
+      <c r="A544" s="37" t="inlineStr">
+        <is>
+          <t>VE5</t>
+        </is>
+      </c>
+      <c r="B544" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C544" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D544" s="39" t="inlineStr">
+        <is>
+          <t>อยากทราบหน่วยกิตของวิชาสถาปัตยกรรมคอมพิวเตอร์และระบบปฏิบัติการ</t>
+        </is>
+      </c>
+      <c r="E544" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F544" s="39" t="inlineStr">
+        <is>
+          <t>3(2-2-5)</t>
+        </is>
+      </c>
+      <c r="G544" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06036125 สถาปัตยกรรมคอมพิวเตอร์และระบบปฏิบัติการ (COMPUTER ARCHITECTURE AND OPERATING SYSTEM) — 3(2-2-5) หน่วยกิต · หลักสูตร BIT 2565 (ปริญญาตรี)
+อยู่ในกลุ่มโครงสร้างพื้นฐานของระบบ (ส่วนของกลุ่มวิชาเฉพาะด้าน) (หน้า 23)
+เรียนตามแผนการศึกษา:
+  - ปีที่ 1 ภาคการศึกษาที่ 2 (ทั้งแผนปกติและแผนสหกิจ, หน้า 27, 32)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H544" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 23, 27, 32, 75, 248, 270</t>
+        </is>
+      </c>
+      <c r="I544" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J544" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="K544" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L544" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M544" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N544" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O544" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="545" ht="14.25" customHeight="1" s="36">
+      <c r="A545" s="37" t="inlineStr">
+        <is>
+          <t>VE6</t>
+        </is>
+      </c>
+      <c r="B545" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C545" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D545" s="39" t="inlineStr">
+        <is>
+          <t>อยากทราบหน่วยกิตของวิชาแนวคิดระบบฐานข้อมูล</t>
+        </is>
+      </c>
+      <c r="E545" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F545" s="39" t="inlineStr">
+        <is>
+          <t>3(2-2-5)</t>
+        </is>
+      </c>
+      <c r="G545" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06036112 แนวคิดระบบฐานข้อมูล (DATABASE SYSTEM CONCEPTS) — 3(2-2-5) หน่วยกิต · หลักสูตร BIT 2565 (ปริญญาตรี)
+อยู่ในกลุ่มเทคโนโลยีเพื่องานประยุกต์ (ส่วนของกลุ่มวิชาเฉพาะด้าน) (หน้า 22)
+เรียนตามแผนการศึกษา:
+  - ปีที่ 2 ภาคการศึกษาที่ 2 (ทั้งแผนปกติและแผนสหกิจ, หน้า 28, 33)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H545" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 22, 28, 33, 74, 243, 249, 269</t>
+        </is>
+      </c>
+      <c r="I545" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J545" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="K545" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L545" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M545" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N545" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O545" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="546" ht="14.25" customHeight="1" s="36">
+      <c r="A546" s="37" t="inlineStr">
+        <is>
+          <t>VE7</t>
+        </is>
+      </c>
+      <c r="B546" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C546" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D546" s="39" t="inlineStr">
+        <is>
+          <t>เทคโนโลยีดิจิทัลสำหรับธุรกิจ เรียนปีอะไร</t>
+        </is>
+      </c>
+      <c r="E546" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F546" s="39" t="inlineStr">
+        <is>
+          <t>ปี 2 ภาค 2</t>
+        </is>
+      </c>
+      <c r="G546" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06036111 เทคโนโลยีดิจิทัลสำหรับธุรกิจ (DIGITAL TECHNOLOGY FOR BUSINESS) — 3(3-0-6) หน่วยกิต · หลักสูตร BIT 2565 (ปริญญาตรี)
+อยู่ในกลุ่มประเด็นด้านองค์การและระบบสารสนเทศ (ส่วนของกลุ่มวิชาเฉพาะด้าน) (หน้า 22)
+เรียนตามแผนการศึกษา:
+  - ปีที่ 2 ภาคการศึกษาที่ 2 (ทั้งแผนปกติและแผนสหกิจ, หน้า 28, 33)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H546" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 22, 28, 33, 74, 243, 268</t>
+        </is>
+      </c>
+      <c r="I546" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J546" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="K546" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L546" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M546" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N546" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O546" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="547" ht="14.25" customHeight="1" s="36">
+      <c r="A547" s="37" t="inlineStr">
+        <is>
+          <t>VM5</t>
+        </is>
+      </c>
+      <c r="B547" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C547" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D547" s="39" t="inlineStr">
+        <is>
+          <t>How many credits is Information Technology Fundamentals?</t>
+        </is>
+      </c>
+      <c r="E547" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F547" s="39" t="inlineStr">
+        <is>
+          <t>3(2-2-5)</t>
+        </is>
+      </c>
+      <c r="G547" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06036100 พื้นฐานทางด้านเทคโนโลยีสารสนเทศ (INFORMATION TECHNOLOGY FUNDAMENTALS) — 3(2-2-5) หน่วยกิต · หลักสูตร BIT 2565 (ปริญญาตรี)
+อยู่ในกลุ่มวิชาแกน (หน้า 21)
+เรียนตามแผนการศึกษา:
+  - ปีที่ 1 ภาคการศึกษาที่ 1 (ทั้งแผนปกติและแผนสหกิจ, หน้า 26, 31)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H547" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 21, 26, 31, 74, 238, 268</t>
+        </is>
+      </c>
+      <c r="I547" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J547" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="K547" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L547" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M547" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N547" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O547" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="548" ht="14.25" customHeight="1" s="36">
+      <c r="A548" s="37" t="inlineStr">
+        <is>
+          <t>VM6</t>
+        </is>
+      </c>
+      <c r="B548" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C548" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D548" s="39" t="inlineStr">
+        <is>
+          <t>How many credits is Enterprise Resource Planning?</t>
+        </is>
+      </c>
+      <c r="E548" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F548" s="39" t="inlineStr">
+        <is>
+          <t>3(3-0-6)</t>
+        </is>
+      </c>
+      <c r="G548" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06036110 การวางแผนทรัพยากรองค์กร (ENTERPRISE RESOURCE PLANNING) — 3(3-0-6) หน่วยกิต · หลักสูตร BIT 2565 (ปริญญาตรี)
+อยู่ในกลุ่มประเด็นด้านองค์การและระบบสารสนเทศ (ส่วนของกลุ่มวิชาเฉพาะด้าน) (หน้า 22)
+เรียนตามแผนการศึกษา:
+  - ปีที่ 3 ภาคการศึกษาที่ 1 (ทั้งแผนปกติและแผนสหกิจ, หน้า 28, 33)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H548" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 22, 28, 33, 74, 243, 269</t>
+        </is>
+      </c>
+      <c r="I548" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J548" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="K548" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L548" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M548" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N548" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O548" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="549" ht="14.25" customHeight="1" s="36">
+      <c r="A549" s="37" t="inlineStr">
+        <is>
+          <t>VM7</t>
+        </is>
+      </c>
+      <c r="B549" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C549" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D549" s="39" t="inlineStr">
+        <is>
+          <t>การพัฒนาเว็บแอปพลิเคชันโดยใช้เฟรมเวิร์ก มี prerequisite อะไร</t>
+        </is>
+      </c>
+      <c r="E549" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F549" s="39" t="inlineStr">
+        <is>
+          <t>06036119 หรือ 06036122</t>
+        </is>
+      </c>
+      <c r="G549" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06036114 การพัฒนาเว็บแอปพลิเคชันโดยใช้เฟรมเวิร์ก (WEB APPLICATION DEVELOPMENT USING FRAMEWORKS) — 3(2-2-5) | ปีที่ 3 ภาคการศึกษาที่ 1
+  ต้องผ่านวิชาบังคับก่อน:
+    • 06036119 พื้นฐานการเขียนโปรแกรม (PROGRAMMING FUNDAMENTALS) — 3(2-2-5) | ปีที่ 1 ภาคการศึกษาที่ 2
+    • 06036122 การสื่อสารด้วยภาพสำหรับธุรกิจ (VISUAL COMMUNICATION FOR BUSINESS) — 3(2-2-5) | ปีที่ 2 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H549" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 75, 23, 244, 270, 22, 27, 28, 32</t>
+        </is>
+      </c>
+      <c r="I549" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (prerequisite) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J549" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K549" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L549" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M549" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N549" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O549" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="550" ht="14.25" customHeight="1" s="36">
+      <c r="A550" s="37" t="inlineStr">
+        <is>
+          <t>VE8</t>
+        </is>
+      </c>
+      <c r="B550" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C550" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D550" s="39" t="inlineStr">
+        <is>
+          <t>อยากทราบหน่วยกิตของวิชาการบริหารเชิงกลยุทธ์และสมรรถะของธุรกิจ</t>
+        </is>
+      </c>
+      <c r="E550" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F550" s="39" t="inlineStr">
+        <is>
+          <t>3(3-0-6)</t>
+        </is>
+      </c>
+      <c r="G550" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06026257 การบริหารเชิงกลยุทธ์และสมรรถะของธุรกิจ (BUSINESS STRATEGIC AND PERFORMANCE MANAGEMENT) — 3(3-0-6) หน่วยกิต · หลักสูตร DSBA 2565 (ปริญญาตรี)
+อยู่ในกลุ่มวิชาเลือก (ส่วนของกลุ่มวิชาการศึกษาทางเลือก) (หน้า 21)
+ไม่ได้กำหนดปี/ภาคตายตัวในแผนการศึกษา (เป็นวิชาเลือกของกลุ่ม) ลงเรียนได้ในช่องวิชาเลือกตามแผน:
+  - แผนปกติ ปีที่ 2 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกด้านภาษาและการสื่อสาร" (หน้า 25)
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกกลุ่มวิทยาการข้อมูล 1" (หน้า 27)
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกกลุ่มการวิเคราะห์เชิงสถิติ 1" (หน้า 27)
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกกลุ่มวิศวกรรมข้อมูล 1" (หน้า 27)
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกกลุ่มวิทยาการข้อมูล 2" (หน้า 27)
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกกลุ่มการวิเคราะห์เชิงสถิติ 2" (หน้า 27)
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกกลุ่มวิศวกรรมข้อมูล 2" (หน้า 27)
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกหมวดวิชาศึกษาทั่วไป" (หน้า 27)
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกกลุ่มวิทยาการข้อมูล 3" (หน้า 28)
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกกลุ่มการวิเคราะห์เชิงสถิติ 3" (หน้า 28)
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกกลุ่มวิศวกรรมข้อมูล 3" (หน้า 28)
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกกลุ่มวิทยาการข้อมูล 4" (หน้า 28)
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกกลุ่มการวิเคราะห์เชิงสถิติ 4" (หน้า 28)
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกกลุ่มวิศวกรรมข้อมูล 4" (หน้า 28)
+  - แผนปกติ ปีที่ 4 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกในกลุ่มวิชาเลือกหรือกลุ่มวิชาชีพเฉพาะด้าน 1" (หน้า 29)
+  - แผนปกติ ปีที่ 4 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกในกลุ่มวิชาเลือกหรือกลุ่มวิชาชีพเฉพาะด้าน 2" (หน้า 29)
+  - แผนปกติ ปีที่ 4 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกหมวดวิชาศึกษาทั่วไป" (หน้า 29)
+  - แผนปกติ ปีที่ 4 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกเสรี 1" (หน้า 29)
+  - แผนปกติ ปีที่ 4 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกเสรี 2" (หน้า 29)
+  - แผนสหกิจ ปีที่ 2 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกด้านภาษาและการสื่อสาร" (หน้า 32)
+  - แผนสหกิจ ปีที่ 3 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกกลุ่มวิทยาการข้อมูล 1" (หน้า 34)
+  - แผนสหกิจ ปีที่ 3 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกกลุ่มการวิเคราะห์เชิงสถิติ 1" (หน้า 34)
+  - แผนสหกิจ ปีที่ 3 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกกลุ่มวิศวกรรมข้อมูล 1" (หน้า 34)
+  - แผนสหกิจ ปีที่ 3 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกกลุ่มวิทยาการข้อมูล 2" (หน้า 34)
+  - แผนสหกิจ ปีที่ 3 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกกลุ่มการวิเคราะห์เชิงสถิติ 2" (หน้า 34)
+  - แผนสหกิจ ปีที่ 3 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกกลุ่มวิศวกรรมข้อมูล 2" (หน้า 34)
+  - แผนสหกิจ ปีที่ 3 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกหมวดวิชาศึกษาทั่วไป" (หน้า 34)
+  - แผนสหกิจ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกกลุ่มวิทยาการข้อมูล 3" (หน้า 35)
+  - แผนสหกิจ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกกลุ่มการวิเคราะห์เชิงสถิติ 3" (หน้า 35)
+  - แผนสหกิจ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกกลุ่มวิศวกรรมข้อมูล 3" (หน้า 35)
+  - แผนสหกิจ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกกลุ่มวิทยาการข้อมูล 4" (หน้า 35)
+  - แผนสหกิจ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกกลุ่มการวิเคราะห์เชิงสถิติ 4" (หน้า 35)
+  - แผนสหกิจ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกกลุ่มวิศวกรรมข้อมูล 4" (หน้า 35)
+  - แผนสหกิจ ปีที่ 4 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกหมวดวิชาศึกษาทั่วไป" (หน้า 36)
+  - แผนสหกิจ ปีที่ 4 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกเสรี 1" (หน้า 36)
+  - แผนสหกิจ ปีที่ 4 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกเสรี 2" (หน้า 36)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H550" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 21, 25, 27, 28, 29, 32, 34, 35</t>
+        </is>
+      </c>
+      <c r="I550" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J550" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K550" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L550" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M550" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N550" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O550" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="551" ht="14.25" customHeight="1" s="36">
+      <c r="A551" s="37" t="inlineStr">
+        <is>
+          <t>VE9</t>
+        </is>
+      </c>
+      <c r="B551" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C551" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D551" s="39" t="inlineStr">
+        <is>
+          <t>อยากทราบหน่วยกิตของวิชาระบบข้อมูลแบบกระจาย</t>
+        </is>
+      </c>
+      <c r="E551" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F551" s="39" t="inlineStr">
+        <is>
+          <t>3(3-0-6)</t>
+        </is>
+      </c>
+      <c r="G551" s="39" t="inlineStr">
+        <is>
+          <t>วิชาที่เกี่ยวข้องกับ "หน่วยกิต ระบบข้อมูลแบบกระจาย" — หลักสูตร DSBA
+■ DSBA 2565 — 8 วิชา รวม 24 หน่วยกิต
+  - 06066300 แนวคิดระบบฐานข้อมูล (DATABASE SYSTEM CONCEPTS)
+      หน่วยกิต 3(2-2-5) | ปีที่ 2 ภาคการศึกษาที่ 1
+  - 06066304 การวิเคราะห์และออกแบบระบบสารสนเทศ (INFORMATION SYSTEM ANALYSIS AND DESIGN)
+      หน่วยกิต 3(3-0-6) | ปีที่ 2 ภาคการศึกษาที่ 1
+  - 06026207 ระบบฐานข้อมูลแบบโนเอสคิวแอล (NOSQL DATABASE SYSTEMS)
+      หน่วยกิต 3(2-2-5) | ปีที่ 2 ภาคการศึกษาที่ 2
+  - 06026212 การสร้างคลังข้อมูล (DATA WAREHOUSING)
+      หน่วยกิต 3(2-2-5) | ปีที่ 3 ภาคการศึกษาที่ 1
+  - 06026213 ระบบข้อมูลมหัต (BIG DATA SYSTEMS)
+      หน่วยกิต 3(2-2-5) | ปีที่ 3 ภาคการศึกษาที่ 2
+  - 06026234 การออกแบบการทดลอง (EXPERIMENTAL DESIGN)
+      หน่วยกิต 3(3-0-6) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)
+  - 06026239 สถาปัตยกรรมข้อมูลแบบไปป์ไลน์ (DATA PIPELINE ARCHITECTURE)
+      หน่วยกิต 3(3-0-6) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)
+  - 06026244 การดูแลและบำรุงรักษาระบบฐานข้อมูล (DATABASE SYSTEM MAINTENANCE AND ADMINISTRATION)
+      หน่วยกิต 3(2-2-5) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)</t>
+        </is>
+      </c>
+      <c r="H551" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 354, 26, 33, 18, 68, 73, 353, 20</t>
+        </is>
+      </c>
+      <c r="I551" s="39" t="inlineStr">
+        <is>
+          <t>Semantic topic search (bge-m3) → จัดรูปคำตอบเอง → Typhoon เรียบเรียง</t>
+        </is>
+      </c>
+      <c r="J551" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K551" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L551" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M551" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N551" s="39" t="inlineStr">
+        <is>
+          <t>0.44s</t>
+        </is>
+      </c>
+      <c r="O551" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="552" ht="14.25" customHeight="1" s="36">
+      <c r="A552" s="37" t="inlineStr">
+        <is>
+          <t>VE10</t>
+        </is>
+      </c>
+      <c r="B552" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C552" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D552" s="39" t="inlineStr">
+        <is>
+          <t>ความน่าจะเป็นและสถิติ เรียนปีอะไร</t>
+        </is>
+      </c>
+      <c r="E552" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F552" s="39" t="inlineStr">
+        <is>
+          <t>ปี 1 ภาค 2</t>
+        </is>
+      </c>
+      <c r="G552" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06066001 ความน่าจะเป็นและสถิติ (PROBABILITY AND STATISTICS) — 3(3-0-6) หน่วยกิต · หลักสูตร DSBA 2565 (ปริญญาตรี)
+อยู่ในกลุ่มคณิตศาสตร์และสถิติ (ส่วนของกลุ่มวิชาแกน) (หน้า 17)
+เรียนตามแผนการศึกษา:
+  - ปีที่ 1 ภาคการศึกษาที่ 2 (ทั้งแผนปกติและแผนสหกิจ, หน้า 24, 31)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H552" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 17, 24, 31, 73, 315, 353</t>
+        </is>
+      </c>
+      <c r="I552" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J552" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="K552" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L552" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M552" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N552" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O552" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="553" ht="14.25" customHeight="1" s="36">
+      <c r="A553" s="37" t="inlineStr">
+        <is>
+          <t>VE11</t>
+        </is>
+      </c>
+      <c r="B553" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C553" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D553" s="39" t="inlineStr">
+        <is>
+          <t>พื้นฐานวิทยาการข้อมูล เรียนปีอะไร</t>
+        </is>
+      </c>
+      <c r="E553" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F553" s="39" t="inlineStr">
+        <is>
+          <t>ปี 2 ภาค 2</t>
+        </is>
+      </c>
+      <c r="G553" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06026208 พื้นฐานวิทยาการข้อมูล (FUNDAMENTALS OF DATA SCIENCE) — 3(3-0-6) หน่วยกิต · หลักสูตร DSBA 2565 (ปริญญาตรี)
+อยู่ในกลุ่มพื้นฐานวิชาชีพ (หน้า 18)
+เรียนตามแผนการศึกษา:
+  - ปีที่ 2 ภาคการศึกษาที่ 2 (ทั้งแผนปกติและแผนสหกิจ, หน้า 26, 33)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H553" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 18, 26, 33, 68, 322, 354</t>
+        </is>
+      </c>
+      <c r="I553" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J553" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="K553" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L553" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M553" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N553" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O553" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="554" ht="14.25" customHeight="1" s="36">
+      <c r="A554" s="37" t="inlineStr">
+        <is>
+          <t>VM8</t>
+        </is>
+      </c>
+      <c r="B554" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C554" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D554" s="39" t="inlineStr">
+        <is>
+          <t>How many credits is Special Workshop In Statistical Analytics 1?</t>
+        </is>
+      </c>
+      <c r="E554" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F554" s="39" t="inlineStr">
+        <is>
+          <t>3(2-2-5)</t>
+        </is>
+      </c>
+      <c r="G554" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06026237 ปฏิบัติการพิเศษทางการวิเคราะห์เชิงสถิติ 1 (SPECIAL WORKSHOP IN STATISTICAL ANALYTICS 1) — 3(2-2-5) หน่วยกิต · หลักสูตร DSBA 2565 (ปริญญาตรี)
+อยู่ในกลุ่มการวิเคราะห์เชิงสถิติ (ส่วนของกลุ่มวิชาชีพเฉพาะด้าน) — ต้องเลือกเรียนกลุ่มใดกลุ่มหนึ่ง (หน้า 20)
+ไม่ได้กำหนดปี/ภาคตายตัวในแผนการศึกษา (เป็นวิชาเลือกของกลุ่ม) ลงเรียนได้ในช่องวิชาเลือกตามแผน:
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกกลุ่มการวิเคราะห์เชิงสถิติ 1" (หน้า 27)
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกกลุ่มการวิเคราะห์เชิงสถิติ 2" (หน้า 27)
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกกลุ่มการวิเคราะห์เชิงสถิติ 3" (หน้า 28)
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกกลุ่มการวิเคราะห์เชิงสถิติ 4" (หน้า 28)
+  - แผนปกติ ปีที่ 4 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกในกลุ่มวิชาเลือกหรือกลุ่มวิชาชีพเฉพาะด้าน 1" (หน้า 29)
+  - แผนปกติ ปีที่ 4 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกในกลุ่มวิชาเลือกหรือกลุ่มวิชาชีพเฉพาะด้าน 2" (หน้า 29)
+  - แผนสหกิจ ปีที่ 3 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกกลุ่มการวิเคราะห์เชิงสถิติ 1" (หน้า 34)
+  - แผนสหกิจ ปีที่ 3 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกกลุ่มการวิเคราะห์เชิงสถิติ 2" (หน้า 34)
+  - แผนสหกิจ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกกลุ่มการวิเคราะห์เชิงสถิติ 3" (หน้า 35)
+  - แผนสหกิจ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกกลุ่มการวิเคราะห์เชิงสถิติ 4" (หน้า 35)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H554" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 20, 27, 28, 29, 34, 35, 71, 333</t>
+        </is>
+      </c>
+      <c r="I554" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J554" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K554" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L554" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M554" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N554" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O554" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="555" ht="14.25" customHeight="1" s="36">
+      <c r="A555" s="37" t="inlineStr">
+        <is>
+          <t>VM9</t>
+        </is>
+      </c>
+      <c r="B555" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C555" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D555" s="39" t="inlineStr">
+        <is>
+          <t>How many credits is Deep Learning In Medical Image And Video Analysis?</t>
+        </is>
+      </c>
+      <c r="E555" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F555" s="39" t="inlineStr">
+        <is>
+          <t>3(2-2-5)</t>
+        </is>
+      </c>
+      <c r="G555" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06026225 การเรียนรู้เชิงลึกสำหรับการวิเคราะห์ภาพและวีดิโอทางการ แพทย์ (DEEP LEARNING IN MEDICAL IMAGE AND VIDEO ANALYSIS) — 3(2-2-5) หน่วยกิต · หลักสูตร DSBA 2565 (ปริญญาตรี)
+อยู่ในกลุ่มวิทยาการข้อมูล (ส่วนของกลุ่มวิชาชีพเฉพาะด้าน) — ต้องเลือกเรียนกลุ่มใดกลุ่มหนึ่ง (หน้า 19)
+ไม่ได้กำหนดปี/ภาคตายตัวในแผนการศึกษา (เป็นวิชาเลือกของกลุ่ม) ลงเรียนได้ในช่องวิชาเลือกตามแผน:
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกกลุ่มวิทยาการข้อมูล 1" (หน้า 27)
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกกลุ่มวิทยาการข้อมูล 2" (หน้า 27)
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกกลุ่มวิทยาการข้อมูล 3" (หน้า 28)
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกกลุ่มวิทยาการข้อมูล 4" (หน้า 28)
+  - แผนปกติ ปีที่ 4 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกในกลุ่มวิชาเลือกหรือกลุ่มวิชาชีพเฉพาะด้าน 1" (หน้า 29)
+  - แผนปกติ ปีที่ 4 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกในกลุ่มวิชาเลือกหรือกลุ่มวิชาชีพเฉพาะด้าน 2" (หน้า 29)
+  - แผนสหกิจ ปีที่ 3 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกกลุ่มวิทยาการข้อมูล 1" (หน้า 34)
+  - แผนสหกิจ ปีที่ 3 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกกลุ่มวิทยาการข้อมูล 2" (หน้า 34)
+  - แผนสหกิจ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกกลุ่มวิทยาการข้อมูล 3" (หน้า 35)
+  - แผนสหกิจ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกกลุ่มวิทยาการข้อมูล 4" (หน้า 35)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H555" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 19, 27, 28, 29, 34, 35, 70, 329</t>
+        </is>
+      </c>
+      <c r="I555" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J555" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K555" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L555" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M555" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N555" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O555" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="556" ht="14.25" customHeight="1" s="36">
+      <c r="A556" s="37" t="inlineStr">
+        <is>
+          <t>VM10</t>
+        </is>
+      </c>
+      <c r="B556" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C556" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D556" s="39" t="inlineStr">
+        <is>
+          <t>Which year and semester is Calculus 2 taught?</t>
+        </is>
+      </c>
+      <c r="E556" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F556" s="39" t="inlineStr">
+        <is>
+          <t>ปี 1 ภาค 2</t>
+        </is>
+      </c>
+      <c r="G556" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06026201 แคลคูลัส 2 (CALCULUS 2) — 3(3-0-6) หน่วยกิต · หลักสูตร DSBA 2565 (ปริญญาตรี)
+อยู่ในกลุ่มคณิตศาสตร์และสถิติ (ส่วนของกลุ่มวิชาแกน) (หน้า 17)
+เรียนตามแผนการศึกษา:
+  - ปีที่ 1 ภาคการศึกษาที่ 2 (ทั้งแผนปกติและแผนสหกิจ, หน้า 24, 31)
+วิชาบังคับก่อน: 06026200 แคลคูลัส 1</t>
+        </is>
+      </c>
+      <c r="H556" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 17, 24, 31, 68, 314, 353</t>
+        </is>
+      </c>
+      <c r="I556" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J556" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="K556" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L556" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M556" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N556" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O556" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="557" ht="14.25" customHeight="1" s="36">
+      <c r="A557" s="37" t="inlineStr">
+        <is>
+          <t>VM11</t>
+        </is>
+      </c>
+      <c r="B557" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C557" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D557" s="39" t="inlineStr">
+        <is>
+          <t>โครงงานวิทยาการข้อมูลและการวิเคราะห์เชิงธุรกิจ 2 มี prerequisite อะไร</t>
+        </is>
+      </c>
+      <c r="E557" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F557" s="39" t="inlineStr">
+        <is>
+          <t>06026214</t>
+        </is>
+      </c>
+      <c r="G557" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06026215 โครงงานวิทยาการข้อมูลและการวิเคราะห์เชิงธุรกิจ 2 (PROJECT IN DATA SCIENCE AND BUSINESS ANALYTICS 2) — 3(0-9-0) | ปีที่ 4 ภาคการศึกษาที่ 1
+  ต้องผ่านวิชาบังคับก่อน:
+    • 06026214 โครงงานวิทยาการข้อมูลและการวิเคราะห์เชิงธุรกิจ 1 (PROJECT IN DATA SCIENCE AND BUSINESS ANALYTICS 1) — 3(0-9-0) | ปีที่ 3 ภาคการศึกษาที่ 2</t>
+        </is>
+      </c>
+      <c r="H557" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 19, 69, 325, 354, 28, 29, 35, 36</t>
+        </is>
+      </c>
+      <c r="I557" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (prerequisite) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J557" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K557" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L557" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M557" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N557" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O557" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="558" ht="14.25" customHeight="1" s="36">
+      <c r="A558" s="37" t="inlineStr">
+        <is>
+          <t>VH2</t>
+        </is>
+      </c>
+      <c r="B558" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C558" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D558" s="39" t="inlineStr">
+        <is>
+          <t>เทอม 1 ปี 1 ต้องลงวิชาบังคับอะไรบ้าง</t>
+        </is>
+      </c>
+      <c r="E558" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F558" s="39" t="inlineStr">
+        <is>
+          <t>06026200, 06026202, 06066101, 06066303, 90641001, 90641003, 90644007</t>
+        </is>
+      </c>
+      <c r="G558" s="39" t="inlineStr">
+        <is>
+          <t>รายวิชาของหลักสูตร DSBA 2565 (current) ปีที่ 1 (จัดกลุ่มตามภาคการศึกษา):
+▶ ภาคการศึกษาที่ 1 — วิชาบังคับ (7 วิชา 18 หน่วยกิต):
+  - 06026200 แคลคูลัส 1 (CALCULUS 1) — 3(3-0-6)
+  - 06026202 พีชคณิตเชิงเส้น (LINEAR ALGEBRA) — 3(3-0-6)
+  - 06066101 พื้นฐานทางธุรกิจสำหรับเทคโนโลยีสารสนเทศ (BUSINESS FUNDAMENTALS FOR INFORMATION TECHNOLOGY) — 3(3-0-6)
+  - 06066303 การแก้ปัญหาและการโปรแกรมคอมพิวเตอร์ (PROBLEM SOLVING AND COMPUTER PROGRAMMING) — 3(2-2-5)
+  - 90641001 โรงเรียนสร้างเสน่ห์ (CHARM SCHOOL) — 2(1-2-3)
+  - 90641003 กีฬาและนันทนาการ (SPORTS AND RECREATIONAL ACTIVITIES) — 1(0-3-2)
+  - 90644007 ภาษาอังกฤษพื้นฐาน 1 (FOUNDATION ENGLISH 1) — 3(3-0-6)
+รวมปีที่ 1 (วิชาบังคับ): 7 วิชา 18 หน่วยกิต (ยังไม่รวมวิชาเลือก)</t>
+        </is>
+      </c>
+      <c r="H558" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 23, 30, 353, 16, 352, 17, 68, 73</t>
+        </is>
+      </c>
+      <c r="I558" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ปี/ภาค) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J558" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K558" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L558" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M558" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N558" s="39" t="inlineStr">
+        <is>
+          <t>0.02s</t>
+        </is>
+      </c>
+      <c r="O558" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="559" ht="14.25" customHeight="1" s="36">
+      <c r="A559" s="37" t="inlineStr">
+        <is>
+          <t>VE12</t>
+        </is>
+      </c>
+      <c r="B559" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C559" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D559" s="39" t="inlineStr">
+        <is>
+          <t>อยากทราบหน่วยกิตของวิชาองค์ประกอบสำคัญของวิทยาการข้อมูล</t>
+        </is>
+      </c>
+      <c r="E559" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F559" s="39" t="inlineStr">
+        <is>
+          <t>3(2-2-5)</t>
+        </is>
+      </c>
+      <c r="G559" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06016435 องค์ประกอบสำคัญของวิทยาการข้อมูล (ELEMENTS OF DATA SCIENCE) — 3(2-2-5) หน่วยกิต · หลักสูตร IT 2565 (ปริญญาตรี)
+อยู่ในกลุ่มวิชาเลือกทางเทคโนโลยีสารสนเทศ (หน้า 26)
+ไม่ได้กำหนดปี/ภาคตายตัวในแผนการศึกษา (เป็นวิชาเลือกของกลุ่ม) ลงเรียนได้ในช่องวิชาเลือกตามแผน:
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกทางเทคโนโลยีสารสนเทศ 1" (หน้า 35, 36)
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกทางเทคโนโลยีสารสนเทศ 2" (หน้า 35, 36)
+  - แผนปกติ ปีที่ 4 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกทางเทคโนโลยีสารสนเทศ 3" (หน้า 37)
+  - แผนสหกิจ ปีที่ 4 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกทางเทคโนโลยีสารสนเทศ 1" (หน้า 43)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H559" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 26, 35, 36, 37, 43, 85, 338, 379</t>
+        </is>
+      </c>
+      <c r="I559" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J559" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K559" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L559" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M559" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N559" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O559" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="560" ht="14.25" customHeight="1" s="36">
+      <c r="A560" s="37" t="inlineStr">
+        <is>
+          <t>VE13</t>
+        </is>
+      </c>
+      <c r="B560" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C560" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D560" s="39" t="inlineStr">
+        <is>
+          <t>อยากทราบหน่วยกิตของวิชาการวิเคราะห์และออกแบบระบบสารสนเทศ</t>
+        </is>
+      </c>
+      <c r="E560" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F560" s="39" t="inlineStr">
+        <is>
+          <t>3(3-0-6)</t>
+        </is>
+      </c>
+      <c r="G560" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06066304 การวิเคราะห์และออกแบบระบบสารสนเทศ (INFORMATION SYSTEM ANALYSIS AND DESIGN) — 3(3-0-6) หน่วยกิต · หลักสูตร IT 2565 (ปริญญาตรี)
+อยู่ในกลุ่มเทคโนโลยีเพื่องานประยุกต์ (ส่วนของกลุ่มวิชาเฉพาะด้าน) (หน้า 23)
+เรียนตามแผนการศึกษา:
+  - ปีที่ 2 ภาคการศึกษาที่ 1 (ทั้งแผนปกติและแผนสหกิจ, หน้า 33, 40)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H560" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 23, 33, 40, 24, 88, 337, 360, 375</t>
+        </is>
+      </c>
+      <c r="I560" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J560" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K560" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L560" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M560" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N560" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O560" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="561" ht="14.25" customHeight="1" s="36">
+      <c r="A561" s="37" t="inlineStr">
+        <is>
+          <t>VE14</t>
+        </is>
+      </c>
+      <c r="B561" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C561" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D561" s="39" t="inlineStr">
+        <is>
+          <t>การออกแบบส่วนต่อประสานกับมนุษย์ เรียนปีอะไร</t>
+        </is>
+      </c>
+      <c r="E561" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F561" s="39" t="inlineStr">
+        <is>
+          <t>ปี 2 ภาค 2</t>
+        </is>
+      </c>
+      <c r="G561" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06016424 การออกแบบส่วนต่อประสานกับมนุษย์ (HUMAN INTERFACE DESIGN) — 3(3-0-6) หน่วยกิต · หลักสูตร IT 2565 (ปริญญาตรี)
+อยู่ในกลุ่มวิชาด้านสื่อประสมสำหรับการพัฒนาสื่อเชิงโต้ตอบ เว็บ และเกม (ส่วนของกลุ่มวิชาบังคับเฉพาะสาขา) — ต้องเลือกเรียนกลุ่มใดกลุ่มหนึ่ง (หน้า 25)
+เรียนตามแผนการศึกษา:
+  - ปีที่ 2 ภาคการศึกษาที่ 2 (ทั้งแผนปกติและแผนสหกิจ, หน้า 34, 41)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H561" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 25, 34, 41, 84, 334</t>
+        </is>
+      </c>
+      <c r="I561" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J561" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="K561" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L561" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M561" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N561" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O561" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="562" ht="14.25" customHeight="1" s="36">
+      <c r="A562" s="37" t="inlineStr">
+        <is>
+          <t>VM12</t>
+        </is>
+      </c>
+      <c r="B562" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C562" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D562" s="39" t="inlineStr">
+        <is>
+          <t>How many credits is Advanced Database Systems?</t>
+        </is>
+      </c>
+      <c r="E562" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F562" s="39" t="inlineStr">
+        <is>
+          <t>3(3-0-6)</t>
+        </is>
+      </c>
+      <c r="G562" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06016457 ระบบฐานข้อมูลขั้นสูง (ADVANCED DATABASE SYSTEMS) — 3(3-0-6) หน่วยกิต · หลักสูตร IT 2565 (ปริญญาตรี)
+อยู่ในกลุ่มวิชาเลือกทางเทคโนโลยีสารสนเทศ (หน้า 26)
+ไม่ได้กำหนดปี/ภาคตายตัวในแผนการศึกษา (เป็นวิชาเลือกของกลุ่ม) ลงเรียนได้ในช่องวิชาเลือกตามแผน:
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกทางเทคโนโลยีสารสนเทศ 1" (หน้า 35, 36)
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกทางเทคโนโลยีสารสนเทศ 2" (หน้า 35, 36)
+  - แผนปกติ ปีที่ 4 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกทางเทคโนโลยีสารสนเทศ 3" (หน้า 37)
+  - แผนสหกิจ ปีที่ 4 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกทางเทคโนโลยีสารสนเทศ 1" (หน้า 43)
+วิชาบังคับก่อน: 06066300 แนวคิดระบบฐานข้อมูล</t>
+        </is>
+      </c>
+      <c r="H562" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 26, 35, 36, 37, 43, 27, 86, 347</t>
+        </is>
+      </c>
+      <c r="I562" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J562" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K562" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L562" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M562" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N562" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O562" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="563" ht="14.25" customHeight="1" s="36">
+      <c r="A563" s="37" t="inlineStr">
+        <is>
+          <t>VM13</t>
+        </is>
+      </c>
+      <c r="B563" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C563" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D563" s="39" t="inlineStr">
+        <is>
+          <t>How many credits is Sports And Recreational Activities?</t>
+        </is>
+      </c>
+      <c r="E563" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F563" s="39" t="inlineStr">
+        <is>
+          <t>1(0-3-2)</t>
+        </is>
+      </c>
+      <c r="G563" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 90641003 กีฬาและนันทนาการ (SPORTS AND RECREATIONAL ACTIVITIES) — 1(0-3-2) หน่วยกิต · หลักสูตร IT 2565 (ปริญญาตรี)
+อยู่ในกลุ่มวิชาพื้นฐาน (หน้า 21)
+เรียนตามแผนการศึกษา:
+  - ปีที่ 1 ภาคการศึกษาที่ 1 (ทั้งแผนปกติและแผนสหกิจ, หน้า 31, 38)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H563" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 21, 31, 38, 136, 245, 373</t>
+        </is>
+      </c>
+      <c r="I563" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J563" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="K563" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L563" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M563" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N563" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O563" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="564" ht="14.25" customHeight="1" s="36">
+      <c r="A564" s="37" t="inlineStr">
+        <is>
+          <t>VM14</t>
+        </is>
+      </c>
+      <c r="B564" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C564" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D564" s="39" t="inlineStr">
+        <is>
+          <t>Which year and semester is Law For New Generation taught?</t>
+        </is>
+      </c>
+      <c r="E564" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F564" s="39" t="inlineStr">
+        <is>
+          <t>ปี 3 ภาค 2</t>
+        </is>
+      </c>
+      <c r="G564" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 90642033 กฎหมายสำหรับคนรุ่นใหม่ (LAW FOR NEW GENERATION) — 3(3-0-6) หน่วยกิต · หลักสูตร IT 2565 (ปริญญาตรี)
+อยู่ในกลุ่มวิชาตามเกณฑ์ของคณะ (หน้า 22)
+เรียนตามแผนการศึกษา:
+  - ปีที่ 3 ภาคการศึกษาที่ 2 (แผนปกติ, หน้า 35, 36)
+  - ปีที่ 4 ภาคการศึกษาที่ 2 (แผนสหกิจ, หน้า 44)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H564" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 22, 35, 36, 44, 137, 172, 373</t>
+        </is>
+      </c>
+      <c r="I564" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J564" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="K564" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L564" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M564" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N564" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O564" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="565" ht="14.25" customHeight="1" s="36">
+      <c r="A565" s="37" t="inlineStr">
+        <is>
+          <t>VM15</t>
+        </is>
+      </c>
+      <c r="B565" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C565" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D565" s="39" t="inlineStr">
+        <is>
+          <t>โครงสร้างพื้นฐานเครือข่ายการสื่อสาร มี prerequisite อะไร</t>
+        </is>
+      </c>
+      <c r="E565" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F565" s="39" t="inlineStr">
+        <is>
+          <t>06016413</t>
+        </is>
+      </c>
+      <c r="G565" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06016419 โครงสร้างพื้นฐานเครือข่ายการสื่อสาร (COMMUNICATION NETWORK INFRASTRUCTURE) — 3(2-2-5) | ปีที่ 2 ภาคการศึกษาที่ 2
+  ต้องผ่านวิชาบังคับก่อน:
+    • 06016413 ระบบเครือข่ายเบื้องต้น (INTRODUCTION TO NETWORK SYSTEMS) — 3(3-0-6) | ปีที่ 2 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H565" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 84, 24, 25, 33, 34, 40, 328, 331</t>
+        </is>
+      </c>
+      <c r="I565" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (prerequisite) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J565" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K565" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L565" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M565" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N565" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O565" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="566" ht="14.25" customHeight="1" s="36">
+      <c r="A566" s="37" t="inlineStr">
+        <is>
+          <t>VM16</t>
+        </is>
+      </c>
+      <c r="B566" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 2: ปานกลาง</t>
+        </is>
+      </c>
+      <c r="C566" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D566" s="39" t="inlineStr">
+        <is>
+          <t>โครงงาน 2 มี prerequisite อะไร</t>
+        </is>
+      </c>
+      <c r="E566" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F566" s="39" t="inlineStr">
+        <is>
+          <t>06016406</t>
+        </is>
+      </c>
+      <c r="G566" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06016407 โครงงาน 2 (PROJECT 2) — 3(0-9-0) | ปีที่ 4 ภาคการศึกษาที่ 2
+  ต้องผ่านวิชาบังคับก่อน:
+    • 06016406 โครงงาน 1 (PROJECT 1) — 3(0-9-0) | ปีที่ 4 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H566" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 23, 37, 83, 326, 43, 44</t>
+        </is>
+      </c>
+      <c r="I566" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (prerequisite) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J566" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="K566" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L566" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M566" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N566" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O566" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="567" ht="14.25" customHeight="1" s="36">
+      <c r="A567" s="37" t="inlineStr">
+        <is>
+          <t>VE15</t>
+        </is>
+      </c>
+      <c r="B567" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C567" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D567" s="39" t="inlineStr">
+        <is>
+          <t>วิชาศึกษาทั่วไป เตรียมความพร้อมสำหรับวิศวกร กี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E567" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F567" s="39" t="inlineStr">
+        <is>
+          <t>1(0-3-0)</t>
+        </is>
+      </c>
+      <c r="G567" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 90642036 เตรียมความพร้อมสําหรับวิศวกร — 1(0-3-0) หน่วยกิต · หลักสูตร IT 2565 (ปริญญาตรี)
+(วิชาศึกษาทั่วไปที่ใช้ร่วมกันทุกหลักสูตร — เล่ม AIT 2566 (ปริญญาตรี) ไม่ได้ลงรายละเอียดวิชานี้ จึงใช้ข้อมูลจากเล่ม IT 2565 (ปริญญาตรี))
+ไม่ได้กำหนดปี/ภาคไว้ในแผนการศึกษาของเล่ม (เป็นวิชาเลือก)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H567" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 138, 266</t>
+        </is>
+      </c>
+      <c r="I567" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J567" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K567" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L567" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M567" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/general_education_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N567" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O567" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="568" ht="14.25" customHeight="1" s="36">
+      <c r="A568" s="37" t="inlineStr">
+        <is>
+          <t>VE16</t>
+        </is>
+      </c>
+      <c r="B568" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C568" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D568" s="39" t="inlineStr">
+        <is>
+          <t>วิชาศึกษาทั่วไป การสื่อสารนวัตกรรม กี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E568" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F568" s="39" t="inlineStr">
+        <is>
+          <t>4(4-0-8)</t>
+        </is>
+      </c>
+      <c r="G568" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 90644070 การสื่อสารนวัตกรรม — 3(3-0-6) หน่วยกิต · หลักสูตร AIT 2566 (ปริญญาตรี)
+(วิชาศึกษาทั่วไปที่ใช้ร่วมกันทุกหลักสูตร — เล่ม BIT 2565 (ปริญญาตรี) ไม่ได้ลงรายละเอียดวิชานี้ จึงใช้ข้อมูลจากเล่ม AIT 2566 (ปริญญาตรี))
+ชื่อวิชาเดียวกันในเล่มอื่น: 90644038 — 4(4-0-8) หน่วยกิต · หลักสูตร IT 2565 (ปริญญาตรี)
+ไม่ได้กำหนดปี/ภาคไว้ในแผนการศึกษาของเล่ม (เป็นวิชาเลือก)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H568" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 228</t>
+        </is>
+      </c>
+      <c r="I568" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J568" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K568" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L568" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M568" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/general_education_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N568" s="39" t="inlineStr">
+        <is>
+          <t>0.02s</t>
+        </is>
+      </c>
+      <c r="O568" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="569" ht="14.25" customHeight="1" s="36">
+      <c r="A569" s="37" t="inlineStr">
+        <is>
+          <t>VE17</t>
+        </is>
+      </c>
+      <c r="B569" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C569" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D569" s="39" t="inlineStr">
+        <is>
+          <t>วิชาศึกษาทั่วไป การจัดการเชิงอุตสาหกรรม กี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E569" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F569" s="39" t="inlineStr">
+        <is>
+          <t>3(3-0-6)</t>
+        </is>
+      </c>
+      <c r="G569" s="39" t="inlineStr">
+        <is>
+          <t>วิชาที่เกี่ยวข้องกับ "ศึกษาทั่วไป การจัดการเชิงอุตสาหกรรม" — หลักสูตร DSBA
+■ DSBA 2565 — 16 วิชา รวม 48 หน่วยกิต
+  - 06026202 พีชคณิตเชิงเส้น (LINEAR ALGEBRA)
+      หน่วยกิต 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 1
+  - 06066102 ระบบสารสนเทศเพื่อการจัดการ (MANAGEMENT INFORMATION SYSTEMS)
+      หน่วยกิต 3(3-0-6) | ปีที่ 2 ภาคการศึกษาที่ 2
+  - 06026211 การเรียนรู้ของเครื่องเชิงประยุกต์ (APPLIED MACHINE LEARNING)
+      หน่วยกิต 3(2-2-5) | ปีที่ 3 ภาคการศึกษาที่ 1
+  - 06026214 โครงงานวิทยาการข้อมูลและการวิเคราะห์เชิงธุรกิจ 1 (PROJECT IN DATA SCIENCE AND BUSINESS ANALYTICS 1)
+      หน่วยกิต 3(0-9-0) | ปีที่ 3 ภาคการศึกษาที่ 2
+  - 06026215 โครงงานวิทยาการข้อมูลและการวิเคราะห์เชิงธุรกิจ 2 (PROJECT IN DATA SCIENCE AND BUSINESS ANALYTICS 2)
+      หน่วยกิต 3(0-9-0) | ปีที่ 4 ภาคการศึกษาที่ 1
+  - 06026218 การเรียนรู้เชิงลึก (DEEP LEARNING)
+      หน่วยกิต 3(2-2-5) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)
+  - 06026225 การเรียนรู้เชิงลึกสำหรับการวิเคราะห์ภาพและวีดิโอทางการ แพทย์ (DEEP LEARNING IN MEDICAL IMAGE AND VIDEO ANALYSIS)
+      หน่วยกิต 3(2-2-5) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)
+  - 06026231 สถิติเชิงเบย์ (BAYESIAN STATISTICS)
+      หน่วยกิต 3(3-0-6) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)
+  - 06026232 กระบวนการสโตแคสติกเบื้องต้น (INTRODUCTION TO STOCHASTIC PROCESS)
+      หน่วยกิต 3(3-0-6) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)
+  - 06026235 หัวข้อพิเศษทางการวิเคราะห์เชิงสถิติ 1 (SPECIAL TOPICS IN STATISTICAL ANALYTICS 1)
+      หน่วยกิต 3(3-0-6) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)
+  - 06026236 หัวข้อพิเศษทางการวิเคราะห์เชิงสถิติ 2 (SPECIAL TOPICS IN STATISTICAL ANALYTICS 2)
+      หน่วยกิต 3(3-0-6) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)
+  - 06026237 ปฏิบัติการพิเศษทางการวิเคราะห์เชิงสถิติ 1 (SPECIAL WORKSHOP IN STATISTICAL ANALYTICS 1)
+      หน่วยกิต 3(2-2-5) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)
+  - 06026238 ปฏิบัติการพิเศษทางการวิเคราะห์เชิงสถิติ 2 (SPECIAL WORKSHOP IN STATISTICAL ANALYTICS 2)
+      หน่วยกิต 3(2-2-5) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)
+  - 06026255 การได้มาและการจัดการข้อมูลทางด้านคลินิก (CLINICAL DATA ACQUISITION AND MANAGEMENT)
+      หน่วยกิต 3(2-2-5) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)
+  - 06026256 การจัดการการปฏิบัติการ (OPERATIONS MANAGEMENT)
+      หน่วยกิต 3(3-0-6) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)
+  - 06026257 การบริหารเชิงกลยุทธ์และสมรรถะของธุรกิจ (BUSINESS STRATEGIC AND PERFORMANCE MANAGEMENT)
+      หน่วยกิต 3(3-0-6) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)</t>
+        </is>
+      </c>
+      <c r="H569" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 20, 355, 70, 354, 72, 22, 69, 71</t>
+        </is>
+      </c>
+      <c r="I569" s="39" t="inlineStr">
+        <is>
+          <t>Semantic topic search (bge-m3) → จัดรูปคำตอบเอง → Typhoon เรียบเรียง</t>
+        </is>
+      </c>
+      <c r="J569" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K569" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L569" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M569" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/general_education_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N569" s="39" t="inlineStr">
+        <is>
+          <t>0.27s</t>
+        </is>
+      </c>
+      <c r="O569" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="570" ht="14.25" customHeight="1" s="36">
+      <c r="A570" s="37" t="inlineStr">
+        <is>
+          <t>VE18</t>
+        </is>
+      </c>
+      <c r="B570" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C570" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D570" s="39" t="inlineStr">
+        <is>
+          <t>วิชาศึกษาทั่วไป ภาษาอังกฤษเพื่อการสื่อสารในงานสถาปัตยกรรม กี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E570" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F570" s="39" t="inlineStr">
+        <is>
+          <t>3(3-0-6)</t>
+        </is>
+      </c>
+      <c r="G570" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 90964446 ภาษาอังกฤษเพื่อก — 3(3-0-6) หน่วยกิต · หลักสูตร IT 2565 (ปริญญาตรี)
+ไม่ได้กำหนดปี/ภาคไว้ในแผนการศึกษาของเล่ม (เป็นวิชาเลือก)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H570" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 312</t>
+        </is>
+      </c>
+      <c r="I570" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J570" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K570" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L570" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M570" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/general_education_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N570" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O570" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="571" ht="14.25" customHeight="1" s="36">
+      <c r="A571" s="37" t="inlineStr">
+        <is>
+          <t>VE19</t>
+        </is>
+      </c>
+      <c r="B571" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C571" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D571" s="39" t="inlineStr">
+        <is>
+          <t>วิชาศึกษาทั่วไป ศัลยกรรมชีวิต กี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E571" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F571" s="39" t="inlineStr">
+        <is>
+          <t>3(3-0-6)</t>
+        </is>
+      </c>
+      <c r="G571" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 90643038 ศัลยกรรมชีวิต — 3(3-0-6) หน่วยกิต · หลักสูตร AIT 2566 (ปริญญาตรี)
+ไม่ได้กำหนดปี/ภาคไว้ในแผนการศึกษาของเล่ม (เป็นวิชาเลือก)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H571" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 133, 208, 246</t>
+        </is>
+      </c>
+      <c r="I571" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J571" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="K571" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L571" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M571" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/general_education_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N571" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O571" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="572" ht="14.25" customHeight="1" s="36">
+      <c r="A572" s="37" t="inlineStr">
+        <is>
+          <t>VE20</t>
+        </is>
+      </c>
+      <c r="B572" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C572" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D572" s="39" t="inlineStr">
+        <is>
+          <t>วิชาศึกษาทั่วไป การพัฒนาทักษะทางภาษาอังกฤษเพื่อการเรียนรู้ตลอดชีวิต กี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E572" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F572" s="39" t="inlineStr">
+        <is>
+          <t>3(3-0-6)</t>
+        </is>
+      </c>
+      <c r="G572" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 90644036 การพัฒนาทักษะทางภาษาอังกฤษเพื่อการเรียนรู้ตลอดชีวิต — 3(3-0-6) หน่วยกิต · หลักสูตร AIT 2566 (ปริญญาตรี)
+(วิชาศึกษาทั่วไปที่ใช้ร่วมกันทุกหลักสูตร — เล่ม BIT 2565 (ปริญญาตรี) ไม่ได้ลงรายละเอียดวิชานี้ จึงใช้ข้อมูลจากเล่ม AIT 2566 (ปริญญาตรี))
+ไม่ได้กำหนดปี/ภาคไว้ในแผนการศึกษาของเล่ม (เป็นวิชาเลือก)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H572" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 135, 219</t>
+        </is>
+      </c>
+      <c r="I572" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J572" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K572" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L572" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M572" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/general_education_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N572" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O572" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="573" ht="14.25" customHeight="1" s="36">
+      <c r="A573" s="37" t="inlineStr">
+        <is>
+          <t>VE21</t>
+        </is>
+      </c>
+      <c r="B573" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C573" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D573" s="39" t="inlineStr">
+        <is>
+          <t>วิชาศึกษาทั่วไป สนุกกับปัญญาประดิษฐ์ กี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E573" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F573" s="39" t="inlineStr">
+        <is>
+          <t>3(3-0-6)</t>
+        </is>
+      </c>
+      <c r="G573" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06026216 ปัญญาประดิษฐ์ (ARTIFICIAL INTELLIGENCE) — 3(3-0-6) หน่วยกิต · หลักสูตร DSBA 2565 (ปริญญาตรี)
+อยู่ในกลุ่มวิทยาการข้อมูล (ส่วนของกลุ่มวิชาชีพเฉพาะด้าน) — ต้องเลือกเรียนกลุ่มใดกลุ่มหนึ่ง (หน้า 19)
+ไม่ได้กำหนดปี/ภาคตายตัวในแผนการศึกษา (เป็นวิชาเลือกของกลุ่ม) ลงเรียนได้ในช่องวิชาเลือกตามแผน:
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกกลุ่มวิทยาการข้อมูล 1" (หน้า 27)
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกกลุ่มวิทยาการข้อมูล 2" (หน้า 27)
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกกลุ่มวิทยาการข้อมูล 3" (หน้า 28)
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกกลุ่มวิทยาการข้อมูล 4" (หน้า 28)
+  - แผนปกติ ปีที่ 4 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกในกลุ่มวิชาเลือกหรือกลุ่มวิชาชีพเฉพาะด้าน 1" (หน้า 29)
+  - แผนปกติ ปีที่ 4 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกในกลุ่มวิชาเลือกหรือกลุ่มวิชาชีพเฉพาะด้าน 2" (หน้า 29)
+  - แผนสหกิจ ปีที่ 3 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกกลุ่มวิทยาการข้อมูล 1" (หน้า 34)
+  - แผนสหกิจ ปีที่ 3 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกกลุ่มวิทยาการข้อมูล 2" (หน้า 34)
+  - แผนสหกิจ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกกลุ่มวิทยาการข้อมูล 3" (หน้า 35)
+  - แผนสหกิจ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกกลุ่มวิทยาการข้อมูล 4" (หน้า 35)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H573" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 19, 27, 28, 29, 34, 35, 69, 325</t>
+        </is>
+      </c>
+      <c r="I573" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J573" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K573" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L573" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M573" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/general_education_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N573" s="39" t="inlineStr">
+        <is>
+          <t>0.02s</t>
+        </is>
+      </c>
+      <c r="O573" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="574" ht="14.25" customHeight="1" s="36">
+      <c r="A574" s="37" t="inlineStr">
+        <is>
+          <t>VE22</t>
+        </is>
+      </c>
+      <c r="B574" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 1: ง่าย</t>
+        </is>
+      </c>
+      <c r="C574" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D574" s="39" t="inlineStr">
+        <is>
+          <t>วิชาศึกษาทั่วไป เทคโนโลยีสีเขียวและพลังงานทดแทน กี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E574" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 4 — ชุดที่ระบบไม่เคยเห็น รอบ 4</t>
+        </is>
+      </c>
+      <c r="F574" s="39" t="inlineStr">
+        <is>
+          <t>3(3-0-6)</t>
+        </is>
+      </c>
+      <c r="G574" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 90642115 เทคโนโลยีสีเขียวและพลังงานทดแท1 — 3(3-0-6) หน่วยกิต · หลักสูตร IT 2565 (ปริญญาตรี)
+ไม่ได้กำหนดปี/ภาคไว้ในแผนการศึกษาของเล่ม (เป็นวิชาเลือก)
+วิชาบังคับก่อน: ไม่มี</t>
+        </is>
+      </c>
+      <c r="H574" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 142, 194</t>
+        </is>
+      </c>
+      <c r="I574" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J574" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K574" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L574" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M574" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/general_education_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N574" s="39" t="inlineStr">
+        <is>
+          <t>0.02s</t>
+        </is>
+      </c>
+      <c r="O574" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
     <row r="575" ht="14.25" customHeight="1" s="36"/>
     <row r="576" ht="14.25" customHeight="1" s="36"/>
     <row r="577" ht="14.25" customHeight="1" s="36"/>

--- a/docs/tester.xlsx
+++ b/docs/tester.xlsx
@@ -577,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O574"/>
+  <dimension ref="A1:O634"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10" customWidth="1" style="36" min="1" max="1"/>
@@ -756,7 +756,7 @@
       </c>
       <c r="N2" s="13" t="inlineStr">
         <is>
-          <t>0.05s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O2" s="21" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="N5" s="25" t="inlineStr">
         <is>
-          <t>0.06s</t>
+          <t>0.05s</t>
         </is>
       </c>
       <c r="O5" s="21" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="N7" s="25" t="inlineStr">
         <is>
-          <t>0.06s</t>
+          <t>0.05s</t>
         </is>
       </c>
       <c r="O7" s="21" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="N9" s="25" t="inlineStr">
         <is>
-          <t>1.04s</t>
+          <t>0.73s</t>
         </is>
       </c>
       <c r="O9" s="21" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="N10" s="13" t="inlineStr">
         <is>
-          <t>0.03s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O10" s="21" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="N11" s="25" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O11" s="21" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="N12" s="13" t="inlineStr">
         <is>
-          <t>0.20s</t>
+          <t>0.19s</t>
         </is>
       </c>
       <c r="O12" s="21" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="N13" s="25" t="inlineStr">
         <is>
-          <t>0.40s</t>
+          <t>0.28s</t>
         </is>
       </c>
       <c r="O13" s="21" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="N14" s="13" t="inlineStr">
         <is>
-          <t>0.31s</t>
+          <t>0.25s</t>
         </is>
       </c>
       <c r="O14" s="21" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="N15" s="25" t="inlineStr">
         <is>
-          <t>0.27s</t>
+          <t>0.24s</t>
         </is>
       </c>
       <c r="O15" s="21" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="N18" s="13" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O18" s="21" t="inlineStr">
@@ -2259,7 +2259,7 @@
 วิธี: ดึงวิชาที่ปกติอยู่ปี 4 ภาคการศึกษาที่ 2 มาลงล่วงหน้าในเทอมก่อนหน้า
 (ต้องตรวจสอบ prerequisite ว่าวิชานั้นเปิดลงล่วงหน้าได้)
 ■ ไม่พบวิชาบังคับในปี 4 ภาคการศึกษาที่ 2 ในแผน (อาจเป็นวิชาเลือกทั้งหมด)
-■ วิชาเลือก/เลือกเสรี ที่ต้องลงให้ครบด้วย (41 วิชา, 123 หน่วยกิต):
+■ วิชาเลือก/เลือกเสรี ที่ต้องลงให้ครบด้วย (43 วิชา, 129 หน่วยกิต):
   (วิชาเหล่านี้ไม่ผูกเทอมตายตัว ลงได้ตั้งแต่เทอมที่เปิดให้ลง)
 ■ แผนบังคับทุกเทอม (ไม่รวมปี 4 เทอม 2):
   ปีที่ 1 ภาคการศึกษาที่ 1 (7 วิชา, 18 หน่วยกิต):
@@ -2316,8 +2316,8 @@
     - 06026215 โครงงานวิทยาการข้อมูลและการวิเคราะห์เชิงธุรกิจ 2 (PROJECT IN DATA SCIENCE AND BUSINESS ANALYTICS 2) — 3(0-9-0)
     + วิชาเลือกเฉพาะแขนง (เลือก 1 แขนง แล้วลงวิชาในแขนงนั้น) กลุ่มที่มี:
       • วิชาเลือกในกลุ่มวิชาเลือกหรือกลุ่มวิชาชีพเฉพาะด้าน
-สรุป: ต้องดึงวิชาปี 4 เทอม 2 (0 หน่วยกิต) + วิชาเลือก/เลือกเสรี (123 หน่วยกิต)
-รวม 123 หน่วยกิต มากระจายลงในเทอมก่อนหน้า
+สรุป: ต้องดึงวิชาปี 4 เทอม 2 (0 หน่วยกิต) + วิชาเลือก/เลือกเสรี (129 หน่วยกิต)
+รวม 129 หน่วยกิต มากระจายลงในเทอมก่อนหน้า
 แนะนำเฉลี่ยเพิ่มเทอมละ 3-6 หน่วยกิต เพื่อไม่ให้หนักเกินไป
 และต้องตรวจ prerequisite ว่าวิชาที่จะดึงขึ้นมาลงก่อนได้จริง</t>
         </is>
@@ -2395,7 +2395,7 @@
       <c r="G21" s="34" t="inlineStr">
         <is>
           <t>ได้  
-นักศึกษาสามารถเรียนวิชาฐานข้อมูลในปีที่ 4 ได้ เนื่องจากหลักสูตรมีวิชาบังคับที่เกี่ยวข้องกับฐานข้อมูล เช่น 06026246 ระบบฐานข้อมูลแบบกระจาย (DISTRIBUTED DATABASE SYSTEMS) ซึ่งเป็นวิชาเลือกในกลุ่มวิชาเลือกหรือกลุ่มวิชาชีพเฉพาะด้าน จัดสอนในปีที่ 4 ภาคการศึกษาที่ 2 และไม่มีข้อกำหนดวิชาบังคับก่อนที่ขัดแย้งกับการเรียนในปีนี้ โดยวิชาดังกล่าวมีรหัส 06026246 ชื่อว่า "ระบบฐานข้อมูลแบบกระจาย" จำนวน 3 หน่วยกิต ประเภทวิชาเลือก (กลุ่มวิชาเลือกหรือกลุ่มวิชาชีพเฉพาะด้าน) ภาคการศึกษาที่ 2 ปีที่ 4.</t>
+นักศึกษาสามารถเรียนวิชาฐานข้อมูลในปีที่ 4 ได้ เนื่องจากหลักสูตรมีวิชาบังคับที่เกี่ยวข้องกับฐานข้อมูล เช่น 06026246 ระบบฐานข้อมูลแบบกระจาย และ 06026247 หัวข้อพิเศษทางวิศวกรรมข้อมูล 1 ซึ่งจัดสอนในภาคการศึกษาที่ 1 ปีที่ 4 โดยมีวิชาบังคับก่อนอย่าง 06066300 แนวคิดระบบฐานข้อมูล (ปีที่ 2 ภาคการศึกษาที่ 1) ที่เป็นพื้นฐานสำคัญ</t>
         </is>
       </c>
       <c r="H21" s="34" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="N21" s="13" t="inlineStr">
         <is>
-          <t>2.21s</t>
+          <t>1.51s</t>
         </is>
       </c>
       <c r="O21" s="21" t="inlineStr">
@@ -2470,18 +2470,21 @@
       </c>
       <c r="G22" s="35" t="inlineStr">
         <is>
-          <t>ไม่ได้  
-วิชา 06026212 การสร้างคลังข้อมูล เป็นวิชาบังคับที่ต้องเรียนหลังจากผ่านวิชา 06066300 แนวคิดระบบฐานข้อมูล ซึ่งจัดสอนในปีที่ 2 ภาคการศึกษาที่ 1 ดังนั้นจึงไม่สามารถลงวิชานี้ได้ในปีที่ 2 เนื่องจากยังไม่ผ่านวิชาพื้นฐานที่กำหนดไว้</t>
+          <t>คำตอบ: ไม่ได้ — ต้องสอบผ่าน 06066300 แนวคิดระบบฐานข้อมูล ก่อน ซึ่งตามแผนเรียนในปีที่ 2 ภาคการศึกษาที่ 1 จึงยังไม่ผ่านวิชานี้ก่อนเริ่มปี 2
+วิชา 06026212 การสร้างคลังข้อมูล (DATA WAREHOUSING) — 3(2-2-5) หน่วยกิต
+ตามแผนการศึกษา: ปีที่ 3 ภาคการศึกษาที่ 1
+วิชาบังคับก่อน (ต้องสอบผ่านก่อนจึงจะลงได้):
+  - 06066300 แนวคิดระบบฐานข้อมูล (DATABASE SYSTEM CONCEPTS) — ปีที่ 2 ภาคการศึกษาที่ 1</t>
         </is>
       </c>
       <c r="H22" s="35" t="inlineStr">
         <is>
-          <t>หน้า 26, 33, 353, 18, 68, 73, 25, 32</t>
+          <t>หน้า 323, 18, 25, 27, 32, 34, 69, 73</t>
         </is>
       </c>
       <c r="I22" s="35" t="inlineStr">
         <is>
-          <t>Structured SQL (ปี/ภาค) → Typhoon เรียบเรียง</t>
+          <t>Multi-hop SQL (ปีตามแผน + วิชาบังคับก่อน → ลงได้/ไม่ได้) — ไม่ผ่าน LLM</t>
         </is>
       </c>
       <c r="J22" s="25" t="n">
@@ -2504,7 +2507,7 @@
       </c>
       <c r="N22" s="25" t="inlineStr">
         <is>
-          <t>1.56s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O22" s="21" t="inlineStr">
@@ -2547,7 +2550,7 @@
       <c r="G23" s="34" t="inlineStr">
         <is>
           <t>เปรียบเทียบหลักสูตร DSBA 2560 (เก่า) vs 2565 (ใหม่) (เทียบด้วยชื่อวิชา):
-วิชาที่มีในหลักสูตรเก่า (2560) แต่ไม่มีในหลักสูตรใหม่ (2565) — 53 วิชา:
+วิชาที่มีในหลักสูตรเก่า (2560) แต่ไม่มีในหลักสูตรใหม่ (2565) — 52 วิชา:
 - กฎหมายทางธุรกิจและภาษี (BUSINESS LAWS AND TAXATION) [รหัสเดิม 06026160]
 - กระบวนการธุรกิจและการวางแผนทรัพยากรองค์กร (BUSINESS PROCESSES AND ENTERPRISE RESOURCE PLANNING) [รหัสเดิม 06026114]
 - การจัดการนวัตกรรมและการเปลี่ยนแปลง (INNOVATION AND CHANGE MANAGEMENT) [รหัสเดิม 06026152]
@@ -2580,7 +2583,6 @@
 - ฝึกวิชาชีพวิทยาการข้อมูลและการวิเคราะห์เชิงธุรกิจ (DATA SCIENCE AND BUSINESS ANALYTICS PROFESSIONAL PRACTICES) [รหัสเดิม 06026129]
 - พื้นฐานทางด้านเทคโนโลยีสารสนเทศ (INFORMATION TECHNOLOGY FUNDAMENTALS) [รหัสเดิม 06026100]
 - ภาษาอังกฤษเพื่อการสื่อสาร (ENGLISH FOR COMMUNICATION) [รหัสเดิม 90201026]
-- ระบบฐานข้อมูลขั้นสูง (ADVANCED DATABASE SYSTEMS) [รหัสเดิม 06026145]
 - ระบบสนับสนุนการตัดสินใจ (DECISION SUPPORT SYSTEMS) [รหัสเดิม 06026133]
 - ระบบอัจฉริยะ (INTELLIGENT SYSTEMS) [รหัสเดิม 06026136]
 - วิทยาการข้อมูลภาคปฏิบัติ (PRACTICAL DATA SCIENCE) [รหัสเดิม 06026159]
@@ -2588,7 +2590,8 @@
 - วิทยาการและการจัดการบริการ (SERVICE SCIENCE AND MANAGEMENT) [รหัสเดิม 06026153]
 - วิศวกรรมความต้องการ (REQUIREMENT ENGINEERING) [รหัสเดิม 06026143]
 - วิศวกรรมซอฟต์แวร์ (SOFTWARE ENGINEERING) [รหัสเดิม 06026142]
-วิชาที่เพิ่มเข้ามาในหลักสูตรใหม่ (2565) — 56 วิชา:
+- วิศวกรรมและการจัดการความรู้ (KNOWLEDGE ENGINEERING AND MANAGEMENT) [รหัสเดิม 06026149]
+วิชาที่เพิ่มเข้ามาในหลักสูตรใหม่ (2565) — 57 วิชา:
 - กฎหมายสำหรับคนรุ่นใหม่ (LAW FOR NEW GENERATION) [รหัส 90642033]
 - กระบวนการสโตแคสติกเบื้องต้น (INTRODUCTION TO STOCHASTIC PROCESS) [รหัส 06026232]
 - การดำเนินงานการเรียนรู้ของเครื่อง (MACHINE LEARNING OPERATIONS) [รหัส 06026241]
@@ -2628,7 +2631,7 @@
 - พีชคณิตเชิงเส้น (LINEAR ALGEBRA) [รหัส 06026202]
 - พื้นฐานทางธุรกิจสำหรับเทคโนโลยีสารสนเทศ (BUSINESS FUNDAMENTALS FOR INFORMATION TECHNOLOGY) [รหัส 06066101]
 - ระบบข้อมูลมหัต (BIG DATA SYSTEMS) [รหัส 06026213]
-- ระบบฐานข้อมูลแบบโนเอสคิวแอล (NOSQL DATABASE SYSTEMS) [รหัส 06026207]</t>
+- ระบบฐานข้อมูลแบบกระจาย (DISTRIBUTED DATABASE SYSTEMS) [รหัส 06026245]</t>
         </is>
       </c>
       <c r="H23" s="34" t="inlineStr">
@@ -2661,7 +2664,7 @@
       </c>
       <c r="N23" s="13" t="inlineStr">
         <is>
-          <t>0.13s</t>
+          <t>0.14s</t>
         </is>
       </c>
       <c r="O23" s="21" t="inlineStr">
@@ -2798,20 +2801,15 @@
       </c>
       <c r="G25" s="34" t="inlineStr">
         <is>
-          <t>ใช่ หลักสูตรวิทยาการข้อมูลและการวิเคราะห์เชิงธุรกิจ (DSBA) ปีที่ 3 มีการเลือกแขนง (หรือที่เรียกว่า "กลุ่มวิชา") ซึ่งแบ่งออกเป็น 3 กลุ่ม ได้แก่:
-- วิชาเลือกกลุ่มวิทยาการข้อมูล 1 (ELECTIVE IN DATA SCIENCE 1) – รหัส 06026xxx [3]
-- วิชาเลือกกลุ่มการวิเคราะห์เชิงสถิติ 1 (ELECTIVE IN STATISTICAL ANALYSIS 1) – รหัส 06026xxx [3]
-- วิชาเลือกกลุ่มวิศวกรรมข้อมูล 1 (ELECTIVE IN DATA ENGINEERING 1) – รหัส 06026xxx [3]
-ในภาคการศึกษาที่ 2 ปีที่ 3 มีการเลือกต่อในกลุ่มเดียวกัน ได้แก่:
-- วิชาเลือกกลุ่มวิทยาการข้อมูล 3 (ELECTIVE IN DATA SCIENCE 3) – รหัส 06026xxx [4]
-- วิชาเลือกกลุ่มการวิเคราะห์เชิงสถิติ 3 (ELECTIVE IN STATISTICAL ANALYTICS 3) – รหัส 06026xxx [4]
-- วิชาเลือกกลุ่มวิศวกรรมข้อมูล 3 (ELECTIVE IN DATA ENGINEERING 3) – รหัส 06026xxx [4]
-นอกจากนี้ยังมีวิชาเลือกในภาคการศึกษาที่ 1 และ 2 ปีที่ 3 สำหรับกลุ่มที่สอง เช่น:
-- วิชาเลือกกลุ่มวิทยาการข้อมูล 2 (ELECTIVE IN DATA SCIENCE 2) – รหัส 06026xxx [3]
-- วิชาเลือกกลุ่มการวิเคราะห์เชิงสถิติ 2 (ELECTIVE IN STATISTICAL ANALYTICS 2) – รหัส 06026xxx [3]
-- วิชาเลือกกลุ่มวิศวกรรมข้อมูล 2 (ELECTIVE IN DATA ENGINEERING 2) – รหัส 06026xxx [3]
-- วิชาเลือกกลุ่มวิทยาการข้อมูล 4 (ELECTIVE IN DATA SCIENCE 4) – รหัส 06026xxx [4]
-- วิชาเลือกกลุ่มการวิเคราะห์เชิงสถิติ 4 (ELECTIVE IN STATIST</t>
+          <t>ใช่ หลักสูตรวิทยาการข้อมูลและการวิเคราะห์เชิงธุรกิจ (DSBA) ปีที่ 3 มีการเลือกแขนง (หรือที่เรียกว่า "กลุ่มวิชา") ซึ่งแบ่งออกเป็น 3 กลุ่ม ดังนี้:
+- วิชาเลือกกลุ่มวิทยาการข้อมูล 1 (ELECTIVE IN DATA SCIENCE 1) – 3 (3-0-6) หรือ 3 (2-2-5) [3]
+- วิชาเลือกกลุ่มการวิเคราะห์เชิงสถิติ 1 (ELECTIVE IN STATISTICAL ANALYSIS 1) – 3 (3-0-6) หรือ 3 (2-2-5) [3]
+- วิชาเลือกกลุ่มวิศวกรรมข้อมูล 1 (ELECTIVE IN DATA ENGINEERING 1) – 3 (3-0-6) หรือ 3 (2-2-5) [3]
+ในภาคการศึกษาที่ 2 ปีที่ 3 ยังมีการเลือกแขนงในลักษณะเดียวกัน ได้แก่:
+- วิชาเลือกกลุ่มวิทยาการข้อมูล 3 (ELECTIVE IN DATA SCIENCE 3) – 3 (3-0-6) หรือ 3 (2-2-5) [4]
+- วิชาเลือกกลุ่มการวิเคราะห์เชิงสถิติ 3 (ELECTIVE IN STATISTICAL ANALYTICS 3) – 3 (3-0-6) หรือ 3 (2-2-5) [4]
+- วิชาเลือกกลุ่มวิศวกรรมข้อมูล 3 (ELECTIVE IN DATA ENGINEERING 3) – 3 (3-0-6) หรือ 3 (2-2-5) [4]
+ดังนั้น แขนงที่สามารถเลือกได้คือ วิทยาการข้อมูล, การวิเคราะห์เชิงสถิติ, และวิศวกรรมข้อมูล [3][4]</t>
         </is>
       </c>
       <c r="H25" s="34" t="inlineStr">
@@ -2844,12 +2842,12 @@
       </c>
       <c r="N25" s="13" t="inlineStr">
         <is>
-          <t>5.40s</t>
+          <t>4.29s</t>
         </is>
       </c>
       <c r="O25" s="21" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2886,9 +2884,9 @@
       </c>
       <c r="G26" s="34" t="inlineStr">
         <is>
-          <t>1. หลักสูตร IT 2565 มีหน่วยกิตรวมน้อยกว่า IT 2560 อยู่ 1 หน่วยกิต และเปลี่ยนโครงสร้างแขนงวิชาเป็น "โมดูลอาชีพ" 3 โมดูลแทนการเลือกแขนงวิชาเดิม
-2. หลักสูตร IT 2560 มีหน่วยกิตรวม 130 หน่วยกิต แบ่งเป็นกลุ่มวิชาเฉพาะ 94 หน่วยกิต (รวมกลุ่มวิชาบังคับเฉพาะแขนง 30 หน่วยกิต), ขณะที่ IT 2565 มีหน่วยกิตรวม 129 หน่วยกิต โดยลดหน่วยกิตกลุ่มวิชาเฉพาะจาก 94 เป็น 93 หน่วยกิต และเปลี่ยนโครงสร้างกลุ่มวิชาเฉพาะแขนงเป็น "โมดูลอาชีพ" 3 โมดูล (M1-M3) แทนการเลือกแขนงวิชาเดิม
-3. อ้างข้อมูลจาก: หน่วยกิตรวม (มคอ.2 IT 2560 หน้า 18, IT 2565 หน้า 6); โครงสร้างกลุ่มวิชาเฉพาะ (IT 2565 หน้า 376, 378); กลุ่มวิชาบังคับเฉพาะแขนง (IT 2565 หน้า 376); กลุ่มวิชาเลือกทางเทคโนโลยีสารสนเทศ (IT 2565 หน้า 378)</t>
+          <t>1. หลักสูตร IT 2565 มีหน่วยกิตรวม 129 หน่วยกิต ลดลง 1 หน่วยกิตจาก IT 2560 ที่มี 130 หน่วยกิต และเปลี่ยนโครงสร้างแขนงวิชาเป็น "โมดูลอาชีพ" 3 โมดูลแทนการเลือกแขนงวิชาเดิม
+2. หลักสูตร IT 2565 ลดหน่วยกิตกลุ่มวิชาเฉพาะด้านจาก 46 หน่วยกิต (IT 2560) เป็น 57 หน่วยกิต แต่เพิ่มหน่วยกิตกลุ่มวิชาเลือกทางเทคโนโลยีสารสนเทศจาก 6 เป็น 9 หน่วยกิต โดยจัดเป็น 3 โมดูลอาชีพ (M1: Full-Stack Web Developer, M2: Network/System Engineer, M3: Game Developer) ซึ่งนักศึกษาสามารถเลือกเรียนได้ตามความสนใจ โดยไม่จำเป็นต้องเลือกครบ 3 โมดูล
+3. อ้างข้อมูลจาก: หน่วยกิตรวม (มคอ.2 IT 2560 หน้า 18, IT 2565 หน้า 6), โครงสร้างหลักสูตร (มคอ.2 IT 2565 หน้า 371, 374, 376, 378), กลุ่มวิชาเลือก (IT 2565 หน้า 378), กลุ่มวิชาเฉพาะด้าน (IT 2565 หน้า 374), กลุ่มวิชาบังคับเฉพาะสาขา (IT 2565 หน้า 376), ประเภทวิชา (บังคับ/เลือก) และการจัดกลุ่มโมดูล (IT 2565 หน้า 370, 378)</t>
         </is>
       </c>
       <c r="H26" s="34" t="inlineStr">
@@ -2921,7 +2919,7 @@
       </c>
       <c r="N26" s="13" t="inlineStr">
         <is>
-          <t>3.81s</t>
+          <t>4.95s</t>
         </is>
       </c>
       <c r="O26" s="21" t="inlineStr">
@@ -3002,7 +3000,7 @@
       </c>
       <c r="N27" s="25" t="inlineStr">
         <is>
-          <t>0.31s</t>
+          <t>0.22s</t>
         </is>
       </c>
       <c r="O27" s="21" t="inlineStr">
@@ -3073,7 +3071,7 @@
       <c r="M28" s="34" t="n"/>
       <c r="N28" s="13" t="inlineStr">
         <is>
-          <t>0.29s</t>
+          <t>0.46s</t>
         </is>
       </c>
       <c r="O28" s="21" t="inlineStr">
@@ -3149,7 +3147,7 @@
       </c>
       <c r="N29" s="25" t="inlineStr">
         <is>
-          <t>0.07s</t>
+          <t>0.10s</t>
         </is>
       </c>
       <c r="O29" s="21" t="inlineStr">
@@ -3228,7 +3226,7 @@
       </c>
       <c r="N30" s="13" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O30" s="21" t="inlineStr">
@@ -3490,7 +3488,7 @@
       </c>
       <c r="N33" s="25" t="inlineStr">
         <is>
-          <t>0.19s</t>
+          <t>0.28s</t>
         </is>
       </c>
       <c r="O33" s="21" t="inlineStr">
@@ -3567,7 +3565,7 @@
       </c>
       <c r="N34" s="13" t="inlineStr">
         <is>
-          <t>0.03s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O34" s="21" t="inlineStr">
@@ -3638,7 +3636,7 @@
       <c r="M35" s="35" t="n"/>
       <c r="N35" s="25" t="inlineStr">
         <is>
-          <t>0.43s</t>
+          <t>0.48s</t>
         </is>
       </c>
       <c r="O35" s="21" t="inlineStr">
@@ -3716,7 +3714,7 @@
       </c>
       <c r="N36" s="13" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O36" s="21" t="inlineStr">
@@ -3806,7 +3804,7 @@
       </c>
       <c r="N37" s="25" t="inlineStr">
         <is>
-          <t>0.24s</t>
+          <t>0.25s</t>
         </is>
       </c>
       <c r="O37" s="21" t="inlineStr">
@@ -3918,7 +3916,7 @@
       </c>
       <c r="N38" s="13" t="inlineStr">
         <is>
-          <t>0.26s</t>
+          <t>0.28s</t>
         </is>
       </c>
       <c r="O38" s="21" t="inlineStr">
@@ -4010,7 +4008,7 @@
       </c>
       <c r="N39" s="25" t="inlineStr">
         <is>
-          <t>0.36s</t>
+          <t>0.41s</t>
         </is>
       </c>
       <c r="O39" s="21" t="inlineStr">
@@ -4105,7 +4103,7 @@
       </c>
       <c r="N40" s="13" t="inlineStr">
         <is>
-          <t>0.08s</t>
+          <t>0.04s</t>
         </is>
       </c>
       <c r="O40" s="21" t="inlineStr">
@@ -4275,7 +4273,7 @@
       <c r="M42" s="34" t="n"/>
       <c r="N42" s="13" t="inlineStr">
         <is>
-          <t>0.13s</t>
+          <t>0.12s</t>
         </is>
       </c>
       <c r="O42" s="21" t="inlineStr">
@@ -4423,7 +4421,7 @@
       </c>
       <c r="N44" s="13" t="inlineStr">
         <is>
-          <t>0.20s</t>
+          <t>0.18s</t>
         </is>
       </c>
       <c r="O44" s="21" t="inlineStr">
@@ -4575,7 +4573,7 @@
       <c r="M46" s="34" t="n"/>
       <c r="N46" s="13" t="inlineStr">
         <is>
-          <t>0.21s</t>
+          <t>0.17s</t>
         </is>
       </c>
       <c r="O46" s="21" t="inlineStr">
@@ -4656,7 +4654,7 @@
       </c>
       <c r="N47" s="25" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O47" s="21" t="inlineStr">
@@ -4744,7 +4742,7 @@
       </c>
       <c r="N48" s="13" t="inlineStr">
         <is>
-          <t>0.04s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O48" s="21" t="inlineStr">
@@ -4904,7 +4902,7 @@
       </c>
       <c r="N50" s="13" t="inlineStr">
         <is>
-          <t>0.17s</t>
+          <t>0.12s</t>
         </is>
       </c>
       <c r="O50" s="21" t="inlineStr">
@@ -4953,9 +4951,9 @@
     - 06026240 การพัฒนาระบบอัจฉริยะ (INTELLIGENT SYSTEM DEVELOPMENT) — 3(2-2-5)
     - 06026241 การดำเนินงานการเรียนรู้ของเครื่อง (MACHINE LEARNING OPERATIONS) — 3(3-0-6)
     - 06026242 โครงสร้างพื้นฐานด้านเทคโนโลยีกลุ่มเมฆ (CLOUD TECHNOLOGY INFRASTRUCTURE) — 3(3-0-6)
-    - 06026243 ระบบฐานข้อมูลขั้นสูง (ADVANCED DATABASE SYSTEMS) — 3 (3-0-6)
+    - 06026243 ระบบฐานข้อมูลขั้นสูง (ADVANCED DATABASE SYSTEMS) — 3(3-0-6)
     - 06026244 การดูแลและบำรุงรักษาระบบฐานข้อมูล (DATABASE SYSTEM MAINTENANCE AND ADMINISTRATION) — 3(2-2-5)
-    - 06026245 ระบบฐานข้อมูลแบบกระจาย (DISTRIBUTED DATABASE SYSTEMS) — 3 (3-0-6)
+    - 06026245 ระบบฐานข้อมูลแบบกระจาย (DISTRIBUTED DATABASE SYSTEMS) — 3(3-0-6)
     - 06026246 หัวข้อพิเศษทางวิศวกรรมข้อมูล 1 (SPECIAL TOPICS IN DATA ENGINEERING 1) — 3(3-0-6)
     - 06026247 หัวข้อพิเศษทางวิศวกรรมข้อมูล 2 (SPECIAL TOPICS IN DATA ENGINEERING 2) — 3(3-0-6)
     - 06026248 ปฏิบัติการพิเศษทางวิศวกรรมข้อมูล 1 (SPECIAL WORKSHOP IN DATA ENGINEERING 1) — 3(2-2-5)
@@ -5003,7 +5001,7 @@
       </c>
       <c r="N51" s="25" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O51" s="21" t="inlineStr">
@@ -5190,7 +5188,7 @@
       </c>
       <c r="N53" s="25" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O53" s="21" t="inlineStr">
@@ -5272,7 +5270,7 @@
       <c r="M54" s="34" t="n"/>
       <c r="N54" s="13" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O54" s="21" t="inlineStr">
@@ -5516,7 +5514,7 @@
       <c r="M57" s="35" t="n"/>
       <c r="N57" s="25" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O57" s="21" t="inlineStr">
@@ -5590,7 +5588,7 @@
       <c r="M58" s="34" t="n"/>
       <c r="N58" s="13" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O58" s="21" t="inlineStr">
@@ -5791,7 +5789,7 @@
       </c>
       <c r="N60" s="13" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O60" s="21" t="inlineStr">
@@ -5875,7 +5873,7 @@
       </c>
       <c r="N61" s="25" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O61" s="21" t="inlineStr">
@@ -5954,7 +5952,7 @@
       </c>
       <c r="N62" s="13" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O62" s="21" t="inlineStr">
@@ -6042,7 +6040,7 @@
       </c>
       <c r="N63" s="25" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O63" s="21" t="inlineStr">
@@ -6235,7 +6233,7 @@
       <c r="M65" s="35" t="n"/>
       <c r="N65" s="25" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O65" s="21" t="inlineStr">
@@ -6313,7 +6311,7 @@
       <c r="M66" s="34" t="n"/>
       <c r="N66" s="13" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O66" s="21" t="inlineStr">
@@ -6395,7 +6393,7 @@
       </c>
       <c r="N67" s="25" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O67" s="21" t="inlineStr">
@@ -6500,7 +6498,7 @@
       <c r="M68" s="34" t="n"/>
       <c r="N68" s="13" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O68" s="21" t="inlineStr">
@@ -6729,7 +6727,7 @@
       </c>
       <c r="N71" s="25" t="inlineStr">
         <is>
-          <t>0.22s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O71" s="21" t="inlineStr">
@@ -6807,7 +6805,7 @@
       </c>
       <c r="N72" s="13" t="inlineStr">
         <is>
-          <t>0.21s</t>
+          <t>0.07s</t>
         </is>
       </c>
       <c r="O72" s="21" t="inlineStr">
@@ -6885,7 +6883,7 @@
       </c>
       <c r="N73" s="25" t="inlineStr">
         <is>
-          <t>0.20s</t>
+          <t>0.07s</t>
         </is>
       </c>
       <c r="O73" s="21" t="inlineStr">
@@ -6964,7 +6962,7 @@
       </c>
       <c r="N74" s="13" t="inlineStr">
         <is>
-          <t>0.35s</t>
+          <t>0.14s</t>
         </is>
       </c>
       <c r="O74" s="21" t="inlineStr">
@@ -7042,7 +7040,7 @@
       </c>
       <c r="N75" s="25" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O75" s="21" t="inlineStr">
@@ -7126,7 +7124,7 @@
       </c>
       <c r="N76" s="13" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O76" s="13" t="inlineStr">
@@ -7168,21 +7166,22 @@
       </c>
       <c r="G77" s="35" t="inlineStr">
         <is>
-          <t>วิชา 06046406 พื้นฐานการเรียนรู้เชิงลึก (FUNDAMENTALS OF DEEP LEARNING) — 3(3-0-6) | ปีที่ 2 ภาคการศึกษาที่ 1
-  ต้องผ่านวิชาบังคับก่อน:
-    • 06046401 แคลคูลัส 2 (CALCULUS 2) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 2
-      ↳ ต้องผ่าน 06046400 แคลคูลัส 1 (CALCULUS 1) ก่อน
-    • 06046402 พีชคณิตเชิงเส้น (LINEAR ALGEBRA) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 1</t>
+          <t>วิชา 06046406 พื้นฐานการเรียนรู้เชิงลึก (FUNDAMENTALS OF DEEP LEARNING) — ปีที่ 2 ภาคการศึกษาที่ 1
+วิชาที่ต้องสอบผ่านก่อน (↳ = วิชาที่ต้องผ่านก่อนวิชาด้านบนอีกชั้น):
+  • 06046401 แคลคูลัส 2 (CALCULUS 2) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 2
+    ↳ 06046400 แคลคูลัส 1 (CALCULUS 1) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 1
+  • 06046402 พีชคณิตเชิงเส้น (LINEAR ALGEBRA) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 1
+รวมต้องผ่านก่อน 3 วิชา</t>
         </is>
       </c>
       <c r="H77" s="35" t="inlineStr">
         <is>
-          <t>หน้า 37, 292, 19, 20, 23, 24, 287, 288</t>
+          <t>หน้า 37, 19, 292, 23, 287, 20, 24, 288</t>
         </is>
       </c>
       <c r="I77" s="35" t="inlineStr">
         <is>
-          <t>Structured SQL (prerequisite) — ไม่ผ่าน LLM</t>
+          <t>Multi-hop SQL (วิชาบังคับก่อนไล่หลายชั้น) — ไม่ผ่าน LLM</t>
         </is>
       </c>
       <c r="J77" s="25" t="n">
@@ -7289,7 +7288,7 @@
       </c>
       <c r="N78" s="13" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O78" s="21" t="inlineStr">
@@ -7398,7 +7397,7 @@
       </c>
       <c r="N79" s="25" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O79" s="21" t="inlineStr">
@@ -7476,7 +7475,7 @@
       </c>
       <c r="N80" s="13" t="inlineStr">
         <is>
-          <t>0.15s</t>
+          <t>0.16s</t>
         </is>
       </c>
       <c r="O80" s="21" t="inlineStr">
@@ -7596,9 +7595,10 @@
       </c>
       <c r="G82" s="34" t="inlineStr">
         <is>
-          <t>วิชา 06046405 การเรียนรู้ของเครื่องเชิงความน่าจะเป็น (PROBABILISTIC MACHINE LEARNING) — 3(3-0-6) | ปีที่ 2 ภาคการศึกษาที่ 1
-  ต้องผ่านวิชาบังคับก่อน:
-    • 06066001 ความน่าจะเป็นและสถิติ (PROBABILITY AND STATISTICS) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 1</t>
+          <t>วิชา 06046405 การเรียนรู้ของเครื่องเชิงความน่าจะเป็น (PROBABILISTIC MACHINE LEARNING) — ปีที่ 2 ภาคการศึกษาที่ 1
+วิชาที่ต้องสอบผ่านก่อน (↳ = วิชาที่ต้องผ่านก่อนวิชาด้านบนอีกชั้น):
+  • 06066001 ความน่าจะเป็นและสถิติ (PROBABILITY AND STATISTICS) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 1
+รวมต้องผ่านก่อน 1 วิชา</t>
         </is>
       </c>
       <c r="H82" s="34" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="I82" s="34" t="inlineStr">
         <is>
-          <t>Structured SQL (prerequisite) — ไม่ผ่าน LLM</t>
+          <t>Multi-hop SQL (วิชาบังคับก่อนไล่หลายชั้น) — ไม่ผ่าน LLM</t>
         </is>
       </c>
       <c r="J82" s="13" t="n">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="N89" s="25" t="inlineStr">
         <is>
-          <t>0.10s</t>
+          <t>0.12s</t>
         </is>
       </c>
       <c r="O89" s="21" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="N93" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O93" s="41" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="N97" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O97" s="41" t="inlineStr">
@@ -10493,17 +10493,19 @@
       </c>
       <c r="G119" s="39" t="inlineStr">
         <is>
-          <t>รหัสวิชา 06046420 คือ ระบบให้คำแนะนำอัจฉริยะ (INTELLIGENT RECOMMENDATION SYSTEMS) จำนวน 3 หน่วยกิต (3-0-6) [1]</t>
+          <t>รหัสวิชา 06046420 คือวิชา (หลักสูตร AIT 2566 (ปริญญาตรี)):
+- ระบบให้คำแนะนำอัจฉริยะ (INTELLIGENT RECOMMENDATION SYSTEMS)
+- จำนวนหน่วยกิต: 3(3-0-6)</t>
         </is>
       </c>
       <c r="H119" s="39" t="inlineStr">
         <is>
-          <t>หน้า 21, 24, 122</t>
+          <t>หน้า 21, 39, 298</t>
         </is>
       </c>
       <c r="I119" s="39" t="inlineStr">
         <is>
-          <t>Hybrid retrieval (คำสำคัญ + bge-m3, RRF) → Typhoon</t>
+          <t>Structured SQL (รหัสวิชา) — ไม่ผ่าน LLM</t>
         </is>
       </c>
       <c r="J119" s="39" t="n">
@@ -10526,7 +10528,7 @@
       </c>
       <c r="N119" s="39" t="inlineStr">
         <is>
-          <t>0.82s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O119" s="41" t="inlineStr">
@@ -10603,7 +10605,7 @@
       </c>
       <c r="N120" s="39" t="inlineStr">
         <is>
-          <t>0.04s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O120" s="41" t="inlineStr">
@@ -10834,7 +10836,7 @@
       </c>
       <c r="N123" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O123" s="41" t="inlineStr">
@@ -11081,7 +11083,7 @@
       </c>
       <c r="N126" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O126" s="41" t="inlineStr">
@@ -11415,7 +11417,7 @@
       </c>
       <c r="N130" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O130" s="41" t="inlineStr">
@@ -11732,7 +11734,7 @@
       </c>
       <c r="N134" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O134" s="41" t="inlineStr">
@@ -11890,7 +11892,7 @@
       </c>
       <c r="N136" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O136" s="41" t="inlineStr">
@@ -12048,7 +12050,7 @@
       </c>
       <c r="N138" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O138" s="41" t="inlineStr">
@@ -12206,7 +12208,7 @@
       </c>
       <c r="N140" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O140" s="41" t="inlineStr">
@@ -12364,7 +12366,7 @@
       </c>
       <c r="N142" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O142" s="41" t="inlineStr">
@@ -12522,7 +12524,7 @@
       </c>
       <c r="N144" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O144" s="41" t="inlineStr">
@@ -12680,7 +12682,7 @@
       </c>
       <c r="N146" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O146" s="41" t="inlineStr">
@@ -12838,7 +12840,7 @@
       </c>
       <c r="N148" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O148" s="41" t="inlineStr">
@@ -12917,7 +12919,7 @@
       </c>
       <c r="N149" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O149" s="41" t="inlineStr">
@@ -13075,7 +13077,7 @@
       </c>
       <c r="N151" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O151" s="41" t="inlineStr">
@@ -13153,7 +13155,7 @@
       </c>
       <c r="N152" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O152" s="41" t="inlineStr">
@@ -13232,7 +13234,7 @@
       </c>
       <c r="N153" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O153" s="41" t="inlineStr">
@@ -13390,7 +13392,7 @@
       </c>
       <c r="N155" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O155" s="41" t="inlineStr">
@@ -13469,7 +13471,7 @@
       </c>
       <c r="N156" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O156" s="41" t="inlineStr">
@@ -13546,7 +13548,7 @@
       </c>
       <c r="N157" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O157" s="41" t="inlineStr">
@@ -13700,7 +13702,7 @@
       </c>
       <c r="N159" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O159" s="41" t="inlineStr">
@@ -13777,7 +13779,7 @@
       </c>
       <c r="N160" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O160" s="41" t="inlineStr">
@@ -14163,7 +14165,7 @@
       </c>
       <c r="N165" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O165" s="41" t="inlineStr">
@@ -15087,7 +15089,7 @@
       </c>
       <c r="N176" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O176" s="41" t="inlineStr">
@@ -15491,7 +15493,7 @@
       </c>
       <c r="N181" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O181" s="41" t="inlineStr">
@@ -15649,7 +15651,7 @@
       </c>
       <c r="N183" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O183" s="41" t="inlineStr">
@@ -16123,7 +16125,7 @@
       </c>
       <c r="N189" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O189" s="41" t="inlineStr">
@@ -16694,7 +16696,7 @@
       </c>
       <c r="N196" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O196" s="41" t="inlineStr">
@@ -16771,7 +16773,7 @@
       </c>
       <c r="N197" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O197" s="41" t="inlineStr">
@@ -16848,7 +16850,7 @@
       </c>
       <c r="N198" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O198" s="41" t="inlineStr">
@@ -16925,7 +16927,7 @@
       </c>
       <c r="N199" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O199" s="41" t="inlineStr">
@@ -17464,7 +17466,7 @@
       </c>
       <c r="N206" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O206" s="41" t="inlineStr">
@@ -18127,7 +18129,7 @@
       </c>
       <c r="N214" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O214" s="41" t="inlineStr">
@@ -19241,7 +19243,7 @@
       </c>
       <c r="N228" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O228" s="41" t="inlineStr">
@@ -19320,7 +19322,7 @@
       </c>
       <c r="N229" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O229" s="41" t="inlineStr">
@@ -19722,7 +19724,7 @@
       </c>
       <c r="N234" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O234" s="41" t="inlineStr">
@@ -20122,7 +20124,7 @@
       </c>
       <c r="N239" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O239" s="41" t="inlineStr">
@@ -20199,7 +20201,7 @@
       </c>
       <c r="N240" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O240" s="41" t="inlineStr">
@@ -20276,7 +20278,7 @@
       </c>
       <c r="N241" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O241" s="41" t="inlineStr">
@@ -20353,7 +20355,7 @@
       </c>
       <c r="N242" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O242" s="41" t="inlineStr">
@@ -20892,7 +20894,7 @@
       </c>
       <c r="N249" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O249" s="41" t="inlineStr">
@@ -21219,7 +21221,7 @@
       </c>
       <c r="N253" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.03s</t>
         </is>
       </c>
       <c r="O253" s="41" t="inlineStr">
@@ -21477,7 +21479,7 @@
       </c>
       <c r="N256" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O256" s="41" t="inlineStr">
@@ -21560,7 +21562,7 @@
       </c>
       <c r="N257" s="39" t="inlineStr">
         <is>
-          <t>0.03s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O257" s="41" t="inlineStr">
@@ -21793,7 +21795,7 @@
       </c>
       <c r="N260" s="39" t="inlineStr">
         <is>
-          <t>0.11s</t>
+          <t>0.10s</t>
         </is>
       </c>
       <c r="O260" s="41" t="inlineStr">
@@ -22347,7 +22349,7 @@
       </c>
       <c r="N267" s="39" t="inlineStr">
         <is>
-          <t>0.05s</t>
+          <t>0.04s</t>
         </is>
       </c>
       <c r="O267" s="41" t="inlineStr">
@@ -22820,7 +22822,7 @@
       </c>
       <c r="N273" s="39" t="inlineStr">
         <is>
-          <t>0.05s</t>
+          <t>0.04s</t>
         </is>
       </c>
       <c r="O273" s="41" t="inlineStr">
@@ -23293,7 +23295,7 @@
       </c>
       <c r="N279" s="39" t="inlineStr">
         <is>
-          <t>0.08s</t>
+          <t>0.07s</t>
         </is>
       </c>
       <c r="O279" s="41" t="inlineStr">
@@ -23768,7 +23770,7 @@
       </c>
       <c r="N285" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O285" s="41" t="inlineStr">
@@ -23845,7 +23847,7 @@
       </c>
       <c r="N286" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O286" s="41" t="inlineStr">
@@ -24692,7 +24694,7 @@
       </c>
       <c r="N297" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O297" s="41" t="inlineStr">
@@ -25476,7 +25478,7 @@
       </c>
       <c r="N307" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O307" s="41" t="inlineStr">
@@ -26257,7 +26259,7 @@
       </c>
       <c r="N317" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O317" s="41" t="inlineStr">
@@ -26413,7 +26415,7 @@
       </c>
       <c r="N319" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O319" s="41" t="inlineStr">
@@ -26738,7 +26740,7 @@
       </c>
       <c r="N323" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O323" s="41" t="inlineStr">
@@ -26817,7 +26819,7 @@
       </c>
       <c r="N324" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O324" s="41" t="inlineStr">
@@ -26896,7 +26898,7 @@
       </c>
       <c r="N325" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O325" s="41" t="inlineStr">
@@ -26975,7 +26977,7 @@
       </c>
       <c r="N326" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O326" s="41" t="inlineStr">
@@ -27063,7 +27065,7 @@
       </c>
       <c r="N327" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O327" s="41" t="inlineStr">
@@ -27217,7 +27219,7 @@
       </c>
       <c r="N329" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O329" s="41" t="inlineStr">
@@ -27608,7 +27610,7 @@
       </c>
       <c r="N334" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O334" s="41" t="inlineStr">
@@ -27764,7 +27766,7 @@
       </c>
       <c r="N336" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O336" s="41" t="inlineStr">
@@ -28083,7 +28085,7 @@
       </c>
       <c r="N340" s="39" t="inlineStr">
         <is>
-          <t>0.03s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O340" s="41" t="inlineStr">
@@ -28241,7 +28243,7 @@
       </c>
       <c r="N342" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O342" s="41" t="inlineStr">
@@ -29700,7 +29702,7 @@
       <c r="G361" s="39" t="inlineStr">
         <is>
           <t>ได้  
-นักศึกษาชั้นปีสุดท้ายที่เหลือรายวิชาไม่ถึง 9 หน่วยกิต หรือต้องลงเกิน 22 หน่วยกิตเพื่อสำเร็จการศึกษา สามารถลงทะเบียนได้สูงสุดไม่เกิน 27 หน่วยกิต โดยต้องได้รับอนุมัติจากสภาวิชาการ ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 82</t>
+นักศึกษาชั้นปีสุดท้ายที่เหลือรายวิชาไม่ถึง 9 หน่วยกิต หรือต้องลงเกิน 22 หน่วยกิตเพื่อสำเร็จการศึกษา สามารถลงทะเบียนได้สูงสุดไม่เกิน 27 หน่วยกิต โดยต้องได้รับอนุมัติจากสภาวิชาการ ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 82 ซึ่งระบุไว้ชัดเจนว่า ข้อยกเว้นสำหรับนักศึกษาชั้นปีสุดท้ายสามารถลงทะเบียนได้สูงสุด 27 หน่วยกิต</t>
         </is>
       </c>
       <c r="H361" s="39" t="inlineStr">
@@ -29733,7 +29735,7 @@
       </c>
       <c r="N361" s="39" t="inlineStr">
         <is>
-          <t>1.61s</t>
+          <t>2.20s</t>
         </is>
       </c>
       <c r="O361" s="41" t="inlineStr">
@@ -29815,7 +29817,7 @@
       </c>
       <c r="N362" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O362" s="41" t="inlineStr">
@@ -29895,7 +29897,7 @@
       </c>
       <c r="N363" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O363" s="41" t="inlineStr">
@@ -29976,7 +29978,7 @@
       </c>
       <c r="N364" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O364" s="41" t="inlineStr">
@@ -30057,7 +30059,7 @@
       </c>
       <c r="N365" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O365" s="41" t="inlineStr">
@@ -30138,7 +30140,7 @@
       </c>
       <c r="N366" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O366" s="41" t="inlineStr">
@@ -30297,7 +30299,7 @@
       </c>
       <c r="N368" s="39" t="inlineStr">
         <is>
-          <t>0.03s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O368" s="41" t="inlineStr">
@@ -30375,7 +30377,7 @@
       </c>
       <c r="N369" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O369" s="41" t="inlineStr">
@@ -30531,7 +30533,7 @@
       </c>
       <c r="N371" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.03s</t>
         </is>
       </c>
       <c r="O371" s="41" t="inlineStr">
@@ -30686,7 +30688,7 @@
       </c>
       <c r="N373" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O373" s="41" t="inlineStr">
@@ -30999,7 +31001,7 @@
       </c>
       <c r="N377" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O377" s="41" t="inlineStr">
@@ -31617,7 +31619,7 @@
       </c>
       <c r="N385" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O385" s="41" t="inlineStr">
@@ -31694,7 +31696,7 @@
       </c>
       <c r="N386" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O386" s="41" t="inlineStr">
@@ -31850,7 +31852,7 @@
       </c>
       <c r="N388" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O388" s="41" t="inlineStr">
@@ -31928,7 +31930,7 @@
       </c>
       <c r="N389" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O389" s="41" t="inlineStr">
@@ -32006,7 +32008,7 @@
       </c>
       <c r="N390" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O390" s="41" t="inlineStr">
@@ -32164,7 +32166,7 @@
       </c>
       <c r="N392" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O392" s="41" t="inlineStr">
@@ -32322,7 +32324,7 @@
       </c>
       <c r="N394" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O394" s="41" t="inlineStr">
@@ -32711,7 +32713,7 @@
       </c>
       <c r="N399" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O399" s="41" t="inlineStr">
@@ -33348,7 +33350,7 @@
       </c>
       <c r="N407" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O407" s="41" t="inlineStr">
@@ -33425,7 +33427,7 @@
       </c>
       <c r="N408" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O408" s="41" t="inlineStr">
@@ -33502,7 +33504,7 @@
       </c>
       <c r="N409" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O409" s="41" t="inlineStr">
@@ -34524,7 +34526,7 @@
       </c>
       <c r="N422" s="39" t="inlineStr">
         <is>
-          <t>0.31s</t>
+          <t>0.23s</t>
         </is>
       </c>
       <c r="O422" s="41" t="inlineStr">
@@ -34603,7 +34605,7 @@
       </c>
       <c r="N423" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O423" s="41" t="inlineStr">
@@ -34848,7 +34850,7 @@
       </c>
       <c r="N426" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O426" s="41" t="inlineStr">
@@ -35085,7 +35087,7 @@
       </c>
       <c r="N429" s="39" t="inlineStr">
         <is>
-          <t>0.03s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O429" s="41" t="inlineStr">
@@ -35626,7 +35628,7 @@
       </c>
       <c r="N436" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O436" s="41" t="inlineStr">
@@ -35872,7 +35874,7 @@
       </c>
       <c r="N439" s="39" t="inlineStr">
         <is>
-          <t>0.03s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O439" s="41" t="inlineStr">
@@ -36265,7 +36267,7 @@
       </c>
       <c r="N444" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O444" s="41" t="inlineStr">
@@ -36344,7 +36346,7 @@
       </c>
       <c r="N445" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O445" s="41" t="inlineStr">
@@ -36498,7 +36500,7 @@
       </c>
       <c r="N447" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O447" s="41" t="inlineStr">
@@ -37600,7 +37602,7 @@
       </c>
       <c r="N461" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O461" s="41" t="inlineStr">
@@ -38233,7 +38235,7 @@
       </c>
       <c r="N469" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O469" s="41" t="inlineStr">
@@ -38710,7 +38712,7 @@
       </c>
       <c r="N475" s="39" t="inlineStr">
         <is>
-          <t>0.08s</t>
+          <t>0.17s</t>
         </is>
       </c>
       <c r="O475" s="41" t="inlineStr">
@@ -39173,7 +39175,7 @@
       </c>
       <c r="N481" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O481" s="41" t="inlineStr">
@@ -39800,7 +39802,7 @@
       </c>
       <c r="N489" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O489" s="41" t="inlineStr">
@@ -39879,7 +39881,7 @@
       </c>
       <c r="N490" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O490" s="41" t="inlineStr">
@@ -39958,7 +39960,7 @@
       </c>
       <c r="N491" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O491" s="41" t="inlineStr">
@@ -40114,7 +40116,7 @@
       </c>
       <c r="N493" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O493" s="41" t="inlineStr">
@@ -40193,7 +40195,7 @@
       </c>
       <c r="N494" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O494" s="41" t="inlineStr">
@@ -40431,7 +40433,7 @@
       </c>
       <c r="N497" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O497" s="41" t="inlineStr">
@@ -40515,7 +40517,7 @@
       </c>
       <c r="N498" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O498" s="41" t="inlineStr">
@@ -40673,7 +40675,7 @@
       </c>
       <c r="N500" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O500" s="41" t="inlineStr">
@@ -40910,7 +40912,7 @@
       </c>
       <c r="N503" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O503" s="41" t="inlineStr">
@@ -40989,7 +40991,7 @@
       </c>
       <c r="N504" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O504" s="41" t="inlineStr">
@@ -41222,7 +41224,7 @@
       </c>
       <c r="N507" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O507" s="41" t="inlineStr">
@@ -41388,7 +41390,7 @@
       </c>
       <c r="N509" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O509" s="41" t="inlineStr">
@@ -41467,7 +41469,7 @@
       </c>
       <c r="N510" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O510" s="41" t="inlineStr">
@@ -41625,7 +41627,7 @@
       </c>
       <c r="N512" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O512" s="41" t="inlineStr">
@@ -42339,7 +42341,7 @@
       </c>
       <c r="N521" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.03s</t>
         </is>
       </c>
       <c r="O521" s="41" t="inlineStr">
@@ -42439,7 +42441,7 @@
       </c>
       <c r="N522" s="39" t="inlineStr">
         <is>
-          <t>0.44s</t>
+          <t>0.49s</t>
         </is>
       </c>
       <c r="O522" s="41" t="inlineStr">
@@ -42517,7 +42519,7 @@
       </c>
       <c r="N523" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.04s</t>
         </is>
       </c>
       <c r="O523" s="41" t="inlineStr">
@@ -42595,7 +42597,7 @@
       </c>
       <c r="N524" s="39" t="inlineStr">
         <is>
-          <t>0.03s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O524" s="41" t="inlineStr">
@@ -42681,7 +42683,7 @@
       </c>
       <c r="N525" s="39" t="inlineStr">
         <is>
-          <t>0.21s</t>
+          <t>0.23s</t>
         </is>
       </c>
       <c r="O525" s="41" t="inlineStr">
@@ -43000,7 +43002,7 @@
       </c>
       <c r="N529" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O529" s="41" t="inlineStr">
@@ -43317,7 +43319,7 @@
       </c>
       <c r="N533" s="39" t="inlineStr">
         <is>
-          <t>0.10s</t>
+          <t>0.18s</t>
         </is>
       </c>
       <c r="O533" s="41" t="inlineStr">
@@ -43395,7 +43397,7 @@
       </c>
       <c r="N534" s="39" t="inlineStr">
         <is>
-          <t>0.03s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O534" s="41" t="inlineStr">
@@ -43472,7 +43474,7 @@
       </c>
       <c r="N535" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O535" s="41" t="inlineStr">
@@ -44013,7 +44015,7 @@
       </c>
       <c r="N542" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O542" s="41" t="inlineStr">
@@ -44332,7 +44334,7 @@
       </c>
       <c r="N546" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O546" s="41" t="inlineStr">
@@ -44411,7 +44413,7 @@
       </c>
       <c r="N547" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O547" s="41" t="inlineStr">
@@ -44568,7 +44570,7 @@
       </c>
       <c r="N549" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O549" s="41" t="inlineStr">
@@ -44724,34 +44726,30 @@
       </c>
       <c r="G551" s="39" t="inlineStr">
         <is>
-          <t>วิชาที่เกี่ยวข้องกับ "หน่วยกิต ระบบข้อมูลแบบกระจาย" — หลักสูตร DSBA
-■ DSBA 2565 — 8 วิชา รวม 24 หน่วยกิต
-  - 06066300 แนวคิดระบบฐานข้อมูล (DATABASE SYSTEM CONCEPTS)
-      หน่วยกิต 3(2-2-5) | ปีที่ 2 ภาคการศึกษาที่ 1
-  - 06066304 การวิเคราะห์และออกแบบระบบสารสนเทศ (INFORMATION SYSTEM ANALYSIS AND DESIGN)
-      หน่วยกิต 3(3-0-6) | ปีที่ 2 ภาคการศึกษาที่ 1
-  - 06026207 ระบบฐานข้อมูลแบบโนเอสคิวแอล (NOSQL DATABASE SYSTEMS)
-      หน่วยกิต 3(2-2-5) | ปีที่ 2 ภาคการศึกษาที่ 2
-  - 06026212 การสร้างคลังข้อมูล (DATA WAREHOUSING)
-      หน่วยกิต 3(2-2-5) | ปีที่ 3 ภาคการศึกษาที่ 1
-  - 06026213 ระบบข้อมูลมหัต (BIG DATA SYSTEMS)
-      หน่วยกิต 3(2-2-5) | ปีที่ 3 ภาคการศึกษาที่ 2
-  - 06026234 การออกแบบการทดลอง (EXPERIMENTAL DESIGN)
-      หน่วยกิต 3(3-0-6) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)
-  - 06026239 สถาปัตยกรรมข้อมูลแบบไปป์ไลน์ (DATA PIPELINE ARCHITECTURE)
-      หน่วยกิต 3(3-0-6) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)
-  - 06026244 การดูแลและบำรุงรักษาระบบฐานข้อมูล (DATABASE SYSTEM MAINTENANCE AND ADMINISTRATION)
-      หน่วยกิต 3(2-2-5) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)</t>
+          <t>วิชา 06026245 ระบบฐานข้อมูลแบบกระจาย (DISTRIBUTED DATABASE SYSTEMS) — 3(3-0-6) หน่วยกิต · หลักสูตร DSBA 2565 (ปริญญาตรี)
+อยู่ในกลุ่มวิศวกรรมข้อมูล (ส่วนของกลุ่มวิชาชีพเฉพาะด้าน) — ต้องเลือกเรียนกลุ่มใดกลุ่มหนึ่ง (หน้า 20)
+ไม่ได้กำหนดปี/ภาคตายตัวในแผนการศึกษา (เป็นวิชาเลือกของกลุ่ม) ลงเรียนได้ในช่องวิชาเลือกตามแผน:
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกกลุ่มวิศวกรรมข้อมูล 1" (หน้า 27)
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกกลุ่มวิศวกรรมข้อมูล 2" (หน้า 27)
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกกลุ่มวิศวกรรมข้อมูล 3" (หน้า 28)
+  - แผนปกติ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกกลุ่มวิศวกรรมข้อมูล 4" (หน้า 28)
+  - แผนปกติ ปีที่ 4 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกในกลุ่มวิชาเลือกหรือกลุ่มวิชาชีพเฉพาะด้าน 1" (หน้า 29)
+  - แผนปกติ ปีที่ 4 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกในกลุ่มวิชาเลือกหรือกลุ่มวิชาชีพเฉพาะด้าน 2" (หน้า 29)
+  - แผนสหกิจ ปีที่ 3 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกกลุ่มวิศวกรรมข้อมูล 1" (หน้า 34)
+  - แผนสหกิจ ปีที่ 3 ภาคการศึกษาที่ 1: ช่อง "วิชาเลือกกลุ่มวิศวกรรมข้อมูล 2" (หน้า 34)
+  - แผนสหกิจ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกกลุ่มวิศวกรรมข้อมูล 3" (หน้า 35)
+  - แผนสหกิจ ปีที่ 3 ภาคการศึกษาที่ 2: ช่อง "วิชาเลือกกลุ่มวิศวกรรมข้อมูล 4" (หน้า 35)
+วิชาบังคับก่อน: ไม่มี</t>
         </is>
       </c>
       <c r="H551" s="39" t="inlineStr">
         <is>
-          <t>หน้า 354, 26, 33, 18, 68, 73, 353, 20</t>
+          <t>หน้า 20, 27, 28, 29, 34, 35, 21, 71</t>
         </is>
       </c>
       <c r="I551" s="39" t="inlineStr">
         <is>
-          <t>Semantic topic search (bge-m3) → จัดรูปคำตอบเอง → Typhoon เรียบเรียง</t>
+          <t>Structured SQL (ค้นวิชา: ตารางแผนและหัวข้อรายวิชา) — ไม่ผ่าน LLM</t>
         </is>
       </c>
       <c r="J551" s="39" t="n">
@@ -44774,7 +44772,7 @@
       </c>
       <c r="N551" s="39" t="inlineStr">
         <is>
-          <t>0.44s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O551" s="41" t="inlineStr">
@@ -44932,7 +44930,7 @@
       </c>
       <c r="N553" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O553" s="41" t="inlineStr">
@@ -45020,7 +45018,7 @@
       </c>
       <c r="N554" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O554" s="41" t="inlineStr">
@@ -45187,7 +45185,7 @@
       </c>
       <c r="N556" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O556" s="41" t="inlineStr">
@@ -45264,7 +45262,7 @@
       </c>
       <c r="N557" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O557" s="41" t="inlineStr">
@@ -46568,7 +46566,7 @@
       </c>
       <c r="N573" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O573" s="41" t="inlineStr">
@@ -46654,66 +46652,4710 @@
         </is>
       </c>
     </row>
-    <row r="575" ht="14.25" customHeight="1" s="36"/>
-    <row r="576" ht="14.25" customHeight="1" s="36"/>
-    <row r="577" ht="14.25" customHeight="1" s="36"/>
-    <row r="578" ht="14.25" customHeight="1" s="36"/>
-    <row r="579" ht="14.25" customHeight="1" s="36"/>
-    <row r="580" ht="14.25" customHeight="1" s="36"/>
-    <row r="581" ht="14.25" customHeight="1" s="36"/>
-    <row r="582" ht="14.25" customHeight="1" s="36"/>
-    <row r="583" ht="14.25" customHeight="1" s="36"/>
-    <row r="584" ht="14.25" customHeight="1" s="36"/>
-    <row r="585" ht="14.25" customHeight="1" s="36"/>
-    <row r="586" ht="14.25" customHeight="1" s="36"/>
-    <row r="587" ht="14.25" customHeight="1" s="36"/>
-    <row r="588" ht="14.25" customHeight="1" s="36"/>
-    <row r="589" ht="14.25" customHeight="1" s="36"/>
-    <row r="590" ht="14.25" customHeight="1" s="36"/>
-    <row r="591" ht="14.25" customHeight="1" s="36"/>
-    <row r="592" ht="14.25" customHeight="1" s="36"/>
-    <row r="593" ht="14.25" customHeight="1" s="36"/>
-    <row r="594" ht="14.25" customHeight="1" s="36"/>
-    <row r="595" ht="14.25" customHeight="1" s="36"/>
-    <row r="596" ht="14.25" customHeight="1" s="36"/>
-    <row r="597" ht="14.25" customHeight="1" s="36"/>
-    <row r="598" ht="14.25" customHeight="1" s="36"/>
-    <row r="599" ht="14.25" customHeight="1" s="36"/>
-    <row r="600" ht="14.25" customHeight="1" s="36"/>
-    <row r="601" ht="14.25" customHeight="1" s="36"/>
-    <row r="602" ht="14.25" customHeight="1" s="36"/>
-    <row r="603" ht="14.25" customHeight="1" s="36"/>
-    <row r="604" ht="14.25" customHeight="1" s="36"/>
-    <row r="605" ht="14.25" customHeight="1" s="36"/>
-    <row r="606" ht="14.25" customHeight="1" s="36"/>
-    <row r="607" ht="14.25" customHeight="1" s="36"/>
-    <row r="608" ht="14.25" customHeight="1" s="36"/>
-    <row r="609" ht="14.25" customHeight="1" s="36"/>
-    <row r="610" ht="14.25" customHeight="1" s="36"/>
-    <row r="611" ht="14.25" customHeight="1" s="36"/>
-    <row r="612" ht="14.25" customHeight="1" s="36"/>
-    <row r="613" ht="14.25" customHeight="1" s="36"/>
-    <row r="614" ht="14.25" customHeight="1" s="36"/>
-    <row r="615" ht="14.25" customHeight="1" s="36"/>
-    <row r="616" ht="14.25" customHeight="1" s="36"/>
-    <row r="617" ht="14.25" customHeight="1" s="36"/>
-    <row r="618" ht="14.25" customHeight="1" s="36"/>
-    <row r="619" ht="14.25" customHeight="1" s="36"/>
-    <row r="620" ht="14.25" customHeight="1" s="36"/>
-    <row r="621" ht="14.25" customHeight="1" s="36"/>
-    <row r="622" ht="14.25" customHeight="1" s="36"/>
-    <row r="623" ht="14.25" customHeight="1" s="36"/>
-    <row r="624" ht="14.25" customHeight="1" s="36"/>
-    <row r="625" ht="14.25" customHeight="1" s="36"/>
-    <row r="626" ht="14.25" customHeight="1" s="36"/>
-    <row r="627" ht="14.25" customHeight="1" s="36"/>
-    <row r="628" ht="14.25" customHeight="1" s="36"/>
-    <row r="629" ht="14.25" customHeight="1" s="36"/>
-    <row r="630" ht="14.25" customHeight="1" s="36"/>
-    <row r="631" ht="14.25" customHeight="1" s="36"/>
-    <row r="632" ht="14.25" customHeight="1" s="36"/>
-    <row r="633" ht="14.25" customHeight="1" s="36"/>
-    <row r="634" ht="14.25" customHeight="1" s="36"/>
+    <row r="575" ht="14.25" customHeight="1" s="36">
+      <c r="A575" s="37" t="inlineStr">
+        <is>
+          <t>WH1</t>
+        </is>
+      </c>
+      <c r="B575" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C575" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D575" s="39" t="inlineStr">
+        <is>
+          <t>ถ้าจะเรียนวิชาพื้นฐานการเรียนรู้เชิงลึก ต้องผ่านวิชาอะไรมาก่อนบ้าง นับรวมวิชาที่เป็นพื้นฐานของวิชานั้นด้วย</t>
+        </is>
+      </c>
+      <c r="E575" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F575" s="39" t="inlineStr">
+        <is>
+          <t>06046401 และก่อนหน้านั้น 06046400</t>
+        </is>
+      </c>
+      <c r="G575" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06046406 พื้นฐานการเรียนรู้เชิงลึก (FUNDAMENTALS OF DEEP LEARNING) — ปีที่ 2 ภาคการศึกษาที่ 1
+วิชาที่ต้องสอบผ่านก่อน (↳ = วิชาที่ต้องผ่านก่อนวิชาด้านบนอีกชั้น):
+  • 06046401 แคลคูลัส 2 (CALCULUS 2) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 2
+    ↳ 06046400 แคลคูลัส 1 (CALCULUS 1) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 1
+  • 06046402 พีชคณิตเชิงเส้น (LINEAR ALGEBRA) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 1
+รวมต้องผ่านก่อน 3 วิชา</t>
+        </is>
+      </c>
+      <c r="H575" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 37, 19, 292, 23, 287, 20, 24, 288</t>
+        </is>
+      </c>
+      <c r="I575" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (วิชาบังคับก่อนไล่หลายชั้น) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J575" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K575" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L575" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M575" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N575" s="39" t="inlineStr">
+        <is>
+          <t>0.02s</t>
+        </is>
+      </c>
+      <c r="O575" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="576" ht="14.25" customHeight="1" s="36">
+      <c r="A576" s="37" t="inlineStr">
+        <is>
+          <t>WH2</t>
+        </is>
+      </c>
+      <c r="B576" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C576" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D576" s="39" t="inlineStr">
+        <is>
+          <t>ขอลงวิชาพื้นฐานการเรียนรู้เชิงลึกตั้งแต่ปี 1 ได้หรือเปล่า</t>
+        </is>
+      </c>
+      <c r="E576" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F576" s="39" t="inlineStr">
+        <is>
+          <t>ตามแผนเรียนปี 2 ภาค 1 ต้องผ่าน 06046401 ก่อน</t>
+        </is>
+      </c>
+      <c r="G576" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ไม่ได้ — ต้องสอบผ่าน 06046401 แคลคูลัส 2 ก่อน ซึ่งตามแผนเรียนในปีที่ 1 ภาคการศึกษาที่ 2 จึงยังไม่ผ่านวิชานี้ก่อนเริ่มปี 1
+วิชา 06046406 พื้นฐานการเรียนรู้เชิงลึก (FUNDAMENTALS OF DEEP LEARNING) — 3(3-0-6) หน่วยกิต
+ตามแผนการศึกษา: ปีที่ 2 ภาคการศึกษาที่ 1
+วิชาบังคับก่อน (ต้องสอบผ่านก่อนจึงจะลงได้):
+  - 06046401 แคลคูลัส 2 (CALCULUS 2) — ปีที่ 1 ภาคการศึกษาที่ 2
+  - 06046402 พีชคณิตเชิงเส้น (LINEAR ALGEBRA) — ปีที่ 1 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H576" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 37, 292, 19, 20, 23, 24, 287, 288</t>
+        </is>
+      </c>
+      <c r="I576" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (ปีตามแผน + วิชาบังคับก่อน → ลงได้/ไม่ได้) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J576" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K576" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L576" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M576" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N576" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O576" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="577" ht="14.25" customHeight="1" s="36">
+      <c r="A577" s="37" t="inlineStr">
+        <is>
+          <t>WH3</t>
+        </is>
+      </c>
+      <c r="B577" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C577" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D577" s="39" t="inlineStr">
+        <is>
+          <t>ถ้าสอบตกวิชาพีชคณิตเชิงเส้น จะกระทบวิชาไหนบ้าง และวิชาเหล่านั้นเรียนปีไหน</t>
+        </is>
+      </c>
+      <c r="E577" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F577" s="39" t="inlineStr">
+        <is>
+          <t>06046406 (06046406 ปี 2 ภาค 1)</t>
+        </is>
+      </c>
+      <c r="G577" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06046402 พีชคณิตเชิงเส้น (LINEAR ALGEBRA) — ปีที่ 1 ภาคการศึกษาที่ 1
+  วิชาที่ต้องผ่านวิชานี้ก่อนจึงจะลงได้ (↳ = ต่อจากวิชาด้านบนอีกชั้น):
+    • 06046406 พื้นฐานการเรียนรู้เชิงลึก (FUNDAMENTALS OF DEEP LEARNING) — 3(3-0-6) | ปีที่ 2 ภาคการศึกษาที่ 1
+  ถ้ายังไม่ผ่านวิชานี้ จะลงวิชาข้างต้นไม่ได้จนกว่าจะผ่าน</t>
+        </is>
+      </c>
+      <c r="H577" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 37, 292, 19, 20, 23, 24, 288</t>
+        </is>
+      </c>
+      <c r="I577" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (prerequisite ทิศกลับ) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J577" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="K577" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L577" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M577" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N577" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O577" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="578" ht="14.25" customHeight="1" s="36">
+      <c r="A578" s="37" t="inlineStr">
+        <is>
+          <t>WH4</t>
+        </is>
+      </c>
+      <c r="B578" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C578" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D578" s="39" t="inlineStr">
+        <is>
+          <t>วิชาการประมวลผลภาษาธรรมชาติเบื้องต้นกับวิชาการวิเคราะห์และเพิ่มประสิทธิภาพเครือข่าย เรียนปีเดียวกันไหม</t>
+        </is>
+      </c>
+      <c r="E578" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F578" s="39" t="inlineStr">
+        <is>
+          <t>06046410 ปี 2 ภาค 2, 06046411 ปี 2 ภาค 2</t>
+        </is>
+      </c>
+      <c r="G578" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: เรียนปีและภาคเดียวกัน (ปีที่ 2 ภาคการศึกษาที่ 2)
+- 06046410 การประมวลผลภาษาธรรมชาติเบื้องต้น (INTRODUCTION TO NATURAL LANGUAGE PROCESSING) — ปีที่ 2 ภาคการศึกษาที่ 2
+- 06046411 การวิเคราะห์และเพิ่มประสิทธิภาพเครือข่าย (NETWORK ANALYSIS AND OPTIMIZATION) — ปีที่ 2 ภาคการศึกษาที่ 2</t>
+        </is>
+      </c>
+      <c r="H578" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 20, 24, 38, 293, 294</t>
+        </is>
+      </c>
+      <c r="I578" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (เทียบปี/ภาคของสองวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J578" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="K578" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L578" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M578" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N578" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O578" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="579" ht="14.25" customHeight="1" s="36">
+      <c r="A579" s="37" t="inlineStr">
+        <is>
+          <t>WH5</t>
+        </is>
+      </c>
+      <c r="B579" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C579" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D579" s="39" t="inlineStr">
+        <is>
+          <t>ขอลงวิชาโครงงานทางด้านเทคโนโลยีสารสนเทศเชิงธุรกิจ 2ตั้งแต่ปี 3 ได้หรือเปล่า</t>
+        </is>
+      </c>
+      <c r="E579" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F579" s="39" t="inlineStr">
+        <is>
+          <t>ตามแผนเรียนปี 4 ภาค 1 ต้องผ่าน 06036145 ก่อน</t>
+        </is>
+      </c>
+      <c r="G579" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ไม่ได้ — ต้องสอบผ่าน 06036145 โครงงานทางด้านเทคโนโลยีสารสนเทศเชิงธุรกิจ 1 ก่อน ซึ่งตามแผนเรียนในปีที่ 3 ภาคการศึกษาที่ 2 จึงยังไม่ผ่านวิชานี้ก่อนเริ่มปี 3
+วิชา 06036146 โครงงานทางด้านเทคโนโลยีสารสนเทศเชิงธุรกิจ 2 (PROJECT IN BUSINESS INFORMATION TECHNOLOGY 2) — 3(0-9-0) หน่วยกิต
+ตามแผนการศึกษา: ปีที่ 4 ภาคการศึกษาที่ 1
+วิชาบังคับก่อน (ต้องสอบผ่านก่อนจึงจะลงได้):
+  - 06036145 โครงงานทางด้านเทคโนโลยีสารสนเทศเชิงธุรกิจ 1 (PROJECT IN BUSINESS INFORMATION TECHNOLOGY 1) — ปีที่ 3 ภาคการศึกษาที่ 2</t>
+        </is>
+      </c>
+      <c r="H579" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 29, 76, 256, 269, 22, 23</t>
+        </is>
+      </c>
+      <c r="I579" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (ปีตามแผน + วิชาบังคับก่อน → ลงได้/ไม่ได้) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J579" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="K579" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L579" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M579" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N579" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O579" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="580" ht="14.25" customHeight="1" s="36">
+      <c r="A580" s="37" t="inlineStr">
+        <is>
+          <t>WH6</t>
+        </is>
+      </c>
+      <c r="B580" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C580" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D580" s="39" t="inlineStr">
+        <is>
+          <t>ถ้าสอบตกวิชาการสื่อสารด้วยภาพสำหรับธุรกิจ จะกระทบวิชาไหนบ้าง และวิชาเหล่านั้นเรียนปีไหน</t>
+        </is>
+      </c>
+      <c r="E580" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F580" s="39" t="inlineStr">
+        <is>
+          <t>06036114 (06036114 ปี 3 ภาค 1)</t>
+        </is>
+      </c>
+      <c r="G580" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06036122 การสื่อสารด้วยภาพสำหรับธุรกิจ (VISUAL COMMUNICATION FOR BUSINESS) — ปีที่ 2 ภาคการศึกษาที่ 1
+  วิชาที่ต้องผ่านวิชานี้ก่อนจึงจะลงได้ (↳ = ต่อจากวิชาด้านบนอีกชั้น):
+    • 06036114 การพัฒนาเว็บแอปพลิเคชันโดยใช้เฟรมเวิร์ก (WEB APPLICATION DEVELOPMENT USING FRAMEWORKS) — 3(2-2-5) | ปีที่ 3 ภาคการศึกษาที่ 1
+  ถ้ายังไม่ผ่านวิชานี้ จะลงวิชาข้างต้นไม่ได้จนกว่าจะผ่าน</t>
+        </is>
+      </c>
+      <c r="H580" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 75, 22, 23, 27, 28, 244, 247, 269</t>
+        </is>
+      </c>
+      <c r="I580" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (prerequisite ทิศกลับ) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J580" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K580" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L580" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M580" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N580" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O580" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="581" ht="14.25" customHeight="1" s="36">
+      <c r="A581" s="37" t="inlineStr">
+        <is>
+          <t>WH7</t>
+        </is>
+      </c>
+      <c r="B581" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C581" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D581" s="39" t="inlineStr">
+        <is>
+          <t>วิชาการวิเคราะห์เชิงสถิติสำหรับธุรกิจกับวิชาบัญชีการเงินสำหรับผู้มิใช่นักบัญชี เรียนปีเดียวกันไหม</t>
+        </is>
+      </c>
+      <c r="E581" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F581" s="39" t="inlineStr">
+        <is>
+          <t>06036102 ปี 1 ภาค 2, 06036105 ปี 2 ภาค 1</t>
+        </is>
+      </c>
+      <c r="G581" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: เรียนคนละปี — การวิเคราะห์เชิงสถิติสำหรับธุรกิจ เรียนก่อน
+- 06036102 การวิเคราะห์เชิงสถิติสำหรับธุรกิจ (STATISTICAL ANALYSIS FOR BUSINESS) — ปีที่ 1 ภาคการศึกษาที่ 2
+- 06036105 บัญชีการเงินสำหรับผู้มิใช่นักบัญชี (FINANCIAL ACCOUNTING FOR NON-ACCOUNTANTS) — ปีที่ 2 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H581" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 74, 21, 22, 27, 32, 239, 240, 268</t>
+        </is>
+      </c>
+      <c r="I581" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (เทียบปี/ภาคของสองวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J581" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K581" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L581" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M581" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N581" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O581" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="582" ht="14.25" customHeight="1" s="36">
+      <c r="A582" s="37" t="inlineStr">
+        <is>
+          <t>WH8</t>
+        </is>
+      </c>
+      <c r="B582" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C582" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D582" s="39" t="inlineStr">
+        <is>
+          <t>ขอลงวิชาโครงงานวิทยาการข้อมูลและการวิเคราะห์เชิงธุรกิจ 2ตั้งแต่ปี 3 ได้หรือเปล่า</t>
+        </is>
+      </c>
+      <c r="E582" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F582" s="39" t="inlineStr">
+        <is>
+          <t>ตามแผนเรียนปี 4 ภาค 1 ต้องผ่าน 06026214 ก่อน</t>
+        </is>
+      </c>
+      <c r="G582" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ไม่ได้ — ต้องสอบผ่าน 06026214 โครงงานวิทยาการข้อมูลและการวิเคราะห์เชิงธุรกิจ 1 ก่อน ซึ่งตามแผนเรียนในปีที่ 3 ภาคการศึกษาที่ 2 จึงยังไม่ผ่านวิชานี้ก่อนเริ่มปี 3
+วิชา 06026215 โครงงานวิทยาการข้อมูลและการวิเคราะห์เชิงธุรกิจ 2 (PROJECT IN DATA SCIENCE AND BUSINESS ANALYTICS 2) — 3(0-9-0) หน่วยกิต
+ตามแผนการศึกษา: ปีที่ 4 ภาคการศึกษาที่ 1
+วิชาบังคับก่อน (ต้องสอบผ่านก่อนจึงจะลงได้):
+  - 06026214 โครงงานวิทยาการข้อมูลและการวิเคราะห์เชิงธุรกิจ 1 (PROJECT IN DATA SCIENCE AND BUSINESS ANALYTICS 1) — ปีที่ 3 ภาคการศึกษาที่ 2</t>
+        </is>
+      </c>
+      <c r="H582" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 19, 69, 325, 354, 28, 29, 35, 36</t>
+        </is>
+      </c>
+      <c r="I582" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (ปีตามแผน + วิชาบังคับก่อน → ลงได้/ไม่ได้) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J582" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K582" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L582" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M582" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N582" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O582" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="583" ht="14.25" customHeight="1" s="36">
+      <c r="A583" s="37" t="inlineStr">
+        <is>
+          <t>WH9</t>
+        </is>
+      </c>
+      <c r="B583" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C583" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D583" s="39" t="inlineStr">
+        <is>
+          <t>ถ้าสอบตกวิชาแนวคิดระบบฐานข้อมูล จะกระทบวิชาไหนบ้าง และวิชาเหล่านั้นเรียนปีไหน</t>
+        </is>
+      </c>
+      <c r="E583" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F583" s="39" t="inlineStr">
+        <is>
+          <t>06026212, 06026213 (06026212 ปี 3 ภาค 1)</t>
+        </is>
+      </c>
+      <c r="G583" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06066300 แนวคิดระบบฐานข้อมูล (DATABASE SYSTEM CONCEPTS) — ปีที่ 2 ภาคการศึกษาที่ 1
+  วิชาที่ต้องผ่านวิชานี้ก่อนจึงจะลงได้ (↳ = ต่อจากวิชาด้านบนอีกชั้น):
+    • 06026212 การสร้างคลังข้อมูล (DATA WAREHOUSING) — 3(2-2-5) | ปีที่ 3 ภาคการศึกษาที่ 1
+    • 06026213 ระบบข้อมูลมหัต (BIG DATA SYSTEMS) — 3(2-2-5) | ปีที่ 3 ภาคการศึกษาที่ 2
+  ถ้ายังไม่ผ่านวิชานี้ จะลงวิชาข้างต้นไม่ได้จนกว่าจะผ่าน</t>
+        </is>
+      </c>
+      <c r="H583" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 69, 323, 354, 18, 19, 25, 27, 28</t>
+        </is>
+      </c>
+      <c r="I583" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (prerequisite ทิศกลับ) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J583" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K583" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L583" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M583" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N583" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O583" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="584" ht="14.25" customHeight="1" s="36">
+      <c r="A584" s="37" t="inlineStr">
+        <is>
+          <t>WH10</t>
+        </is>
+      </c>
+      <c r="B584" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C584" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D584" s="39" t="inlineStr">
+        <is>
+          <t>วิชาผู้ประกอบการสมัยใหม่กับวิชาพื้นฐานวิทยาการข้อมูล เรียนปีเดียวกันไหม</t>
+        </is>
+      </c>
+      <c r="E584" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F584" s="39" t="inlineStr">
+        <is>
+          <t>90643021 ปี 3 ภาค 2, 06026208 ปี 2 ภาค 2</t>
+        </is>
+      </c>
+      <c r="G584" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: เรียนคนละปี — พื้นฐานวิทยาการข้อมูล เรียนก่อน
+- 90643021 ผู้ประกอบการสมัยใหม่ (MODERN ENTREPRENEURS) — ปีที่ 3 ภาคการศึกษาที่ 2
+- 06026208 พื้นฐานวิทยาการข้อมูล (FUNDAMENTALS OF DATA SCIENCE) — ปีที่ 2 ภาคการศึกษาที่ 2</t>
+        </is>
+      </c>
+      <c r="H584" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 16, 18, 26, 28, 33, 35, 68, 322</t>
+        </is>
+      </c>
+      <c r="I584" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (เทียบปี/ภาคของสองวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J584" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K584" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L584" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M584" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N584" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O584" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="585" ht="14.25" customHeight="1" s="36">
+      <c r="A585" s="37" t="inlineStr">
+        <is>
+          <t>WH11</t>
+        </is>
+      </c>
+      <c r="B585" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C585" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D585" s="39" t="inlineStr">
+        <is>
+          <t>ขอลงวิชาโครงสร้างพื้นฐานเครือข่ายการสื่อสารตั้งแต่ปี 1 ได้หรือเปล่า</t>
+        </is>
+      </c>
+      <c r="E585" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F585" s="39" t="inlineStr">
+        <is>
+          <t>ตามแผนเรียนปี 2 ภาค 2 ต้องผ่าน 06016413 ก่อน</t>
+        </is>
+      </c>
+      <c r="G585" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ไม่ได้ — ต้องสอบผ่าน 06016413 ระบบเครือข่ายเบื้องต้น ก่อน ซึ่งตามแผนเรียนในปีที่ 2 ภาคการศึกษาที่ 1 จึงยังไม่ผ่านวิชานี้ก่อนเริ่มปี 1
+วิชา 06016419 โครงสร้างพื้นฐานเครือข่ายการสื่อสาร (COMMUNICATION NETWORK INFRASTRUCTURE) — 3(2-2-5) หน่วยกิต
+ตามแผนการศึกษา: ปีที่ 2 ภาคการศึกษาที่ 2
+วิชาบังคับก่อน (ต้องสอบผ่านก่อนจึงจะลงได้):
+  - 06016413 ระบบเครือข่ายเบื้องต้น (INTRODUCTION TO NETWORK SYSTEMS) — ปีที่ 2 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H585" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 84, 24, 25, 33, 34, 40, 328, 331</t>
+        </is>
+      </c>
+      <c r="I585" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (ปีตามแผน + วิชาบังคับก่อน → ลงได้/ไม่ได้) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J585" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K585" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L585" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M585" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N585" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O585" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="586" ht="14.25" customHeight="1" s="36">
+      <c r="A586" s="37" t="inlineStr">
+        <is>
+          <t>WH12</t>
+        </is>
+      </c>
+      <c r="B586" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C586" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D586" s="39" t="inlineStr">
+        <is>
+          <t>ถ้าสอบตกวิชาการสร้างโปรแกรมเชิงวัตถุ จะกระทบวิชาไหนบ้าง และวิชาเหล่านั้นเรียนปีไหน</t>
+        </is>
+      </c>
+      <c r="E586" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F586" s="39" t="inlineStr">
+        <is>
+          <t>06016418 (06016418 ปี 3 ภาค 1)</t>
+        </is>
+      </c>
+      <c r="G586" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06016408 การสร้างโปรแกรมเชิงวัตถุ (OBJECT-ORIENTED PROGRAMMING) — ปีที่ 1 ภาคการศึกษาที่ 2
+  วิชาที่ต้องผ่านวิชานี้ก่อนจึงจะลงได้ (↳ = ต่อจากวิชาด้านบนอีกชั้น):
+    • 06016418 การพัฒนาเว็บฝั่งเซิร์ฟเวอร์ (SERVER-SIDE WEB DEVELOPMENT) — 3(2-2-5) | ปีที่ 3 ภาคการศึกษาที่ 1
+  ถ้ายังไม่ผ่านวิชานี้ จะลงวิชาข้างต้นไม่ได้จนกว่าจะผ่าน</t>
+        </is>
+      </c>
+      <c r="H586" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 331, 24, 25, 26, 32, 35, 39, 83</t>
+        </is>
+      </c>
+      <c r="I586" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (prerequisite ทิศกลับ) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J586" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K586" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L586" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M586" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N586" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O586" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="587" ht="14.25" customHeight="1" s="36">
+      <c r="A587" s="37" t="inlineStr">
+        <is>
+          <t>WH13</t>
+        </is>
+      </c>
+      <c r="B587" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C587" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D587" s="39" t="inlineStr">
+        <is>
+          <t>วิชาพื้นฐานการออกแบบทัศนศิลป์สำหรับสื่อปฏิสัมพันธ์กับวิชาผู้ประกอบการสมัยใหม่ เรียนปีเดียวกันไหม</t>
+        </is>
+      </c>
+      <c r="E587" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F587" s="39" t="inlineStr">
+        <is>
+          <t>06016425 ปี 2 ภาค 2, 90643021 ปี 4 ภาค 1</t>
+        </is>
+      </c>
+      <c r="G587" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: เรียนคนละปี — พื้นฐานการออกแบบทัศนศิลป์สำหรับสื่อปฏิสัมพันธ์ เรียนก่อน
+- 06016425 พื้นฐานการออกแบบทัศนศิลป์สำหรับสื่อปฏิสัมพันธ์ (VISUAL DESIGN FUNDAMENTALS FOR INTERACTIVE MEDIA) — ปีที่ 2 ภาคการศึกษาที่ 2
+- 90643021 ผู้ประกอบการสมัยใหม่ (MODERN ENTREPRENEURS) — ปีที่ 4 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H587" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 22, 26, 34, 37, 43, 84, 268, 334</t>
+        </is>
+      </c>
+      <c r="I587" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (เทียบปี/ภาคของสองวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J587" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K587" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L587" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M587" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N587" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O587" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="588" ht="14.25" customHeight="1" s="36">
+      <c r="A588" s="37" t="inlineStr">
+        <is>
+          <t>WH14</t>
+        </is>
+      </c>
+      <c r="B588" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C588" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D588" s="39" t="inlineStr">
+        <is>
+          <t>ปี 4 เทอม 2 ถ้าเลือกแผนสหกิจ จะเรียนต่างจากแผนปกติอย่างไร</t>
+        </is>
+      </c>
+      <c r="E588" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F588" s="39" t="inlineStr">
+        <is>
+          <t>06036147</t>
+        </is>
+      </c>
+      <c r="G588" s="39" t="inlineStr">
+        <is>
+          <t>แผนปกติ (ไม่เข้าโครงการสหกิจศึกษา) — ปีที่ 4 ภาคการศึกษาที่ 2 (หน้า 30):
+  - วิชาเลือกที่ต้องลงตามแผน: 2 ช่อง
+      • วิชาเลือกทางเทคโนโลยีสารสนเทศทางธุรกิจ 1
+      • วิชาเลือกทางเทคโนโลยีสารสนเทศทางธุรกิจ 2
+  รวมภาคนี้ตามแผนในเล่ม: 12 หน่วยกิต
+แผนที่เข้าโครงการสหกิจศึกษา — ปีที่ 4 ภาคการศึกษาที่ 2 (หน้า 35):
+  - 06036147 สหกิจศึกษา — 6(0-35-0)
+  - 06036148 สหกิจศึกษาต่างประเทศ — 6(0-35-0)
+  รวมภาคนี้ตามแผนในเล่ม: 6 หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="H588" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 30, 35</t>
+        </is>
+      </c>
+      <c r="I588" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ตารางแผนปกติ/แผนสหกิจ) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J588" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K588" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L588" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M588" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_coop.json เทียบ BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N588" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O588" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="589" ht="14.25" customHeight="1" s="36">
+      <c r="A589" s="37" t="inlineStr">
+        <is>
+          <t>WC1</t>
+        </is>
+      </c>
+      <c r="B589" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C589" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D589" s="39" t="inlineStr">
+        <is>
+          <t>นักศึกษา IT เก็บได้ 123 หน่วยกิต เกรดเฉลี่ยสะสม 2.45 จบได้หรือยัง ถ้ายังต้องเก็บเพิ่มอีกกี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E589" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F589" s="39" t="inlineStr">
+        <is>
+          <t>ยังไม่จบ ต้องครบ 129 ขาด 6</t>
+        </is>
+      </c>
+      <c r="G589" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ยังจบไม่ได้
+หลักสูตร IT 2565 (ปริญญาตรี) ต้องเรียนครบไม่น้อยกว่า 129 หน่วยกิต (หน้า 6)
+- หน่วยกิต: เก็บได้ 123 หน่วยกิต → ยังขาดอีก 6 หน่วยกิต (ต้องครบ 129)
+- เกรดเฉลี่ยสะสม 2.45 → ผ่านเกณฑ์ขั้นต่ำ 2.00 (ข้อ 34)
+- เงื่อนไขอื่นตามข้อ 34: สอบผ่านทุกรายวิชาตามโครงสร้างหลักสูตร และผ่านการสอบภาษาอังกฤษ (English Exit exam)</t>
+        </is>
+      </c>
+      <c r="H589" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 6, 88</t>
+        </is>
+      </c>
+      <c r="I589" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวม + เกรดขั้นต่ำ ข้อ 34) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J589" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K589" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L589" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M589" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N589" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O589" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="590" ht="14.25" customHeight="1" s="36">
+      <c r="A590" s="37" t="inlineStr">
+        <is>
+          <t>WC2</t>
+        </is>
+      </c>
+      <c r="B590" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C590" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D590" s="39" t="inlineStr">
+        <is>
+          <t>ถ้าเกรดเฉลี่ยสะสม 1.95 แต่เรียนครบ 129 หน่วยกิตแล้ว จะจบการศึกษาได้ไหม</t>
+        </is>
+      </c>
+      <c r="E590" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F590" s="39" t="inlineStr">
+        <is>
+          <t>ไม่ได้ ต้องได้ไม่ต่ำกว่า 2.00</t>
+        </is>
+      </c>
+      <c r="G590" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ยังจบไม่ได้
+หลักสูตร IT 2565 (ปริญญาตรี) ต้องเรียนครบไม่น้อยกว่า 129 หน่วยกิต (หน้า 6)
+- หน่วยกิต: เก็บได้ 129 หน่วยกิต → ครบเกณฑ์ 129 หน่วยกิต
+- เกรดเฉลี่ยสะสม 1.95 → ต่ำกว่าเกณฑ์ขั้นต่ำ 2.00 (ข้อ 34) จึงยังจบไม่ได้ และเกรดเฉลี่ยสะสมต่ำกว่า 2.00 ต้องถูกภาคทัณฑ์ (ข้อ 31)
+- เงื่อนไขอื่นตามข้อ 34: สอบผ่านทุกรายวิชาตามโครงสร้างหลักสูตร และผ่านการสอบภาษาอังกฤษ (English Exit exam)</t>
+        </is>
+      </c>
+      <c r="H590" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 6, 88</t>
+        </is>
+      </c>
+      <c r="I590" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวม + เกรดขั้นต่ำ ข้อ 34) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J590" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K590" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L590" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M590" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N590" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O590" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="591" ht="14.25" customHeight="1" s="36">
+      <c r="A591" s="37" t="inlineStr">
+        <is>
+          <t>WC3</t>
+        </is>
+      </c>
+      <c r="B591" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C591" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D591" s="39" t="inlineStr">
+        <is>
+          <t>นักศึกษา DSBA เก็บได้ 126 หน่วยกิต เกรดเฉลี่ยสะสม 2.45 จบได้หรือยัง ถ้ายังต้องเก็บเพิ่มอีกกี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E591" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F591" s="39" t="inlineStr">
+        <is>
+          <t>ยังไม่จบ ต้องครบ 132 ขาด 6</t>
+        </is>
+      </c>
+      <c r="G591" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ยังจบไม่ได้
+หลักสูตร DSBA 2565 (ปริญญาตรี) ต้องเรียนครบไม่น้อยกว่า 132 หน่วยกิต (หน้า 2)
+- หน่วยกิต: เก็บได้ 126 หน่วยกิต → ยังขาดอีก 6 หน่วยกิต (ต้องครบ 132)
+- เกรดเฉลี่ยสะสม 2.45 → ผ่านเกณฑ์ขั้นต่ำ 2.00 (ข้อ 34)
+- เงื่อนไขอื่นตามข้อ 34: สอบผ่านทุกรายวิชาตามโครงสร้างหลักสูตร และผ่านการสอบภาษาอังกฤษ (English Exit exam)</t>
+        </is>
+      </c>
+      <c r="H591" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 2, 88</t>
+        </is>
+      </c>
+      <c r="I591" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวม + เกรดขั้นต่ำ ข้อ 34) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J591" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K591" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L591" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M591" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N591" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O591" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="592" ht="14.25" customHeight="1" s="36">
+      <c r="A592" s="37" t="inlineStr">
+        <is>
+          <t>WC4</t>
+        </is>
+      </c>
+      <c r="B592" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C592" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D592" s="39" t="inlineStr">
+        <is>
+          <t>ถ้าเกรดเฉลี่ยสะสม 1.95 แต่เรียนครบ 132 หน่วยกิตแล้ว จะจบการศึกษาได้ไหม</t>
+        </is>
+      </c>
+      <c r="E592" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F592" s="39" t="inlineStr">
+        <is>
+          <t>ไม่ได้ ต้องได้ไม่ต่ำกว่า 2.00</t>
+        </is>
+      </c>
+      <c r="G592" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ยังจบไม่ได้
+หลักสูตร DSBA 2565 (ปริญญาตรี) ต้องเรียนครบไม่น้อยกว่า 132 หน่วยกิต (หน้า 2)
+- หน่วยกิต: เก็บได้ 132 หน่วยกิต → ครบเกณฑ์ 132 หน่วยกิต
+- เกรดเฉลี่ยสะสม 1.95 → ต่ำกว่าเกณฑ์ขั้นต่ำ 2.00 (ข้อ 34) จึงยังจบไม่ได้ และเกรดเฉลี่ยสะสมต่ำกว่า 2.00 ต้องถูกภาคทัณฑ์ (ข้อ 31)
+- เงื่อนไขอื่นตามข้อ 34: สอบผ่านทุกรายวิชาตามโครงสร้างหลักสูตร และผ่านการสอบภาษาอังกฤษ (English Exit exam)</t>
+        </is>
+      </c>
+      <c r="H592" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 2, 88</t>
+        </is>
+      </c>
+      <c r="I592" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวม + เกรดขั้นต่ำ ข้อ 34) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J592" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K592" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L592" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M592" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N592" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O592" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="593" ht="14.25" customHeight="1" s="36">
+      <c r="A593" s="37" t="inlineStr">
+        <is>
+          <t>WC5</t>
+        </is>
+      </c>
+      <c r="B593" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C593" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D593" s="39" t="inlineStr">
+        <is>
+          <t>นักศึกษา AIT เก็บได้ 114 หน่วยกิต เกรดเฉลี่ยสะสม 2.45 จบได้หรือยัง ถ้ายังต้องเก็บเพิ่มอีกกี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E593" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F593" s="39" t="inlineStr">
+        <is>
+          <t>ยังไม่จบ ต้องครบ 120 ขาด 6</t>
+        </is>
+      </c>
+      <c r="G593" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ยังจบไม่ได้
+หลักสูตร AIT 2566 (ปริญญาตรี) ต้องเรียนครบไม่น้อยกว่า 120 หน่วยกิต (หน้า 5)
+- หน่วยกิต: เก็บได้ 114 หน่วยกิต → ยังขาดอีก 6 หน่วยกิต (ต้องครบ 120)
+- เกรดเฉลี่ยสะสม 2.45 → ผ่านเกณฑ์ขั้นต่ำ 2.00 (ข้อ 34)
+- เงื่อนไขอื่นตามข้อ 34: สอบผ่านทุกรายวิชาตามโครงสร้างหลักสูตร และผ่านการสอบภาษาอังกฤษ (English Exit exam)</t>
+        </is>
+      </c>
+      <c r="H593" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 5, 88</t>
+        </is>
+      </c>
+      <c r="I593" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวม + เกรดขั้นต่ำ ข้อ 34) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J593" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K593" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L593" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M593" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N593" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O593" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="594" ht="14.25" customHeight="1" s="36">
+      <c r="A594" s="37" t="inlineStr">
+        <is>
+          <t>WC6</t>
+        </is>
+      </c>
+      <c r="B594" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C594" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D594" s="39" t="inlineStr">
+        <is>
+          <t>ถ้าเกรดเฉลี่ยสะสม 1.95 แต่เรียนครบ 120 หน่วยกิตแล้ว จะจบการศึกษาได้ไหม</t>
+        </is>
+      </c>
+      <c r="E594" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F594" s="39" t="inlineStr">
+        <is>
+          <t>ไม่ได้ ต้องได้ไม่ต่ำกว่า 2.00</t>
+        </is>
+      </c>
+      <c r="G594" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ยังจบไม่ได้
+หลักสูตร AIT 2566 (ปริญญาตรี) ต้องเรียนครบไม่น้อยกว่า 120 หน่วยกิต (หน้า 5)
+- หน่วยกิต: เก็บได้ 120 หน่วยกิต → ครบเกณฑ์ 120 หน่วยกิต
+- เกรดเฉลี่ยสะสม 1.95 → ต่ำกว่าเกณฑ์ขั้นต่ำ 2.00 (ข้อ 34) จึงยังจบไม่ได้ และเกรดเฉลี่ยสะสมต่ำกว่า 2.00 ต้องถูกภาคทัณฑ์ (ข้อ 31)
+- เงื่อนไขอื่นตามข้อ 34: สอบผ่านทุกรายวิชาตามโครงสร้างหลักสูตร และผ่านการสอบภาษาอังกฤษ (English Exit exam)</t>
+        </is>
+      </c>
+      <c r="H594" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 5, 88</t>
+        </is>
+      </c>
+      <c r="I594" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวม + เกรดขั้นต่ำ ข้อ 34) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J594" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K594" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L594" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M594" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N594" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O594" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="595" ht="14.25" customHeight="1" s="36">
+      <c r="A595" s="37" t="inlineStr">
+        <is>
+          <t>WC7</t>
+        </is>
+      </c>
+      <c r="B595" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C595" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D595" s="39" t="inlineStr">
+        <is>
+          <t>หลักสูตร IT กับ DSBA ต้องเรียนหน่วยกิตรวมต่างกันกี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E595" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F595" s="39" t="inlineStr">
+        <is>
+          <t>IT 129, DSBA 132</t>
+        </is>
+      </c>
+      <c r="G595" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ต่างกัน 3 หน่วยกิต (DSBA 2565 (ปริญญาตรี) มากกว่า IT 2565 (ปริญญาตรี))
+- IT 2565 (ปริญญาตรี): ไม่น้อยกว่า 129 หน่วยกิต (หน้า 6)
+- DSBA 2565 (ปริญญาตรี): ไม่น้อยกว่า 132 หน่วยกิต (หน้า 2)</t>
+        </is>
+      </c>
+      <c r="H595" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 6, 2</t>
+        </is>
+      </c>
+      <c r="I595" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวมข้ามหลักสูตร) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J595" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K595" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L595" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M595" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N595" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O595" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="596" ht="14.25" customHeight="1" s="36">
+      <c r="A596" s="37" t="inlineStr">
+        <is>
+          <t>WC8</t>
+        </is>
+      </c>
+      <c r="B596" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C596" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D596" s="39" t="inlineStr">
+        <is>
+          <t>หลักสูตร AIT กับ IT ต้องเรียนหน่วยกิตรวมต่างกันกี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E596" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F596" s="39" t="inlineStr">
+        <is>
+          <t>AIT 120, IT 129</t>
+        </is>
+      </c>
+      <c r="G596" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ต่างกัน 9 หน่วยกิต (IT 2565 (ปริญญาตรี) มากกว่า AIT 2566 (ปริญญาตรี))
+- AIT 2566 (ปริญญาตรี): ไม่น้อยกว่า 120 หน่วยกิต (หน้า 5)
+- IT 2565 (ปริญญาตรี): ไม่น้อยกว่า 129 หน่วยกิต (หน้า 6)</t>
+        </is>
+      </c>
+      <c r="H596" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 5, 6</t>
+        </is>
+      </c>
+      <c r="I596" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวมข้ามหลักสูตร) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J596" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K596" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L596" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M596" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N596" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O596" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="597" ht="14.25" customHeight="1" s="36">
+      <c r="A597" s="37" t="inlineStr">
+        <is>
+          <t>WC9</t>
+        </is>
+      </c>
+      <c r="B597" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C597" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D597" s="39" t="inlineStr">
+        <is>
+          <t>หลักสูตร DSBA กับ AIT ต้องเรียนหน่วยกิตรวมต่างกันกี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E597" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F597" s="39" t="inlineStr">
+        <is>
+          <t>DSBA 132, AIT 120</t>
+        </is>
+      </c>
+      <c r="G597" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ต่างกัน 12 หน่วยกิต (DSBA 2565 (ปริญญาตรี) มากกว่า AIT 2566 (ปริญญาตรี))
+- DSBA 2565 (ปริญญาตรี): ไม่น้อยกว่า 132 หน่วยกิต (หน้า 2)
+- AIT 2566 (ปริญญาตรี): ไม่น้อยกว่า 120 หน่วยกิต (หน้า 5)</t>
+        </is>
+      </c>
+      <c r="H597" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 2, 5</t>
+        </is>
+      </c>
+      <c r="I597" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวมข้ามหลักสูตร) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J597" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K597" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L597" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M597" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N597" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O597" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="598" ht="14.25" customHeight="1" s="36">
+      <c r="A598" s="37" t="inlineStr">
+        <is>
+          <t>WC10</t>
+        </is>
+      </c>
+      <c r="B598" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C598" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D598" s="39" t="inlineStr">
+        <is>
+          <t>จบด้วยเกรดเฉลี่ย 3.60 จะได้เกียรตินิยมอันดับไหน</t>
+        </is>
+      </c>
+      <c r="E598" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F598" s="39" t="inlineStr">
+        <is>
+          <t>อันดับ 1 (&gt;= 3.50)</t>
+        </is>
+      </c>
+      <c r="G598" s="39" t="inlineStr">
+        <is>
+          <t>ปริญญาเกียรตินิยม — ข้อ 36 ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 88, 89
+(ข้อบังคับของสถาบัน ใช้กับทุกหลักสูตรปริญญาตรี)
+- เกียรตินิยมอันดับหนึ่งและเหรียญทอง: ค่าระดับคะแนนเฉลี่ยสะสมตามโครงสร้างหลักสูตรสูงสุดในกลุ่มผู้สำเร็จการศึกษาปีเดียวกันของหลักสูตร และค่าระดับคะแนนเฉลี่ยสะสมไม่ต่ำกว่า 3.75 และต้องไม่เทียบโอนผลการเรียนจากสถาบันอื่น
+- เกียรตินิยมอันดับหนึ่ง: ค่าระดับคะแนนเฉลี่ยสะสมไม่ต่ำกว่า 3.50
+- เกียรตินิยมอันดับสอง: ค่าระดับคะแนนเฉลี่ยสะสมไม่ต่ำกว่า 3.25
+- กรณีโอนผลการเรียนจากสถาบันอื่น ทุกรายวิชาต้องได้ไม่ต่ำกว่า B หรือ S และต้องเรียนในหลักสูตรของสถาบันไม่น้อยกว่า 2 ใน 3 ของหน่วยกิตรวม
+- เงื่อนไขทั่วไป (ข้อ 36.1): เรียนไม่เกินระยะเวลาตามแผนการศึกษา · ไม่มีรายวิชาใดได้ F หรือ U · ไม่เคยเรียนซ้ำเพื่อเปลี่ยนเกรด · ไม่เคยลาพักเพราะไม่ลงทะเบียนตามกำหนด และไม่เคยถูกลงโทษทางวินัย</t>
+        </is>
+      </c>
+      <c r="H598" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 88, 89</t>
+        </is>
+      </c>
+      <c r="I598" s="39" t="inlineStr">
+        <is>
+          <t>ข้อบังคับปริญญาตรี (ภาคผนวกเล่ม AIT 2566) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J598" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K598" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L598" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M598" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N598" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O598" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="599" ht="14.25" customHeight="1" s="36">
+      <c r="A599" s="37" t="inlineStr">
+        <is>
+          <t>WC11</t>
+        </is>
+      </c>
+      <c r="B599" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C599" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D599" s="39" t="inlineStr">
+        <is>
+          <t>เกรดเฉลี่ยตอนจบ 3.30 ได้เกียรตินิยมไหม</t>
+        </is>
+      </c>
+      <c r="E599" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F599" s="39" t="inlineStr">
+        <is>
+          <t>อันดับ 2 (&gt;= 3.25)</t>
+        </is>
+      </c>
+      <c r="G599" s="39" t="inlineStr">
+        <is>
+          <t>ปริญญาเกียรตินิยม — ข้อ 36 ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 88, 89
+(ข้อบังคับของสถาบัน ใช้กับทุกหลักสูตรปริญญาตรี)
+- เกียรตินิยมอันดับหนึ่งและเหรียญทอง: ค่าระดับคะแนนเฉลี่ยสะสมตามโครงสร้างหลักสูตรสูงสุดในกลุ่มผู้สำเร็จการศึกษาปีเดียวกันของหลักสูตร และค่าระดับคะแนนเฉลี่ยสะสมไม่ต่ำกว่า 3.75 และต้องไม่เทียบโอนผลการเรียนจากสถาบันอื่น
+- เกียรตินิยมอันดับหนึ่ง: ค่าระดับคะแนนเฉลี่ยสะสมไม่ต่ำกว่า 3.50
+- เกียรตินิยมอันดับสอง: ค่าระดับคะแนนเฉลี่ยสะสมไม่ต่ำกว่า 3.25
+- กรณีโอนผลการเรียนจากสถาบันอื่น ทุกรายวิชาต้องได้ไม่ต่ำกว่า B หรือ S และต้องเรียนในหลักสูตรของสถาบันไม่น้อยกว่า 2 ใน 3 ของหน่วยกิตรวม
+- เงื่อนไขทั่วไป (ข้อ 36.1): เรียนไม่เกินระยะเวลาตามแผนการศึกษา · ไม่มีรายวิชาใดได้ F หรือ U · ไม่เคยเรียนซ้ำเพื่อเปลี่ยนเกรด · ไม่เคยลาพักเพราะไม่ลงทะเบียนตามกำหนด และไม่เคยถูกลงโทษทางวินัย</t>
+        </is>
+      </c>
+      <c r="H599" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 88, 89</t>
+        </is>
+      </c>
+      <c r="I599" s="39" t="inlineStr">
+        <is>
+          <t>ข้อบังคับปริญญาตรี (ภาคผนวกเล่ม AIT 2566) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J599" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K599" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L599" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M599" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N599" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O599" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="600" ht="14.25" customHeight="1" s="36">
+      <c r="A600" s="37" t="inlineStr">
+        <is>
+          <t>WC12</t>
+        </is>
+      </c>
+      <c r="B600" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C600" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D600" s="39" t="inlineStr">
+        <is>
+          <t>เทอมหน้าอยากลง 25 หน่วยกิตในภาคปกติ ทำได้ไหม</t>
+        </is>
+      </c>
+      <c r="E600" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F600" s="39" t="inlineStr">
+        <is>
+          <t>ไม่ได้ ภาคปกติสูงสุด 22</t>
+        </is>
+      </c>
+      <c r="G600" s="39" t="inlineStr">
+        <is>
+          <t>ไม่ได้  
+นักศึกษาทั่วไปต้องลงทะเบียนไม่เกิน 22 หน่วยกิตต่อภาคการศึกษาปกติ ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (หน้า 82) แม้จะเป็นนักศึกษาชั้นปีสุดท้ายก็ยังจำกัดที่ 27 หน่วยกิต แต่ต้องมีเหตุผลเฉพาะเจาะจง และต้องได้รับอนุมัติจากสภาวิชาการ ซึ่งไม่ได้ระบุว่าสามารถลง 25 หน่วยกิตได้โดยอัตโนมัติ</t>
+        </is>
+      </c>
+      <c r="H600" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 82</t>
+        </is>
+      </c>
+      <c r="I600" s="39" t="inlineStr">
+        <is>
+          <t>ข้อบังคับปริญญาตรี (ภาคผนวกเล่ม AIT 2566) → Typhoon เรียบเรียง</t>
+        </is>
+      </c>
+      <c r="J600" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K600" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L600" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M600" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N600" s="39" t="inlineStr">
+        <is>
+          <t>1.47s</t>
+        </is>
+      </c>
+      <c r="O600" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="601" ht="14.25" customHeight="1" s="36">
+      <c r="A601" s="37" t="inlineStr">
+        <is>
+          <t>WC13</t>
+        </is>
+      </c>
+      <c r="B601" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C601" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D601" s="39" t="inlineStr">
+        <is>
+          <t>ภาคปกติต้องลงทะเบียนอย่างน้อยกี่หน่วยกิต และมากสุดได้เท่าไร</t>
+        </is>
+      </c>
+      <c r="E601" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F601" s="39" t="inlineStr">
+        <is>
+          <t>9-22</t>
+        </is>
+      </c>
+      <c r="G601" s="39" t="inlineStr">
+        <is>
+          <t>การลงทะเบียนเรียน (หน่วยกิตต่อภาค) ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 82
+(ข้อบังคับของสถาบัน ใช้กับทุกหลักสูตรปริญญาตรี)
+- ภาคการศึกษาปกติ: ต้องลงทะเบียนไม่น้อยกว่า 9 หน่วยกิต และไม่เกิน 22 หน่วยกิต
+- ข้อยกเว้น: นักศึกษาชั้นปีสุดท้าย (หรือก่อนปีสุดท้ายที่ต้องไปฝึกสอนในปีสุดท้าย) ที่เหลือรายวิชาน้อยกว่า 9 หน่วยกิต หรือต้องลงมากกว่า 22 หน่วยกิตเพื่อสำเร็จการศึกษา ลงได้แต่ต้องไม่เกิน 27 หน่วยกิต
+- ภาคการศึกษาพิเศษ (ภาคฤดูร้อน): ลงทะเบียนได้ไม่เกิน 9 หน่วยกิต ถ้าลงรายวิชาประเภทฝึกงานในภาคพิเศษ จะลงวิชาอื่นในภาคนั้นไม่ได้
+- การลงทะเบียนที่มีหน่วยกิตต่างจากที่กำหนด ให้สภาวิชาการพิจารณาอนุมัติ</t>
+        </is>
+      </c>
+      <c r="H601" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 82</t>
+        </is>
+      </c>
+      <c r="I601" s="39" t="inlineStr">
+        <is>
+          <t>ข้อบังคับปริญญาตรี (ภาคผนวกเล่ม AIT 2566) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J601" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K601" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L601" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M601" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N601" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O601" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="602" ht="14.25" customHeight="1" s="36">
+      <c r="A602" s="37" t="inlineStr">
+        <is>
+          <t>WC14</t>
+        </is>
+      </c>
+      <c r="B602" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C602" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D602" s="39" t="inlineStr">
+        <is>
+          <t>วิชากฎหมายสำหรับคนรุ่นใหม่ ของหลักสูตร DSBA กับ IT เรียนปีและเทอมเดียวกันหรือไม่</t>
+        </is>
+      </c>
+      <c r="E602" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F602" s="39" t="inlineStr">
+        <is>
+          <t>DSBA ปี 1 ภาค 2, IT ปี 3 ภาค 2</t>
+        </is>
+      </c>
+      <c r="G602" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: เรียนต่างปี/ภาคกัน — DSBA ปีที่ 1 ภาค 2, IT ปีที่ 3 ภาค 2
+- หลักสูตร DSBA 2565 (ปริญญาตรี): 90642033 กฎหมายสำหรับคนรุ่นใหม่ (LAW FOR NEW GENERATION) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 2
+- หลักสูตร IT 2565 (ปริญญาตรี): 90642033 กฎหมายสำหรับคนรุ่นใหม่ (LAW FOR NEW GENERATION) — 3(3-0-6) | ปีที่ 3 ภาคการศึกษาที่ 2</t>
+        </is>
+      </c>
+      <c r="H602" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 16, 24, 31, 353</t>
+        </is>
+      </c>
+      <c r="I602" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (วิชาเดียวกันข้ามหลักสูตร) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J602" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="K602" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L602" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M602" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt (แผนของทั้งสองหลักสูตร))</t>
+        </is>
+      </c>
+      <c r="N602" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O602" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="603" ht="14.25" customHeight="1" s="36">
+      <c r="A603" s="37" t="inlineStr">
+        <is>
+          <t>WC15</t>
+        </is>
+      </c>
+      <c r="B603" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C603" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D603" s="39" t="inlineStr">
+        <is>
+          <t>วิชาคณิตศาสตร์ไม่ต่อเนื่อง ของหลักสูตร AIT กับ DSBA เรียนปีและเทอมเดียวกันหรือไม่</t>
+        </is>
+      </c>
+      <c r="E603" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F603" s="39" t="inlineStr">
+        <is>
+          <t>AIT ปี 1 ภาค 1, DSBA ปี 2 ภาค 1</t>
+        </is>
+      </c>
+      <c r="G603" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: เรียนต่างปี/ภาคกัน — AIT ปีที่ 1 ภาค 1, DSBA ปีที่ 2 ภาค 1
+- หลักสูตร AIT 2566 (ปริญญาตรี): 06066000 คณิตศาสตร์ไม่ต่อเนื่อง (DISCRETE MATHEMATICS) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 1
+- หลักสูตร DSBA 2565 (ปริญญาตรี): 06066000 คณิตศาสตร์ไม่ต่อเนื่อง (DISCRETE MATHEMATICS) — 3(3-0-6) | ปีที่ 2 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H603" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 19, 23, 37, 288</t>
+        </is>
+      </c>
+      <c r="I603" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (วิชาเดียวกันข้ามหลักสูตร) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J603" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="K603" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L603" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M603" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt (แผนของทั้งสองหลักสูตร))</t>
+        </is>
+      </c>
+      <c r="N603" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O603" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="604" ht="14.25" customHeight="1" s="36">
+      <c r="A604" s="37" t="inlineStr">
+        <is>
+          <t>WC16</t>
+        </is>
+      </c>
+      <c r="B604" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C604" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D604" s="39" t="inlineStr">
+        <is>
+          <t>วิชาการสื่อสารและการนำเสนออย่างมืออาชีพ ของหลักสูตร DSBA กับ IT เรียนปีและเทอมเดียวกันหรือไม่</t>
+        </is>
+      </c>
+      <c r="E604" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 5 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F604" s="39" t="inlineStr">
+        <is>
+          <t>DSBA ปี 3 ภาค 1, IT ปี 3 ภาค 2</t>
+        </is>
+      </c>
+      <c r="G604" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: เรียนต่างปี/ภาคกัน — DSBA ปีที่ 3 ภาค 1, IT ปีที่ 3 ภาค 2
+- หลักสูตร DSBA 2565 (ปริญญาตรี): 90644042 การสื่อสารและการนำเสนออย่างมืออาชีพ (PROFESSIONAL COMMUNICATION AND PRESENTATION) — 3(3-0-6) | ปีที่ 3 ภาคการศึกษาที่ 1
+- หลักสูตร IT 2565 (ปริญญาตรี): 90644042 การสื่อสารและการนำเสนออย่างมืออาชีพ (PROFESSIONAL COMMUNICATION AND PRESENTATION) — 3(3-0-6) | ปีที่ 3 ภาคการศึกษาที่ 2</t>
+        </is>
+      </c>
+      <c r="H604" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 16, 27, 34, 353</t>
+        </is>
+      </c>
+      <c r="I604" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (วิชาเดียวกันข้ามหลักสูตร) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J604" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="K604" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L604" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M604" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt (แผนของทั้งสองหลักสูตร))</t>
+        </is>
+      </c>
+      <c r="N604" s="39" t="inlineStr">
+        <is>
+          <t>0.02s</t>
+        </is>
+      </c>
+      <c r="O604" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="605" ht="14.25" customHeight="1" s="36">
+      <c r="A605" s="37" t="inlineStr">
+        <is>
+          <t>ZH1</t>
+        </is>
+      </c>
+      <c r="B605" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C605" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D605" s="39" t="inlineStr">
+        <is>
+          <t>อยากเรียนพื้นฐานการเรียนรู้เชิงลึก ต้องเรียนอะไรให้ผ่านก่อนทั้งหมด รวมถึงวิชาที่ต้องผ่านก่อนวิชาเหล่านั้นด้วย</t>
+        </is>
+      </c>
+      <c r="E605" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F605" s="39" t="inlineStr">
+        <is>
+          <t>06046401 และก่อนหน้านั้น 06046400</t>
+        </is>
+      </c>
+      <c r="G605" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06046406 พื้นฐานการเรียนรู้เชิงลึก (FUNDAMENTALS OF DEEP LEARNING) — ปีที่ 2 ภาคการศึกษาที่ 1
+วิชาที่ต้องสอบผ่านก่อน (↳ = วิชาที่ต้องผ่านก่อนวิชาด้านบนอีกชั้น):
+  • 06046401 แคลคูลัส 2 (CALCULUS 2) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 2
+    ↳ 06046400 แคลคูลัส 1 (CALCULUS 1) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 1
+  • 06046402 พีชคณิตเชิงเส้น (LINEAR ALGEBRA) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 1
+รวมต้องผ่านก่อน 3 วิชา</t>
+        </is>
+      </c>
+      <c r="H605" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 37, 19, 292, 23, 287, 20, 24, 288</t>
+        </is>
+      </c>
+      <c r="I605" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (วิชาบังคับก่อนไล่หลายชั้น) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J605" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K605" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L605" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M605" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N605" s="39" t="inlineStr">
+        <is>
+          <t>0.02s</t>
+        </is>
+      </c>
+      <c r="O605" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="606" ht="14.25" customHeight="1" s="36">
+      <c r="A606" s="37" t="inlineStr">
+        <is>
+          <t>ZH2</t>
+        </is>
+      </c>
+      <c r="B606" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C606" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D606" s="39" t="inlineStr">
+        <is>
+          <t>ตอนอยู่ปี 1 จะลงเรียนการเรียนรู้ของเครื่องเชิงความน่าจะเป็นเลยได้มั้ย</t>
+        </is>
+      </c>
+      <c r="E606" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F606" s="39" t="inlineStr">
+        <is>
+          <t>ตามแผนเรียนปี 2 ภาค 1 ต้องผ่าน 06066001 ก่อน</t>
+        </is>
+      </c>
+      <c r="G606" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ไม่ได้ — ต้องสอบผ่าน 06066001 ความน่าจะเป็นและสถิติ ก่อน ซึ่งตามแผนเรียนในปีที่ 1 ภาคการศึกษาที่ 1 จึงยังไม่ผ่านวิชานี้ก่อนเริ่มปี 1
+วิชา 06046405 การเรียนรู้ของเครื่องเชิงความน่าจะเป็น (PROBABILISTIC MACHINE LEARNING) — 3(3-0-6) หน่วยกิต
+ตามแผนการศึกษา: ปีที่ 2 ภาคการศึกษาที่ 1
+วิชาบังคับก่อน (ต้องสอบผ่านก่อนจึงจะลงได้):
+  - 06066001 ความน่าจะเป็นและสถิติ (PROBABILITY AND STATISTICS) — ปีที่ 1 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H606" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 37, 291, 19, 20, 23, 24, 289</t>
+        </is>
+      </c>
+      <c r="I606" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (ปีตามแผน + วิชาบังคับก่อน → ลงได้/ไม่ได้) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J606" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="K606" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L606" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M606" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N606" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O606" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="607" ht="14.25" customHeight="1" s="36">
+      <c r="A607" s="37" t="inlineStr">
+        <is>
+          <t>ZH3</t>
+        </is>
+      </c>
+      <c r="B607" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C607" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D607" s="39" t="inlineStr">
+        <is>
+          <t>ได้ F วิชาแคลคูลัส 2 แล้ววิชาไหนจะลงต่อไม่ได้ วิชาพวกนั้นอยู่ปีไหน</t>
+        </is>
+      </c>
+      <c r="E607" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F607" s="39" t="inlineStr">
+        <is>
+          <t>06046406 (06046406 ปี 2 ภาค 1)</t>
+        </is>
+      </c>
+      <c r="G607" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06046401 แคลคูลัส 2 (CALCULUS 2) — ปีที่ 1 ภาคการศึกษาที่ 2
+  วิชาที่ต้องผ่านวิชานี้ก่อนจึงจะลงได้ (↳ = ต่อจากวิชาด้านบนอีกชั้น):
+    • 06046406 พื้นฐานการเรียนรู้เชิงลึก (FUNDAMENTALS OF DEEP LEARNING) — 3(3-0-6) | ปีที่ 2 ภาคการศึกษาที่ 1
+  ถ้ายังไม่ผ่านวิชานี้ จะลงวิชาข้างต้นไม่ได้จนกว่าจะผ่าน</t>
+        </is>
+      </c>
+      <c r="H607" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 37, 292, 19, 20, 23, 24, 287</t>
+        </is>
+      </c>
+      <c r="I607" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (prerequisite ทิศกลับ) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J607" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="K607" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L607" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M607" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N607" s="39" t="inlineStr">
+        <is>
+          <t>0.02s</t>
+        </is>
+      </c>
+      <c r="O607" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="608" ht="14.25" customHeight="1" s="36">
+      <c r="A608" s="37" t="inlineStr">
+        <is>
+          <t>ZH4</t>
+        </is>
+      </c>
+      <c r="B608" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C608" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D608" s="39" t="inlineStr">
+        <is>
+          <t>การวิเคราะห์และเพิ่มประสิทธิภาพเครือข่าย กับ ทักษะการสื่อสารภาษาอังกฤษระหว่างวัฒนธรรม 1 วิชาไหนเรียนก่อน</t>
+        </is>
+      </c>
+      <c r="E608" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F608" s="39" t="inlineStr">
+        <is>
+          <t>06046411 ปี 2 ภาค 2, 90641009 ปี 2 ภาค 1</t>
+        </is>
+      </c>
+      <c r="G608" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: เรียนปีเดียวกัน (ปีที่ 2) แต่คนละภาค
+- 06046411 การวิเคราะห์และเพิ่มประสิทธิภาพเครือข่าย (NETWORK ANALYSIS AND OPTIMIZATION) — ปีที่ 2 ภาคการศึกษาที่ 2
+- 90641009 ทักษะการสื่อสารภาษาอังกฤษระหว่างวัฒนธรรม 1 (INTERCULTURAL COMMUNICATION SKILLS IN ENGLISH 1) — ปีที่ 2 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H608" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 19, 20, 24, 38, 119, 120, 145, 233</t>
+        </is>
+      </c>
+      <c r="I608" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (เทียบปี/ภาคของสองวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J608" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K608" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L608" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M608" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N608" s="39" t="inlineStr">
+        <is>
+          <t>0.02s</t>
+        </is>
+      </c>
+      <c r="O608" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="609" ht="14.25" customHeight="1" s="36">
+      <c r="A609" s="37" t="inlineStr">
+        <is>
+          <t>ZH5</t>
+        </is>
+      </c>
+      <c r="B609" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C609" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D609" s="39" t="inlineStr">
+        <is>
+          <t>ตอนอยู่ปี 3 จะลงเรียนโครงงานทางด้านเทคโนโลยีสารสนเทศเชิงธุรกิจ 2เลยได้มั้ย</t>
+        </is>
+      </c>
+      <c r="E609" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F609" s="39" t="inlineStr">
+        <is>
+          <t>ตามแผนเรียนปี 4 ภาค 1 ต้องผ่าน 06036145 ก่อน</t>
+        </is>
+      </c>
+      <c r="G609" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ไม่ได้ — ต้องสอบผ่าน 06036145 โครงงานทางด้านเทคโนโลยีสารสนเทศเชิงธุรกิจ 1 ก่อน ซึ่งตามแผนเรียนในปีที่ 3 ภาคการศึกษาที่ 2 จึงยังไม่ผ่านวิชานี้ก่อนเริ่มปี 3
+วิชา 06036146 โครงงานทางด้านเทคโนโลยีสารสนเทศเชิงธุรกิจ 2 (PROJECT IN BUSINESS INFORMATION TECHNOLOGY 2) — 3(0-9-0) หน่วยกิต
+ตามแผนการศึกษา: ปีที่ 4 ภาคการศึกษาที่ 1
+วิชาบังคับก่อน (ต้องสอบผ่านก่อนจึงจะลงได้):
+  - 06036145 โครงงานทางด้านเทคโนโลยีสารสนเทศเชิงธุรกิจ 1 (PROJECT IN BUSINESS INFORMATION TECHNOLOGY 1) — ปีที่ 3 ภาคการศึกษาที่ 2</t>
+        </is>
+      </c>
+      <c r="H609" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 29, 76, 256, 269, 22, 23</t>
+        </is>
+      </c>
+      <c r="I609" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (ปีตามแผน + วิชาบังคับก่อน → ลงได้/ไม่ได้) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J609" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="K609" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L609" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M609" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N609" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O609" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="610" ht="14.25" customHeight="1" s="36">
+      <c r="A610" s="37" t="inlineStr">
+        <is>
+          <t>ZH6</t>
+        </is>
+      </c>
+      <c r="B610" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C610" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D610" s="39" t="inlineStr">
+        <is>
+          <t>ได้ F วิชาโครงงานทางด้านเทคโนโลยีสารสนเทศเชิงธุรกิจ 1 แล้ววิชาไหนจะลงต่อไม่ได้ วิชาพวกนั้นอยู่ปีไหน</t>
+        </is>
+      </c>
+      <c r="E610" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F610" s="39" t="inlineStr">
+        <is>
+          <t>06036146 (06036146 ปี 4 ภาค 1)</t>
+        </is>
+      </c>
+      <c r="G610" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06036145 โครงงานทางด้านเทคโนโลยีสารสนเทศเชิงธุรกิจ 1 (PROJECT IN BUSINESS INFORMATION TECHNOLOGY 1) — ปีที่ 3 ภาคการศึกษาที่ 2
+  วิชาที่ต้องผ่านวิชานี้ก่อนจึงจะลงได้ (↳ = ต่อจากวิชาด้านบนอีกชั้น):
+    • 06036146 โครงงานทางด้านเทคโนโลยีสารสนเทศเชิงธุรกิจ 2 (PROJECT IN BUSINESS INFORMATION TECHNOLOGY 2) — 3(0-9-0) | ปีที่ 4 ภาคการศึกษาที่ 1
+  ถ้ายังไม่ผ่านวิชานี้ จะลงวิชาข้างต้นไม่ได้จนกว่าจะผ่าน</t>
+        </is>
+      </c>
+      <c r="H610" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 29, 76, 256, 269, 22, 23</t>
+        </is>
+      </c>
+      <c r="I610" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (prerequisite ทิศกลับ) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J610" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="K610" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L610" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M610" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N610" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O610" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="611" ht="14.25" customHeight="1" s="36">
+      <c r="A611" s="37" t="inlineStr">
+        <is>
+          <t>ZH7</t>
+        </is>
+      </c>
+      <c r="B611" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C611" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D611" s="39" t="inlineStr">
+        <is>
+          <t>ภาษาอังกฤษพื้นฐาน 1 กับ พื้นฐานการเขียนโปรแกรม วิชาไหนเรียนก่อน</t>
+        </is>
+      </c>
+      <c r="E611" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F611" s="39" t="inlineStr">
+        <is>
+          <t>96644007 ปี 1 ภาค 1, 06036119 ปี 1 ภาค 2</t>
+        </is>
+      </c>
+      <c r="G611" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: เรียนปีเดียวกัน (ปีที่ 1) แต่คนละภาค
+- 96644007 ภาษาอังกฤษพื้นฐาน 1 (FOUNDATION ENGLISH 1) — ปีที่ 1 ภาคการศึกษาที่ 1
+- 06036119 พื้นฐานการเขียนโปรแกรม (PROGRAMMING FUNDAMENTALS) — ปีที่ 1 ภาคการศึกษาที่ 2</t>
+        </is>
+      </c>
+      <c r="H611" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 20, 23, 26, 27, 31, 32, 75, 244</t>
+        </is>
+      </c>
+      <c r="I611" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (เทียบปี/ภาคของสองวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J611" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K611" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L611" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M611" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N611" s="39" t="inlineStr">
+        <is>
+          <t>0.02s</t>
+        </is>
+      </c>
+      <c r="O611" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="612" ht="14.25" customHeight="1" s="36">
+      <c r="A612" s="37" t="inlineStr">
+        <is>
+          <t>ZH8</t>
+        </is>
+      </c>
+      <c r="B612" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C612" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D612" s="39" t="inlineStr">
+        <is>
+          <t>ตอนอยู่ปี 2 จะลงเรียนการสร้างคลังข้อมูลเลยได้มั้ย</t>
+        </is>
+      </c>
+      <c r="E612" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F612" s="39" t="inlineStr">
+        <is>
+          <t>ตามแผนเรียนปี 3 ภาค 1 ต้องผ่าน 06066300 ก่อน</t>
+        </is>
+      </c>
+      <c r="G612" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ไม่ได้ — ต้องสอบผ่าน 06066300 แนวคิดระบบฐานข้อมูล ก่อน ซึ่งตามแผนเรียนในปีที่ 2 ภาคการศึกษาที่ 1 จึงยังไม่ผ่านวิชานี้ก่อนเริ่มปี 2
+วิชา 06026212 การสร้างคลังข้อมูล (DATA WAREHOUSING) — 3(2-2-5) หน่วยกิต
+ตามแผนการศึกษา: ปีที่ 3 ภาคการศึกษาที่ 1
+วิชาบังคับก่อน (ต้องสอบผ่านก่อนจึงจะลงได้):
+  - 06066300 แนวคิดระบบฐานข้อมูล (DATABASE SYSTEM CONCEPTS) — ปีที่ 2 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H612" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 323, 18, 25, 27, 32, 34, 69, 73</t>
+        </is>
+      </c>
+      <c r="I612" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (ปีตามแผน + วิชาบังคับก่อน → ลงได้/ไม่ได้) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J612" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K612" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L612" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M612" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N612" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O612" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="613" ht="14.25" customHeight="1" s="36">
+      <c r="A613" s="37" t="inlineStr">
+        <is>
+          <t>ZH9</t>
+        </is>
+      </c>
+      <c r="B613" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C613" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D613" s="39" t="inlineStr">
+        <is>
+          <t>ได้ F วิชาโครงงานวิทยาการข้อมูลและการวิเคราะห์เชิงธุรกิจ 1 แล้ววิชาไหนจะลงต่อไม่ได้ วิชาพวกนั้นอยู่ปีไหน</t>
+        </is>
+      </c>
+      <c r="E613" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F613" s="39" t="inlineStr">
+        <is>
+          <t>06026215 (06026215 ปี 4 ภาค 1)</t>
+        </is>
+      </c>
+      <c r="G613" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06026214 โครงงานวิทยาการข้อมูลและการวิเคราะห์เชิงธุรกิจ 1 (PROJECT IN DATA SCIENCE AND BUSINESS ANALYTICS 1) — ปีที่ 3 ภาคการศึกษาที่ 2
+  วิชาที่ต้องผ่านวิชานี้ก่อนจึงจะลงได้ (↳ = ต่อจากวิชาด้านบนอีกชั้น):
+    • 06026215 โครงงานวิทยาการข้อมูลและการวิเคราะห์เชิงธุรกิจ 2 (PROJECT IN DATA SCIENCE AND BUSINESS ANALYTICS 2) — 3(0-9-0) | ปีที่ 4 ภาคการศึกษาที่ 1
+  ถ้ายังไม่ผ่านวิชานี้ จะลงวิชาข้างต้นไม่ได้จนกว่าจะผ่าน</t>
+        </is>
+      </c>
+      <c r="H613" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 19, 69, 325, 354, 28, 29, 35, 36</t>
+        </is>
+      </c>
+      <c r="I613" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (prerequisite ทิศกลับ) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J613" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K613" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L613" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M613" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N613" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O613" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="614" ht="14.25" customHeight="1" s="36">
+      <c r="A614" s="37" t="inlineStr">
+        <is>
+          <t>ZH10</t>
+        </is>
+      </c>
+      <c r="B614" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C614" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D614" s="39" t="inlineStr">
+        <is>
+          <t>แคลคูลัส 2 กับ โครงงานวิทยาการข้อมูลและการวิเคราะห์เชิงธุรกิจ 1 วิชาไหนเรียนก่อน</t>
+        </is>
+      </c>
+      <c r="E614" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F614" s="39" t="inlineStr">
+        <is>
+          <t>06026201 ปี 1 ภาค 2, 06026214 ปี 3 ภาค 2</t>
+        </is>
+      </c>
+      <c r="G614" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: เรียนคนละปี — แคลคูลัส 2 เรียนก่อน
+- 06026201 แคลคูลัส 2 (CALCULUS 2) — ปีที่ 1 ภาคการศึกษาที่ 2
+- 06026214 โครงงานวิทยาการข้อมูลและการวิเคราะห์เชิงธุรกิจ 1 (PROJECT IN DATA SCIENCE AND BUSINESS ANALYTICS 1) — ปีที่ 3 ภาคการศึกษาที่ 2</t>
+        </is>
+      </c>
+      <c r="H614" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 17, 19, 24, 28, 31, 35, 68, 69</t>
+        </is>
+      </c>
+      <c r="I614" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (เทียบปี/ภาคของสองวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J614" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K614" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L614" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M614" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N614" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O614" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="615" ht="14.25" customHeight="1" s="36">
+      <c r="A615" s="37" t="inlineStr">
+        <is>
+          <t>ZH11</t>
+        </is>
+      </c>
+      <c r="B615" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C615" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D615" s="39" t="inlineStr">
+        <is>
+          <t>ตอนอยู่ปี 1 จะลงเรียนระบบโครงสร้างพื้นฐานและการบริการเลยได้มั้ย</t>
+        </is>
+      </c>
+      <c r="E615" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F615" s="39" t="inlineStr">
+        <is>
+          <t>ตามแผนเรียนปี 2 ภาค 2 ต้องผ่าน 06016413 ก่อน</t>
+        </is>
+      </c>
+      <c r="G615" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ไม่ได้ — ต้องสอบผ่าน 06016413 ระบบเครือข่ายเบื้องต้น ก่อน ซึ่งตามแผนเรียนในปีที่ 2 ภาคการศึกษาที่ 1 จึงยังไม่ผ่านวิชานี้ก่อนเริ่มปี 1
+วิชา 06016420 ระบบโครงสร้างพื้นฐานและการบริการ (INFRASTRUCTURE SYSTEMS AND SERVICES) — 3(2-2-5) หน่วยกิต
+ตามแผนการศึกษา: ปีที่ 2 ภาคการศึกษาที่ 2
+วิชาบังคับก่อน (ต้องสอบผ่านก่อนจึงจะลงได้):
+  - 06016413 ระบบเครือข่ายเบื้องต้น (INTRODUCTION TO NETWORK SYSTEMS) — ปีที่ 2 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H615" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 84, 24, 25, 33, 34, 40, 328, 331</t>
+        </is>
+      </c>
+      <c r="I615" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (ปีตามแผน + วิชาบังคับก่อน → ลงได้/ไม่ได้) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J615" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K615" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L615" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M615" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N615" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O615" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="616" ht="14.25" customHeight="1" s="36">
+      <c r="A616" s="37" t="inlineStr">
+        <is>
+          <t>ZH12</t>
+        </is>
+      </c>
+      <c r="B616" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C616" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D616" s="39" t="inlineStr">
+        <is>
+          <t>ได้ F วิชาการสร้างโปรแกรมเชิงวัตถุ แล้ววิชาไหนจะลงต่อไม่ได้ วิชาพวกนั้นอยู่ปีไหน</t>
+        </is>
+      </c>
+      <c r="E616" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F616" s="39" t="inlineStr">
+        <is>
+          <t>06016418 (06016418 ปี 3 ภาค 1)</t>
+        </is>
+      </c>
+      <c r="G616" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06016408 การสร้างโปรแกรมเชิงวัตถุ (OBJECT-ORIENTED PROGRAMMING) — ปีที่ 1 ภาคการศึกษาที่ 2
+  วิชาที่ต้องผ่านวิชานี้ก่อนจึงจะลงได้ (↳ = ต่อจากวิชาด้านบนอีกชั้น):
+    • 06016418 การพัฒนาเว็บฝั่งเซิร์ฟเวอร์ (SERVER-SIDE WEB DEVELOPMENT) — 3(2-2-5) | ปีที่ 3 ภาคการศึกษาที่ 1
+  ถ้ายังไม่ผ่านวิชานี้ จะลงวิชาข้างต้นไม่ได้จนกว่าจะผ่าน</t>
+        </is>
+      </c>
+      <c r="H616" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 331, 24, 25, 26, 32, 35, 39, 83</t>
+        </is>
+      </c>
+      <c r="I616" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (prerequisite ทิศกลับ) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J616" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K616" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L616" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M616" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N616" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O616" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="617" ht="14.25" customHeight="1" s="36">
+      <c r="A617" s="37" t="inlineStr">
+        <is>
+          <t>ZH13</t>
+        </is>
+      </c>
+      <c r="B617" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C617" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D617" s="39" t="inlineStr">
+        <is>
+          <t>การบริหารโครงการเทคโนโลยีสารสนเทศ กับ โรงเรียนสร้างเสน่ห์ วิชาไหนเรียนก่อน</t>
+        </is>
+      </c>
+      <c r="E617" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F617" s="39" t="inlineStr">
+        <is>
+          <t>06066100 ปี 3 ภาค 2, 90641001 ปี 1 ภาค 1</t>
+        </is>
+      </c>
+      <c r="G617" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: เรียนคนละปี — โรงเรียนสร้างเสน่ห์ เรียนก่อน
+- 06066100 การบริหารโครงการเทคโนโลยีสารสนเทศ (INFORMATION TECHNOLOGY PROJECT MANAGEMENT) — ปีที่ 3 ภาคการศึกษาที่ 2
+- 90641001 โรงเรียนสร้างเสน่ห์ (CHARM SCHOOL) — ปีที่ 1 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H617" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 21, 23, 31, 36, 44, 87, 134, 136</t>
+        </is>
+      </c>
+      <c r="I617" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (เทียบปี/ภาคของสองวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J617" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K617" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L617" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M617" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N617" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O617" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="618" ht="14.25" customHeight="1" s="36">
+      <c r="A618" s="37" t="inlineStr">
+        <is>
+          <t>ZH14</t>
+        </is>
+      </c>
+      <c r="B618" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C618" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D618" s="39" t="inlineStr">
+        <is>
+          <t>เลือกทำสหกิจศึกษาแล้ว ปี 4 ภาค 2 เรียนไม่เหมือนแผนปกติตรงไหน</t>
+        </is>
+      </c>
+      <c r="E618" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F618" s="39" t="inlineStr">
+        <is>
+          <t>06036147</t>
+        </is>
+      </c>
+      <c r="G618" s="39" t="inlineStr">
+        <is>
+          <t>แผนปกติ (ไม่เข้าโครงการสหกิจศึกษา) — ปีที่ 4 ภาคการศึกษาที่ 2 (หน้า 30):
+  - วิชาเลือกที่ต้องลงตามแผน: 2 ช่อง
+      • วิชาเลือกทางเทคโนโลยีสารสนเทศทางธุรกิจ 1
+      • วิชาเลือกทางเทคโนโลยีสารสนเทศทางธุรกิจ 2
+  รวมภาคนี้ตามแผนในเล่ม: 12 หน่วยกิต
+แผนที่เข้าโครงการสหกิจศึกษา — ปีที่ 4 ภาคการศึกษาที่ 2 (หน้า 35):
+  - 06036147 สหกิจศึกษา — 6(0-35-0)
+  - 06036148 สหกิจศึกษาต่างประเทศ — 6(0-35-0)
+  รวมภาคนี้ตามแผนในเล่ม: 6 หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="H618" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 30, 35</t>
+        </is>
+      </c>
+      <c r="I618" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ตารางแผนปกติ/แผนสหกิจ) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J618" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K618" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L618" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M618" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_coop.json เทียบ BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N618" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O618" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="619" ht="14.25" customHeight="1" s="36">
+      <c r="A619" s="37" t="inlineStr">
+        <is>
+          <t>ZC1</t>
+        </is>
+      </c>
+      <c r="B619" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C619" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D619" s="39" t="inlineStr">
+        <is>
+          <t>ตอนนี้มี 123 หน่วยกิต GPA 2.45 อยู่หลักสูตร IT ขาดอีกเท่าไหร่ถึงจะจบ</t>
+        </is>
+      </c>
+      <c r="E619" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F619" s="39" t="inlineStr">
+        <is>
+          <t>ยังไม่จบ ต้องครบ 129 ขาด 6</t>
+        </is>
+      </c>
+      <c r="G619" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ยังจบไม่ได้
+หลักสูตร IT 2565 (ปริญญาตรี) ต้องเรียนครบไม่น้อยกว่า 129 หน่วยกิต (หน้า 6)
+- หน่วยกิต: เก็บได้ 123 หน่วยกิต → ยังขาดอีก 6 หน่วยกิต (ต้องครบ 129)
+- เกรดเฉลี่ยสะสม 2.45 → ผ่านเกณฑ์ขั้นต่ำ 2.00 (ข้อ 34)
+- เงื่อนไขอื่นตามข้อ 34: สอบผ่านทุกรายวิชาตามโครงสร้างหลักสูตร และผ่านการสอบภาษาอังกฤษ (English Exit exam)</t>
+        </is>
+      </c>
+      <c r="H619" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 6, 88</t>
+        </is>
+      </c>
+      <c r="I619" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวม + เกรดขั้นต่ำ ข้อ 34) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J619" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K619" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L619" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M619" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N619" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O619" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="620" ht="14.25" customHeight="1" s="36">
+      <c r="A620" s="37" t="inlineStr">
+        <is>
+          <t>ZC2</t>
+        </is>
+      </c>
+      <c r="B620" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C620" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D620" s="39" t="inlineStr">
+        <is>
+          <t>เรียนครบ 129 หน่วยกิตแล้วแต่ GPA 1.95 สำเร็จการศึกษาได้หรือเปล่า</t>
+        </is>
+      </c>
+      <c r="E620" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F620" s="39" t="inlineStr">
+        <is>
+          <t>ไม่ได้ ต้องได้ไม่ต่ำกว่า 2.00</t>
+        </is>
+      </c>
+      <c r="G620" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ยังจบไม่ได้
+หลักสูตร IT 2565 (ปริญญาตรี) ต้องเรียนครบไม่น้อยกว่า 129 หน่วยกิต (หน้า 6)
+- หน่วยกิต: เก็บได้ 129 หน่วยกิต → ครบเกณฑ์ 129 หน่วยกิต
+- เกรดเฉลี่ยสะสม 1.95 → ต่ำกว่าเกณฑ์ขั้นต่ำ 2.00 (ข้อ 34) จึงยังจบไม่ได้ และเกรดเฉลี่ยสะสมต่ำกว่า 2.00 ต้องถูกภาคทัณฑ์ (ข้อ 31)
+- เงื่อนไขอื่นตามข้อ 34: สอบผ่านทุกรายวิชาตามโครงสร้างหลักสูตร และผ่านการสอบภาษาอังกฤษ (English Exit exam)</t>
+        </is>
+      </c>
+      <c r="H620" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 6, 88</t>
+        </is>
+      </c>
+      <c r="I620" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวม + เกรดขั้นต่ำ ข้อ 34) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J620" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K620" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L620" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M620" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N620" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O620" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="621" ht="14.25" customHeight="1" s="36">
+      <c r="A621" s="37" t="inlineStr">
+        <is>
+          <t>ZC3</t>
+        </is>
+      </c>
+      <c r="B621" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C621" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D621" s="39" t="inlineStr">
+        <is>
+          <t>ตอนนี้มี 126 หน่วยกิต GPA 2.45 อยู่หลักสูตร DSBA ขาดอีกเท่าไหร่ถึงจะจบ</t>
+        </is>
+      </c>
+      <c r="E621" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F621" s="39" t="inlineStr">
+        <is>
+          <t>ยังไม่จบ ต้องครบ 132 ขาด 6</t>
+        </is>
+      </c>
+      <c r="G621" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ยังจบไม่ได้
+หลักสูตร DSBA 2565 (ปริญญาตรี) ต้องเรียนครบไม่น้อยกว่า 132 หน่วยกิต (หน้า 2)
+- หน่วยกิต: เก็บได้ 126 หน่วยกิต → ยังขาดอีก 6 หน่วยกิต (ต้องครบ 132)
+- เกรดเฉลี่ยสะสม 2.45 → ผ่านเกณฑ์ขั้นต่ำ 2.00 (ข้อ 34)
+- เงื่อนไขอื่นตามข้อ 34: สอบผ่านทุกรายวิชาตามโครงสร้างหลักสูตร และผ่านการสอบภาษาอังกฤษ (English Exit exam)</t>
+        </is>
+      </c>
+      <c r="H621" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 2, 88</t>
+        </is>
+      </c>
+      <c r="I621" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวม + เกรดขั้นต่ำ ข้อ 34) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J621" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K621" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L621" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M621" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N621" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O621" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="622" ht="14.25" customHeight="1" s="36">
+      <c r="A622" s="37" t="inlineStr">
+        <is>
+          <t>ZC4</t>
+        </is>
+      </c>
+      <c r="B622" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C622" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D622" s="39" t="inlineStr">
+        <is>
+          <t>เรียนครบ 132 หน่วยกิตแล้วแต่ GPA 1.95 สำเร็จการศึกษาได้หรือเปล่า</t>
+        </is>
+      </c>
+      <c r="E622" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F622" s="39" t="inlineStr">
+        <is>
+          <t>ไม่ได้ ต้องได้ไม่ต่ำกว่า 2.00</t>
+        </is>
+      </c>
+      <c r="G622" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ยังจบไม่ได้
+หลักสูตร DSBA 2565 (ปริญญาตรี) ต้องเรียนครบไม่น้อยกว่า 132 หน่วยกิต (หน้า 2)
+- หน่วยกิต: เก็บได้ 132 หน่วยกิต → ครบเกณฑ์ 132 หน่วยกิต
+- เกรดเฉลี่ยสะสม 1.95 → ต่ำกว่าเกณฑ์ขั้นต่ำ 2.00 (ข้อ 34) จึงยังจบไม่ได้ และเกรดเฉลี่ยสะสมต่ำกว่า 2.00 ต้องถูกภาคทัณฑ์ (ข้อ 31)
+- เงื่อนไขอื่นตามข้อ 34: สอบผ่านทุกรายวิชาตามโครงสร้างหลักสูตร และผ่านการสอบภาษาอังกฤษ (English Exit exam)</t>
+        </is>
+      </c>
+      <c r="H622" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 2, 88</t>
+        </is>
+      </c>
+      <c r="I622" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวม + เกรดขั้นต่ำ ข้อ 34) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J622" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K622" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L622" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M622" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N622" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O622" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="623" ht="14.25" customHeight="1" s="36">
+      <c r="A623" s="37" t="inlineStr">
+        <is>
+          <t>ZC5</t>
+        </is>
+      </c>
+      <c r="B623" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C623" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D623" s="39" t="inlineStr">
+        <is>
+          <t>ตอนนี้มี 114 หน่วยกิต GPA 2.45 อยู่หลักสูตร AIT ขาดอีกเท่าไหร่ถึงจะจบ</t>
+        </is>
+      </c>
+      <c r="E623" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F623" s="39" t="inlineStr">
+        <is>
+          <t>ยังไม่จบ ต้องครบ 120 ขาด 6</t>
+        </is>
+      </c>
+      <c r="G623" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ยังจบไม่ได้
+หลักสูตร AIT 2566 (ปริญญาตรี) ต้องเรียนครบไม่น้อยกว่า 120 หน่วยกิต (หน้า 5)
+- หน่วยกิต: เก็บได้ 114 หน่วยกิต → ยังขาดอีก 6 หน่วยกิต (ต้องครบ 120)
+- เกรดเฉลี่ยสะสม 2.45 → ผ่านเกณฑ์ขั้นต่ำ 2.00 (ข้อ 34)
+- เงื่อนไขอื่นตามข้อ 34: สอบผ่านทุกรายวิชาตามโครงสร้างหลักสูตร และผ่านการสอบภาษาอังกฤษ (English Exit exam)</t>
+        </is>
+      </c>
+      <c r="H623" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 5, 88</t>
+        </is>
+      </c>
+      <c r="I623" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวม + เกรดขั้นต่ำ ข้อ 34) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J623" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K623" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L623" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M623" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N623" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O623" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="624" ht="14.25" customHeight="1" s="36">
+      <c r="A624" s="37" t="inlineStr">
+        <is>
+          <t>ZC6</t>
+        </is>
+      </c>
+      <c r="B624" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C624" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D624" s="39" t="inlineStr">
+        <is>
+          <t>เรียนครบ 120 หน่วยกิตแล้วแต่ GPA 1.95 สำเร็จการศึกษาได้หรือเปล่า</t>
+        </is>
+      </c>
+      <c r="E624" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F624" s="39" t="inlineStr">
+        <is>
+          <t>ไม่ได้ ต้องได้ไม่ต่ำกว่า 2.00</t>
+        </is>
+      </c>
+      <c r="G624" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ยังจบไม่ได้
+หลักสูตร AIT 2566 (ปริญญาตรี) ต้องเรียนครบไม่น้อยกว่า 120 หน่วยกิต (หน้า 5)
+- หน่วยกิต: เก็บได้ 120 หน่วยกิต → ครบเกณฑ์ 120 หน่วยกิต
+- เกรดเฉลี่ยสะสม 1.95 → ต่ำกว่าเกณฑ์ขั้นต่ำ 2.00 (ข้อ 34) จึงยังจบไม่ได้ และเกรดเฉลี่ยสะสมต่ำกว่า 2.00 ต้องถูกภาคทัณฑ์ (ข้อ 31)
+- เงื่อนไขอื่นตามข้อ 34: สอบผ่านทุกรายวิชาตามโครงสร้างหลักสูตร และผ่านการสอบภาษาอังกฤษ (English Exit exam)</t>
+        </is>
+      </c>
+      <c r="H624" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 5, 88</t>
+        </is>
+      </c>
+      <c r="I624" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวม + เกรดขั้นต่ำ ข้อ 34) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J624" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K624" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L624" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M624" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N624" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O624" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="625" ht="14.25" customHeight="1" s="36">
+      <c r="A625" s="37" t="inlineStr">
+        <is>
+          <t>ZC7</t>
+        </is>
+      </c>
+      <c r="B625" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C625" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D625" s="39" t="inlineStr">
+        <is>
+          <t>IT หรือ DSBA หลักสูตรไหนต้องเรียนหน่วยกิตมากกว่ากัน</t>
+        </is>
+      </c>
+      <c r="E625" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F625" s="39" t="inlineStr">
+        <is>
+          <t>IT 129, DSBA 132</t>
+        </is>
+      </c>
+      <c r="G625" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ต่างกัน 3 หน่วยกิต (DSBA 2565 (ปริญญาตรี) มากกว่า IT 2565 (ปริญญาตรี))
+- IT 2565 (ปริญญาตรี): ไม่น้อยกว่า 129 หน่วยกิต (หน้า 6)
+- DSBA 2565 (ปริญญาตรี): ไม่น้อยกว่า 132 หน่วยกิต (หน้า 2)</t>
+        </is>
+      </c>
+      <c r="H625" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 6, 2</t>
+        </is>
+      </c>
+      <c r="I625" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวมข้ามหลักสูตร) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J625" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K625" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L625" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M625" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N625" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O625" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="626" ht="14.25" customHeight="1" s="36">
+      <c r="A626" s="37" t="inlineStr">
+        <is>
+          <t>ZC8</t>
+        </is>
+      </c>
+      <c r="B626" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C626" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D626" s="39" t="inlineStr">
+        <is>
+          <t>AIT หรือ IT หลักสูตรไหนต้องเรียนหน่วยกิตมากกว่ากัน</t>
+        </is>
+      </c>
+      <c r="E626" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F626" s="39" t="inlineStr">
+        <is>
+          <t>AIT 120, IT 129</t>
+        </is>
+      </c>
+      <c r="G626" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ต่างกัน 9 หน่วยกิต (IT 2565 (ปริญญาตรี) มากกว่า AIT 2566 (ปริญญาตรี))
+- AIT 2566 (ปริญญาตรี): ไม่น้อยกว่า 120 หน่วยกิต (หน้า 5)
+- IT 2565 (ปริญญาตรี): ไม่น้อยกว่า 129 หน่วยกิต (หน้า 6)</t>
+        </is>
+      </c>
+      <c r="H626" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 5, 6</t>
+        </is>
+      </c>
+      <c r="I626" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวมข้ามหลักสูตร) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J626" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K626" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L626" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M626" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N626" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O626" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="627" ht="14.25" customHeight="1" s="36">
+      <c r="A627" s="37" t="inlineStr">
+        <is>
+          <t>ZC9</t>
+        </is>
+      </c>
+      <c r="B627" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C627" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D627" s="39" t="inlineStr">
+        <is>
+          <t>DSBA หรือ AIT หลักสูตรไหนต้องเรียนหน่วยกิตมากกว่ากัน</t>
+        </is>
+      </c>
+      <c r="E627" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F627" s="39" t="inlineStr">
+        <is>
+          <t>DSBA 132, AIT 120</t>
+        </is>
+      </c>
+      <c r="G627" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ต่างกัน 12 หน่วยกิต (DSBA 2565 (ปริญญาตรี) มากกว่า AIT 2566 (ปริญญาตรี))
+- DSBA 2565 (ปริญญาตรี): ไม่น้อยกว่า 132 หน่วยกิต (หน้า 2)
+- AIT 2566 (ปริญญาตรี): ไม่น้อยกว่า 120 หน่วยกิต (หน้า 5)</t>
+        </is>
+      </c>
+      <c r="H627" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 2, 5</t>
+        </is>
+      </c>
+      <c r="I627" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวมข้ามหลักสูตร) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J627" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K627" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L627" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M627" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N627" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O627" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="628" ht="14.25" customHeight="1" s="36">
+      <c r="A628" s="37" t="inlineStr">
+        <is>
+          <t>ZC10</t>
+        </is>
+      </c>
+      <c r="B628" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C628" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D628" s="39" t="inlineStr">
+        <is>
+          <t>GPA ตอนจบ 3.55 ได้เกียรตินิยมไหม อันดับเท่าไร</t>
+        </is>
+      </c>
+      <c r="E628" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F628" s="39" t="inlineStr">
+        <is>
+          <t>อันดับ 1 (&gt;= 3.50)</t>
+        </is>
+      </c>
+      <c r="G628" s="39" t="inlineStr">
+        <is>
+          <t>ปริญญาเกียรตินิยม — ข้อ 36 ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 88, 89
+(ข้อบังคับของสถาบัน ใช้กับทุกหลักสูตรปริญญาตรี)
+- เกียรตินิยมอันดับหนึ่งและเหรียญทอง: ค่าระดับคะแนนเฉลี่ยสะสมตามโครงสร้างหลักสูตรสูงสุดในกลุ่มผู้สำเร็จการศึกษาปีเดียวกันของหลักสูตร และค่าระดับคะแนนเฉลี่ยสะสมไม่ต่ำกว่า 3.75 และต้องไม่เทียบโอนผลการเรียนจากสถาบันอื่น
+- เกียรตินิยมอันดับหนึ่ง: ค่าระดับคะแนนเฉลี่ยสะสมไม่ต่ำกว่า 3.50
+- เกียรตินิยมอันดับสอง: ค่าระดับคะแนนเฉลี่ยสะสมไม่ต่ำกว่า 3.25
+- กรณีโอนผลการเรียนจากสถาบันอื่น ทุกรายวิชาต้องได้ไม่ต่ำกว่า B หรือ S และต้องเรียนในหลักสูตรของสถาบันไม่น้อยกว่า 2 ใน 3 ของหน่วยกิตรวม
+- เงื่อนไขทั่วไป (ข้อ 36.1): เรียนไม่เกินระยะเวลาตามแผนการศึกษา · ไม่มีรายวิชาใดได้ F หรือ U · ไม่เคยเรียนซ้ำเพื่อเปลี่ยนเกรด · ไม่เคยลาพักเพราะไม่ลงทะเบียนตามกำหนด และไม่เคยถูกลงโทษทางวินัย</t>
+        </is>
+      </c>
+      <c r="H628" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 88, 89</t>
+        </is>
+      </c>
+      <c r="I628" s="39" t="inlineStr">
+        <is>
+          <t>ข้อบังคับปริญญาตรี (ภาคผนวกเล่ม AIT 2566) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J628" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K628" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L628" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M628" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N628" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O628" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="629" ht="14.25" customHeight="1" s="36">
+      <c r="A629" s="37" t="inlineStr">
+        <is>
+          <t>ZC11</t>
+        </is>
+      </c>
+      <c r="B629" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C629" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D629" s="39" t="inlineStr">
+        <is>
+          <t>เกรดเฉลี่ย 3.40 จะได้เกียรตินิยมอันดับสองหรือเปล่า</t>
+        </is>
+      </c>
+      <c r="E629" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F629" s="39" t="inlineStr">
+        <is>
+          <t>อันดับ 2 (&gt;= 3.25)</t>
+        </is>
+      </c>
+      <c r="G629" s="39" t="inlineStr">
+        <is>
+          <t>ปริญญาเกียรตินิยม — ข้อ 36 ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 88, 89
+(ข้อบังคับของสถาบัน ใช้กับทุกหลักสูตรปริญญาตรี)
+- เกียรตินิยมอันดับหนึ่งและเหรียญทอง: ค่าระดับคะแนนเฉลี่ยสะสมตามโครงสร้างหลักสูตรสูงสุดในกลุ่มผู้สำเร็จการศึกษาปีเดียวกันของหลักสูตร และค่าระดับคะแนนเฉลี่ยสะสมไม่ต่ำกว่า 3.75 และต้องไม่เทียบโอนผลการเรียนจากสถาบันอื่น
+- เกียรตินิยมอันดับหนึ่ง: ค่าระดับคะแนนเฉลี่ยสะสมไม่ต่ำกว่า 3.50
+- เกียรตินิยมอันดับสอง: ค่าระดับคะแนนเฉลี่ยสะสมไม่ต่ำกว่า 3.25
+- กรณีโอนผลการเรียนจากสถาบันอื่น ทุกรายวิชาต้องได้ไม่ต่ำกว่า B หรือ S และต้องเรียนในหลักสูตรของสถาบันไม่น้อยกว่า 2 ใน 3 ของหน่วยกิตรวม
+- เงื่อนไขทั่วไป (ข้อ 36.1): เรียนไม่เกินระยะเวลาตามแผนการศึกษา · ไม่มีรายวิชาใดได้ F หรือ U · ไม่เคยเรียนซ้ำเพื่อเปลี่ยนเกรด · ไม่เคยลาพักเพราะไม่ลงทะเบียนตามกำหนด และไม่เคยถูกลงโทษทางวินัย</t>
+        </is>
+      </c>
+      <c r="H629" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 88, 89</t>
+        </is>
+      </c>
+      <c r="I629" s="39" t="inlineStr">
+        <is>
+          <t>ข้อบังคับปริญญาตรี (ภาคผนวกเล่ม AIT 2566) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J629" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K629" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L629" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M629" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N629" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O629" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="630" ht="14.25" customHeight="1" s="36">
+      <c r="A630" s="37" t="inlineStr">
+        <is>
+          <t>ZC12</t>
+        </is>
+      </c>
+      <c r="B630" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C630" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D630" s="39" t="inlineStr">
+        <is>
+          <t>ภาคเรียนปกติลง 8 หน่วยกิตได้ไหม</t>
+        </is>
+      </c>
+      <c r="E630" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F630" s="39" t="inlineStr">
+        <is>
+          <t>ไม่ได้ ขั้นต่ำ 9</t>
+        </is>
+      </c>
+      <c r="G630" s="39" t="inlineStr">
+        <is>
+          <t>ไม่ได้  
+นักศึกษาต้องลงทะเบียนไม่น้อยกว่า 9 หน่วยกิตในภาคการศึกษาปกติ ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 82 ซึ่งเป็นข้อกำหนดบังคับสำหรับทุกหลักสูตรปริญญาตรี ไม่ใช่ข้อยกเว้นเฉพาะหลักสูตร DSBA</t>
+        </is>
+      </c>
+      <c r="H630" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 82</t>
+        </is>
+      </c>
+      <c r="I630" s="39" t="inlineStr">
+        <is>
+          <t>ข้อบังคับปริญญาตรี (ภาคผนวกเล่ม AIT 2566) → Typhoon เรียบเรียง</t>
+        </is>
+      </c>
+      <c r="J630" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K630" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L630" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M630" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N630" s="39" t="inlineStr">
+        <is>
+          <t>1.41s</t>
+        </is>
+      </c>
+      <c r="O630" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="631" ht="14.25" customHeight="1" s="36">
+      <c r="A631" s="37" t="inlineStr">
+        <is>
+          <t>ZC13</t>
+        </is>
+      </c>
+      <c r="B631" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C631" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D631" s="39" t="inlineStr">
+        <is>
+          <t>ซัมเมอร์ลงได้มากสุดกี่หน่วยกิต ถ้าลงฝึกงานด้วยจะลงวิชาอื่นได้ไหม</t>
+        </is>
+      </c>
+      <c r="E631" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F631" s="39" t="inlineStr">
+        <is>
+          <t>ไม่เกิน 9 ฝึกงานแล้วลงวิชาอื่นไม่ได้</t>
+        </is>
+      </c>
+      <c r="G631" s="39" t="inlineStr">
+        <is>
+          <t>ได้  
+นักศึกษาสามารถลงทะเบียนเรียนได้ไม่เกิน 9 หน่วยกิตในภาคการศึกษาพิเศษ (ซัมเมอร์) ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 82 หากลงฝึกงานในภาคพิเศษ จะไม่สามารถลงวิชาอื่นได้ในภาคเดียวกัน เนื่องจากเป็นข้อห้ามโดยตรงในข้อบังคับดังกล่าว</t>
+        </is>
+      </c>
+      <c r="H631" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 82</t>
+        </is>
+      </c>
+      <c r="I631" s="39" t="inlineStr">
+        <is>
+          <t>ข้อบังคับปริญญาตรี (ภาคผนวกเล่ม AIT 2566) → Typhoon เรียบเรียง</t>
+        </is>
+      </c>
+      <c r="J631" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K631" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L631" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M631" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N631" s="39" t="inlineStr">
+        <is>
+          <t>1.52s</t>
+        </is>
+      </c>
+      <c r="O631" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="632" ht="14.25" customHeight="1" s="36">
+      <c r="A632" s="37" t="inlineStr">
+        <is>
+          <t>ZC14</t>
+        </is>
+      </c>
+      <c r="B632" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C632" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D632" s="39" t="inlineStr">
+        <is>
+          <t>ผู้ประกอบการสมัยใหม่ ใน DSBA และ IT อยู่ปีไหนเทอมไหนบ้าง</t>
+        </is>
+      </c>
+      <c r="E632" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F632" s="39" t="inlineStr">
+        <is>
+          <t>DSBA ปี 3 ภาค 2, IT ปี 4 ภาค 1</t>
+        </is>
+      </c>
+      <c r="G632" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: เรียนต่างปี/ภาคกัน — DSBA ปีที่ 3 ภาค 2, IT ปีที่ 4 ภาค 1
+- หลักสูตร DSBA 2565 (ปริญญาตรี): 90643021 ผู้ประกอบการสมัยใหม่ (MODERN ENTREPRENEURS) — 3(3-0-6) | ปีที่ 3 ภาคการศึกษาที่ 2
+- หลักสูตร IT 2565 (ปริญญาตรี): 90643021 ผู้ประกอบการสมัยใหม่ (MODERN ENTREPRENEURS) — 3(3-0-6) | ปีที่ 4 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H632" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 16, 28, 35, 353</t>
+        </is>
+      </c>
+      <c r="I632" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (วิชาเดียวกันข้ามหลักสูตร) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J632" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="K632" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L632" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M632" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt (แผนของทั้งสองหลักสูตร))</t>
+        </is>
+      </c>
+      <c r="N632" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O632" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="633" ht="14.25" customHeight="1" s="36">
+      <c r="A633" s="37" t="inlineStr">
+        <is>
+          <t>ZC15</t>
+        </is>
+      </c>
+      <c r="B633" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C633" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D633" s="39" t="inlineStr">
+        <is>
+          <t>โครงสร้างข้อมูลและอัลกอริทึม ใน AIT และ DSBA อยู่ปีไหนเทอมไหนบ้าง</t>
+        </is>
+      </c>
+      <c r="E633" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F633" s="39" t="inlineStr">
+        <is>
+          <t>AIT ปี 1 ภาค 2, DSBA ปี 2 ภาค 2</t>
+        </is>
+      </c>
+      <c r="G633" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: เรียนต่างปี/ภาคกัน — AIT ปีที่ 1 ภาค 2, DSBA ปีที่ 2 ภาค 2
+- หลักสูตร AIT 2566 (ปริญญาตรี): 06066301 โครงสร้างข้อมูลและอัลกอริทึม (DATA STRUCTURES AND ALGORITHMS) — 3(2-2-5) | ปีที่ 1 ภาคการศึกษาที่ 2
+- หลักสูตร DSBA 2565 (ปริญญาตรี): 06066301 โครงสร้างข้อมูลและอัลกอริทึม (DATA STRUCTURES AND ALGORITHMS) — 3(2-2-5) | ปีที่ 2 ภาคการศึกษาที่ 2</t>
+        </is>
+      </c>
+      <c r="H633" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 20, 23, 37, 290</t>
+        </is>
+      </c>
+      <c r="I633" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (วิชาเดียวกันข้ามหลักสูตร) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J633" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="K633" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L633" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M633" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt (แผนของทั้งสองหลักสูตร))</t>
+        </is>
+      </c>
+      <c r="N633" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O633" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="634" ht="14.25" customHeight="1" s="36">
+      <c r="A634" s="37" t="inlineStr">
+        <is>
+          <t>ZC16</t>
+        </is>
+      </c>
+      <c r="B634" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C634" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D634" s="39" t="inlineStr">
+        <is>
+          <t>พื้นฐานทางธุรกิจสำหรับเทคโนโลยีสารสนเทศ ใน DSBA และ IT อยู่ปีไหนเทอมไหนบ้าง</t>
+        </is>
+      </c>
+      <c r="E634" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 6 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F634" s="39" t="inlineStr">
+        <is>
+          <t>DSBA ปี 1 ภาค 1, IT ปี 1 ภาค 2</t>
+        </is>
+      </c>
+      <c r="G634" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: เรียนต่างปี/ภาคกัน — DSBA ปีที่ 1 ภาค 1, IT ปีที่ 1 ภาค 2
+- หลักสูตร DSBA 2565 (ปริญญาตรี): 06066101 พื้นฐานทางธุรกิจสำหรับเทคโนโลยีสารสนเทศ (BUSINESS FUNDAMENTALS FOR INFORMATION TECHNOLOGY) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 1
+- หลักสูตร IT 2565 (ปริญญาตรี): 06066101 พื้นฐานทางธุรกิจสำหรับเทคโนโลยีสารสนเทศ (BUSINESS FUNDAMENTALS FOR INFORMATION TECHNOLOGY) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 2</t>
+        </is>
+      </c>
+      <c r="H634" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 18, 23, 30, 73, 317, 318, 353</t>
+        </is>
+      </c>
+      <c r="I634" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (วิชาเดียวกันข้ามหลักสูตร) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J634" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="K634" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L634" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M634" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt (แผนของทั้งสองหลักสูตร))</t>
+        </is>
+      </c>
+      <c r="N634" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O634" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
     <row r="635" ht="14.25" customHeight="1" s="36"/>
     <row r="636" ht="14.25" customHeight="1" s="36"/>
     <row r="637" ht="14.25" customHeight="1" s="36"/>

--- a/docs/tester.xlsx
+++ b/docs/tester.xlsx
@@ -577,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O634"/>
+  <dimension ref="A1:O662"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10" customWidth="1" style="36" min="1" max="1"/>
@@ -756,7 +756,7 @@
       </c>
       <c r="N2" s="13" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.03s</t>
         </is>
       </c>
       <c r="O2" s="21" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="N7" s="25" t="inlineStr">
         <is>
-          <t>0.05s</t>
+          <t>0.04s</t>
         </is>
       </c>
       <c r="O7" s="21" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="N9" s="25" t="inlineStr">
         <is>
-          <t>0.73s</t>
+          <t>0.62s</t>
         </is>
       </c>
       <c r="O9" s="21" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="N10" s="13" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O10" s="21" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="N11" s="25" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O11" s="21" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="N12" s="13" t="inlineStr">
         <is>
-          <t>0.19s</t>
+          <t>0.18s</t>
         </is>
       </c>
       <c r="O12" s="21" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="N13" s="25" t="inlineStr">
         <is>
-          <t>0.28s</t>
+          <t>0.35s</t>
         </is>
       </c>
       <c r="O13" s="21" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="N14" s="13" t="inlineStr">
         <is>
-          <t>0.25s</t>
+          <t>0.26s</t>
         </is>
       </c>
       <c r="O14" s="21" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="N15" s="25" t="inlineStr">
         <is>
-          <t>0.24s</t>
+          <t>0.23s</t>
         </is>
       </c>
       <c r="O15" s="21" t="inlineStr">
@@ -2395,7 +2395,7 @@
       <c r="G21" s="34" t="inlineStr">
         <is>
           <t>ได้  
-นักศึกษาสามารถเรียนวิชาฐานข้อมูลในปีที่ 4 ได้ เนื่องจากหลักสูตรมีวิชาบังคับที่เกี่ยวข้องกับฐานข้อมูล เช่น 06026246 ระบบฐานข้อมูลแบบกระจาย และ 06026247 หัวข้อพิเศษทางวิศวกรรมข้อมูล 1 ซึ่งจัดสอนในภาคการศึกษาที่ 1 ปีที่ 4 โดยมีวิชาบังคับก่อนอย่าง 06066300 แนวคิดระบบฐานข้อมูล (ปีที่ 2 ภาคการศึกษาที่ 1) ที่เป็นพื้นฐานสำคัญ</t>
+นักศึกษาสามารถเรียนวิชาที่เกี่ยวข้องกับฐานข้อมูลในปีที่ 4 ได้ เนื่องจากมีวิชาบังคับก่อนหน้า เช่น 06066300 แนวคิดระบบฐานข้อมูล (ปี 2 ภาค 1) และ 06026212 การสร้างคลังข้อมูล (ปี 3 ภาค 1) ซึ่งเป็นพื้นฐานจำเป็น วิชาที่เกี่ยวข้องในปี 4 ได้แก่ 06026246 หัวข้อพิเศษทางวิศวกรรมข้อมูล 1 และ 06026247 หัวข้อพิเศษทางวิศวกรรมข้อมูล 2 ที่จัดสอนในภาคการศึกษาที่ 1 ปีที่ 4 ประเภทวิชาบังคับในกลุ่มวิชาเลือกเฉพาะแขนง ตามหลักสูตร DSBA 2565</t>
         </is>
       </c>
       <c r="H21" s="34" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="K21" s="19" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="L21" s="21" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="N21" s="13" t="inlineStr">
         <is>
-          <t>1.51s</t>
+          <t>2.88s</t>
         </is>
       </c>
       <c r="O21" s="21" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="N23" s="13" t="inlineStr">
         <is>
-          <t>0.14s</t>
+          <t>0.15s</t>
         </is>
       </c>
       <c r="O23" s="21" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="N24" s="25" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O24" s="21" t="inlineStr">
@@ -2801,15 +2801,11 @@
       </c>
       <c r="G25" s="34" t="inlineStr">
         <is>
-          <t>ใช่ หลักสูตรวิทยาการข้อมูลและการวิเคราะห์เชิงธุรกิจ (DSBA) ปีที่ 3 มีการเลือกแขนง (หรือที่เรียกว่า "กลุ่มวิชา") ซึ่งแบ่งออกเป็น 3 กลุ่ม ดังนี้:
-- วิชาเลือกกลุ่มวิทยาการข้อมูล 1 (ELECTIVE IN DATA SCIENCE 1) – 3 (3-0-6) หรือ 3 (2-2-5) [3]
-- วิชาเลือกกลุ่มการวิเคราะห์เชิงสถิติ 1 (ELECTIVE IN STATISTICAL ANALYSIS 1) – 3 (3-0-6) หรือ 3 (2-2-5) [3]
-- วิชาเลือกกลุ่มวิศวกรรมข้อมูล 1 (ELECTIVE IN DATA ENGINEERING 1) – 3 (3-0-6) หรือ 3 (2-2-5) [3]
-ในภาคการศึกษาที่ 2 ปีที่ 3 ยังมีการเลือกแขนงในลักษณะเดียวกัน ได้แก่:
-- วิชาเลือกกลุ่มวิทยาการข้อมูล 3 (ELECTIVE IN DATA SCIENCE 3) – 3 (3-0-6) หรือ 3 (2-2-5) [4]
-- วิชาเลือกกลุ่มการวิเคราะห์เชิงสถิติ 3 (ELECTIVE IN STATISTICAL ANALYTICS 3) – 3 (3-0-6) หรือ 3 (2-2-5) [4]
-- วิชาเลือกกลุ่มวิศวกรรมข้อมูล 3 (ELECTIVE IN DATA ENGINEERING 3) – 3 (3-0-6) หรือ 3 (2-2-5) [4]
-ดังนั้น แขนงที่สามารถเลือกได้คือ วิทยาการข้อมูล, การวิเคราะห์เชิงสถิติ, และวิศวกรรมข้อมูล [3][4]</t>
+          <t>ใช่ หลักสูตรวิทยาการข้อมูลและการวิเคราะห์เชิงธุรกิจ (DSBA) ปีที่ 3 มีการเลือกแขนง (หรือที่เรียกว่า "กลุ่มวิชา") ให้เลือก โดยมี 3 แขนง ดังนี้:
+- กลุ่มวิทยาการข้อมูล (Data Science)  
+- กลุ่มการวิเคราะห์เชิงสถิติ (Statistical Analytics)  
+- กลุ่มวิศวกรรมข้อมูล (Data Engineering)  
+[3][4][6]</t>
         </is>
       </c>
       <c r="H25" s="34" t="inlineStr">
@@ -2842,7 +2838,7 @@
       </c>
       <c r="N25" s="13" t="inlineStr">
         <is>
-          <t>4.29s</t>
+          <t>1.64s</t>
         </is>
       </c>
       <c r="O25" s="21" t="inlineStr">
@@ -2884,9 +2880,9 @@
       </c>
       <c r="G26" s="34" t="inlineStr">
         <is>
-          <t>1. หลักสูตร IT 2565 มีหน่วยกิตรวม 129 หน่วยกิต ลดลง 1 หน่วยกิตจาก IT 2560 ที่มี 130 หน่วยกิต และเปลี่ยนโครงสร้างแขนงวิชาเป็น "โมดูลอาชีพ" 3 โมดูลแทนการเลือกแขนงวิชาเดิม
-2. หลักสูตร IT 2565 ลดหน่วยกิตกลุ่มวิชาเฉพาะด้านจาก 46 หน่วยกิต (IT 2560) เป็น 57 หน่วยกิต แต่เพิ่มหน่วยกิตกลุ่มวิชาเลือกทางเทคโนโลยีสารสนเทศจาก 6 เป็น 9 หน่วยกิต โดยจัดเป็น 3 โมดูลอาชีพ (M1: Full-Stack Web Developer, M2: Network/System Engineer, M3: Game Developer) ซึ่งนักศึกษาสามารถเลือกเรียนได้ตามความสนใจ โดยไม่จำเป็นต้องเลือกครบ 3 โมดูล
-3. อ้างข้อมูลจาก: หน่วยกิตรวม (มคอ.2 IT 2560 หน้า 18, IT 2565 หน้า 6), โครงสร้างหลักสูตร (มคอ.2 IT 2565 หน้า 371, 374, 376, 378), กลุ่มวิชาเลือก (IT 2565 หน้า 378), กลุ่มวิชาเฉพาะด้าน (IT 2565 หน้า 374), กลุ่มวิชาบังคับเฉพาะสาขา (IT 2565 หน้า 376), ประเภทวิชา (บังคับ/เลือก) และการจัดกลุ่มโมดูล (IT 2565 หน้า 370, 378)</t>
+          <t>1. หลักสูตร IT 2565 มีหน่วยกิตรวมน้อยกว่า IT 2560 อยู่ 1 หน่วยกิต และเปลี่ยนโครงสร้างแขนงวิชาเป็น "โมดูลอาชีพ" 3 โมดูลแทนการเลือกแขนงวิชาเดิม
+2. หลักสูตร IT 2560 มีหน่วยกิตรวม 130 หน่วยกิต (มคอ.2 IT 2560 หน้า 18) ขณะที่ IT 2565 มี 129 หน่วยกิต (มคอ.2 IT 2565 หน้า 6) ลดลง 1 หน่วยกิต ซึ่งสะท้อนจากการปรับโครงสร้างกลุ่มวิชาเฉพาะด้านและวิชาเลือก โดยเฉพาะการเปลี่ยนจาก "แขนงวิชา" มาเป็น "โมดูลอาชีพ" 3 โมดูล (M1-M3) ที่มีความยืดหยุ่นในการเลือกวิชา และลดหน่วยกิตในกลุ่มวิชาบังคับเฉพาะแขนงจาก 30 เป็น 15 หน่วยกิต (ข้อมูลจาก [3], [4], [8])
+3. อ้างข้อมูลจากหลักฐาน: หน่วยกิตรวม (IT 2560 vs IT 2565), ประเภทวิชา (บังคับ/เลือก), ภาค/ปีที่เปิดสอน (IT 2560 เริ่มภาค 1/2560, IT 2565 เริ่มภาค 1/2565), โครงสร้างแขนงวิชา (เปลี่ยนจาก "แขนงวิชา" เป็น "โมดูลอาชีพ")</t>
         </is>
       </c>
       <c r="H26" s="34" t="inlineStr">
@@ -2919,7 +2915,7 @@
       </c>
       <c r="N26" s="13" t="inlineStr">
         <is>
-          <t>4.95s</t>
+          <t>4.90s</t>
         </is>
       </c>
       <c r="O26" s="21" t="inlineStr">
@@ -3071,7 +3067,7 @@
       <c r="M28" s="34" t="n"/>
       <c r="N28" s="13" t="inlineStr">
         <is>
-          <t>0.46s</t>
+          <t>0.44s</t>
         </is>
       </c>
       <c r="O28" s="21" t="inlineStr">
@@ -3147,7 +3143,7 @@
       </c>
       <c r="N29" s="25" t="inlineStr">
         <is>
-          <t>0.10s</t>
+          <t>0.16s</t>
         </is>
       </c>
       <c r="O29" s="21" t="inlineStr">
@@ -3488,7 +3484,7 @@
       </c>
       <c r="N33" s="25" t="inlineStr">
         <is>
-          <t>0.28s</t>
+          <t>0.30s</t>
         </is>
       </c>
       <c r="O33" s="21" t="inlineStr">
@@ -3636,7 +3632,7 @@
       <c r="M35" s="35" t="n"/>
       <c r="N35" s="25" t="inlineStr">
         <is>
-          <t>0.48s</t>
+          <t>0.52s</t>
         </is>
       </c>
       <c r="O35" s="21" t="inlineStr">
@@ -3804,7 +3800,7 @@
       </c>
       <c r="N37" s="25" t="inlineStr">
         <is>
-          <t>0.25s</t>
+          <t>0.23s</t>
         </is>
       </c>
       <c r="O37" s="21" t="inlineStr">
@@ -3916,7 +3912,7 @@
       </c>
       <c r="N38" s="13" t="inlineStr">
         <is>
-          <t>0.28s</t>
+          <t>0.34s</t>
         </is>
       </c>
       <c r="O38" s="21" t="inlineStr">
@@ -4008,7 +4004,7 @@
       </c>
       <c r="N39" s="25" t="inlineStr">
         <is>
-          <t>0.41s</t>
+          <t>0.38s</t>
         </is>
       </c>
       <c r="O39" s="21" t="inlineStr">
@@ -4273,7 +4269,7 @@
       <c r="M42" s="34" t="n"/>
       <c r="N42" s="13" t="inlineStr">
         <is>
-          <t>0.12s</t>
+          <t>0.18s</t>
         </is>
       </c>
       <c r="O42" s="21" t="inlineStr">
@@ -4345,7 +4341,7 @@
       <c r="M43" s="35" t="n"/>
       <c r="N43" s="25" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O43" s="21" t="inlineStr">
@@ -4654,7 +4650,7 @@
       </c>
       <c r="N47" s="25" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O47" s="21" t="inlineStr">
@@ -4902,7 +4898,7 @@
       </c>
       <c r="N50" s="13" t="inlineStr">
         <is>
-          <t>0.12s</t>
+          <t>0.14s</t>
         </is>
       </c>
       <c r="O50" s="21" t="inlineStr">
@@ -5001,7 +4997,7 @@
       </c>
       <c r="N51" s="25" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O51" s="21" t="inlineStr">
@@ -5588,7 +5584,7 @@
       <c r="M58" s="34" t="n"/>
       <c r="N58" s="13" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O58" s="21" t="inlineStr">
@@ -5789,7 +5785,7 @@
       </c>
       <c r="N60" s="13" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O60" s="21" t="inlineStr">
@@ -5873,7 +5869,7 @@
       </c>
       <c r="N61" s="25" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O61" s="21" t="inlineStr">
@@ -6142,7 +6138,7 @@
       </c>
       <c r="N64" s="13" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.03s</t>
         </is>
       </c>
       <c r="O64" s="21" t="inlineStr">
@@ -6233,7 +6229,7 @@
       <c r="M65" s="35" t="n"/>
       <c r="N65" s="25" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O65" s="21" t="inlineStr">
@@ -6311,7 +6307,7 @@
       <c r="M66" s="34" t="n"/>
       <c r="N66" s="13" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O66" s="21" t="inlineStr">
@@ -6393,7 +6389,7 @@
       </c>
       <c r="N67" s="25" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O67" s="21" t="inlineStr">
@@ -6649,7 +6645,7 @@
       <c r="M70" s="34" t="n"/>
       <c r="N70" s="13" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O70" s="21" t="inlineStr">
@@ -6727,7 +6723,7 @@
       </c>
       <c r="N71" s="25" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O71" s="21" t="inlineStr">
@@ -6805,7 +6801,7 @@
       </c>
       <c r="N72" s="13" t="inlineStr">
         <is>
-          <t>0.07s</t>
+          <t>0.08s</t>
         </is>
       </c>
       <c r="O72" s="21" t="inlineStr">
@@ -7288,7 +7284,7 @@
       </c>
       <c r="N78" s="13" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O78" s="21" t="inlineStr">
@@ -8214,7 +8210,7 @@
       </c>
       <c r="N89" s="25" t="inlineStr">
         <is>
-          <t>0.12s</t>
+          <t>0.10s</t>
         </is>
       </c>
       <c r="O89" s="21" t="inlineStr">
@@ -10998,7 +10994,7 @@
       </c>
       <c r="N125" s="39" t="inlineStr">
         <is>
-          <t>0.03s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O125" s="41" t="inlineStr">
@@ -11166,7 +11162,7 @@
       </c>
       <c r="N127" s="39" t="inlineStr">
         <is>
-          <t>0.03s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O127" s="41" t="inlineStr">
@@ -11892,7 +11888,7 @@
       </c>
       <c r="N136" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O136" s="41" t="inlineStr">
@@ -12208,7 +12204,7 @@
       </c>
       <c r="N140" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O140" s="41" t="inlineStr">
@@ -12682,7 +12678,7 @@
       </c>
       <c r="N146" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O146" s="41" t="inlineStr">
@@ -12761,7 +12757,7 @@
       </c>
       <c r="N147" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O147" s="41" t="inlineStr">
@@ -12840,7 +12836,7 @@
       </c>
       <c r="N148" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O148" s="41" t="inlineStr">
@@ -12919,7 +12915,7 @@
       </c>
       <c r="N149" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O149" s="41" t="inlineStr">
@@ -13234,7 +13230,7 @@
       </c>
       <c r="N153" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O153" s="41" t="inlineStr">
@@ -13471,7 +13467,7 @@
       </c>
       <c r="N156" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O156" s="41" t="inlineStr">
@@ -13548,7 +13544,7 @@
       </c>
       <c r="N157" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O157" s="41" t="inlineStr">
@@ -13702,7 +13698,7 @@
       </c>
       <c r="N159" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O159" s="41" t="inlineStr">
@@ -13856,7 +13852,7 @@
       </c>
       <c r="N161" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O161" s="41" t="inlineStr">
@@ -14010,7 +14006,7 @@
       </c>
       <c r="N163" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O163" s="41" t="inlineStr">
@@ -14165,7 +14161,7 @@
       </c>
       <c r="N165" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O165" s="41" t="inlineStr">
@@ -15089,7 +15085,7 @@
       </c>
       <c r="N176" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O176" s="41" t="inlineStr">
@@ -15493,7 +15489,7 @@
       </c>
       <c r="N181" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O181" s="41" t="inlineStr">
@@ -16696,7 +16692,7 @@
       </c>
       <c r="N196" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O196" s="41" t="inlineStr">
@@ -16773,7 +16769,7 @@
       </c>
       <c r="N197" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O197" s="41" t="inlineStr">
@@ -17543,7 +17539,7 @@
       </c>
       <c r="N207" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O207" s="41" t="inlineStr">
@@ -18129,7 +18125,7 @@
       </c>
       <c r="N214" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O214" s="41" t="inlineStr">
@@ -19243,7 +19239,7 @@
       </c>
       <c r="N228" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O228" s="41" t="inlineStr">
@@ -19322,7 +19318,7 @@
       </c>
       <c r="N229" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O229" s="41" t="inlineStr">
@@ -19401,7 +19397,7 @@
       </c>
       <c r="N230" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O230" s="41" t="inlineStr">
@@ -20124,7 +20120,7 @@
       </c>
       <c r="N239" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O239" s="41" t="inlineStr">
@@ -20201,7 +20197,7 @@
       </c>
       <c r="N240" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O240" s="41" t="inlineStr">
@@ -20278,7 +20274,7 @@
       </c>
       <c r="N241" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O241" s="41" t="inlineStr">
@@ -20355,7 +20351,7 @@
       </c>
       <c r="N242" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O242" s="41" t="inlineStr">
@@ -20894,7 +20890,7 @@
       </c>
       <c r="N249" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O249" s="41" t="inlineStr">
@@ -21055,7 +21051,7 @@
       </c>
       <c r="N251" s="39" t="inlineStr">
         <is>
-          <t>0.03s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O251" s="41" t="inlineStr">
@@ -21221,7 +21217,7 @@
       </c>
       <c r="N253" s="39" t="inlineStr">
         <is>
-          <t>0.03s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O253" s="41" t="inlineStr">
@@ -21397,7 +21393,7 @@
       </c>
       <c r="N255" s="39" t="inlineStr">
         <is>
-          <t>0.03s</t>
+          <t>0.04s</t>
         </is>
       </c>
       <c r="O255" s="41" t="inlineStr">
@@ -21562,7 +21558,7 @@
       </c>
       <c r="N257" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O257" s="41" t="inlineStr">
@@ -21719,7 +21715,7 @@
       </c>
       <c r="N259" s="39" t="inlineStr">
         <is>
-          <t>0.11s</t>
+          <t>0.12s</t>
         </is>
       </c>
       <c r="O259" s="41" t="inlineStr">
@@ -22273,7 +22269,7 @@
       </c>
       <c r="N266" s="39" t="inlineStr">
         <is>
-          <t>0.05s</t>
+          <t>0.04s</t>
         </is>
       </c>
       <c r="O266" s="41" t="inlineStr">
@@ -22349,7 +22345,7 @@
       </c>
       <c r="N267" s="39" t="inlineStr">
         <is>
-          <t>0.04s</t>
+          <t>0.05s</t>
         </is>
       </c>
       <c r="O267" s="41" t="inlineStr">
@@ -22746,7 +22742,7 @@
       </c>
       <c r="N272" s="39" t="inlineStr">
         <is>
-          <t>0.05s</t>
+          <t>0.04s</t>
         </is>
       </c>
       <c r="O272" s="41" t="inlineStr">
@@ -24694,7 +24690,7 @@
       </c>
       <c r="N297" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O297" s="41" t="inlineStr">
@@ -24928,7 +24924,7 @@
       </c>
       <c r="N300" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O300" s="41" t="inlineStr">
@@ -25636,7 +25632,7 @@
       </c>
       <c r="N309" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O309" s="41" t="inlineStr">
@@ -26259,7 +26255,7 @@
       </c>
       <c r="N317" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O317" s="41" t="inlineStr">
@@ -26337,7 +26333,7 @@
       </c>
       <c r="N318" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O318" s="41" t="inlineStr">
@@ -26415,7 +26411,7 @@
       </c>
       <c r="N319" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O319" s="41" t="inlineStr">
@@ -26573,7 +26569,7 @@
       </c>
       <c r="N321" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O321" s="41" t="inlineStr">
@@ -27142,7 +27138,7 @@
       </c>
       <c r="N328" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O328" s="41" t="inlineStr">
@@ -27766,7 +27762,7 @@
       </c>
       <c r="N336" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O336" s="41" t="inlineStr">
@@ -27845,7 +27841,7 @@
       </c>
       <c r="N337" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O337" s="41" t="inlineStr">
@@ -29702,7 +29698,7 @@
       <c r="G361" s="39" t="inlineStr">
         <is>
           <t>ได้  
-นักศึกษาชั้นปีสุดท้ายที่เหลือรายวิชาไม่ถึง 9 หน่วยกิต หรือต้องลงเกิน 22 หน่วยกิตเพื่อสำเร็จการศึกษา สามารถลงทะเบียนได้สูงสุดไม่เกิน 27 หน่วยกิต โดยต้องได้รับอนุมัติจากสภาวิชาการ ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 82 ซึ่งระบุไว้ชัดเจนว่า ข้อยกเว้นสำหรับนักศึกษาชั้นปีสุดท้ายสามารถลงทะเบียนได้สูงสุด 27 หน่วยกิต</t>
+นักศึกษาชั้นปีสุดท้ายที่เหลือรายวิชาไม่ถึง 9 หน่วยกิต หรือต้องลงเกิน 22 หน่วยกิตเพื่อสำเร็จการศึกษา สามารถลงทะเบียนได้สูงสุดไม่เกิน 27 หน่วยกิต โดยต้องได้รับอนุมัติจากสภาวิชาการ ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 82 ซึ่งระบุไว้ชัดเจนสำหรับกรณีปีสุดท้าย</t>
         </is>
       </c>
       <c r="H361" s="39" t="inlineStr">
@@ -29735,7 +29731,7 @@
       </c>
       <c r="N361" s="39" t="inlineStr">
         <is>
-          <t>2.20s</t>
+          <t>1.51s</t>
         </is>
       </c>
       <c r="O361" s="41" t="inlineStr">
@@ -30688,7 +30684,7 @@
       </c>
       <c r="N373" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O373" s="41" t="inlineStr">
@@ -30843,7 +30839,7 @@
       </c>
       <c r="N375" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O375" s="41" t="inlineStr">
@@ -32008,7 +32004,7 @@
       </c>
       <c r="N390" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O390" s="41" t="inlineStr">
@@ -32087,7 +32083,7 @@
       </c>
       <c r="N391" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O391" s="41" t="inlineStr">
@@ -32558,7 +32554,7 @@
       </c>
       <c r="N397" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O397" s="41" t="inlineStr">
@@ -33196,7 +33192,7 @@
       </c>
       <c r="N405" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O405" s="41" t="inlineStr">
@@ -33350,7 +33346,7 @@
       </c>
       <c r="N407" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O407" s="41" t="inlineStr">
@@ -33504,7 +33500,7 @@
       </c>
       <c r="N409" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O409" s="41" t="inlineStr">
@@ -36267,7 +36263,7 @@
       </c>
       <c r="N444" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O444" s="41" t="inlineStr">
@@ -36346,7 +36342,7 @@
       </c>
       <c r="N445" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O445" s="41" t="inlineStr">
@@ -36423,7 +36419,7 @@
       </c>
       <c r="N446" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O446" s="41" t="inlineStr">
@@ -36577,7 +36573,7 @@
       </c>
       <c r="N448" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O448" s="41" t="inlineStr">
@@ -36820,7 +36816,7 @@
       </c>
       <c r="N451" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O451" s="41" t="inlineStr">
@@ -37445,7 +37441,7 @@
       </c>
       <c r="N459" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O459" s="41" t="inlineStr">
@@ -39175,7 +39171,7 @@
       </c>
       <c r="N481" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O481" s="41" t="inlineStr">
@@ -39881,7 +39877,7 @@
       </c>
       <c r="N490" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O490" s="41" t="inlineStr">
@@ -40195,7 +40191,7 @@
       </c>
       <c r="N494" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O494" s="41" t="inlineStr">
@@ -40349,7 +40345,7 @@
       </c>
       <c r="N496" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O496" s="41" t="inlineStr">
@@ -40675,7 +40671,7 @@
       </c>
       <c r="N500" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O500" s="41" t="inlineStr">
@@ -40912,7 +40908,7 @@
       </c>
       <c r="N503" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O503" s="41" t="inlineStr">
@@ -40991,7 +40987,7 @@
       </c>
       <c r="N504" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O504" s="41" t="inlineStr">
@@ -41147,7 +41143,7 @@
       </c>
       <c r="N506" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O506" s="41" t="inlineStr">
@@ -41224,7 +41220,7 @@
       </c>
       <c r="N507" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O507" s="41" t="inlineStr">
@@ -41390,7 +41386,7 @@
       </c>
       <c r="N509" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O509" s="41" t="inlineStr">
@@ -41469,7 +41465,7 @@
       </c>
       <c r="N510" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O510" s="41" t="inlineStr">
@@ -41627,7 +41623,7 @@
       </c>
       <c r="N512" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O512" s="41" t="inlineStr">
@@ -42441,7 +42437,7 @@
       </c>
       <c r="N522" s="39" t="inlineStr">
         <is>
-          <t>0.49s</t>
+          <t>0.53s</t>
         </is>
       </c>
       <c r="O522" s="41" t="inlineStr">
@@ -42519,7 +42515,7 @@
       </c>
       <c r="N523" s="39" t="inlineStr">
         <is>
-          <t>0.04s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O523" s="41" t="inlineStr">
@@ -42683,7 +42679,7 @@
       </c>
       <c r="N525" s="39" t="inlineStr">
         <is>
-          <t>0.23s</t>
+          <t>0.26s</t>
         </is>
       </c>
       <c r="O525" s="41" t="inlineStr">
@@ -43002,7 +42998,7 @@
       </c>
       <c r="N529" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O529" s="41" t="inlineStr">
@@ -43474,7 +43470,7 @@
       </c>
       <c r="N535" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O535" s="41" t="inlineStr">
@@ -44334,7 +44330,7 @@
       </c>
       <c r="N546" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O546" s="41" t="inlineStr">
@@ -44413,7 +44409,7 @@
       </c>
       <c r="N547" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O547" s="41" t="inlineStr">
@@ -44570,7 +44566,7 @@
       </c>
       <c r="N549" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O549" s="41" t="inlineStr">
@@ -44930,7 +44926,7 @@
       </c>
       <c r="N553" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O553" s="41" t="inlineStr">
@@ -45262,7 +45258,7 @@
       </c>
       <c r="N557" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O557" s="41" t="inlineStr">
@@ -45346,7 +45342,7 @@
       </c>
       <c r="N558" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O558" s="41" t="inlineStr">
@@ -46059,7 +46055,7 @@
       </c>
       <c r="N567" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O567" s="41" t="inlineStr">
@@ -46138,7 +46134,7 @@
       </c>
       <c r="N568" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O568" s="41" t="inlineStr">
@@ -46246,7 +46242,7 @@
       </c>
       <c r="N569" s="39" t="inlineStr">
         <is>
-          <t>0.27s</t>
+          <t>0.34s</t>
         </is>
       </c>
       <c r="O569" s="41" t="inlineStr">
@@ -47115,7 +47111,7 @@
       </c>
       <c r="N580" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O580" s="41" t="inlineStr">
@@ -48611,7 +48607,7 @@
       </c>
       <c r="N599" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O599" s="41" t="inlineStr">
@@ -48654,7 +48650,7 @@
       <c r="G600" s="39" t="inlineStr">
         <is>
           <t>ไม่ได้  
-นักศึกษาทั่วไปต้องลงทะเบียนไม่เกิน 22 หน่วยกิตต่อภาคการศึกษาปกติ ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (หน้า 82) แม้จะเป็นนักศึกษาชั้นปีสุดท้ายก็ยังจำกัดที่ 27 หน่วยกิต แต่ต้องมีเหตุผลเฉพาะเจาะจง และต้องได้รับอนุมัติจากสภาวิชาการ ซึ่งไม่ได้ระบุว่าสามารถลง 25 หน่วยกิตได้โดยอัตโนมัติ</t>
+นักศึกษาทั่วไปต้องลงทะเบียนไม่เกิน 22 หน่วยกิตต่อภาคการศึกษาปกติ ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 82 แม้จะเป็นนักศึกษาชั้นปีสุดท้ายก็ตาม แต่ต้องไม่เกิน 27 หน่วยกิต หากมีข้อยกเว้นเฉพาะกรณีที่เหลือรายวิชาไม่ถึง 3 หน่วยกิต หรือต้องลงเพื่อสำเร็จการศึกษา ซึ่งไม่ได้ระบุว่าเป็นกรณีนี้ ดังนั้นการลง 25 หน่วยกิตเกินข้อจำกัดปกติ และไม่มีหลักฐานยืนยันว่าเข้าข่ายข้อยกเว้น</t>
         </is>
       </c>
       <c r="H600" s="39" t="inlineStr">
@@ -48687,7 +48683,7 @@
       </c>
       <c r="N600" s="39" t="inlineStr">
         <is>
-          <t>1.47s</t>
+          <t>2.24s</t>
         </is>
       </c>
       <c r="O600" s="41" t="inlineStr">
@@ -48767,7 +48763,7 @@
       </c>
       <c r="N601" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O601" s="41" t="inlineStr">
@@ -48921,7 +48917,7 @@
       </c>
       <c r="N603" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O603" s="41" t="inlineStr">
@@ -48998,7 +48994,7 @@
       </c>
       <c r="N604" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O604" s="41" t="inlineStr">
@@ -49157,7 +49153,7 @@
       </c>
       <c r="N606" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O606" s="41" t="inlineStr">
@@ -49235,7 +49231,7 @@
       </c>
       <c r="N607" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O607" s="41" t="inlineStr">
@@ -49312,7 +49308,7 @@
       </c>
       <c r="N608" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O608" s="41" t="inlineStr">
@@ -49469,7 +49465,7 @@
       </c>
       <c r="N610" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O610" s="41" t="inlineStr">
@@ -49546,7 +49542,7 @@
       </c>
       <c r="N611" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O611" s="41" t="inlineStr">
@@ -51007,7 +51003,7 @@
       <c r="G630" s="39" t="inlineStr">
         <is>
           <t>ไม่ได้  
-นักศึกษาต้องลงทะเบียนไม่น้อยกว่า 9 หน่วยกิตในภาคการศึกษาปกติ ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 82 ซึ่งเป็นข้อกำหนดบังคับสำหรับทุกหลักสูตรปริญญาตรี ไม่ใช่ข้อยกเว้นเฉพาะหลักสูตร DSBA</t>
+นักศึกษาต้องลงทะเบียนไม่น้อยกว่า 9 หน่วยกิตในภาคการศึกษาปกติ ตามข้อบังคับสถาบันเทคโนโลยีพระจอมเกล้าเจ้าคุณทหารลาดกระบัง ว่าด้วยการศึกษาระดับปริญญาตรี พ.ศ. 2564 (ภาคผนวก ก) ซึ่งใช้กับหลักสูตรวท.บ. (วิทยาการข้อมูลและการวิเคราะห์เชิงธุรกิจ) คณะเทคโนโลยีสารสนเทศ สจล. ทุกภาคการศึกษาปกติ</t>
         </is>
       </c>
       <c r="H630" s="39" t="inlineStr">
@@ -51040,7 +51036,7 @@
       </c>
       <c r="N630" s="39" t="inlineStr">
         <is>
-          <t>1.41s</t>
+          <t>1.61s</t>
         </is>
       </c>
       <c r="O630" s="41" t="inlineStr">
@@ -51083,7 +51079,9 @@
       <c r="G631" s="39" t="inlineStr">
         <is>
           <t>ได้  
-นักศึกษาสามารถลงทะเบียนเรียนได้ไม่เกิน 9 หน่วยกิตในภาคการศึกษาพิเศษ (ซัมเมอร์) ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 82 หากลงฝึกงานในภาคพิเศษ จะไม่สามารถลงวิชาอื่นได้ในภาคเดียวกัน เนื่องจากเป็นข้อห้ามโดยตรงในข้อบังคับดังกล่าว</t>
+นักศึกษาสามารถลงทะเบียนเรียนได้ไม่เกิน 9 หน่วยกิตในภาคการศึกษาพิเศษ (ภาคฤดูร้อน) ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 82  
+หากลงฝึกงานในภาคพิเศษ ห้ามลงทะเบียนเรียนรายวิชาอื่นเพิ่มเติมได้  
+ประเภทวิชา: ภาคการศึกษาพิเศษ, ข้อบังคับการลงทะเบียนเรียน</t>
         </is>
       </c>
       <c r="H631" s="39" t="inlineStr">
@@ -51116,7 +51114,7 @@
       </c>
       <c r="N631" s="39" t="inlineStr">
         <is>
-          <t>1.52s</t>
+          <t>1.75s</t>
         </is>
       </c>
       <c r="O631" s="41" t="inlineStr">
@@ -51356,34 +51354,2182 @@
         </is>
       </c>
     </row>
-    <row r="635" ht="14.25" customHeight="1" s="36"/>
-    <row r="636" ht="14.25" customHeight="1" s="36"/>
-    <row r="637" ht="14.25" customHeight="1" s="36"/>
-    <row r="638" ht="14.25" customHeight="1" s="36"/>
-    <row r="639" ht="14.25" customHeight="1" s="36"/>
-    <row r="640" ht="14.25" customHeight="1" s="36"/>
-    <row r="641" ht="14.25" customHeight="1" s="36"/>
-    <row r="642" ht="14.25" customHeight="1" s="36"/>
-    <row r="643" ht="14.25" customHeight="1" s="36"/>
-    <row r="644" ht="14.25" customHeight="1" s="36"/>
-    <row r="645" ht="14.25" customHeight="1" s="36"/>
-    <row r="646" ht="14.25" customHeight="1" s="36"/>
-    <row r="647" ht="14.25" customHeight="1" s="36"/>
-    <row r="648" ht="14.25" customHeight="1" s="36"/>
-    <row r="649" ht="14.25" customHeight="1" s="36"/>
-    <row r="650" ht="14.25" customHeight="1" s="36"/>
-    <row r="651" ht="14.25" customHeight="1" s="36"/>
-    <row r="652" ht="14.25" customHeight="1" s="36"/>
-    <row r="653" ht="14.25" customHeight="1" s="36"/>
-    <row r="654" ht="14.25" customHeight="1" s="36"/>
-    <row r="655" ht="14.25" customHeight="1" s="36"/>
-    <row r="656" ht="14.25" customHeight="1" s="36"/>
-    <row r="657" ht="14.25" customHeight="1" s="36"/>
-    <row r="658" ht="14.25" customHeight="1" s="36"/>
-    <row r="659" ht="14.25" customHeight="1" s="36"/>
-    <row r="660" ht="14.25" customHeight="1" s="36"/>
-    <row r="661" ht="14.25" customHeight="1" s="36"/>
-    <row r="662" ht="14.25" customHeight="1" s="36"/>
+    <row r="635" ht="14.25" customHeight="1" s="36">
+      <c r="A635" s="37" t="inlineStr">
+        <is>
+          <t>QH1</t>
+        </is>
+      </c>
+      <c r="B635" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C635" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D635" s="39" t="inlineStr">
+        <is>
+          <t>ถ้าลงตามแผน ปี 3 เทอม 1 ทั้งเทอมรวมกี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E635" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่) — ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่)</t>
+        </is>
+      </c>
+      <c r="F635" s="39" t="inlineStr">
+        <is>
+          <t>18 หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="G635" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ปีที่ 3 ภาคการศึกษาที่ 1 ตามแผนปกติของ AIT 2566 (ปริญญาตรี) ลงรวม 18 หน่วยกิต
+- จากบรรทัด 'รวม' ของภาคนี้ในตารางแผนการศึกษา หน้า 25 (รวมวิชาเลือก/ศึกษาทั่วไปที่แผนกำหนดไว้แล้ว ไม่ใช่เฉพาะวิชาบังคับ)</t>
+        </is>
+      </c>
+      <c r="H635" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 25</t>
+        </is>
+      </c>
+      <c r="I635" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวมของภาคตามแผน) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J635" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K635" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L635" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M635" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N635" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O635" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="636" ht="14.25" customHeight="1" s="36">
+      <c r="A636" s="37" t="inlineStr">
+        <is>
+          <t>QH2</t>
+        </is>
+      </c>
+      <c r="B636" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C636" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D636" s="39" t="inlineStr">
+        <is>
+          <t>วิชาที่ต้องผ่านก่อนลงการเรียนรู้ของเครื่องเชิงความน่าจะเป็น คือวิชาอะไร แล้ววิชานั้นอยู่ปีไหนเทอมไหน</t>
+        </is>
+      </c>
+      <c r="E636" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่) — ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่)</t>
+        </is>
+      </c>
+      <c r="F636" s="39" t="inlineStr">
+        <is>
+          <t>06066001 ปี 1 ภาค 1</t>
+        </is>
+      </c>
+      <c r="G636" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06046405 การเรียนรู้ของเครื่องเชิงความน่าจะเป็น (PROBABILISTIC MACHINE LEARNING) — 3(3-0-6) | ปีที่ 2 ภาคการศึกษาที่ 1
+  ต้องผ่านวิชาบังคับก่อน:
+    • 06066001 ความน่าจะเป็นและสถิติ (PROBABILITY AND STATISTICS) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H636" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 37, 291, 19, 20, 23, 24, 289</t>
+        </is>
+      </c>
+      <c r="I636" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (prerequisite) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J636" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="K636" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L636" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M636" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N636" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O636" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="637" ht="14.25" customHeight="1" s="36">
+      <c r="A637" s="37" t="inlineStr">
+        <is>
+          <t>QH3</t>
+        </is>
+      </c>
+      <c r="B637" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C637" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D637" s="39" t="inlineStr">
+        <is>
+          <t>ก่อนจะลงวิชาการเรียนรู้ของเครื่องเชิงความน่าจะเป็น ต้องสอบผ่านวิชาอะไรมาก่อน และตัววิชานี้อยู่ในแผนปีไหน</t>
+        </is>
+      </c>
+      <c r="E637" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่) — ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่)</t>
+        </is>
+      </c>
+      <c r="F637" s="39" t="inlineStr">
+        <is>
+          <t>06066001; ปี 2 ภาค 1</t>
+        </is>
+      </c>
+      <c r="G637" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06046405 การเรียนรู้ของเครื่องเชิงความน่าจะเป็น (PROBABILISTIC MACHINE LEARNING) — 3(3-0-6) | ปีที่ 2 ภาคการศึกษาที่ 1
+  ต้องผ่านวิชาบังคับก่อน:
+    • 06066001 ความน่าจะเป็นและสถิติ (PROBABILITY AND STATISTICS) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H637" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 37, 291, 19, 20, 23, 24, 289</t>
+        </is>
+      </c>
+      <c r="I637" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (prerequisite) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J637" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="K637" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L637" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M637" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N637" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O637" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="638" ht="14.25" customHeight="1" s="36">
+      <c r="A638" s="37" t="inlineStr">
+        <is>
+          <t>QC1</t>
+        </is>
+      </c>
+      <c r="B638" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C638" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D638" s="39" t="inlineStr">
+        <is>
+          <t>เทอมเดียวกันจะลงแคลคูลัส 2 พร้อมกับพื้นฐานการเรียนรู้เชิงลึก เลยได้ไหม</t>
+        </is>
+      </c>
+      <c r="E638" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่) — ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่)</t>
+        </is>
+      </c>
+      <c r="F638" s="39" t="inlineStr">
+        <is>
+          <t>ไม่ได้ ต้องผ่าน 06046401 ก่อน</t>
+        </is>
+      </c>
+      <c r="G638" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ไม่ได้ — ต้องสอบผ่าน 06046401 แคลคูลัส 2 ก่อน จึงจะลง 06046406 พื้นฐานการเรียนรู้เชิงลึก ได้ จึงลงพร้อมกันในภาคเดียวกันไม่ได้
+- 06046401 แคลคูลัส 2 (CALCULUS 2) — ปีที่ 1 ภาคการศึกษาที่ 2
+- 06046406 พื้นฐานการเรียนรู้เชิงลึก (FUNDAMENTALS OF DEEP LEARNING) — ปีที่ 2 ภาคการศึกษาที่ 1
+- 06046406 มีวิชาบังคับก่อนเป็น 06046401 (ต้องสอบผ่าน 06046401 ก่อนจึงลง 06046406 ได้)</t>
+        </is>
+      </c>
+      <c r="H638" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 37, 292, 19, 20, 23, 24, 287</t>
+        </is>
+      </c>
+      <c r="I638" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (เทียบปี/ภาคของสองวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J638" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="K638" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L638" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M638" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N638" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O638" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="639" ht="14.25" customHeight="1" s="36">
+      <c r="A639" s="37" t="inlineStr">
+        <is>
+          <t>QC2</t>
+        </is>
+      </c>
+      <c r="B639" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C639" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D639" s="39" t="inlineStr">
+        <is>
+          <t>ปี 2 ภาค 2 ตามแผนต้องลงกี่หน่วยกิต เกินเพดานที่ลงได้ต่อภาคปกติไหม</t>
+        </is>
+      </c>
+      <c r="E639" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่) — ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่)</t>
+        </is>
+      </c>
+      <c r="F639" s="39" t="inlineStr">
+        <is>
+          <t>19 หน่วยกิต ไม่เกิน 22</t>
+        </is>
+      </c>
+      <c r="G639" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ปีที่ 2 ภาคการศึกษาที่ 2 ตามแผนปกติของ AIT 2566 (ปริญญาตรี) ลงรวม 19 หน่วยกิต
+- จากบรรทัด 'รวม' ของภาคนี้ในตารางแผนการศึกษา หน้า 24 (รวมวิชาเลือก/ศึกษาทั่วไปที่แผนกำหนดไว้แล้ว ไม่ใช่เฉพาะวิชาบังคับ)
+- ข้อบังคับ: ภาคการศึกษาปกติลงทะเบียนได้ 9–22 หน่วยกิต → 19 หน่วยกิต อยู่ในเกณฑ์ ไม่เกินเพดาน 22</t>
+        </is>
+      </c>
+      <c r="H639" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 24, 82</t>
+        </is>
+      </c>
+      <c r="I639" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวมของภาคตามแผน) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J639" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K639" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L639" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M639" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N639" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O639" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="640" ht="14.25" customHeight="1" s="36">
+      <c r="A640" s="37" t="inlineStr">
+        <is>
+          <t>QH4</t>
+        </is>
+      </c>
+      <c r="B640" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C640" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D640" s="39" t="inlineStr">
+        <is>
+          <t>ถ้าลงตามแผน ปี 3 เทอม 2 ทั้งเทอมรวมกี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E640" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่) — ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่)</t>
+        </is>
+      </c>
+      <c r="F640" s="39" t="inlineStr">
+        <is>
+          <t>9 หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="G640" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ปีที่ 3 ภาคการศึกษาที่ 2 ตามแผนปกติของ BIT 2565 (ปริญญาตรี) ลงรวม 12 หน่วยกิต
+- จากบรรทัด 'รวม' ของภาคนี้ในตารางแผนการศึกษา หน้า 29 (รวมวิชาเลือก/ศึกษาทั่วไปที่แผนกำหนดไว้แล้ว ไม่ใช่เฉพาะวิชาบังคับ)</t>
+        </is>
+      </c>
+      <c r="H640" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 29</t>
+        </is>
+      </c>
+      <c r="I640" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวมของภาคตามแผน) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J640" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K640" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L640" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M640" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N640" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O640" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="641" ht="14.25" customHeight="1" s="36">
+      <c r="A641" s="37" t="inlineStr">
+        <is>
+          <t>QH5</t>
+        </is>
+      </c>
+      <c r="B641" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C641" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D641" s="39" t="inlineStr">
+        <is>
+          <t>วิชาที่ต้องผ่านก่อนลงการพัฒนาเว็บแอปพลิเคชันโดยใช้เฟรมเวิร์ก คือวิชาอะไร แล้ววิชานั้นอยู่ปีไหนเทอมไหน</t>
+        </is>
+      </c>
+      <c r="E641" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่) — ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่)</t>
+        </is>
+      </c>
+      <c r="F641" s="39" t="inlineStr">
+        <is>
+          <t>06036119 ปี 1 ภาค 2</t>
+        </is>
+      </c>
+      <c r="G641" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06036114 การพัฒนาเว็บแอปพลิเคชันโดยใช้เฟรมเวิร์ก (WEB APPLICATION DEVELOPMENT USING FRAMEWORKS) — 3(2-2-5) | ปีที่ 3 ภาคการศึกษาที่ 1
+  ต้องผ่านวิชาบังคับก่อน:
+    • 06036119 พื้นฐานการเขียนโปรแกรม (PROGRAMMING FUNDAMENTALS) — 3(2-2-5) | ปีที่ 1 ภาคการศึกษาที่ 2
+    • 06036122 การสื่อสารด้วยภาพสำหรับธุรกิจ (VISUAL COMMUNICATION FOR BUSINESS) — 3(2-2-5) | ปีที่ 2 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H641" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 75, 23, 244, 270, 22, 27, 28, 32</t>
+        </is>
+      </c>
+      <c r="I641" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (prerequisite) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J641" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K641" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L641" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M641" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N641" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O641" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="642" ht="14.25" customHeight="1" s="36">
+      <c r="A642" s="37" t="inlineStr">
+        <is>
+          <t>QH6</t>
+        </is>
+      </c>
+      <c r="B642" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C642" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D642" s="39" t="inlineStr">
+        <is>
+          <t>ก่อนจะลงวิชาการพัฒนาเว็บแอปพลิเคชันโดยใช้เฟรมเวิร์ก ต้องสอบผ่านวิชาอะไรมาก่อน และตัววิชานี้อยู่ในแผนปีไหน</t>
+        </is>
+      </c>
+      <c r="E642" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่) — ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่)</t>
+        </is>
+      </c>
+      <c r="F642" s="39" t="inlineStr">
+        <is>
+          <t>06036119, 06036122; ปี 3 ภาค 1</t>
+        </is>
+      </c>
+      <c r="G642" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06036114 การพัฒนาเว็บแอปพลิเคชันโดยใช้เฟรมเวิร์ก (WEB APPLICATION DEVELOPMENT USING FRAMEWORKS) — 3(2-2-5) | ปีที่ 3 ภาคการศึกษาที่ 1
+  ต้องผ่านวิชาบังคับก่อน:
+    • 06036119 พื้นฐานการเขียนโปรแกรม (PROGRAMMING FUNDAMENTALS) — 3(2-2-5) | ปีที่ 1 ภาคการศึกษาที่ 2
+    • 06036122 การสื่อสารด้วยภาพสำหรับธุรกิจ (VISUAL COMMUNICATION FOR BUSINESS) — 3(2-2-5) | ปีที่ 2 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H642" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 75, 23, 244, 270, 22, 27, 28, 32</t>
+        </is>
+      </c>
+      <c r="I642" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (prerequisite) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J642" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K642" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L642" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M642" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N642" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O642" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="643" ht="14.25" customHeight="1" s="36">
+      <c r="A643" s="37" t="inlineStr">
+        <is>
+          <t>QC3</t>
+        </is>
+      </c>
+      <c r="B643" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C643" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D643" s="39" t="inlineStr">
+        <is>
+          <t>เทอมเดียวกันจะลงการสื่อสารด้วยภาพสำหรับธุรกิจ พร้อมกับการพัฒนาเว็บแอปพลิเคชันโดยใช้เฟรมเวิร์ก เลยได้ไหม</t>
+        </is>
+      </c>
+      <c r="E643" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่) — ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่)</t>
+        </is>
+      </c>
+      <c r="F643" s="39" t="inlineStr">
+        <is>
+          <t>ไม่ได้ ต้องผ่าน 06036122 ก่อน</t>
+        </is>
+      </c>
+      <c r="G643" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ไม่ได้ — ต้องสอบผ่าน 06036122 การสื่อสารด้วยภาพสำหรับธุรกิจ ก่อน จึงจะลง 06036114 การพัฒนาเว็บแอปพลิเคชันโดยใช้เฟรมเวิร์ก ได้ จึงลงพร้อมกันในภาคเดียวกันไม่ได้
+- 06036122 การสื่อสารด้วยภาพสำหรับธุรกิจ (VISUAL COMMUNICATION FOR BUSINESS) — ปีที่ 2 ภาคการศึกษาที่ 1
+- 06036114 การพัฒนาเว็บแอปพลิเคชันโดยใช้เฟรมเวิร์ก (WEB APPLICATION DEVELOPMENT USING FRAMEWORKS) — ปีที่ 3 ภาคการศึกษาที่ 1
+- 06036114 มีวิชาบังคับก่อนเป็น 06036122 (ต้องสอบผ่าน 06036122 ก่อนจึงลง 06036114 ได้)</t>
+        </is>
+      </c>
+      <c r="H643" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 75, 22, 23, 27, 28, 244, 247, 269</t>
+        </is>
+      </c>
+      <c r="I643" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (เทียบปี/ภาคของสองวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J643" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K643" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L643" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M643" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N643" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O643" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="644" ht="14.25" customHeight="1" s="36">
+      <c r="A644" s="37" t="inlineStr">
+        <is>
+          <t>QC4</t>
+        </is>
+      </c>
+      <c r="B644" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C644" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D644" s="39" t="inlineStr">
+        <is>
+          <t>ปี 3 ภาค 1 ตามแผนต้องลงกี่หน่วยกิต เกินเพดานที่ลงได้ต่อภาคปกติไหม</t>
+        </is>
+      </c>
+      <c r="E644" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่) — ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่)</t>
+        </is>
+      </c>
+      <c r="F644" s="39" t="inlineStr">
+        <is>
+          <t>18 หน่วยกิต ไม่เกิน 22</t>
+        </is>
+      </c>
+      <c r="G644" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ปีที่ 3 ภาคการศึกษาที่ 1 ตามแผนปกติของ BIT 2565 (ปริญญาตรี) ลงรวม 18 หน่วยกิต
+- จากบรรทัด 'รวม' ของภาคนี้ในตารางแผนการศึกษา หน้า 28 (รวมวิชาเลือก/ศึกษาทั่วไปที่แผนกำหนดไว้แล้ว ไม่ใช่เฉพาะวิชาบังคับ)
+- ข้อบังคับ: ภาคการศึกษาปกติลงทะเบียนได้ 9–22 หน่วยกิต → 18 หน่วยกิต อยู่ในเกณฑ์ ไม่เกินเพดาน 22</t>
+        </is>
+      </c>
+      <c r="H644" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 28, 82</t>
+        </is>
+      </c>
+      <c r="I644" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวมของภาคตามแผน) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J644" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K644" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L644" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M644" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N644" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O644" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="645" ht="14.25" customHeight="1" s="36">
+      <c r="A645" s="37" t="inlineStr">
+        <is>
+          <t>QH7</t>
+        </is>
+      </c>
+      <c r="B645" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C645" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D645" s="39" t="inlineStr">
+        <is>
+          <t>ถ้าลงตามแผน ปี 2 เทอม 2 ทั้งเทอมรวมกี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E645" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่) — ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่)</t>
+        </is>
+      </c>
+      <c r="F645" s="39" t="inlineStr">
+        <is>
+          <t>21 หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="G645" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ปีที่ 2 ภาคการศึกษาที่ 2 ตามแผนปกติของ DSBA 2565 (ปริญญาตรี) ลงรวม 21 หน่วยกิต
+- จากบรรทัด 'รวม' ของภาคนี้ในตารางแผนการศึกษา หน้า 26 (รวมวิชาเลือก/ศึกษาทั่วไปที่แผนกำหนดไว้แล้ว ไม่ใช่เฉพาะวิชาบังคับ)</t>
+        </is>
+      </c>
+      <c r="H645" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 26</t>
+        </is>
+      </c>
+      <c r="I645" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวมของภาคตามแผน) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J645" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K645" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L645" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M645" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N645" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O645" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="646" ht="14.25" customHeight="1" s="36">
+      <c r="A646" s="37" t="inlineStr">
+        <is>
+          <t>QH8</t>
+        </is>
+      </c>
+      <c r="B646" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C646" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D646" s="39" t="inlineStr">
+        <is>
+          <t>วิชาที่ต้องผ่านก่อนลงแคลคูลัส 2 คือวิชาอะไร แล้ววิชานั้นอยู่ปีไหนเทอมไหน</t>
+        </is>
+      </c>
+      <c r="E646" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่) — ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่)</t>
+        </is>
+      </c>
+      <c r="F646" s="39" t="inlineStr">
+        <is>
+          <t>06026200 ปี 1 ภาค 1</t>
+        </is>
+      </c>
+      <c r="G646" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06026201 แคลคูลัส 2 (CALCULUS 2) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 2
+  ต้องผ่านวิชาบังคับก่อน:
+    • 06026200 แคลคูลัส 1 (CALCULUS 1) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H646" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 17, 68, 314, 353, 23, 24, 30, 31</t>
+        </is>
+      </c>
+      <c r="I646" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (prerequisite) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J646" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K646" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L646" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M646" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N646" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O646" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="647" ht="14.25" customHeight="1" s="36">
+      <c r="A647" s="37" t="inlineStr">
+        <is>
+          <t>QH9</t>
+        </is>
+      </c>
+      <c r="B647" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C647" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D647" s="39" t="inlineStr">
+        <is>
+          <t>ก่อนจะลงวิชาโครงงานวิทยาการข้อมูลและการวิเคราะห์เชิงธุรกิจ 2 ต้องสอบผ่านวิชาอะไรมาก่อน และตัววิชานี้อยู่ในแผนปีไหน</t>
+        </is>
+      </c>
+      <c r="E647" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่) — ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่)</t>
+        </is>
+      </c>
+      <c r="F647" s="39" t="inlineStr">
+        <is>
+          <t>06026214; ปี 4 ภาค 1</t>
+        </is>
+      </c>
+      <c r="G647" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06026215 โครงงานวิทยาการข้อมูลและการวิเคราะห์เชิงธุรกิจ 2 (PROJECT IN DATA SCIENCE AND BUSINESS ANALYTICS 2) — 3(0-9-0) | ปีที่ 4 ภาคการศึกษาที่ 1
+  ต้องผ่านวิชาบังคับก่อน:
+    • 06026214 โครงงานวิทยาการข้อมูลและการวิเคราะห์เชิงธุรกิจ 1 (PROJECT IN DATA SCIENCE AND BUSINESS ANALYTICS 1) — 3(0-9-0) | ปีที่ 3 ภาคการศึกษาที่ 2</t>
+        </is>
+      </c>
+      <c r="H647" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 19, 69, 325, 354, 28, 29, 35, 36</t>
+        </is>
+      </c>
+      <c r="I647" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (prerequisite) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J647" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K647" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L647" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M647" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N647" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O647" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="648" ht="14.25" customHeight="1" s="36">
+      <c r="A648" s="37" t="inlineStr">
+        <is>
+          <t>QC5</t>
+        </is>
+      </c>
+      <c r="B648" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C648" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D648" s="39" t="inlineStr">
+        <is>
+          <t>เทอมเดียวกันจะลงแนวคิดระบบฐานข้อมูล พร้อมกับระบบข้อมูลมหัต เลยได้ไหม</t>
+        </is>
+      </c>
+      <c r="E648" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่) — ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่)</t>
+        </is>
+      </c>
+      <c r="F648" s="39" t="inlineStr">
+        <is>
+          <t>ไม่ได้ ต้องผ่าน 06066300 ก่อน</t>
+        </is>
+      </c>
+      <c r="G648" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ไม่ได้ — ต้องสอบผ่าน 06066300 แนวคิดระบบฐานข้อมูล ก่อน จึงจะลง 06026213 ระบบข้อมูลมหัต ได้ จึงลงพร้อมกันในภาคเดียวกันไม่ได้
+- 06066300 แนวคิดระบบฐานข้อมูล (DATABASE SYSTEM CONCEPTS) — ปีที่ 2 ภาคการศึกษาที่ 1
+- 06026213 ระบบข้อมูลมหัต (BIG DATA SYSTEMS) — ปีที่ 3 ภาคการศึกษาที่ 2
+- 06026213 มีวิชาบังคับก่อนเป็น 06066300 (ต้องสอบผ่าน 06066300 ก่อนจึงลง 06026213 ได้)</t>
+        </is>
+      </c>
+      <c r="H648" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 18, 19, 25, 28, 32, 35, 69, 73</t>
+        </is>
+      </c>
+      <c r="I648" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (เทียบปี/ภาคของสองวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J648" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K648" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L648" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M648" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N648" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O648" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="649" ht="14.25" customHeight="1" s="36">
+      <c r="A649" s="37" t="inlineStr">
+        <is>
+          <t>QH10</t>
+        </is>
+      </c>
+      <c r="B649" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C649" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D649" s="39" t="inlineStr">
+        <is>
+          <t>ถ้าลงตามแผน ปี 2 เทอม 1 ทั้งเทอมรวมกี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E649" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่) — ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่)</t>
+        </is>
+      </c>
+      <c r="F649" s="39" t="inlineStr">
+        <is>
+          <t>18 หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="G649" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ปีที่ 2 ภาคการศึกษาที่ 1 ตามแผนปกติของ IT 2565 (ปริญญาตรี) ลงรวม 18 หน่วยกิต
+- จากบรรทัด 'รวม' ของภาคนี้ในตารางแผนการศึกษา หน้า 33 (รวมวิชาเลือก/ศึกษาทั่วไปที่แผนกำหนดไว้แล้ว ไม่ใช่เฉพาะวิชาบังคับ)</t>
+        </is>
+      </c>
+      <c r="H649" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 33</t>
+        </is>
+      </c>
+      <c r="I649" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวมของภาคตามแผน) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J649" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K649" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L649" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M649" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N649" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O649" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="650" ht="14.25" customHeight="1" s="36">
+      <c r="A650" s="37" t="inlineStr">
+        <is>
+          <t>QH11</t>
+        </is>
+      </c>
+      <c r="B650" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C650" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D650" s="39" t="inlineStr">
+        <is>
+          <t>วิชาที่ต้องผ่านก่อนลงอินเทอร์เน็ตของสรรพสิ่ง คือวิชาอะไร แล้ววิชานั้นอยู่ปีไหนเทอมไหน</t>
+        </is>
+      </c>
+      <c r="E650" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่) — ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่)</t>
+        </is>
+      </c>
+      <c r="F650" s="39" t="inlineStr">
+        <is>
+          <t>06016413 ปี 2 ภาค 1</t>
+        </is>
+      </c>
+      <c r="G650" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06016422 อินเทอร์เน็ตของสรรพสิ่ง (INTERNET OF THINGS) — 3(2-2-5) | ปีที่ 3 ภาคการศึกษาที่ 1
+  ต้องผ่านวิชาบังคับก่อน:
+    • 06016413 ระบบเครือข่ายเบื้องต้น (INTRODUCTION TO NETWORK SYSTEMS) — 3(3-0-6) | ปีที่ 2 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H650" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 84, 333, 24, 25, 33, 35, 40, 328</t>
+        </is>
+      </c>
+      <c r="I650" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (prerequisite) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J650" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K650" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L650" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M650" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N650" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O650" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="651" ht="14.25" customHeight="1" s="36">
+      <c r="A651" s="37" t="inlineStr">
+        <is>
+          <t>QH12</t>
+        </is>
+      </c>
+      <c r="B651" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C651" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D651" s="39" t="inlineStr">
+        <is>
+          <t>ก่อนจะลงวิชาระบบโครงสร้างพื้นฐานและการบริการ ต้องสอบผ่านวิชาอะไรมาก่อน และตัววิชานี้อยู่ในแผนปีไหน</t>
+        </is>
+      </c>
+      <c r="E651" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่) — ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่)</t>
+        </is>
+      </c>
+      <c r="F651" s="39" t="inlineStr">
+        <is>
+          <t>06016413; ปี 2 ภาค 2</t>
+        </is>
+      </c>
+      <c r="G651" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06016420 ระบบโครงสร้างพื้นฐานและการบริการ (INFRASTRUCTURE SYSTEMS AND SERVICES) — 3(2-2-5) | ปีที่ 2 ภาคการศึกษาที่ 2
+  ต้องผ่านวิชาบังคับก่อน:
+    • 06016413 ระบบเครือข่ายเบื้องต้น (INTRODUCTION TO NETWORK SYSTEMS) — 3(3-0-6) | ปีที่ 2 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H651" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 84, 24, 25, 33, 34, 40, 328, 331</t>
+        </is>
+      </c>
+      <c r="I651" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (prerequisite) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J651" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K651" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L651" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M651" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N651" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O651" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="652" ht="14.25" customHeight="1" s="36">
+      <c r="A652" s="37" t="inlineStr">
+        <is>
+          <t>QC6</t>
+        </is>
+      </c>
+      <c r="B652" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C652" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D652" s="39" t="inlineStr">
+        <is>
+          <t>เทอมเดียวกันจะลงการเขียนโปรแกรมเว็บพื้นฐาน พร้อมกับการออกแบบเว็บ เลยได้ไหม</t>
+        </is>
+      </c>
+      <c r="E652" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่) — ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่)</t>
+        </is>
+      </c>
+      <c r="F652" s="39" t="inlineStr">
+        <is>
+          <t>ไม่ได้ ต้องผ่าน 06066302 ก่อน</t>
+        </is>
+      </c>
+      <c r="G652" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ไม่ได้ — ต้องสอบผ่าน 06066302 การเขียนโปรแกรมเว็บพื้นฐาน ก่อน จึงจะลง 06016444 การออกแบบเว็บ ได้ จึงลงพร้อมกันในภาคเดียวกันไม่ได้
+- 06066302 การเขียนโปรแกรมเว็บพื้นฐาน (FUNDAMENTAL WEB PROGRAMMING) — ปีที่ 2 ภาคการศึกษาที่ 2
+- 06016444 การออกแบบเว็บ (WEB DESIGN) — ไม่ได้กำหนดปี/ภาคในแผนการศึกษา (วิชาเลือก)
+- 06016444 มีวิชาบังคับก่อนเป็น 06066302 (ต้องสอบผ่าน 06066302 ก่อนจึงลง 06016444 ได้)</t>
+        </is>
+      </c>
+      <c r="H652" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 342, 24, 27, 34, 41, 85, 88, 336</t>
+        </is>
+      </c>
+      <c r="I652" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (เทียบปี/ภาคของสองวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J652" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K652" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L652" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M652" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N652" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O652" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="653" ht="14.25" customHeight="1" s="36">
+      <c r="A653" s="37" t="inlineStr">
+        <is>
+          <t>QH13</t>
+        </is>
+      </c>
+      <c r="B653" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C653" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D653" s="39" t="inlineStr">
+        <is>
+          <t>ถ้าเลือกแผนสหกิจศึกษา จะได้ออกไปสหกิจตอนปีไหน เทอมไหน และวิชาสหกิจกี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E653" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่) — ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่)</t>
+        </is>
+      </c>
+      <c r="F653" s="39" t="inlineStr">
+        <is>
+          <t>ปี 4 ภาค 2 6 หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="G653" s="39" t="inlineStr">
+        <is>
+          <t>รายวิชาที่มีเฉพาะในแผนที่เข้าโครงการสหกิจศึกษา (BIT 2565 (ปริญญาตรี)):
+- 06036147 สหกิจศึกษา — 6(0-35-0) | ปีที่ 4 ภาคการศึกษาที่ 2 (หน้า 35)
+- 06036148 สหกิจศึกษาต่างประเทศ — 6(0-35-0) | ปีที่ 4 ภาคการศึกษาที่ 2 (หน้า 35)
+ภาคนั้นรวม 6 หน่วยกิตตามแผนในเล่ม (ในแผนปกติภาคเดียวกันรวม 12 หน่วยกิต)</t>
+        </is>
+      </c>
+      <c r="H653" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 35</t>
+        </is>
+      </c>
+      <c r="I653" s="39" t="inlineStr">
+        <is>
+          <t>Structured SQL (ตารางแผนปกติ/แผนสหกิจ) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J653" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K653" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L653" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M653" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_coop.json)</t>
+        </is>
+      </c>
+      <c r="N653" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O653" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="654" ht="14.25" customHeight="1" s="36">
+      <c r="A654" s="37" t="inlineStr">
+        <is>
+          <t>QC7</t>
+        </is>
+      </c>
+      <c r="B654" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C654" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D654" s="39" t="inlineStr">
+        <is>
+          <t>เก็บครบ 129 หน่วยกิตพอดี เกรดเฉลี่ยสะสม 2.00 พอดี จบได้ไหม</t>
+        </is>
+      </c>
+      <c r="E654" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่) — ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่)</t>
+        </is>
+      </c>
+      <c r="F654" s="39" t="inlineStr">
+        <is>
+          <t>จบได้ (ครบหน่วยกิตและไม่ต่ำกว่า 2.00)</t>
+        </is>
+      </c>
+      <c r="G654" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: จบได้ตามเกณฑ์หน่วยกิตและเกรด (ถ้าผ่านเงื่อนไขอื่นครบ)
+หลักสูตร IT 2565 (ปริญญาตรี) ต้องเรียนครบไม่น้อยกว่า 129 หน่วยกิต (หน้า 6)
+- หน่วยกิต: เก็บได้ 129 หน่วยกิต → ครบเกณฑ์ 129 หน่วยกิต
+- เกรดเฉลี่ยสะสม 2.00 → ผ่านเกณฑ์ขั้นต่ำ 2.00 (ข้อ 34)
+- เงื่อนไขอื่นตามข้อ 34: สอบผ่านทุกรายวิชาตามโครงสร้างหลักสูตร และผ่านการสอบภาษาอังกฤษ (English Exit exam)</t>
+        </is>
+      </c>
+      <c r="H654" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 6, 88</t>
+        </is>
+      </c>
+      <c r="I654" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวม + เกรดขั้นต่ำ ข้อ 34) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J654" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K654" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L654" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M654" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N654" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O654" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="655" ht="14.25" customHeight="1" s="36">
+      <c r="A655" s="37" t="inlineStr">
+        <is>
+          <t>QC8</t>
+        </is>
+      </c>
+      <c r="B655" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C655" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D655" s="39" t="inlineStr">
+        <is>
+          <t>ตอนนี้มี 130 หน่วยกิต เกรดเฉลี่ย 3.10 จบได้ยัง</t>
+        </is>
+      </c>
+      <c r="E655" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่) — ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่)</t>
+        </is>
+      </c>
+      <c r="F655" s="39" t="inlineStr">
+        <is>
+          <t>ยังไม่ได้ ต้องครบ 132 ขาด 2</t>
+        </is>
+      </c>
+      <c r="G655" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ยังจบไม่ได้
+หลักสูตร DSBA 2565 (ปริญญาตรี) ต้องเรียนครบไม่น้อยกว่า 132 หน่วยกิต (หน้า 2)
+- หน่วยกิต: เก็บได้ 130 หน่วยกิต → ยังขาดอีก 2 หน่วยกิต (ต้องครบ 132)
+- เกรดเฉลี่ยสะสม 3.10 → ผ่านเกณฑ์ขั้นต่ำ 2.00 (ข้อ 34)
+- เงื่อนไขอื่นตามข้อ 34: สอบผ่านทุกรายวิชาตามโครงสร้างหลักสูตร และผ่านการสอบภาษาอังกฤษ (English Exit exam)</t>
+        </is>
+      </c>
+      <c r="H655" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 2, 88</t>
+        </is>
+      </c>
+      <c r="I655" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวม + เกรดขั้นต่ำ ข้อ 34) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J655" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K655" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L655" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M655" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N655" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O655" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="656" ht="14.25" customHeight="1" s="36">
+      <c r="A656" s="37" t="inlineStr">
+        <is>
+          <t>QC9</t>
+        </is>
+      </c>
+      <c r="B656" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C656" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D656" s="39" t="inlineStr">
+        <is>
+          <t>จบด้วยเกรดเฉลี่ย 3.75 พอดี จะได้เกียรตินิยมอันดับ 1 เหรียญทองไหม</t>
+        </is>
+      </c>
+      <c r="E656" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่) — ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่)</t>
+        </is>
+      </c>
+      <c r="F656" s="39" t="inlineStr">
+        <is>
+          <t>ได้ (&gt;= 3.75)</t>
+        </is>
+      </c>
+      <c r="G656" s="39" t="inlineStr">
+        <is>
+          <t>ปริญญาเกียรตินิยม — ข้อ 36 ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 88, 89
+(ข้อบังคับของสถาบัน ใช้กับทุกหลักสูตรปริญญาตรี)
+- เกียรตินิยมอันดับหนึ่งและเหรียญทอง: ค่าระดับคะแนนเฉลี่ยสะสมตามโครงสร้างหลักสูตรสูงสุดในกลุ่มผู้สำเร็จการศึกษาปีเดียวกันของหลักสูตร และค่าระดับคะแนนเฉลี่ยสะสมไม่ต่ำกว่า 3.75 และต้องไม่เทียบโอนผลการเรียนจากสถาบันอื่น
+- เกียรตินิยมอันดับหนึ่ง: ค่าระดับคะแนนเฉลี่ยสะสมไม่ต่ำกว่า 3.50
+- เกียรตินิยมอันดับสอง: ค่าระดับคะแนนเฉลี่ยสะสมไม่ต่ำกว่า 3.25
+- กรณีโอนผลการเรียนจากสถาบันอื่น ทุกรายวิชาต้องได้ไม่ต่ำกว่า B หรือ S และต้องเรียนในหลักสูตรของสถาบันไม่น้อยกว่า 2 ใน 3 ของหน่วยกิตรวม
+- เงื่อนไขทั่วไป (ข้อ 36.1): เรียนไม่เกินระยะเวลาตามแผนการศึกษา · ไม่มีรายวิชาใดได้ F หรือ U · ไม่เคยเรียนซ้ำเพื่อเปลี่ยนเกรด · ไม่เคยลาพักเพราะไม่ลงทะเบียนตามกำหนด และไม่เคยถูกลงโทษทางวินัย</t>
+        </is>
+      </c>
+      <c r="H656" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 88, 89</t>
+        </is>
+      </c>
+      <c r="I656" s="39" t="inlineStr">
+        <is>
+          <t>ข้อบังคับปริญญาตรี (ภาคผนวกเล่ม AIT 2566) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J656" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K656" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L656" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M656" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N656" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O656" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="657" ht="14.25" customHeight="1" s="36">
+      <c r="A657" s="37" t="inlineStr">
+        <is>
+          <t>QC10</t>
+        </is>
+      </c>
+      <c r="B657" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C657" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D657" s="39" t="inlineStr">
+        <is>
+          <t>เกรดเฉลี่ยสะสมตอนจบ 3.20 ยังได้เกียรตินิยมอยู่ไหม</t>
+        </is>
+      </c>
+      <c r="E657" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่) — ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่)</t>
+        </is>
+      </c>
+      <c r="F657" s="39" t="inlineStr">
+        <is>
+          <t>ไม่ได้ อันดับ 2 ต้อง &gt;= 3.25</t>
+        </is>
+      </c>
+      <c r="G657" s="39" t="inlineStr">
+        <is>
+          <t>ปริญญาเกียรตินิยม — ข้อ 36 ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 88, 89
+(ข้อบังคับของสถาบัน ใช้กับทุกหลักสูตรปริญญาตรี)
+- เกียรตินิยมอันดับหนึ่งและเหรียญทอง: ค่าระดับคะแนนเฉลี่ยสะสมตามโครงสร้างหลักสูตรสูงสุดในกลุ่มผู้สำเร็จการศึกษาปีเดียวกันของหลักสูตร และค่าระดับคะแนนเฉลี่ยสะสมไม่ต่ำกว่า 3.75 และต้องไม่เทียบโอนผลการเรียนจากสถาบันอื่น
+- เกียรตินิยมอันดับหนึ่ง: ค่าระดับคะแนนเฉลี่ยสะสมไม่ต่ำกว่า 3.50
+- เกียรตินิยมอันดับสอง: ค่าระดับคะแนนเฉลี่ยสะสมไม่ต่ำกว่า 3.25
+- กรณีโอนผลการเรียนจากสถาบันอื่น ทุกรายวิชาต้องได้ไม่ต่ำกว่า B หรือ S และต้องเรียนในหลักสูตรของสถาบันไม่น้อยกว่า 2 ใน 3 ของหน่วยกิตรวม
+- เงื่อนไขทั่วไป (ข้อ 36.1): เรียนไม่เกินระยะเวลาตามแผนการศึกษา · ไม่มีรายวิชาใดได้ F หรือ U · ไม่เคยเรียนซ้ำเพื่อเปลี่ยนเกรด · ไม่เคยลาพักเพราะไม่ลงทะเบียนตามกำหนด และไม่เคยถูกลงโทษทางวินัย</t>
+        </is>
+      </c>
+      <c r="H657" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 88, 89</t>
+        </is>
+      </c>
+      <c r="I657" s="39" t="inlineStr">
+        <is>
+          <t>ข้อบังคับปริญญาตรี (ภาคผนวกเล่ม AIT 2566) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J657" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K657" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L657" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M657" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N657" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O657" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="658" ht="14.25" customHeight="1" s="36">
+      <c r="A658" s="37" t="inlineStr">
+        <is>
+          <t>QC11</t>
+        </is>
+      </c>
+      <c r="B658" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C658" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D658" s="39" t="inlineStr">
+        <is>
+          <t>ย้ายจาก IT ไป DSBA ต้องเรียนรวมกี่หน่วยกิต มากกว่าของเดิมกี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E658" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่) — ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่)</t>
+        </is>
+      </c>
+      <c r="F658" s="39" t="inlineStr">
+        <is>
+          <t>DSBA 132 มากกว่า IT 129 อยู่ 3</t>
+        </is>
+      </c>
+      <c r="G658" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ต่างกัน 3 หน่วยกิต (DSBA 2565 (ปริญญาตรี) มากกว่า IT 2565 (ปริญญาตรี))
+- IT 2565 (ปริญญาตรี): ไม่น้อยกว่า 129 หน่วยกิต (หน้า 6)
+- DSBA 2565 (ปริญญาตรี): ไม่น้อยกว่า 132 หน่วยกิต (หน้า 2)</t>
+        </is>
+      </c>
+      <c r="H658" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 6, 2</t>
+        </is>
+      </c>
+      <c r="I658" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวมข้ามหลักสูตร) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J658" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K658" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L658" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M658" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N658" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O658" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="659" ht="14.25" customHeight="1" s="36">
+      <c r="A659" s="37" t="inlineStr">
+        <is>
+          <t>QC12</t>
+        </is>
+      </c>
+      <c r="B659" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C659" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D659" s="39" t="inlineStr">
+        <is>
+          <t>เทอมแรกได้เกรดเฉลี่ย 1.80 จะเกิดอะไรขึ้น</t>
+        </is>
+      </c>
+      <c r="E659" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่) — ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่)</t>
+        </is>
+      </c>
+      <c r="F659" s="39" t="inlineStr">
+        <is>
+          <t>ถูกภาคทัณฑ์ (ต่ำกว่า 2.00)</t>
+        </is>
+      </c>
+      <c r="G659" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: เกรดเฉลี่ย 1.80 ต่ำกว่า 2.00 → ถูกภาคทัณฑ์ (ข้อ 31) ถ้าภาคถัดไปเกรดเฉลี่ยประจำภาคยังต่ำกว่า 2.00 จะพ้นสภาพ (ข้อ 43.10)
+เมื่อเกรดเฉลี่ยต่ำกว่าเกณฑ์ — ภาคทัณฑ์ (ข้อ 31) และพ้นสภาพ (ข้อ 43) ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 87, 94, 95
+(ข้อบังคับของสถาบัน ใช้กับทุกหลักสูตรปริญญาตรี)
+- ค่าระดับคะแนนเฉลี่ยสะสมต่ำกว่า 2.00: ถูกภาคทัณฑ์ และพ้นภาคทัณฑ์เมื่อกลับมาไม่ต่ำกว่า 2.00 (นับรวมภาคพิเศษ)
+- ระหว่างภาคทัณฑ์ ถ้าค่าระดับคะแนนเฉลี่ยประจำภาคถัดไปต่ำกว่า 2.00: พ้นสภาพนักศึกษา (ข้อ 43.10)
+- ค่าระดับคะแนนเฉลี่ยสะสมต่ำกว่า 1.00: พ้นสภาพนักศึกษา (ข้อ 43.11)
+- สำเร็จการศึกษาได้ต้องมีค่าระดับคะแนนเฉลี่ยสะสมไม่ต่ำกว่า 2.00 (ข้อ 34)</t>
+        </is>
+      </c>
+      <c r="H659" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 87, 94, 95</t>
+        </is>
+      </c>
+      <c r="I659" s="39" t="inlineStr">
+        <is>
+          <t>ข้อบังคับปริญญาตรี (ภาคผนวกเล่ม AIT 2566) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J659" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="K659" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L659" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M659" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก ข้อบังคับ ป.ตรี (AIT 2566 ภาคผนวก หน้า 87, 94-95))</t>
+        </is>
+      </c>
+      <c r="N659" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O659" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="660" ht="14.25" customHeight="1" s="36">
+      <c r="A660" s="37" t="inlineStr">
+        <is>
+          <t>QC13</t>
+        </is>
+      </c>
+      <c r="B660" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C660" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D660" s="39" t="inlineStr">
+        <is>
+          <t>ติดโปรอยู่ แล้วเทอมถัดมาได้เกรดเฉลี่ยประจำภาค 1.90 จะโดนรีไทร์ไหม</t>
+        </is>
+      </c>
+      <c r="E660" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่) — ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่)</t>
+        </is>
+      </c>
+      <c r="F660" s="39" t="inlineStr">
+        <is>
+          <t>พ้นสภาพ (ข้อ 43.10)</t>
+        </is>
+      </c>
+      <c r="G660" s="39" t="inlineStr">
+        <is>
+          <t>การภาคทัณฑ์ — ข้อ 31 ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 87
+(ข้อบังคับของสถาบัน ใช้กับทุกหลักสูตรปริญญาตรี)
+- นักศึกษาที่ได้ค่าระดับคะแนนเฉลี่ยสะสมต่ำกว่า 2.00 ต้องถูกภาคทัณฑ์
+- จะพ้นภาคทัณฑ์เมื่อค่าระดับคะแนนเฉลี่ยสะสมไม่ต่ำกว่า 2.00 (นับรวมภาคการศึกษาพิเศษด้วย)
+- ถ้าระหว่างภาคทัณฑ์ได้ค่าระดับคะแนนเฉลี่ยประจำภาคถัดไปต่ำกว่า 2.00 จะพ้นสภาพนักศึกษา (ข้อ 43.10)</t>
+        </is>
+      </c>
+      <c r="H660" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 87</t>
+        </is>
+      </c>
+      <c r="I660" s="39" t="inlineStr">
+        <is>
+          <t>ข้อบังคับปริญญาตรี (ภาคผนวกเล่ม AIT 2566) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J660" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K660" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L660" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M660" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก ข้อบังคับ ป.ตรี (AIT 2566 ภาคผนวก หน้า 87, 94-95))</t>
+        </is>
+      </c>
+      <c r="N660" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O660" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="661" ht="14.25" customHeight="1" s="36">
+      <c r="A661" s="37" t="inlineStr">
+        <is>
+          <t>QC14</t>
+        </is>
+      </c>
+      <c r="B661" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C661" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D661" s="39" t="inlineStr">
+        <is>
+          <t>เกรดเฉลี่ยสะสม 0.95 ยังเรียนต่อได้ไหม</t>
+        </is>
+      </c>
+      <c r="E661" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่) — ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่)</t>
+        </is>
+      </c>
+      <c r="F661" s="39" t="inlineStr">
+        <is>
+          <t>พ้นสภาพ (ต่ำกว่า 1.00 ข้อ 43.11)</t>
+        </is>
+      </c>
+      <c r="G661" s="39" t="inlineStr">
+        <is>
+          <t>ไม่ได้  
+เกรดเฉลี่ยสะสม 0.95 ต่ำกว่าเกณฑ์ 1.00 ตามข้อ 43.11 แห่งข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (หน้า 95) ทำให้พ้นสภาพนักศึกษาทันที ไม่สามารถเรียนต่อได้  
+ข้อมูลอ้างอิง: ข้อ 43.11 (ภาคผนวกในเล่ม มคอ.2 AIT 2566)</t>
+        </is>
+      </c>
+      <c r="H661" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 87, 94, 95</t>
+        </is>
+      </c>
+      <c r="I661" s="39" t="inlineStr">
+        <is>
+          <t>ข้อบังคับปริญญาตรี (ภาคผนวกเล่ม AIT 2566) → Typhoon เรียบเรียง</t>
+        </is>
+      </c>
+      <c r="J661" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="K661" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L661" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M661" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก ข้อบังคับ ป.ตรี (AIT 2566 ภาคผนวก หน้า 87, 94-95))</t>
+        </is>
+      </c>
+      <c r="N661" s="39" t="inlineStr">
+        <is>
+          <t>1.29s</t>
+        </is>
+      </c>
+      <c r="O661" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="662" ht="14.25" customHeight="1" s="36">
+      <c r="A662" s="37" t="inlineStr">
+        <is>
+          <t>QC15</t>
+        </is>
+      </c>
+      <c r="B662" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C662" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D662" s="39" t="inlineStr">
+        <is>
+          <t>เหลืออีก 9 หน่วยกิตจะจบ ลงซัมเมอร์เทอมเดียวให้ครบเลยได้ไหม</t>
+        </is>
+      </c>
+      <c r="E662" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่) — ชุดที่ระบบไม่เคยเห็น รอบ 7 (ยาก/ท้าทาย แบบใหม่)</t>
+        </is>
+      </c>
+      <c r="F662" s="39" t="inlineStr">
+        <is>
+          <t>ได้ ภาคฤดูร้อนลงได้ไม่เกิน 9</t>
+        </is>
+      </c>
+      <c r="G662" s="39" t="inlineStr">
+        <is>
+          <t>ได้  
+นักศึกษาชั้นปีสุดท้ายที่เหลือรายวิชาไม่ถึง 9 หน่วยกิตสามารถลงทะเบียนเพิ่มได้ถึง 27 หน่วยกิตในภาคการศึกษาปกติหรือภาคพิเศษ ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 82 โดยวิชาที่เรียนในภาคฤดูร้อน (ซัมเมอร์เทอม) สามารถลงทะเบียนได้ไม่เกิน 9 หน่วยกิต แต่หากเป็นวิชาฝึกงาน ห้ามลงวิชาอื่นในภาคเดียวกัน ดังนั้นหากวิชาที่เหลือเป็นวิชาทั่วไปหรือวิชาเลือกที่ไม่ใช่ฝึกงาน สามารถลงได้ในซัมเมอร์เทอมเพื่อให้ครบ 9 หน่วยกิตได้</t>
+        </is>
+      </c>
+      <c r="H662" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 82</t>
+        </is>
+      </c>
+      <c r="I662" s="39" t="inlineStr">
+        <is>
+          <t>ข้อบังคับปริญญาตรี (ภาคผนวกเล่ม AIT 2566) → Typhoon เรียบเรียง</t>
+        </is>
+      </c>
+      <c r="J662" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K662" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L662" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M662" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก ข้อบังคับ ป.ตรี (AIT 2566 ภาคผนวก หน้า 85))</t>
+        </is>
+      </c>
+      <c r="N662" s="39" t="inlineStr">
+        <is>
+          <t>2.04s</t>
+        </is>
+      </c>
+      <c r="O662" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
     <row r="663" ht="14.25" customHeight="1" s="36"/>
     <row r="664" ht="14.25" customHeight="1" s="36"/>
     <row r="665" ht="14.25" customHeight="1" s="36"/>

--- a/docs/tester.xlsx
+++ b/docs/tester.xlsx
@@ -577,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O662"/>
+  <dimension ref="A1:O706"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10" customWidth="1" style="36" min="1" max="1"/>
@@ -756,7 +756,7 @@
       </c>
       <c r="N2" s="13" t="inlineStr">
         <is>
-          <t>0.03s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O2" s="21" t="inlineStr">
@@ -1340,12 +1340,12 @@
       </c>
       <c r="N9" s="25" t="inlineStr">
         <is>
-          <t>0.62s</t>
+          <t>7.79s</t>
         </is>
       </c>
       <c r="O9" s="21" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="N10" s="13" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O10" s="21" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="N11" s="25" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O11" s="21" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="N12" s="13" t="inlineStr">
         <is>
-          <t>0.18s</t>
+          <t>4.63s</t>
         </is>
       </c>
       <c r="O12" s="21" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="N13" s="25" t="inlineStr">
         <is>
-          <t>0.35s</t>
+          <t>3.12s</t>
         </is>
       </c>
       <c r="O13" s="21" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="N14" s="13" t="inlineStr">
         <is>
-          <t>0.26s</t>
+          <t>0.80s</t>
         </is>
       </c>
       <c r="O14" s="21" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="N15" s="25" t="inlineStr">
         <is>
-          <t>0.23s</t>
+          <t>0.34s</t>
         </is>
       </c>
       <c r="O15" s="21" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="N20" s="13" t="inlineStr">
         <is>
-          <t>0.05s</t>
+          <t>0.10s</t>
         </is>
       </c>
       <c r="O20" s="21" t="inlineStr">
@@ -2395,7 +2395,7 @@
       <c r="G21" s="34" t="inlineStr">
         <is>
           <t>ได้  
-นักศึกษาสามารถเรียนวิชาที่เกี่ยวข้องกับฐานข้อมูลในปีที่ 4 ได้ เนื่องจากมีวิชาบังคับก่อนหน้า เช่น 06066300 แนวคิดระบบฐานข้อมูล (ปี 2 ภาค 1) และ 06026212 การสร้างคลังข้อมูล (ปี 3 ภาค 1) ซึ่งเป็นพื้นฐานจำเป็น วิชาที่เกี่ยวข้องในปี 4 ได้แก่ 06026246 หัวข้อพิเศษทางวิศวกรรมข้อมูล 1 และ 06026247 หัวข้อพิเศษทางวิศวกรรมข้อมูล 2 ที่จัดสอนในภาคการศึกษาที่ 1 ปีที่ 4 ประเภทวิชาบังคับในกลุ่มวิชาเลือกเฉพาะแขนง ตามหลักสูตร DSBA 2565</t>
+นักศึกษาสามารถเรียนวิชาฐานข้อมูลในปีที่ 4 ได้ เนื่องจากมีวิชาบังคับในกลุ่มวิชาเลือกเฉพาะแขนง เช่น 06026246 หัวข้อพิเศษทางวิศวกรรมข้อมูล 1 และ 06026247 หัวข้อพิเศษทางวิศวกรรมข้อมูล 2 ซึ่งจัดสอนในภาคการศึกษาที่ 2 ปีที่ 4 โดยมีวิชาบังคับก่อนหน้าคือ 06066300 แนวคิดระบบฐานข้อมูล (ปีที่ 2 ภาคการศึกษาที่ 1) และ 06026212 การสร้างคลังข้อมูล (ปีที่ 3 ภาคการศึกษาที่ 1) ที่ครอบคลุมเนื้อหาพื้นฐานด้านฐานข้อมูลอย่างเพียงพอ</t>
         </is>
       </c>
       <c r="H21" s="34" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="N21" s="13" t="inlineStr">
         <is>
-          <t>2.88s</t>
+          <t>1.90s</t>
         </is>
       </c>
       <c r="O21" s="21" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="N23" s="13" t="inlineStr">
         <is>
-          <t>0.15s</t>
+          <t>0.26s</t>
         </is>
       </c>
       <c r="O23" s="21" t="inlineStr">
@@ -2801,11 +2801,15 @@
       </c>
       <c r="G25" s="34" t="inlineStr">
         <is>
-          <t>ใช่ หลักสูตรวิทยาการข้อมูลและการวิเคราะห์เชิงธุรกิจ (DSBA) ปีที่ 3 มีการเลือกแขนง (หรือที่เรียกว่า "กลุ่มวิชา") ให้เลือก โดยมี 3 แขนง ดังนี้:
-- กลุ่มวิทยาการข้อมูล (Data Science)  
-- กลุ่มการวิเคราะห์เชิงสถิติ (Statistical Analytics)  
-- กลุ่มวิศวกรรมข้อมูล (Data Engineering)  
-[3][4][6]</t>
+          <t>ใช่ หลักสูตรวิทยาการข้อมูลและการวิเคราะห์เชิงธุรกิจ (DSBA) ปีที่ 3 มีการเลือกแขนง (หรือที่เรียกว่า "กลุ่มวิชา") ซึ่งแบ่งออกเป็น 3 แขนง ดังนี้:
+- วิทยาการข้อมูล (Data Science)  
+- การวิเคราะห์เชิงสถิติ (Statistical Analysis)  
+- วิศวกรรมข้อมูล (Data Engineering)  
+แต่ละแขนงมีรายวิชาเลือกที่เกี่ยวข้อง ได้แก่:
+- วิชาเลือกกลุ่มวิทยาการข้อมูล 1–4 (ELECTIVE IN DATA SCIENCE 1–4)  
+- วิชาเลือกกลุ่มการวิเคราะห์เชิงสถิติ 1–4 (ELECTIVE IN STATISTICAL ANALYTICS 1–4)  
+- วิชาเลือกกลุ่มวิศวกรรมข้อมูล 1–4 (ELECTIVE IN DATA ENGINEERING 1–4)  
+[3], [4], [6]</t>
         </is>
       </c>
       <c r="H25" s="34" t="inlineStr">
@@ -2838,7 +2842,7 @@
       </c>
       <c r="N25" s="13" t="inlineStr">
         <is>
-          <t>1.64s</t>
+          <t>2.33s</t>
         </is>
       </c>
       <c r="O25" s="21" t="inlineStr">
@@ -2880,9 +2884,9 @@
       </c>
       <c r="G26" s="34" t="inlineStr">
         <is>
-          <t>1. หลักสูตร IT 2565 มีหน่วยกิตรวมน้อยกว่า IT 2560 อยู่ 1 หน่วยกิต และเปลี่ยนโครงสร้างแขนงวิชาเป็น "โมดูลอาชีพ" 3 โมดูลแทนการเลือกแขนงวิชาเดิม
-2. หลักสูตร IT 2560 มีหน่วยกิตรวม 130 หน่วยกิต (มคอ.2 IT 2560 หน้า 18) ขณะที่ IT 2565 มี 129 หน่วยกิต (มคอ.2 IT 2565 หน้า 6) ลดลง 1 หน่วยกิต ซึ่งสะท้อนจากการปรับโครงสร้างกลุ่มวิชาเฉพาะด้านและวิชาเลือก โดยเฉพาะการเปลี่ยนจาก "แขนงวิชา" มาเป็น "โมดูลอาชีพ" 3 โมดูล (M1-M3) ที่มีความยืดหยุ่นในการเลือกวิชา และลดหน่วยกิตในกลุ่มวิชาบังคับเฉพาะแขนงจาก 30 เป็น 15 หน่วยกิต (ข้อมูลจาก [3], [4], [8])
-3. อ้างข้อมูลจากหลักฐาน: หน่วยกิตรวม (IT 2560 vs IT 2565), ประเภทวิชา (บังคับ/เลือก), ภาค/ปีที่เปิดสอน (IT 2560 เริ่มภาค 1/2560, IT 2565 เริ่มภาค 1/2565), โครงสร้างแขนงวิชา (เปลี่ยนจาก "แขนงวิชา" เป็น "โมดูลอาชีพ")</t>
+          <t>1. หลักสูตร IT 2565 มีหน่วยกิตรวม 129 หน่วยกิต ลดลง 1 หน่วยกิตจาก IT 2560 ที่มี 130 หน่วยกิต และเปลี่ยนโครงสร้างแขนงวิชาเป็น "โมดูลอาชีพ" 3 โมดูลแทนการเลือกแขนงวิชาเดิม
+2. หลักสูตร IT 2565 ปรับโครงสร้างให้เน้นความรู้เชิงลึกผ่าน "โมดูลอาชีพ" 3 โมดูล (Full-Stack Web Developer, Network/System Engineer, Game Developer) แทนการเลือก "แขนงวิชา" 3 แขนงใน IT 2560 พร้อมเพิ่มหน่วยกิตวิชาเลือกทางเทคโนโลยีสารสนเทศจาก 6 เป็น 9 หน่วยกิต และย้ายรายวิชาบางวิชาเข้าโมดูลเพื่อความสอดคล้องกับความต้องการตลาดแรงงาน
+3. อ้างข้อมูลจาก: หน่วยกิตรวม (มคอ.2 IT 2560 หน้า 18, IT 2565 หน้า 6), โครงสร้างหลักสูตร (IT 2565 หน้า 371, 374, 376, 378), การปรับโครงสร้าง (IT 2565 หน้า 370, 374), ประเภทวิชา (บังคับ/เลือก) และการเปลี่ยนแปลงจาก "แขนงวิชา" เป็น "โมดูลอาชีพ" (IT 2565 หน้า 370, 376, 378)</t>
         </is>
       </c>
       <c r="H26" s="34" t="inlineStr">
@@ -2915,7 +2919,7 @@
       </c>
       <c r="N26" s="13" t="inlineStr">
         <is>
-          <t>4.90s</t>
+          <t>3.43s</t>
         </is>
       </c>
       <c r="O26" s="21" t="inlineStr">
@@ -3067,7 +3071,7 @@
       <c r="M28" s="34" t="n"/>
       <c r="N28" s="13" t="inlineStr">
         <is>
-          <t>0.44s</t>
+          <t>0.40s</t>
         </is>
       </c>
       <c r="O28" s="21" t="inlineStr">
@@ -3143,7 +3147,7 @@
       </c>
       <c r="N29" s="25" t="inlineStr">
         <is>
-          <t>0.16s</t>
+          <t>0.17s</t>
         </is>
       </c>
       <c r="O29" s="21" t="inlineStr">
@@ -3404,7 +3408,7 @@
       </c>
       <c r="N32" s="13" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O32" s="21" t="inlineStr">
@@ -3484,7 +3488,7 @@
       </c>
       <c r="N33" s="25" t="inlineStr">
         <is>
-          <t>0.30s</t>
+          <t>0.27s</t>
         </is>
       </c>
       <c r="O33" s="21" t="inlineStr">
@@ -3632,7 +3636,7 @@
       <c r="M35" s="35" t="n"/>
       <c r="N35" s="25" t="inlineStr">
         <is>
-          <t>0.52s</t>
+          <t>0.54s</t>
         </is>
       </c>
       <c r="O35" s="21" t="inlineStr">
@@ -3710,7 +3714,7 @@
       </c>
       <c r="N36" s="13" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O36" s="21" t="inlineStr">
@@ -3753,16 +3757,20 @@
       <c r="G37" s="35" t="inlineStr">
         <is>
           <t>วิชาที่เกี่ยวข้องกับ "machine learning" — หลักสูตร AIT
-■ AIT 2566 — 7 วิชา รวม 17 หน่วยกิต
+■ AIT 2566 — 9 วิชา รวม 23 หน่วยกิต
   - 06046405 การเรียนรู้ของเครื่องเชิงความน่าจะเป็น (PROBABILISTIC MACHINE LEARNING)
       หน่วยกิต 3(3-0-6) | ปีที่ 2 ภาคการศึกษาที่ 1
   - 06046406 พื้นฐานการเรียนรู้เชิงลึก (FUNDAMENTALS OF DEEP LEARNING)
       หน่วยกิต 3(3-0-6) | ปีที่ 2 ภาคการศึกษาที่ 1
   - 06046414 การประมวลผลภาษาธรรมชาติด้วยการเรียนรู้เชิงลึก (NATURAL LANGUAGE PROCESSING WITH DEEP LEARNING)
       หน่วยกิต 3(3-0-6) | ปีที่ 3 ภาคการศึกษาที่ 1
+  - 06046415 การประมวลผลสัญญาณ (SIGNAL PROCESSING)
+      หน่วยกิต 3(3-0-6) | ปีที่ 3 ภาคการศึกษาที่ 1
   - 06046416 การเรียนรู้เชิงลึกสำหรับคอมพิวเตอร์วิทัศน์ (DEEP LEARNING FOR COMPUTER VISION)
       หน่วยกิต 3(3-0-6) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)
   - 06046419 การเรียนรู้แบบเสริมกำลัง (REINFORCEMENT LEARNING)
+      หน่วยกิต 3(3-0-6) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)
+  - 90642113 หุ่นยนต์และปัญญาประดิษฐ์ (ROBOTICS A)
       หน่วยกิต 3(3-0-6) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)
   - 90964204 สารสนเทศเพื่อการเรียนรู้ (INFORMATION FOR LEARNING)
       หน่วยกิต 1(0-2-1) | ไม่ระบุชั้นปี (วิชาเลือก/วิชาในหมวดเลือก)
@@ -3800,7 +3808,7 @@
       </c>
       <c r="N37" s="25" t="inlineStr">
         <is>
-          <t>0.23s</t>
+          <t>0.36s</t>
         </is>
       </c>
       <c r="O37" s="21" t="inlineStr">
@@ -3912,7 +3920,7 @@
       </c>
       <c r="N38" s="13" t="inlineStr">
         <is>
-          <t>0.34s</t>
+          <t>0.28s</t>
         </is>
       </c>
       <c r="O38" s="21" t="inlineStr">
@@ -4004,7 +4012,7 @@
       </c>
       <c r="N39" s="25" t="inlineStr">
         <is>
-          <t>0.38s</t>
+          <t>0.40s</t>
         </is>
       </c>
       <c r="O39" s="21" t="inlineStr">
@@ -4341,7 +4349,7 @@
       <c r="M43" s="35" t="n"/>
       <c r="N43" s="25" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O43" s="21" t="inlineStr">
@@ -4417,7 +4425,7 @@
       </c>
       <c r="N44" s="13" t="inlineStr">
         <is>
-          <t>0.18s</t>
+          <t>0.25s</t>
         </is>
       </c>
       <c r="O44" s="21" t="inlineStr">
@@ -4650,7 +4658,7 @@
       </c>
       <c r="N47" s="25" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O47" s="21" t="inlineStr">
@@ -4898,7 +4906,7 @@
       </c>
       <c r="N50" s="13" t="inlineStr">
         <is>
-          <t>0.14s</t>
+          <t>0.17s</t>
         </is>
       </c>
       <c r="O50" s="21" t="inlineStr">
@@ -6645,7 +6653,7 @@
       <c r="M70" s="34" t="n"/>
       <c r="N70" s="13" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O70" s="21" t="inlineStr">
@@ -6723,7 +6731,7 @@
       </c>
       <c r="N71" s="25" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O71" s="21" t="inlineStr">
@@ -6801,7 +6809,7 @@
       </c>
       <c r="N72" s="13" t="inlineStr">
         <is>
-          <t>0.08s</t>
+          <t>0.18s</t>
         </is>
       </c>
       <c r="O72" s="21" t="inlineStr">
@@ -7200,7 +7208,7 @@
       </c>
       <c r="N77" s="25" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O77" s="21" t="inlineStr">
@@ -7284,7 +7292,7 @@
       </c>
       <c r="N78" s="13" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O78" s="21" t="inlineStr">
@@ -7393,7 +7401,7 @@
       </c>
       <c r="N79" s="25" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O79" s="21" t="inlineStr">
@@ -7549,7 +7557,7 @@
       </c>
       <c r="N81" s="25" t="inlineStr">
         <is>
-          <t>0.08s</t>
+          <t>0.07s</t>
         </is>
       </c>
       <c r="O81" s="21" t="inlineStr">
@@ -7736,7 +7744,7 @@
       </c>
       <c r="N83" s="25" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O83" s="21" t="inlineStr">
@@ -11809,7 +11817,7 @@
       </c>
       <c r="N135" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O135" s="41" t="inlineStr">
@@ -12046,7 +12054,7 @@
       </c>
       <c r="N138" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O138" s="41" t="inlineStr">
@@ -12204,7 +12212,7 @@
       </c>
       <c r="N140" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O140" s="41" t="inlineStr">
@@ -12362,7 +12370,7 @@
       </c>
       <c r="N142" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O142" s="41" t="inlineStr">
@@ -12520,7 +12528,7 @@
       </c>
       <c r="N144" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O144" s="41" t="inlineStr">
@@ -12678,7 +12686,7 @@
       </c>
       <c r="N146" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O146" s="41" t="inlineStr">
@@ -12757,7 +12765,7 @@
       </c>
       <c r="N147" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O147" s="41" t="inlineStr">
@@ -13309,7 +13317,7 @@
       </c>
       <c r="N154" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O154" s="41" t="inlineStr">
@@ -13467,7 +13475,7 @@
       </c>
       <c r="N156" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O156" s="41" t="inlineStr">
@@ -14245,7 +14253,7 @@
       </c>
       <c r="N166" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O166" s="41" t="inlineStr">
@@ -14821,7 +14829,7 @@
       </c>
       <c r="N173" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O173" s="41" t="inlineStr">
@@ -17462,7 +17470,7 @@
       </c>
       <c r="N206" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O206" s="41" t="inlineStr">
@@ -17539,7 +17547,7 @@
       </c>
       <c r="N207" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O207" s="41" t="inlineStr">
@@ -18125,7 +18133,7 @@
       </c>
       <c r="N214" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O214" s="41" t="inlineStr">
@@ -19476,7 +19484,7 @@
       </c>
       <c r="N231" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O231" s="41" t="inlineStr">
@@ -19556,7 +19564,7 @@
       </c>
       <c r="N232" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O232" s="41" t="inlineStr">
@@ -20043,7 +20051,7 @@
       </c>
       <c r="N238" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O238" s="41" t="inlineStr">
@@ -20120,7 +20128,7 @@
       </c>
       <c r="N239" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O239" s="41" t="inlineStr">
@@ -20197,7 +20205,7 @@
       </c>
       <c r="N240" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O240" s="41" t="inlineStr">
@@ -20274,7 +20282,7 @@
       </c>
       <c r="N241" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O241" s="41" t="inlineStr">
@@ -20351,7 +20359,7 @@
       </c>
       <c r="N242" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O242" s="41" t="inlineStr">
@@ -21051,7 +21059,7 @@
       </c>
       <c r="N251" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.03s</t>
         </is>
       </c>
       <c r="O251" s="41" t="inlineStr">
@@ -21393,7 +21401,7 @@
       </c>
       <c r="N255" s="39" t="inlineStr">
         <is>
-          <t>0.04s</t>
+          <t>0.03s</t>
         </is>
       </c>
       <c r="O255" s="41" t="inlineStr">
@@ -21475,7 +21483,7 @@
       </c>
       <c r="N256" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O256" s="41" t="inlineStr">
@@ -21558,7 +21566,7 @@
       </c>
       <c r="N257" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O257" s="41" t="inlineStr">
@@ -21715,7 +21723,7 @@
       </c>
       <c r="N259" s="39" t="inlineStr">
         <is>
-          <t>0.12s</t>
+          <t>0.11s</t>
         </is>
       </c>
       <c r="O259" s="41" t="inlineStr">
@@ -22742,7 +22750,7 @@
       </c>
       <c r="N272" s="39" t="inlineStr">
         <is>
-          <t>0.04s</t>
+          <t>0.05s</t>
         </is>
       </c>
       <c r="O272" s="41" t="inlineStr">
@@ -25317,7 +25325,7 @@
       </c>
       <c r="N305" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O305" s="41" t="inlineStr">
@@ -25632,7 +25640,7 @@
       </c>
       <c r="N309" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O309" s="41" t="inlineStr">
@@ -27762,7 +27770,7 @@
       </c>
       <c r="N336" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O336" s="41" t="inlineStr">
@@ -27841,7 +27849,7 @@
       </c>
       <c r="N337" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O337" s="41" t="inlineStr">
@@ -28633,7 +28641,7 @@
       </c>
       <c r="N347" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O347" s="41" t="inlineStr">
@@ -28710,7 +28718,7 @@
       </c>
       <c r="N348" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O348" s="41" t="inlineStr">
@@ -28787,7 +28795,7 @@
       </c>
       <c r="N349" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O349" s="41" t="inlineStr">
@@ -29495,7 +29503,7 @@
       </c>
       <c r="N358" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O358" s="41" t="inlineStr">
@@ -29697,8 +29705,7 @@
       </c>
       <c r="G361" s="39" t="inlineStr">
         <is>
-          <t>ได้  
-นักศึกษาชั้นปีสุดท้ายที่เหลือรายวิชาไม่ถึง 9 หน่วยกิต หรือต้องลงเกิน 22 หน่วยกิตเพื่อสำเร็จการศึกษา สามารถลงทะเบียนได้สูงสุดไม่เกิน 27 หน่วยกิต โดยต้องได้รับอนุมัติจากสภาวิชาการ ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 82 ซึ่งระบุไว้ชัดเจนสำหรับกรณีปีสุดท้าย</t>
+          <t>ได้ — นักศึกษาชั้นปีสุดท้ายที่เหลือรายวิชาไม่ถึง 9 หน่วยกิต หรือต้องลงเกิน 22 หน่วยกิตเพื่อสำเร็จการศึกษา สามารถลงทะเบียนได้สูงสุด 27 หน่วยกิต โดยต้องได้รับอนุมัติจากสภาวิชาการ ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 82 ประเภทวิชา: บังคับ (สำหรับนักศึกษาที่ต้องการสำเร็จการศึกษา)</t>
         </is>
       </c>
       <c r="H361" s="39" t="inlineStr">
@@ -29731,7 +29738,7 @@
       </c>
       <c r="N361" s="39" t="inlineStr">
         <is>
-          <t>1.51s</t>
+          <t>1.58s</t>
         </is>
       </c>
       <c r="O361" s="41" t="inlineStr">
@@ -29813,7 +29820,7 @@
       </c>
       <c r="N362" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O362" s="41" t="inlineStr">
@@ -30529,7 +30536,7 @@
       </c>
       <c r="N371" s="39" t="inlineStr">
         <is>
-          <t>0.03s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="O371" s="41" t="inlineStr">
@@ -32083,7 +32090,7 @@
       </c>
       <c r="N391" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O391" s="41" t="inlineStr">
@@ -32399,7 +32406,7 @@
       </c>
       <c r="N395" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O395" s="41" t="inlineStr">
@@ -33192,7 +33199,7 @@
       </c>
       <c r="N405" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O405" s="41" t="inlineStr">
@@ -33269,7 +33276,7 @@
       </c>
       <c r="N406" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O406" s="41" t="inlineStr">
@@ -33346,7 +33353,7 @@
       </c>
       <c r="N407" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O407" s="41" t="inlineStr">
@@ -33500,7 +33507,7 @@
       </c>
       <c r="N409" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O409" s="41" t="inlineStr">
@@ -34522,7 +34529,7 @@
       </c>
       <c r="N422" s="39" t="inlineStr">
         <is>
-          <t>0.23s</t>
+          <t>0.22s</t>
         </is>
       </c>
       <c r="O422" s="41" t="inlineStr">
@@ -36816,7 +36823,7 @@
       </c>
       <c r="N451" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O451" s="41" t="inlineStr">
@@ -36973,7 +36980,7 @@
       </c>
       <c r="N453" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O453" s="41" t="inlineStr">
@@ -37287,7 +37294,7 @@
       </c>
       <c r="N457" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O457" s="41" t="inlineStr">
@@ -37364,7 +37371,7 @@
       </c>
       <c r="N458" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O458" s="41" t="inlineStr">
@@ -37441,7 +37448,7 @@
       </c>
       <c r="N459" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O459" s="41" t="inlineStr">
@@ -40268,7 +40275,7 @@
       </c>
       <c r="N495" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O495" s="41" t="inlineStr">
@@ -41143,7 +41150,7 @@
       </c>
       <c r="N506" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O506" s="41" t="inlineStr">
@@ -41220,7 +41227,7 @@
       </c>
       <c r="N507" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O507" s="41" t="inlineStr">
@@ -42437,7 +42444,7 @@
       </c>
       <c r="N522" s="39" t="inlineStr">
         <is>
-          <t>0.53s</t>
+          <t>0.80s</t>
         </is>
       </c>
       <c r="O522" s="41" t="inlineStr">
@@ -42679,7 +42686,7 @@
       </c>
       <c r="N525" s="39" t="inlineStr">
         <is>
-          <t>0.26s</t>
+          <t>0.78s</t>
         </is>
       </c>
       <c r="O525" s="41" t="inlineStr">
@@ -43315,7 +43322,7 @@
       </c>
       <c r="N533" s="39" t="inlineStr">
         <is>
-          <t>0.18s</t>
+          <t>0.10s</t>
         </is>
       </c>
       <c r="O533" s="41" t="inlineStr">
@@ -43624,7 +43631,7 @@
       </c>
       <c r="N537" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O537" s="41" t="inlineStr">
@@ -44172,7 +44179,7 @@
       </c>
       <c r="N544" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O544" s="41" t="inlineStr">
@@ -44409,7 +44416,7 @@
       </c>
       <c r="N547" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O547" s="41" t="inlineStr">
@@ -44488,7 +44495,7 @@
       </c>
       <c r="N548" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O548" s="41" t="inlineStr">
@@ -45258,7 +45265,7 @@
       </c>
       <c r="N557" s="39" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
       <c r="O557" s="41" t="inlineStr">
@@ -46055,7 +46062,7 @@
       </c>
       <c r="N567" s="39" t="inlineStr">
         <is>
-          <t>0.02s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O567" s="41" t="inlineStr">
@@ -46242,7 +46249,7 @@
       </c>
       <c r="N569" s="39" t="inlineStr">
         <is>
-          <t>0.34s</t>
+          <t>1.07s</t>
         </is>
       </c>
       <c r="O569" s="41" t="inlineStr">
@@ -47111,7 +47118,7 @@
       </c>
       <c r="N580" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O580" s="41" t="inlineStr">
@@ -48650,7 +48657,9 @@
       <c r="G600" s="39" t="inlineStr">
         <is>
           <t>ไม่ได้  
-นักศึกษาทั่วไปต้องลงทะเบียนไม่เกิน 22 หน่วยกิตต่อภาคการศึกษาปกติ ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 82 แม้จะเป็นนักศึกษาชั้นปีสุดท้ายก็ตาม แต่ต้องไม่เกิน 27 หน่วยกิต หากมีข้อยกเว้นเฉพาะกรณีที่เหลือรายวิชาไม่ถึง 3 หน่วยกิต หรือต้องลงเพื่อสำเร็จการศึกษา ซึ่งไม่ได้ระบุว่าเป็นกรณีนี้ ดังนั้นการลง 25 หน่วยกิตเกินข้อจำกัดปกติ และไม่มีหลักฐานยืนยันว่าเข้าข่ายข้อยกเว้น</t>
+นักศึกษาทั่วไปต้องลงทะเบียนไม่เกิน 22 หน่วยกิตต่อภาคการศึกษาปกติ ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 82  
+แม้จะมีข้อยกเว้นสำหรับนักศึกษาชั้นปีสุดท้ายที่อาจลงได้ไม่เกิน 27 หน่วยกิต แต่ต้องมีเหตุผลชัดเจน เช่น เหลือรายวิชาไม่ถึง 3 หน่วยกิต หรือต้องลงเพื่อสำเร็จการศึกษา  
+การลง 25 หน่วยกิตโดยไม่เข้าเงื่อนไขข้อยกเว้นดังกล่าว จึงไม่ได้รับอนุญาตตามข้อบังคับโดยตรง</t>
         </is>
       </c>
       <c r="H600" s="39" t="inlineStr">
@@ -48683,7 +48692,7 @@
       </c>
       <c r="N600" s="39" t="inlineStr">
         <is>
-          <t>2.24s</t>
+          <t>3.51s</t>
         </is>
       </c>
       <c r="O600" s="41" t="inlineStr">
@@ -49387,7 +49396,7 @@
       </c>
       <c r="N609" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O609" s="41" t="inlineStr">
@@ -51003,7 +51012,7 @@
       <c r="G630" s="39" t="inlineStr">
         <is>
           <t>ไม่ได้  
-นักศึกษาต้องลงทะเบียนไม่น้อยกว่า 9 หน่วยกิตในภาคการศึกษาปกติ ตามข้อบังคับสถาบันเทคโนโลยีพระจอมเกล้าเจ้าคุณทหารลาดกระบัง ว่าด้วยการศึกษาระดับปริญญาตรี พ.ศ. 2564 (ภาคผนวก ก) ซึ่งใช้กับหลักสูตรวท.บ. (วิทยาการข้อมูลและการวิเคราะห์เชิงธุรกิจ) คณะเทคโนโลยีสารสนเทศ สจล. ทุกภาคการศึกษาปกติ</t>
+นักศึกษาต้องลงทะเบียนไม่น้อยกว่า 9 หน่วยกิตในภาคการศึกษาปกติ ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 82 ซึ่งเป็นข้อกำหนดบังคับสำหรับทุกหลักสูตรปริญญาตรี ทั้งนี้ ไม่มีข้อยกเว้นสำหรับนักศึกษาชั้นปีที่ 1 หรือภาคเรียนแรกที่สามารถลงทะเบียนต่ำกว่า 9 หน่วยกิตได้</t>
         </is>
       </c>
       <c r="H630" s="39" t="inlineStr">
@@ -51036,7 +51045,7 @@
       </c>
       <c r="N630" s="39" t="inlineStr">
         <is>
-          <t>1.61s</t>
+          <t>3.10s</t>
         </is>
       </c>
       <c r="O630" s="41" t="inlineStr">
@@ -51080,8 +51089,8 @@
         <is>
           <t>ได้  
 นักศึกษาสามารถลงทะเบียนเรียนได้ไม่เกิน 9 หน่วยกิตในภาคการศึกษาพิเศษ (ภาคฤดูร้อน) ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 82  
-หากลงฝึกงานในภาคพิเศษ ห้ามลงทะเบียนเรียนรายวิชาอื่นเพิ่มเติมได้  
-ประเภทวิชา: ภาคการศึกษาพิเศษ, ข้อบังคับการลงทะเบียนเรียน</t>
+หากลงรายวิชาฝึกงานในภาคพิเศษ จะไม่สามารถลงวิชาอื่นได้ ตามข้อบังคับเดียวกัน  
+ดังนั้น ถ้าลงฝึกงาน ไม่สามารถลงวิชาอื่นได้ และจำนวนหน่วยกิตสูงสุดที่สามารถลงทะเบียนได้คือ 9 หน่วยกิต (เฉพาะฝึกงาน)</t>
         </is>
       </c>
       <c r="H631" s="39" t="inlineStr">
@@ -51114,7 +51123,7 @@
       </c>
       <c r="N631" s="39" t="inlineStr">
         <is>
-          <t>1.75s</t>
+          <t>2.86s</t>
         </is>
       </c>
       <c r="O631" s="41" t="inlineStr">
@@ -52270,7 +52279,7 @@
       </c>
       <c r="N646" s="39" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
       <c r="O646" s="41" t="inlineStr">
@@ -53411,8 +53420,8 @@
       <c r="G661" s="39" t="inlineStr">
         <is>
           <t>ไม่ได้  
-เกรดเฉลี่ยสะสม 0.95 ต่ำกว่าเกณฑ์ 1.00 ตามข้อ 43.11 แห่งข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (หน้า 95) ทำให้พ้นสภาพนักศึกษาทันที ไม่สามารถเรียนต่อได้  
-ข้อมูลอ้างอิง: ข้อ 43.11 (ภาคผนวกในเล่ม มคอ.2 AIT 2566)</t>
+เกรดเฉลี่ยสะสม 0.95 ต่ำกว่าเกณฑ์ 1.00 ตามข้อ 43.11 ของข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (หน้า 95) ทำให้พ้นสภาพนักศึกษาทันที ไม่สามารถเรียนต่อได้  
+ข้อมูลอ้างอิง: ข้อ 43.11, หน้า 95, ข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566)</t>
         </is>
       </c>
       <c r="H661" s="39" t="inlineStr">
@@ -53445,7 +53454,7 @@
       </c>
       <c r="N661" s="39" t="inlineStr">
         <is>
-          <t>1.29s</t>
+          <t>2.26s</t>
         </is>
       </c>
       <c r="O661" s="41" t="inlineStr">
@@ -53488,7 +53497,7 @@
       <c r="G662" s="39" t="inlineStr">
         <is>
           <t>ได้  
-นักศึกษาชั้นปีสุดท้ายที่เหลือรายวิชาไม่ถึง 9 หน่วยกิตสามารถลงทะเบียนเพิ่มได้ถึง 27 หน่วยกิตในภาคการศึกษาปกติหรือภาคพิเศษ ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 82 โดยวิชาที่เรียนในภาคฤดูร้อน (ซัมเมอร์เทอม) สามารถลงทะเบียนได้ไม่เกิน 9 หน่วยกิต แต่หากเป็นวิชาฝึกงาน ห้ามลงวิชาอื่นในภาคเดียวกัน ดังนั้นหากวิชาที่เหลือเป็นวิชาทั่วไปหรือวิชาเลือกที่ไม่ใช่ฝึกงาน สามารถลงได้ในซัมเมอร์เทอมเพื่อให้ครบ 9 หน่วยกิตได้</t>
+นักศึกษาที่เหลืออีก 9 หน่วยกิตสามารถลงทะเบียนเรียนในภาคฤดูร้อน (ซัมเมอร์เทอม) เพื่อสำเร็จการศึกษาได้ เนื่องจากข้อบังคับอนุญาตให้นักศึกษาชั้นปีสุดท้ายที่เหลือหน่วยกิตน้อยกว่า 9 หน่วยกิต ลงทะเบียนได้ไม่เกิน 27 หน่วยกิต แม้ภาคฤดูร้อนจะจำกัดไว้ที่ไม่เกิน 9 หน่วยกิต แต่หากเป็นรายวิชาที่จำเป็นต้องใช้เพื่อจบการศึกษา สามารถขออนุมัติจากสภาวิชาการได้ ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 82 และหลักสูตร BIT 2565 กำหนดให้ต้องเรียนรวม 90 หน่วยกิต (ไม่รวมสหกิจศึกษา) ซึ่งนักศึกษาที่เหลือ 9 หน่วยกิตจึงสามารถใช้ภาคฤดูร้อนเพื่อจบได้</t>
         </is>
       </c>
       <c r="H662" s="39" t="inlineStr">
@@ -53521,7 +53530,7 @@
       </c>
       <c r="N662" s="39" t="inlineStr">
         <is>
-          <t>2.04s</t>
+          <t>2.95s</t>
         </is>
       </c>
       <c r="O662" s="41" t="inlineStr">
@@ -53530,50 +53539,3457 @@
         </is>
       </c>
     </row>
-    <row r="663" ht="14.25" customHeight="1" s="36"/>
-    <row r="664" ht="14.25" customHeight="1" s="36"/>
-    <row r="665" ht="14.25" customHeight="1" s="36"/>
-    <row r="666" ht="14.25" customHeight="1" s="36"/>
-    <row r="667" ht="14.25" customHeight="1" s="36"/>
-    <row r="668" ht="14.25" customHeight="1" s="36"/>
-    <row r="669" ht="14.25" customHeight="1" s="36"/>
-    <row r="670" ht="14.25" customHeight="1" s="36"/>
-    <row r="671" ht="14.25" customHeight="1" s="36"/>
-    <row r="672" ht="14.25" customHeight="1" s="36"/>
-    <row r="673" ht="14.25" customHeight="1" s="36"/>
-    <row r="674" ht="14.25" customHeight="1" s="36"/>
-    <row r="675" ht="14.25" customHeight="1" s="36"/>
-    <row r="676" ht="14.25" customHeight="1" s="36"/>
-    <row r="677" ht="14.25" customHeight="1" s="36"/>
-    <row r="678" ht="14.25" customHeight="1" s="36"/>
-    <row r="679" ht="14.25" customHeight="1" s="36"/>
-    <row r="680" ht="14.25" customHeight="1" s="36"/>
-    <row r="681" ht="14.25" customHeight="1" s="36"/>
-    <row r="682" ht="14.25" customHeight="1" s="36"/>
-    <row r="683" ht="14.25" customHeight="1" s="36"/>
-    <row r="684" ht="14.25" customHeight="1" s="36"/>
-    <row r="685" ht="14.25" customHeight="1" s="36"/>
-    <row r="686" ht="14.25" customHeight="1" s="36"/>
-    <row r="687" ht="14.25" customHeight="1" s="36"/>
-    <row r="688" ht="14.25" customHeight="1" s="36"/>
-    <row r="689" ht="14.25" customHeight="1" s="36"/>
-    <row r="690" ht="14.25" customHeight="1" s="36"/>
-    <row r="691" ht="14.25" customHeight="1" s="36"/>
-    <row r="692" ht="14.25" customHeight="1" s="36"/>
-    <row r="693" ht="14.25" customHeight="1" s="36"/>
-    <row r="694" ht="14.25" customHeight="1" s="36"/>
-    <row r="695" ht="14.25" customHeight="1" s="36"/>
-    <row r="696" ht="14.25" customHeight="1" s="36"/>
-    <row r="697" ht="14.25" customHeight="1" s="36"/>
-    <row r="698" ht="14.25" customHeight="1" s="36"/>
-    <row r="699" ht="14.25" customHeight="1" s="36"/>
-    <row r="700" ht="14.25" customHeight="1" s="36"/>
-    <row r="701" ht="14.25" customHeight="1" s="36"/>
-    <row r="702" ht="14.25" customHeight="1" s="36"/>
-    <row r="703" ht="14.25" customHeight="1" s="36"/>
-    <row r="704" ht="14.25" customHeight="1" s="36"/>
-    <row r="705" ht="14.25" customHeight="1" s="36"/>
-    <row r="706" ht="14.25" customHeight="1" s="36"/>
+    <row r="663" ht="14.25" customHeight="1" s="36">
+      <c r="A663" s="37" t="inlineStr">
+        <is>
+          <t>RH1</t>
+        </is>
+      </c>
+      <c r="B663" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C663" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D663" s="39" t="inlineStr">
+        <is>
+          <t>ปี 4 เทอม 1 กับเทอม 2 เทอมไหนต้องลงหน่วยกิตเยอะกว่ากัน</t>
+        </is>
+      </c>
+      <c r="E663" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F663" s="39" t="inlineStr">
+        <is>
+          <t>ภาค 1 12, ภาค 2 6</t>
+        </is>
+      </c>
+      <c r="G663" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ปีที่ 4 ภาคการศึกษาที่ 1 หนักกว่า (12 เทียบกับ 6 หน่วยกิต) ต่างกัน 6 หน่วยกิต
+หน่วยกิตต่อภาคตามแผนปกติของ AIT 2566 (ปริญญาตรี) (บรรทัด 'รวม' ของแต่ละภาค รวมวิชาเลือกที่แผนกำหนดแล้ว):
+- ปีที่ 4 ภาคการศึกษาที่ 1: 12 หน่วยกิต (หน้า 26)
+- ปีที่ 4 ภาคการศึกษาที่ 2: 6 หน่วยกิต (หน้า 26)</t>
+        </is>
+      </c>
+      <c r="H663" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 26</t>
+        </is>
+      </c>
+      <c r="I663" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (เทียบภาค/ทั้งปี/สะสมตามแผน) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J663" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K663" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L663" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M663" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N663" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O663" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="664" ht="14.25" customHeight="1" s="36">
+      <c r="A664" s="37" t="inlineStr">
+        <is>
+          <t>RH2</t>
+        </is>
+      </c>
+      <c r="B664" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C664" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D664" s="39" t="inlineStr">
+        <is>
+          <t>ตามแผน ปี 4 ทั้งปีต้องเรียนกี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E664" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F664" s="39" t="inlineStr">
+        <is>
+          <t>12 + 6</t>
+        </is>
+      </c>
+      <c r="G664" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ปีที่ 4 ตามแผนปกติเรียนรวม 18 หน่วยกิต
+หน่วยกิตต่อภาคตามแผนปกติของ AIT 2566 (ปริญญาตรี) (บรรทัด 'รวม' ของแต่ละภาค รวมวิชาเลือกที่แผนกำหนดแล้ว):
+- ปีที่ 4 ภาคการศึกษาที่ 1: 12 หน่วยกิต (หน้า 26)
+- ปีที่ 4 ภาคการศึกษาที่ 2: 6 หน่วยกิต (หน้า 26)</t>
+        </is>
+      </c>
+      <c r="H664" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 26</t>
+        </is>
+      </c>
+      <c r="I664" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (เทียบภาค/ทั้งปี/สะสมตามแผน) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J664" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K664" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L664" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M664" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N664" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O664" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="665" ht="14.25" customHeight="1" s="36">
+      <c r="A665" s="37" t="inlineStr">
+        <is>
+          <t>RH3</t>
+        </is>
+      </c>
+      <c r="B665" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C665" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D665" s="39" t="inlineStr">
+        <is>
+          <t>ถ้าลงวิชาการเพิ่มประสิทธิภาพโครงข่ายประสาทเทียม และวิชาแคลคูลัส 1 รวมกันกี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E665" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F665" s="39" t="inlineStr">
+        <is>
+          <t>3 + 3</t>
+        </is>
+      </c>
+      <c r="G665" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: รวม 6 หน่วยกิต (3 + 3)
+- 06046412 การเพิ่มประสิทธิภาพโครงข่ายประสาทเทียม (NEURAL NETWORK OPTIMIZATION) — 3(3-0-6) | ปีที่ 2 ภาคการศึกษาที่ 2
+- 06046400 แคลคูลัส 1 (CALCULUS 1) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H665" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 19, 20, 23, 24, 37, 38, 287, 295</t>
+        </is>
+      </c>
+      <c r="I665" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวมของสองวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J665" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K665" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L665" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M665" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N665" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O665" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="666" ht="14.25" customHeight="1" s="36">
+      <c r="A666" s="37" t="inlineStr">
+        <is>
+          <t>RH4</t>
+        </is>
+      </c>
+      <c r="B666" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C666" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D666" s="39" t="inlineStr">
+        <is>
+          <t>ไม่ทันลงวิชาการเรียนรู้ของเครื่องเชิงความน่าจะเป็น ตามแผน ไปลงตอนปี 3 แทนได้ไหม</t>
+        </is>
+      </c>
+      <c r="E666" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F666" s="39" t="inlineStr">
+        <is>
+          <t>ได้ ตามแผนปี 2 ต้องผ่าน 06066001</t>
+        </is>
+      </c>
+      <c r="G666" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ได้ — ตามแผนวิชานี้อยู่ปีที่ 2 อยู่แล้ว (ต้องผ่านวิชาบังคับก่อนข้างต้นก่อน)
+วิชา 06046405 การเรียนรู้ของเครื่องเชิงความน่าจะเป็น (PROBABILISTIC MACHINE LEARNING) — 3(3-0-6) หน่วยกิต
+ตามแผนการศึกษา: ปีที่ 2 ภาคการศึกษาที่ 1
+วิชาบังคับก่อน (ต้องสอบผ่านก่อนจึงจะลงได้):
+  - 06066001 ความน่าจะเป็นและสถิติ (PROBABILITY AND STATISTICS) — ปีที่ 1 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H666" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 37, 291, 19, 20, 23, 24, 289</t>
+        </is>
+      </c>
+      <c r="I666" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (ปีตามแผน + วิชาบังคับก่อน → ลงได้/ไม่ได้) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J666" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="K666" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L666" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M666" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N666" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O666" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="667" ht="14.25" customHeight="1" s="36">
+      <c r="A667" s="37" t="inlineStr">
+        <is>
+          <t>RC1</t>
+        </is>
+      </c>
+      <c r="B667" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C667" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D667" s="39" t="inlineStr">
+        <is>
+          <t>ถ้าเรียนตามแผนครบถึงปี 2 แล้ว จะมีหน่วยกิตสะสมเท่าไร และเหลืออีกกี่หน่วยกิตถึงจะจบ</t>
+        </is>
+      </c>
+      <c r="E667" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F667" s="39" t="inlineStr">
+        <is>
+          <t>สะสม 71 เหลือ 49</t>
+        </is>
+      </c>
+      <c r="G667" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: เรียนครบตามแผนถึงปีที่ 2 มีหน่วยกิตสะสม 71 หน่วยกิต เหลืออีก 49 หน่วยกิตจึงครบ 120 หน่วยกิตตามเกณฑ์จบ (หน้า 5)
+หน่วยกิตต่อภาคตามแผนปกติของ AIT 2566 (ปริญญาตรี) (บรรทัด 'รวม' ของแต่ละภาค รวมวิชาเลือกที่แผนกำหนดแล้ว):
+- ปีที่ 1 ภาคการศึกษาที่ 1: 15 หน่วยกิต (หน้า 23)
+- ปีที่ 1 ภาคการศึกษาที่ 2: 19 หน่วยกิต (หน้า 23)
+- ปีที่ 2 ภาคการศึกษาที่ 1: 18 หน่วยกิต (หน้า 24)
+- ปีที่ 2 ภาคการศึกษาที่ 2: 19 หน่วยกิต (หน้า 24)</t>
+        </is>
+      </c>
+      <c r="H667" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 23, 24</t>
+        </is>
+      </c>
+      <c r="I667" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (เทียบภาค/ทั้งปี/สะสมตามแผน) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J667" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K667" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L667" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M667" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N667" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O667" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="668" ht="14.25" customHeight="1" s="36">
+      <c r="A668" s="37" t="inlineStr">
+        <is>
+          <t>RC2</t>
+        </is>
+      </c>
+      <c r="B668" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C668" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D668" s="39" t="inlineStr">
+        <is>
+          <t>กว่าจะได้ลงวิชาพื้นฐานการเรียนรู้เชิงลึก ต้องสอบผ่านกี่วิชา นับทุกทอด</t>
+        </is>
+      </c>
+      <c r="E668" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F668" s="39" t="inlineStr">
+        <is>
+          <t>3 วิชา: 06046400, 06046401, 06046402</t>
+        </is>
+      </c>
+      <c r="G668" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06046406 พื้นฐานการเรียนรู้เชิงลึก (FUNDAMENTALS OF DEEP LEARNING) — ปีที่ 2 ภาคการศึกษาที่ 1
+วิชาที่ต้องสอบผ่านก่อน (↳ = วิชาที่ต้องผ่านก่อนวิชาด้านบนอีกชั้น):
+  • 06046401 แคลคูลัส 2 (CALCULUS 2) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 2
+    ↳ 06046400 แคลคูลัส 1 (CALCULUS 1) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 1
+  • 06046402 พีชคณิตเชิงเส้น (LINEAR ALGEBRA) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 1
+รวมต้องผ่านก่อน 3 วิชา</t>
+        </is>
+      </c>
+      <c r="H668" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 37, 19, 292, 23, 287, 20, 24, 288</t>
+        </is>
+      </c>
+      <c r="I668" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (วิชาบังคับก่อนไล่หลายชั้น) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J668" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K668" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L668" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M668" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N668" s="39" t="inlineStr">
+        <is>
+          <t>0.02s</t>
+        </is>
+      </c>
+      <c r="O668" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="669" ht="14.25" customHeight="1" s="36">
+      <c r="A669" s="37" t="inlineStr">
+        <is>
+          <t>RH5</t>
+        </is>
+      </c>
+      <c r="B669" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C669" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D669" s="39" t="inlineStr">
+        <is>
+          <t>ปี 3 เทอม 1 กับเทอม 2 เทอมไหนต้องลงหน่วยกิตเยอะกว่ากัน</t>
+        </is>
+      </c>
+      <c r="E669" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F669" s="39" t="inlineStr">
+        <is>
+          <t>ภาค 1 18, ภาค 2 9</t>
+        </is>
+      </c>
+      <c r="G669" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ปีที่ 3 ภาคการศึกษาที่ 1 หนักกว่า (18 เทียบกับ 12 หน่วยกิต) ต่างกัน 6 หน่วยกิต
+หน่วยกิตต่อภาคตามแผนปกติของ BIT 2565 (ปริญญาตรี) (บรรทัด 'รวม' ของแต่ละภาค รวมวิชาเลือกที่แผนกำหนดแล้ว):
+- ปีที่ 3 ภาคการศึกษาที่ 1: 18 หน่วยกิต (หน้า 28)
+- ปีที่ 3 ภาคการศึกษาที่ 2: 12 หน่วยกิต (หน้า 29)</t>
+        </is>
+      </c>
+      <c r="H669" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 28, 29</t>
+        </is>
+      </c>
+      <c r="I669" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (เทียบภาค/ทั้งปี/สะสมตามแผน) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J669" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K669" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L669" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M669" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N669" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O669" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="670" ht="14.25" customHeight="1" s="36">
+      <c r="A670" s="37" t="inlineStr">
+        <is>
+          <t>RH6</t>
+        </is>
+      </c>
+      <c r="B670" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C670" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D670" s="39" t="inlineStr">
+        <is>
+          <t>ถ้าลงวิชาโครงงานทางด้านเทคโนโลยีสารสนเทศเชิงธุรกิจ 2 และวิชาการแก้ปัญหาทางด้านเทคโนโลยีสารสนเทศ รวมกันกี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E670" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F670" s="39" t="inlineStr">
+        <is>
+          <t>3 + 3</t>
+        </is>
+      </c>
+      <c r="G670" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: รวม 6 หน่วยกิต (3 + 3)
+- 06036146 โครงงานทางด้านเทคโนโลยีสารสนเทศเชิงธุรกิจ 2 (PROJECT IN BUSINESS INFORMATION TECHNOLOGY 2) — 3(0-9-0) | ปีที่ 4 ภาคการศึกษาที่ 1
+- 06036118 การแก้ปัญหาทางด้านเทคโนโลยีสารสนเทศ (PROBLEM SOLVING IN INFORMATION TECHNOLOGY) — 3(2-2-5) | ปีที่ 1 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H670" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 23, 26, 29, 31, 75, 76, 246, 256</t>
+        </is>
+      </c>
+      <c r="I670" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวมของสองวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J670" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K670" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L670" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M670" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N670" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O670" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="671" ht="14.25" customHeight="1" s="36">
+      <c r="A671" s="37" t="inlineStr">
+        <is>
+          <t>RH7</t>
+        </is>
+      </c>
+      <c r="B671" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C671" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D671" s="39" t="inlineStr">
+        <is>
+          <t>ไม่ทันลงวิชาการพัฒนาเว็บแอปพลิเคชันโดยใช้เฟรมเวิร์ก ตามแผน ไปลงตอนปี 4 แทนได้ไหม</t>
+        </is>
+      </c>
+      <c r="E671" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F671" s="39" t="inlineStr">
+        <is>
+          <t>ได้ ตามแผนปี 3 ต้องผ่าน 06036119</t>
+        </is>
+      </c>
+      <c r="G671" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ได้ — ตามแผนวิชานี้อยู่ปีที่ 3 อยู่แล้ว (ต้องผ่านวิชาบังคับก่อนข้างต้นก่อน)
+วิชา 06036114 การพัฒนาเว็บแอปพลิเคชันโดยใช้เฟรมเวิร์ก (WEB APPLICATION DEVELOPMENT USING FRAMEWORKS) — 3(2-2-5) หน่วยกิต
+ตามแผนการศึกษา: ปีที่ 3 ภาคการศึกษาที่ 1
+วิชาบังคับก่อน (ต้องสอบผ่านก่อนจึงจะลงได้):
+  - 06036119 พื้นฐานการเขียนโปรแกรม (PROGRAMMING FUNDAMENTALS) — ปีที่ 1 ภาคการศึกษาที่ 2
+  - 06036122 การสื่อสารด้วยภาพสำหรับธุรกิจ (VISUAL COMMUNICATION FOR BUSINESS) — ปีที่ 2 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H671" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 75, 23, 244, 270, 22, 27, 28, 32</t>
+        </is>
+      </c>
+      <c r="I671" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (ปีตามแผน + วิชาบังคับก่อน → ลงได้/ไม่ได้) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J671" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K671" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L671" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M671" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N671" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O671" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="672" ht="14.25" customHeight="1" s="36">
+      <c r="A672" s="37" t="inlineStr">
+        <is>
+          <t>RC3</t>
+        </is>
+      </c>
+      <c r="B672" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C672" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D672" s="39" t="inlineStr">
+        <is>
+          <t>กว่าจะได้ลงวิชาการพัฒนาเว็บแอปพลิเคชันโดยใช้เฟรมเวิร์ก ต้องสอบผ่านกี่วิชา นับทุกทอด</t>
+        </is>
+      </c>
+      <c r="E672" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F672" s="39" t="inlineStr">
+        <is>
+          <t>2 วิชา: 06036119, 06036122</t>
+        </is>
+      </c>
+      <c r="G672" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06036114 การพัฒนาเว็บแอปพลิเคชันโดยใช้เฟรมเวิร์ก (WEB APPLICATION DEVELOPMENT USING FRAMEWORKS) — ปีที่ 3 ภาคการศึกษาที่ 1
+วิชาที่ต้องสอบผ่านก่อน (↳ = วิชาที่ต้องผ่านก่อนวิชาด้านบนอีกชั้น):
+  • 06036119 พื้นฐานการเขียนโปรแกรม (PROGRAMMING FUNDAMENTALS) — 3(2-2-5) | ปีที่ 1 ภาคการศึกษาที่ 2
+  • 06036122 การสื่อสารด้วยภาพสำหรับธุรกิจ (VISUAL COMMUNICATION FOR BUSINESS) — 3(2-2-5) | ปีที่ 2 ภาคการศึกษาที่ 1
+รวมต้องผ่านก่อน 2 วิชา</t>
+        </is>
+      </c>
+      <c r="H672" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 75, 23, 244, 270, 22, 27, 28, 32</t>
+        </is>
+      </c>
+      <c r="I672" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (วิชาบังคับก่อนไล่หลายชั้น) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J672" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K672" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L672" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M672" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N672" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O672" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="673" ht="14.25" customHeight="1" s="36">
+      <c r="A673" s="37" t="inlineStr">
+        <is>
+          <t>RH8</t>
+        </is>
+      </c>
+      <c r="B673" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C673" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D673" s="39" t="inlineStr">
+        <is>
+          <t>ปี 1 เทอม 1 กับเทอม 2 เทอมไหนต้องลงหน่วยกิตเยอะกว่ากัน</t>
+        </is>
+      </c>
+      <c r="E673" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F673" s="39" t="inlineStr">
+        <is>
+          <t>ภาค 1 18, ภาค 2 21</t>
+        </is>
+      </c>
+      <c r="G673" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ปีที่ 1 ภาคการศึกษาที่ 2 หนักกว่า (21 เทียบกับ 18 หน่วยกิต) ต่างกัน 3 หน่วยกิต
+หน่วยกิตต่อภาคตามแผนปกติของ DSBA 2565 (ปริญญาตรี) (บรรทัด 'รวม' ของแต่ละภาค รวมวิชาเลือกที่แผนกำหนดแล้ว):
+- ปีที่ 1 ภาคการศึกษาที่ 1: 18 หน่วยกิต (หน้า 23)
+- ปีที่ 1 ภาคการศึกษาที่ 2: 21 หน่วยกิต (หน้า 24)</t>
+        </is>
+      </c>
+      <c r="H673" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 23, 24</t>
+        </is>
+      </c>
+      <c r="I673" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (เทียบภาค/ทั้งปี/สะสมตามแผน) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J673" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K673" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L673" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M673" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N673" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O673" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="674" ht="14.25" customHeight="1" s="36">
+      <c r="A674" s="37" t="inlineStr">
+        <is>
+          <t>RH9</t>
+        </is>
+      </c>
+      <c r="B674" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C674" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D674" s="39" t="inlineStr">
+        <is>
+          <t>ตามแผน ปี 3 ทั้งปีต้องเรียนกี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E674" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F674" s="39" t="inlineStr">
+        <is>
+          <t>18 + 18</t>
+        </is>
+      </c>
+      <c r="G674" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ปีที่ 3 ตามแผนปกติเรียนรวม 36 หน่วยกิต
+หน่วยกิตต่อภาคตามแผนปกติของ DSBA 2565 (ปริญญาตรี) (บรรทัด 'รวม' ของแต่ละภาค รวมวิชาเลือกที่แผนกำหนดแล้ว):
+- ปีที่ 3 ภาคการศึกษาที่ 1: 18 หน่วยกิต (หน้า 27)
+- ปีที่ 3 ภาคการศึกษาที่ 2: 18 หน่วยกิต (หน้า 28)</t>
+        </is>
+      </c>
+      <c r="H674" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 27, 28</t>
+        </is>
+      </c>
+      <c r="I674" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (เทียบภาค/ทั้งปี/สะสมตามแผน) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J674" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K674" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L674" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M674" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N674" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O674" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="675" ht="14.25" customHeight="1" s="36">
+      <c r="A675" s="37" t="inlineStr">
+        <is>
+          <t>RH10</t>
+        </is>
+      </c>
+      <c r="B675" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C675" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D675" s="39" t="inlineStr">
+        <is>
+          <t>ถ้าลงวิชาการเรียนรู้ของเครื่องเชิงประยุกต์ และวิชาการสื่อสารและการนำเสนออย่างมืออาชีพ รวมกันกี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E675" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F675" s="39" t="inlineStr">
+        <is>
+          <t>3 + 3</t>
+        </is>
+      </c>
+      <c r="G675" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: รวม 6 หน่วยกิต (3 + 3)
+- 06026211 การเรียนรู้ของเครื่องเชิงประยุกต์ (APPLIED MACHINE LEARNING) — 3(2-2-5) | ปีที่ 3 ภาคการศึกษาที่ 1
+- 90644042 การสื่อสารและการนำเสนออย่างมืออาชีพ (PROFESSIONAL COMMUNICATION AND PRESENTATION) — 3(3-0-6) | ปีที่ 3 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H675" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 27, 34, 16, 18, 68, 323, 353, 354</t>
+        </is>
+      </c>
+      <c r="I675" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวมของสองวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J675" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K675" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L675" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M675" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N675" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O675" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="676" ht="14.25" customHeight="1" s="36">
+      <c r="A676" s="37" t="inlineStr">
+        <is>
+          <t>RH11</t>
+        </is>
+      </c>
+      <c r="B676" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C676" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D676" s="39" t="inlineStr">
+        <is>
+          <t>ไม่ทันลงวิชาระบบสารสนเทศเพื่อการจัดการ ตามแผน ไปลงตอนปี 3 แทนได้ไหม</t>
+        </is>
+      </c>
+      <c r="E676" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F676" s="39" t="inlineStr">
+        <is>
+          <t>ได้ ตามแผนปี 2 ต้องผ่าน 06066101</t>
+        </is>
+      </c>
+      <c r="G676" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ได้ — ตามแผนวิชานี้อยู่ปีที่ 2 อยู่แล้ว (ต้องผ่านวิชาบังคับก่อนข้างต้นก่อน)
+วิชา 06066102 ระบบสารสนเทศเพื่อการจัดการ (MANAGEMENT INFORMATION SYSTEMS) — 3(3-0-6) หน่วยกิต
+ตามแผนการศึกษา: ปีที่ 2 ภาคการศึกษาที่ 2
+วิชาบังคับก่อน (ต้องสอบผ่านก่อนจึงจะลงได้):
+  - 06066101 พื้นฐานทางธุรกิจสำหรับเทคโนโลยีสารสนเทศ (BUSINESS FUNDAMENTALS FOR INFORMATION TECHNOLOGY) — ปีที่ 1 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H676" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 18, 73, 353, 23, 26, 30, 33, 317</t>
+        </is>
+      </c>
+      <c r="I676" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (ปีตามแผน + วิชาบังคับก่อน → ลงได้/ไม่ได้) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J676" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K676" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L676" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M676" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N676" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O676" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="677" ht="14.25" customHeight="1" s="36">
+      <c r="A677" s="37" t="inlineStr">
+        <is>
+          <t>RC4</t>
+        </is>
+      </c>
+      <c r="B677" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C677" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D677" s="39" t="inlineStr">
+        <is>
+          <t>ถ้าเรียนตามแผนครบถึงปี 3 แล้ว จะมีหน่วยกิตสะสมเท่าไร และเหลืออีกกี่หน่วยกิตถึงจะจบ</t>
+        </is>
+      </c>
+      <c r="E677" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F677" s="39" t="inlineStr">
+        <is>
+          <t>สะสม 114 เหลือ 18</t>
+        </is>
+      </c>
+      <c r="G677" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: เรียนครบตามแผนถึงปีที่ 3 มีหน่วยกิตสะสม 114 หน่วยกิต เหลืออีก 18 หน่วยกิตจึงครบ 132 หน่วยกิตตามเกณฑ์จบ (หน้า 2)
+หน่วยกิตต่อภาคตามแผนปกติของ DSBA 2565 (ปริญญาตรี) (บรรทัด 'รวม' ของแต่ละภาค รวมวิชาเลือกที่แผนกำหนดแล้ว):
+- ปีที่ 1 ภาคการศึกษาที่ 1: 18 หน่วยกิต (หน้า 23)
+- ปีที่ 1 ภาคการศึกษาที่ 2: 21 หน่วยกิต (หน้า 24)
+- ปีที่ 2 ภาคการศึกษาที่ 1: 18 หน่วยกิต (หน้า 25)
+- ปีที่ 2 ภาคการศึกษาที่ 2: 21 หน่วยกิต (หน้า 26)
+- ปีที่ 3 ภาคการศึกษาที่ 1: 18 หน่วยกิต (หน้า 27)
+- ปีที่ 3 ภาคการศึกษาที่ 2: 18 หน่วยกิต (หน้า 28)</t>
+        </is>
+      </c>
+      <c r="H677" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 23, 24, 25, 26, 27, 28</t>
+        </is>
+      </c>
+      <c r="I677" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (เทียบภาค/ทั้งปี/สะสมตามแผน) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J677" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="K677" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L677" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M677" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N677" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O677" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="678" ht="14.25" customHeight="1" s="36">
+      <c r="A678" s="37" t="inlineStr">
+        <is>
+          <t>RH12</t>
+        </is>
+      </c>
+      <c r="B678" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C678" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D678" s="39" t="inlineStr">
+        <is>
+          <t>ถ้าลงวิชาระบบโครงสร้างพื้นฐานและการบริการ และวิชาการวิเคราะห์และออกแบบระบบสารสนเทศ รวมกันกี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E678" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F678" s="39" t="inlineStr">
+        <is>
+          <t>3 + 3</t>
+        </is>
+      </c>
+      <c r="G678" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: รวม 6 หน่วยกิต (3 + 3)
+- 06016420 ระบบโครงสร้างพื้นฐานและการบริการ (INFRASTRUCTURE SYSTEMS AND SERVICES) — 3(2-2-5) | ปีที่ 2 ภาคการศึกษาที่ 2
+- 06066304 การวิเคราะห์และออกแบบระบบสารสนเทศ (INFORMATION SYSTEM ANALYSIS AND DESIGN) — 3(3-0-6) | ปีที่ 2 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H678" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 24, 25, 33, 34, 84, 88, 332, 337</t>
+        </is>
+      </c>
+      <c r="I678" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวมของสองวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J678" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K678" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L678" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M678" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N678" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O678" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="679" ht="14.25" customHeight="1" s="36">
+      <c r="A679" s="37" t="inlineStr">
+        <is>
+          <t>RH13</t>
+        </is>
+      </c>
+      <c r="B679" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C679" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D679" s="39" t="inlineStr">
+        <is>
+          <t>ไม่ทันลงวิชาโครงสร้างพื้นฐานเครือข่ายการสื่อสาร ตามแผน ไปลงตอนปี 3 แทนได้ไหม</t>
+        </is>
+      </c>
+      <c r="E679" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F679" s="39" t="inlineStr">
+        <is>
+          <t>ได้ ตามแผนปี 2 ต้องผ่าน 06016413</t>
+        </is>
+      </c>
+      <c r="G679" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ได้ — ตามแผนวิชานี้อยู่ปีที่ 2 อยู่แล้ว (ต้องผ่านวิชาบังคับก่อนข้างต้นก่อน)
+วิชา 06016419 โครงสร้างพื้นฐานเครือข่ายการสื่อสาร (COMMUNICATION NETWORK INFRASTRUCTURE) — 3(2-2-5) หน่วยกิต
+ตามแผนการศึกษา: ปีที่ 2 ภาคการศึกษาที่ 2
+วิชาบังคับก่อน (ต้องสอบผ่านก่อนจึงจะลงได้):
+  - 06016413 ระบบเครือข่ายเบื้องต้น (INTRODUCTION TO NETWORK SYSTEMS) — ปีที่ 2 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H679" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 84, 24, 25, 33, 34, 40, 328, 331</t>
+        </is>
+      </c>
+      <c r="I679" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (ปีตามแผน + วิชาบังคับก่อน → ลงได้/ไม่ได้) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J679" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K679" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L679" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M679" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N679" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O679" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="680" ht="14.25" customHeight="1" s="36">
+      <c r="A680" s="37" t="inlineStr">
+        <is>
+          <t>RC5</t>
+        </is>
+      </c>
+      <c r="B680" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C680" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D680" s="39" t="inlineStr">
+        <is>
+          <t>จบมาด้วยเกรดเฉลี่ย 3.74 ได้เหรียญทองไหม</t>
+        </is>
+      </c>
+      <c r="E680" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F680" s="39" t="inlineStr">
+        <is>
+          <t>ไม่ได้ (ต้อง &gt;= 3.75) ได้อันดับ 1</t>
+        </is>
+      </c>
+      <c r="G680" s="39" t="inlineStr">
+        <is>
+          <t>ปริญญาเกียรตินิยม — ข้อ 36 ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 88, 89
+(ข้อบังคับของสถาบัน ใช้กับทุกหลักสูตรปริญญาตรี)
+- เกียรตินิยมอันดับหนึ่งและเหรียญทอง: ค่าระดับคะแนนเฉลี่ยสะสมตามโครงสร้างหลักสูตรสูงสุดในกลุ่มผู้สำเร็จการศึกษาปีเดียวกันของหลักสูตร และค่าระดับคะแนนเฉลี่ยสะสมไม่ต่ำกว่า 3.75 และต้องไม่เทียบโอนผลการเรียนจากสถาบันอื่น
+- เกียรตินิยมอันดับหนึ่ง: ค่าระดับคะแนนเฉลี่ยสะสมไม่ต่ำกว่า 3.50
+- เกียรตินิยมอันดับสอง: ค่าระดับคะแนนเฉลี่ยสะสมไม่ต่ำกว่า 3.25
+- กรณีโอนผลการเรียนจากสถาบันอื่น ทุกรายวิชาต้องได้ไม่ต่ำกว่า B หรือ S และต้องเรียนในหลักสูตรของสถาบันไม่น้อยกว่า 2 ใน 3 ของหน่วยกิตรวม
+- เงื่อนไขทั่วไป (ข้อ 36.1): เรียนไม่เกินระยะเวลาตามแผนการศึกษา · ไม่มีรายวิชาใดได้ F หรือ U · ไม่เคยเรียนซ้ำเพื่อเปลี่ยนเกรด · ไม่เคยลาพักเพราะไม่ลงทะเบียนตามกำหนด และไม่เคยถูกลงโทษทางวินัย</t>
+        </is>
+      </c>
+      <c r="H680" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 88, 89</t>
+        </is>
+      </c>
+      <c r="I680" s="39" t="inlineStr">
+        <is>
+          <t>ข้อบังคับปริญญาตรี (ภาคผนวกเล่ม AIT 2566) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J680" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K680" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L680" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M680" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N680" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O680" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="681" ht="14.25" customHeight="1" s="36">
+      <c r="A681" s="37" t="inlineStr">
+        <is>
+          <t>RC6</t>
+        </is>
+      </c>
+      <c r="B681" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C681" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D681" s="39" t="inlineStr">
+        <is>
+          <t>ปีสี่เทอมสุดท้ายเหลือ 24 หน่วยกิต ลงทีเดียวหมดได้ไหม</t>
+        </is>
+      </c>
+      <c r="E681" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F681" s="39" t="inlineStr">
+        <is>
+          <t>ได้ ข้อยกเว้นปีสุดท้ายไม่เกิน 27</t>
+        </is>
+      </c>
+      <c r="G681" s="39" t="inlineStr">
+        <is>
+          <t>ได้ — นักศึกษาชั้นปีสุดท้ายที่เหลือหน่วยกิตน้อยกว่า 9 หน่วยกิตหรือต้องลงเกิน 22 หน่วยกิตเพื่อสำเร็จการศึกษา สามารถลงทะเบียนได้ไม่เกิน 27 หน่วยกิตตามข้อยกเว้นในข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวก มคอ.2 AIT 2566) หน้า 82 ซึ่งครอบคลุมกรณีนี้ โดยหลักสูตรวท.บ. (เทคโนโลยีสารสนเทศ) ต้องเรียนรวม 129 หน่วยกิต (ข้อมูลจาก มคอ.2 หลักสูตร IT 2565 หน้า 6)</t>
+        </is>
+      </c>
+      <c r="H681" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 82</t>
+        </is>
+      </c>
+      <c r="I681" s="39" t="inlineStr">
+        <is>
+          <t>ข้อบังคับปริญญาตรี (ภาคผนวกเล่ม AIT 2566) → Typhoon เรียบเรียง</t>
+        </is>
+      </c>
+      <c r="J681" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K681" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L681" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M681" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก ข้อบังคับ ป.ตรี (AIT 2566 ภาคผนวก หน้า 82, 87, 89))</t>
+        </is>
+      </c>
+      <c r="N681" s="39" t="inlineStr">
+        <is>
+          <t>2.13s</t>
+        </is>
+      </c>
+      <c r="O681" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="682" ht="14.25" customHeight="1" s="36">
+      <c r="A682" s="37" t="inlineStr">
+        <is>
+          <t>RC7</t>
+        </is>
+      </c>
+      <c r="B682" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C682" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D682" s="39" t="inlineStr">
+        <is>
+          <t>โดนภาคทัณฑ์แล้วต้องทำยังไงถึงจะพ้น</t>
+        </is>
+      </c>
+      <c r="E682" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F682" s="39" t="inlineStr">
+        <is>
+          <t>เกรดเฉลี่ยสะสมไม่ต่ำกว่า 2.00</t>
+        </is>
+      </c>
+      <c r="G682" s="39" t="inlineStr">
+        <is>
+          <t>การภาคทัณฑ์ — ข้อ 31 ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 87
+(ข้อบังคับของสถาบัน ใช้กับทุกหลักสูตรปริญญาตรี)
+- นักศึกษาที่ได้ค่าระดับคะแนนเฉลี่ยสะสมต่ำกว่า 2.00 ต้องถูกภาคทัณฑ์
+- จะพ้นภาคทัณฑ์เมื่อค่าระดับคะแนนเฉลี่ยสะสมไม่ต่ำกว่า 2.00 (นับรวมภาคการศึกษาพิเศษด้วย)
+- ถ้าระหว่างภาคทัณฑ์ได้ค่าระดับคะแนนเฉลี่ยประจำภาคถัดไปต่ำกว่า 2.00 จะพ้นสภาพนักศึกษา (ข้อ 43.10)</t>
+        </is>
+      </c>
+      <c r="H682" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 87</t>
+        </is>
+      </c>
+      <c r="I682" s="39" t="inlineStr">
+        <is>
+          <t>ข้อบังคับปริญญาตรี (ภาคผนวกเล่ม AIT 2566) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J682" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K682" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L682" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M682" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก ข้อบังคับ ป.ตรี (AIT 2566 ภาคผนวก หน้า 82, 87, 89))</t>
+        </is>
+      </c>
+      <c r="N682" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O682" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="683" ht="14.25" customHeight="1" s="36">
+      <c r="A683" s="37" t="inlineStr">
+        <is>
+          <t>RC8</t>
+        </is>
+      </c>
+      <c r="B683" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C683" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D683" s="39" t="inlineStr">
+        <is>
+          <t>สะสมได้ 117 หน่วยกิต GPA 3.20 ขาดอีกกี่หน่วยกิตถึงจบ</t>
+        </is>
+      </c>
+      <c r="E683" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F683" s="39" t="inlineStr">
+        <is>
+          <t>ขาด 3</t>
+        </is>
+      </c>
+      <c r="G683" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ยังจบไม่ได้
+หลักสูตร AIT 2566 (ปริญญาตรี) ต้องเรียนครบไม่น้อยกว่า 120 หน่วยกิต (หน้า 5)
+- หน่วยกิต: เก็บได้ 117 หน่วยกิต → ยังขาดอีก 3 หน่วยกิต (ต้องครบ 120)
+- เกรดเฉลี่ยสะสม 3.20 → ผ่านเกณฑ์ขั้นต่ำ 2.00 (ข้อ 34)
+- เงื่อนไขอื่นตามข้อ 34: สอบผ่านทุกรายวิชาตามโครงสร้างหลักสูตร และผ่านการสอบภาษาอังกฤษ (English Exit exam)</t>
+        </is>
+      </c>
+      <c r="H683" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 5, 88</t>
+        </is>
+      </c>
+      <c r="I683" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวม + เกรดขั้นต่ำ ข้อ 34) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J683" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K683" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L683" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M683" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N683" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O683" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="684" ht="14.25" customHeight="1" s="36">
+      <c r="A684" s="37" t="inlineStr">
+        <is>
+          <t>RC9</t>
+        </is>
+      </c>
+      <c r="B684" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C684" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D684" s="39" t="inlineStr">
+        <is>
+          <t>BIT กับ DSBA ต้องเรียนรวมต่างกันกี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E684" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 8 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F684" s="39" t="inlineStr">
+        <is>
+          <t>ต่างกัน 6</t>
+        </is>
+      </c>
+      <c r="G684" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ต่างกัน 6 หน่วยกิต (DSBA 2565 (ปริญญาตรี) มากกว่า BIT 2565 (ปริญญาตรี))
+- BIT 2565 (ปริญญาตรี): ไม่น้อยกว่า 126 หน่วยกิต (หน้า 6)
+- DSBA 2565 (ปริญญาตรี): ไม่น้อยกว่า 132 หน่วยกิต (หน้า 2)</t>
+        </is>
+      </c>
+      <c r="H684" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 6, 2</t>
+        </is>
+      </c>
+      <c r="I684" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวมข้ามหลักสูตร) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J684" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K684" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L684" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M684" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N684" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O684" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="685" ht="14.25" customHeight="1" s="36">
+      <c r="A685" s="37" t="inlineStr">
+        <is>
+          <t>SH1</t>
+        </is>
+      </c>
+      <c r="B685" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C685" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D685" s="39" t="inlineStr">
+        <is>
+          <t>ปี 2 ภาคต้นกับภาคปลาย ภาคไหนเรียนหนักกว่า ต่างกันกี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E685" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F685" s="39" t="inlineStr">
+        <is>
+          <t>ภาค 1 18, ภาค 2 19</t>
+        </is>
+      </c>
+      <c r="G685" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ปีที่ 2 ภาคการศึกษาที่ 2 หนักกว่า (19 เทียบกับ 18 หน่วยกิต) ต่างกัน 1 หน่วยกิต
+หน่วยกิตต่อภาคตามแผนปกติของ AIT 2566 (ปริญญาตรี) (บรรทัด 'รวม' ของแต่ละภาค รวมวิชาเลือกที่แผนกำหนดแล้ว):
+- ปีที่ 2 ภาคการศึกษาที่ 1: 18 หน่วยกิต (หน้า 24)
+- ปีที่ 2 ภาคการศึกษาที่ 2: 19 หน่วยกิต (หน้า 24)</t>
+        </is>
+      </c>
+      <c r="H685" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 24</t>
+        </is>
+      </c>
+      <c r="I685" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (เทียบภาค/ทั้งปี/สะสมตามแผน) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J685" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K685" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L685" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M685" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N685" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O685" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="686" ht="14.25" customHeight="1" s="36">
+      <c r="A686" s="37" t="inlineStr">
+        <is>
+          <t>SH2</t>
+        </is>
+      </c>
+      <c r="B686" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C686" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D686" s="39" t="inlineStr">
+        <is>
+          <t>ถ้าเรียนตามแผน ตลอดปีที่ 2 รวมสองเทอมได้กี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E686" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F686" s="39" t="inlineStr">
+        <is>
+          <t>18 + 19</t>
+        </is>
+      </c>
+      <c r="G686" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ปีที่ 2 ตามแผนปกติเรียนรวม 37 หน่วยกิต
+หน่วยกิตต่อภาคตามแผนปกติของ AIT 2566 (ปริญญาตรี) (บรรทัด 'รวม' ของแต่ละภาค รวมวิชาเลือกที่แผนกำหนดแล้ว):
+- ปีที่ 2 ภาคการศึกษาที่ 1: 18 หน่วยกิต (หน้า 24)
+- ปีที่ 2 ภาคการศึกษาที่ 2: 19 หน่วยกิต (หน้า 24)</t>
+        </is>
+      </c>
+      <c r="H686" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 24</t>
+        </is>
+      </c>
+      <c r="I686" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (เทียบภาค/ทั้งปี/สะสมตามแผน) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J686" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K686" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L686" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M686" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N686" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O686" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="687" ht="14.25" customHeight="1" s="36">
+      <c r="A687" s="37" t="inlineStr">
+        <is>
+          <t>SH3</t>
+        </is>
+      </c>
+      <c r="B687" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C687" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D687" s="39" t="inlineStr">
+        <is>
+          <t>วิชาสัมมนาปัญญาประดิษฐ์ บวก พลเมืองดิจิทัล ได้หน่วยกิตรวมเท่าไร</t>
+        </is>
+      </c>
+      <c r="E687" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F687" s="39" t="inlineStr">
+        <is>
+          <t>3 + 3</t>
+        </is>
+      </c>
+      <c r="G687" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: รวม 6 หน่วยกิต (3 + 3)
+- 06046440 วิชาสัมมนาปัญญาประดิษฐ์ (SEMINAR IN ARTIFICIAL INTELLIGENCE) — 3(2-2-5) | ปีที่ 3 ภาคการศึกษาที่ 1
+- 90641007 พลเมืองดิจิทัล (DIGITAL CITIZEN) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 2</t>
+        </is>
+      </c>
+      <c r="H687" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 19, 22, 23, 25, 36, 40, 119, 120</t>
+        </is>
+      </c>
+      <c r="I687" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวมของสองวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J687" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K687" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L687" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M687" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N687" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O687" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="688" ht="14.25" customHeight="1" s="36">
+      <c r="A688" s="37" t="inlineStr">
+        <is>
+          <t>SH4</t>
+        </is>
+      </c>
+      <c r="B688" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C688" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D688" s="39" t="inlineStr">
+        <is>
+          <t>ถ้าเลื่อนวิชาแคลคูลัส 2 ไปเรียนปี 2 จะได้หรือเปล่า</t>
+        </is>
+      </c>
+      <c r="E688" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F688" s="39" t="inlineStr">
+        <is>
+          <t>ได้ ตามแผนปี 1 ต้องผ่าน 06046400</t>
+        </is>
+      </c>
+      <c r="G688" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ได้ — ตามแผนวิชานี้อยู่ปีที่ 1 อยู่แล้ว (ต้องผ่านวิชาบังคับก่อนข้างต้นก่อน)
+วิชา 06046401 แคลคูลัส 2 (CALCULUS 2) — 3(3-0-6) หน่วยกิต
+ตามแผนการศึกษา: ปีที่ 1 ภาคการศึกษาที่ 2
+วิชาบังคับก่อน (ต้องสอบผ่านก่อนจึงจะลงได้):
+  - 06046400 แคลคูลัส 1 (CALCULUS 1) — ปีที่ 1 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H688" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 19, 37, 287, 23, 292</t>
+        </is>
+      </c>
+      <c r="I688" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (ปีตามแผน + วิชาบังคับก่อน → ลงได้/ไม่ได้) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J688" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="K688" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L688" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M688" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N688" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O688" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="689" ht="14.25" customHeight="1" s="36">
+      <c r="A689" s="37" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B689" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C689" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D689" s="39" t="inlineStr">
+        <is>
+          <t>จบปี 3 ตามแผนพอดี เก็บหน่วยกิตได้กี่หน่วยกิต ยังขาดอีกเท่าไหร่</t>
+        </is>
+      </c>
+      <c r="E689" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F689" s="39" t="inlineStr">
+        <is>
+          <t>สะสม 102 เหลือ 18</t>
+        </is>
+      </c>
+      <c r="G689" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: เรียนครบตามแผนถึงปีที่ 3 มีหน่วยกิตสะสม 102 หน่วยกิต เหลืออีก 18 หน่วยกิตจึงครบ 120 หน่วยกิตตามเกณฑ์จบ (หน้า 5)
+หน่วยกิตต่อภาคตามแผนปกติของ AIT 2566 (ปริญญาตรี) (บรรทัด 'รวม' ของแต่ละภาค รวมวิชาเลือกที่แผนกำหนดแล้ว):
+- ปีที่ 1 ภาคการศึกษาที่ 1: 15 หน่วยกิต (หน้า 23)
+- ปีที่ 1 ภาคการศึกษาที่ 2: 19 หน่วยกิต (หน้า 23)
+- ปีที่ 2 ภาคการศึกษาที่ 1: 18 หน่วยกิต (หน้า 24)
+- ปีที่ 2 ภาคการศึกษาที่ 2: 19 หน่วยกิต (หน้า 24)
+- ปีที่ 3 ภาคการศึกษาที่ 1: 18 หน่วยกิต (หน้า 25)
+- ปีที่ 3 ภาคการศึกษาที่ 2: 13 หน่วยกิต (หน้า 25)</t>
+        </is>
+      </c>
+      <c r="H689" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 23, 24, 25</t>
+        </is>
+      </c>
+      <c r="I689" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (เทียบภาค/ทั้งปี/สะสมตามแผน) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J689" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="K689" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L689" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M689" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N689" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O689" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="690" ht="14.25" customHeight="1" s="36">
+      <c r="A690" s="37" t="inlineStr">
+        <is>
+          <t>SC2</t>
+        </is>
+      </c>
+      <c r="B690" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C690" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D690" s="39" t="inlineStr">
+        <is>
+          <t>วิชาพื้นฐานการเรียนรู้เชิงลึก มีวิชาที่ต้องผ่านก่อนทั้งทางตรงและทางอ้อมกี่วิชา อะไรบ้าง</t>
+        </is>
+      </c>
+      <c r="E690" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F690" s="39" t="inlineStr">
+        <is>
+          <t>3 วิชา: 06046400, 06046401, 06046402</t>
+        </is>
+      </c>
+      <c r="G690" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06046406 พื้นฐานการเรียนรู้เชิงลึก (FUNDAMENTALS OF DEEP LEARNING) — ปีที่ 2 ภาคการศึกษาที่ 1
+วิชาที่ต้องสอบผ่านก่อน (↳ = วิชาที่ต้องผ่านก่อนวิชาด้านบนอีกชั้น):
+  • 06046401 แคลคูลัส 2 (CALCULUS 2) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 2
+    ↳ 06046400 แคลคูลัส 1 (CALCULUS 1) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 1
+  • 06046402 พีชคณิตเชิงเส้น (LINEAR ALGEBRA) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 1
+รวมต้องผ่านก่อน 3 วิชา</t>
+        </is>
+      </c>
+      <c r="H690" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 37, 19, 292, 23, 287, 20, 24, 288</t>
+        </is>
+      </c>
+      <c r="I690" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (วิชาบังคับก่อนไล่หลายชั้น) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J690" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K690" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L690" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M690" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/AIT/AIT_academic_plan.json)</t>
+        </is>
+      </c>
+      <c r="N690" s="39" t="inlineStr">
+        <is>
+          <t>0.02s</t>
+        </is>
+      </c>
+      <c r="O690" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="691" ht="14.25" customHeight="1" s="36">
+      <c r="A691" s="37" t="inlineStr">
+        <is>
+          <t>SH5</t>
+        </is>
+      </c>
+      <c r="B691" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C691" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D691" s="39" t="inlineStr">
+        <is>
+          <t>ปี 3 ภาคต้นกับภาคปลาย ภาคไหนเรียนหนักกว่า ต่างกันกี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E691" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F691" s="39" t="inlineStr">
+        <is>
+          <t>ภาค 1 18, ภาค 2 9</t>
+        </is>
+      </c>
+      <c r="G691" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ปีที่ 3 ภาคการศึกษาที่ 1 หนักกว่า (18 เทียบกับ 12 หน่วยกิต) ต่างกัน 6 หน่วยกิต
+หน่วยกิตต่อภาคตามแผนปกติของ BIT 2565 (ปริญญาตรี) (บรรทัด 'รวม' ของแต่ละภาค รวมวิชาเลือกที่แผนกำหนดแล้ว):
+- ปีที่ 3 ภาคการศึกษาที่ 1: 18 หน่วยกิต (หน้า 28)
+- ปีที่ 3 ภาคการศึกษาที่ 2: 12 หน่วยกิต (หน้า 29)</t>
+        </is>
+      </c>
+      <c r="H691" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 28, 29</t>
+        </is>
+      </c>
+      <c r="I691" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (เทียบภาค/ทั้งปี/สะสมตามแผน) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J691" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K691" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L691" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M691" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N691" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O691" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="692" ht="14.25" customHeight="1" s="36">
+      <c r="A692" s="37" t="inlineStr">
+        <is>
+          <t>SH6</t>
+        </is>
+      </c>
+      <c r="B692" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C692" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D692" s="39" t="inlineStr">
+        <is>
+          <t>ถ้าเรียนตามแผน ตลอดปีที่ 4 รวมสองเทอมได้กี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E692" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F692" s="39" t="inlineStr">
+        <is>
+          <t>12 + 12</t>
+        </is>
+      </c>
+      <c r="G692" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ปีที่ 4 ตามแผนปกติเรียนรวม 24 หน่วยกิต
+หน่วยกิตต่อภาคตามแผนปกติของ BIT 2565 (ปริญญาตรี) (บรรทัด 'รวม' ของแต่ละภาค รวมวิชาเลือกที่แผนกำหนดแล้ว):
+- ปีที่ 4 ภาคการศึกษาที่ 1: 12 หน่วยกิต (หน้า 29)
+- ปีที่ 4 ภาคการศึกษาที่ 2: 12 หน่วยกิต (หน้า 30)</t>
+        </is>
+      </c>
+      <c r="H692" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 29, 30</t>
+        </is>
+      </c>
+      <c r="I692" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (เทียบภาค/ทั้งปี/สะสมตามแผน) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J692" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K692" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L692" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M692" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N692" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O692" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="693" ht="14.25" customHeight="1" s="36">
+      <c r="A693" s="37" t="inlineStr">
+        <is>
+          <t>SH7</t>
+        </is>
+      </c>
+      <c r="B693" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C693" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D693" s="39" t="inlineStr">
+        <is>
+          <t>ภาษาอังกฤษพื้นฐาน 2 บวก คณิตศาสตร์สำหรับธุรกิจ ได้หน่วยกิตรวมเท่าไร</t>
+        </is>
+      </c>
+      <c r="E693" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F693" s="39" t="inlineStr">
+        <is>
+          <t>3 + 3</t>
+        </is>
+      </c>
+      <c r="G693" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: รวม 6 หน่วยกิต (3 + 3)
+- 96644008 ภาษาอังกฤษพื้นฐาน 2 (FOUNDATION ENGLISH 2) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 2
+- 06036101 คณิตศาสตร์สำหรับธุรกิจ (MATHEMATICS FOR BUSINESS) — 3(3-0-6) | ปีที่ 1 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H693" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 20, 21, 26, 27, 31, 32, 74, 238</t>
+        </is>
+      </c>
+      <c r="I693" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวมของสองวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J693" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K693" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L693" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M693" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N693" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O693" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="694" ht="14.25" customHeight="1" s="36">
+      <c r="A694" s="37" t="inlineStr">
+        <is>
+          <t>SH8</t>
+        </is>
+      </c>
+      <c r="B694" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C694" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D694" s="39" t="inlineStr">
+        <is>
+          <t>ถ้าเลื่อนวิชาการพัฒนาเว็บแอปพลิเคชันโดยใช้เฟรมเวิร์ก ไปเรียนปี 4 จะได้หรือเปล่า</t>
+        </is>
+      </c>
+      <c r="E694" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F694" s="39" t="inlineStr">
+        <is>
+          <t>ได้ ตามแผนปี 3 ต้องผ่าน 06036119</t>
+        </is>
+      </c>
+      <c r="G694" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ได้ — ตามแผนวิชานี้อยู่ปีที่ 3 อยู่แล้ว (ต้องผ่านวิชาบังคับก่อนข้างต้นก่อน)
+วิชา 06036114 การพัฒนาเว็บแอปพลิเคชันโดยใช้เฟรมเวิร์ก (WEB APPLICATION DEVELOPMENT USING FRAMEWORKS) — 3(2-2-5) หน่วยกิต
+ตามแผนการศึกษา: ปีที่ 3 ภาคการศึกษาที่ 1
+วิชาบังคับก่อน (ต้องสอบผ่านก่อนจึงจะลงได้):
+  - 06036119 พื้นฐานการเขียนโปรแกรม (PROGRAMMING FUNDAMENTALS) — ปีที่ 1 ภาคการศึกษาที่ 2
+  - 06036122 การสื่อสารด้วยภาพสำหรับธุรกิจ (VISUAL COMMUNICATION FOR BUSINESS) — ปีที่ 2 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H694" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 75, 23, 244, 270, 22, 27, 28, 32</t>
+        </is>
+      </c>
+      <c r="I694" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (ปีตามแผน + วิชาบังคับก่อน → ลงได้/ไม่ได้) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J694" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K694" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L694" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M694" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N694" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O694" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="695" ht="14.25" customHeight="1" s="36">
+      <c r="A695" s="37" t="inlineStr">
+        <is>
+          <t>SC3</t>
+        </is>
+      </c>
+      <c r="B695" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C695" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D695" s="39" t="inlineStr">
+        <is>
+          <t>วิชาการพัฒนาเว็บแอปพลิเคชันโดยใช้เฟรมเวิร์ก มีวิชาที่ต้องผ่านก่อนทั้งทางตรงและทางอ้อมกี่วิชา อะไรบ้าง</t>
+        </is>
+      </c>
+      <c r="E695" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F695" s="39" t="inlineStr">
+        <is>
+          <t>2 วิชา: 06036119, 06036122</t>
+        </is>
+      </c>
+      <c r="G695" s="39" t="inlineStr">
+        <is>
+          <t>วิชา 06036114 การพัฒนาเว็บแอปพลิเคชันโดยใช้เฟรมเวิร์ก (WEB APPLICATION DEVELOPMENT USING FRAMEWORKS) — ปีที่ 3 ภาคการศึกษาที่ 1
+วิชาที่ต้องสอบผ่านก่อน (↳ = วิชาที่ต้องผ่านก่อนวิชาด้านบนอีกชั้น):
+  • 06036119 พื้นฐานการเขียนโปรแกรม (PROGRAMMING FUNDAMENTALS) — 3(2-2-5) | ปีที่ 1 ภาคการศึกษาที่ 2
+  • 06036122 การสื่อสารด้วยภาพสำหรับธุรกิจ (VISUAL COMMUNICATION FOR BUSINESS) — 3(2-2-5) | ปีที่ 2 ภาคการศึกษาที่ 1
+รวมต้องผ่านก่อน 2 วิชา</t>
+        </is>
+      </c>
+      <c r="H695" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 75, 23, 244, 270, 22, 27, 28, 32</t>
+        </is>
+      </c>
+      <c r="I695" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (วิชาบังคับก่อนไล่หลายชั้น) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J695" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K695" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L695" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M695" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/BIT/BIT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N695" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O695" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="696" ht="14.25" customHeight="1" s="36">
+      <c r="A696" s="37" t="inlineStr">
+        <is>
+          <t>SH9</t>
+        </is>
+      </c>
+      <c r="B696" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C696" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D696" s="39" t="inlineStr">
+        <is>
+          <t>ปี 1 ภาคต้นกับภาคปลาย ภาคไหนเรียนหนักกว่า ต่างกันกี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E696" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F696" s="39" t="inlineStr">
+        <is>
+          <t>ภาค 1 18, ภาค 2 21</t>
+        </is>
+      </c>
+      <c r="G696" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ปีที่ 1 ภาคการศึกษาที่ 2 หนักกว่า (21 เทียบกับ 18 หน่วยกิต) ต่างกัน 3 หน่วยกิต
+หน่วยกิตต่อภาคตามแผนปกติของ DSBA 2565 (ปริญญาตรี) (บรรทัด 'รวม' ของแต่ละภาค รวมวิชาเลือกที่แผนกำหนดแล้ว):
+- ปีที่ 1 ภาคการศึกษาที่ 1: 18 หน่วยกิต (หน้า 23)
+- ปีที่ 1 ภาคการศึกษาที่ 2: 21 หน่วยกิต (หน้า 24)</t>
+        </is>
+      </c>
+      <c r="H696" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 23, 24</t>
+        </is>
+      </c>
+      <c r="I696" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (เทียบภาค/ทั้งปี/สะสมตามแผน) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J696" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K696" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L696" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M696" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N696" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O696" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="697" ht="14.25" customHeight="1" s="36">
+      <c r="A697" s="37" t="inlineStr">
+        <is>
+          <t>SH10</t>
+        </is>
+      </c>
+      <c r="B697" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C697" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D697" s="39" t="inlineStr">
+        <is>
+          <t>ถ้าเรียนตามแผน ตลอดปีที่ 3 รวมสองเทอมได้กี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E697" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F697" s="39" t="inlineStr">
+        <is>
+          <t>18 + 18</t>
+        </is>
+      </c>
+      <c r="G697" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ปีที่ 3 ตามแผนปกติเรียนรวม 36 หน่วยกิต
+หน่วยกิตต่อภาคตามแผนปกติของ DSBA 2565 (ปริญญาตรี) (บรรทัด 'รวม' ของแต่ละภาค รวมวิชาเลือกที่แผนกำหนดแล้ว):
+- ปีที่ 3 ภาคการศึกษาที่ 1: 18 หน่วยกิต (หน้า 27)
+- ปีที่ 3 ภาคการศึกษาที่ 2: 18 หน่วยกิต (หน้า 28)</t>
+        </is>
+      </c>
+      <c r="H697" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 27, 28</t>
+        </is>
+      </c>
+      <c r="I697" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (เทียบภาค/ทั้งปี/สะสมตามแผน) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J697" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K697" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L697" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M697" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N697" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O697" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="698" ht="14.25" customHeight="1" s="36">
+      <c r="A698" s="37" t="inlineStr">
+        <is>
+          <t>SH11</t>
+        </is>
+      </c>
+      <c r="B698" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C698" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D698" s="39" t="inlineStr">
+        <is>
+          <t>การแสดงข้อมูลด้วยแผนภาพ บวก เครือข่ายและความมั่นคงทางไซเบอร์เบื่องต้น ได้หน่วยกิตรวมเท่าไร</t>
+        </is>
+      </c>
+      <c r="E698" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F698" s="39" t="inlineStr">
+        <is>
+          <t>3 + 3</t>
+        </is>
+      </c>
+      <c r="G698" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: รวม 6 หน่วยกิต (3 + 3)
+- 06026209 การแสดงข้อมูลด้วยแผนภาพ (DATA VISUALIZATION) — 3(2-2-5) | ปีที่ 2 ภาคการศึกษาที่ 2
+- 06026204 เครือข่ายและความมั่นคงทางไซเบอร์เบื้องต้น (INTRODUCTION TO NETWORKS AND CYBERSECURITY) — 3(3-0-6) | ปีที่ 2 ภาคการศึกษาที่ 2</t>
+        </is>
+      </c>
+      <c r="H698" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 26, 33, 68, 17, 18, 316, 322, 353</t>
+        </is>
+      </c>
+      <c r="I698" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวมของสองวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J698" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K698" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L698" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M698" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/DSBA/DSBA_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N698" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O698" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="699" ht="14.25" customHeight="1" s="36">
+      <c r="A699" s="37" t="inlineStr">
+        <is>
+          <t>SH12</t>
+        </is>
+      </c>
+      <c r="B699" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C699" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D699" s="39" t="inlineStr">
+        <is>
+          <t>ปี 4 ภาคต้นกับภาคปลาย ภาคไหนเรียนหนักกว่า ต่างกันกี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E699" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F699" s="39" t="inlineStr">
+        <is>
+          <t>ภาค 1 15, ภาค 2 9</t>
+        </is>
+      </c>
+      <c r="G699" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ปีที่ 4 ภาคการศึกษาที่ 1 หนักกว่า (15 เทียบกับ 9 หน่วยกิต) ต่างกัน 6 หน่วยกิต
+หน่วยกิตต่อภาคตามแผนปกติของ IT 2565 (ปริญญาตรี) (บรรทัด 'รวม' ของแต่ละภาค รวมวิชาเลือกที่แผนกำหนดแล้ว):
+- ปีที่ 4 ภาคการศึกษาที่ 1: 15 หน่วยกิต (หน้า 37)
+- ปีที่ 4 ภาคการศึกษาที่ 2: 9 หน่วยกิต (หน้า 37)</t>
+        </is>
+      </c>
+      <c r="H699" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 37</t>
+        </is>
+      </c>
+      <c r="I699" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (เทียบภาค/ทั้งปี/สะสมตามแผน) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J699" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K699" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L699" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M699" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N699" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O699" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="700" ht="14.25" customHeight="1" s="36">
+      <c r="A700" s="37" t="inlineStr">
+        <is>
+          <t>SH13</t>
+        </is>
+      </c>
+      <c r="B700" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C700" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D700" s="39" t="inlineStr">
+        <is>
+          <t>ระบบคอมพิวเตอร์เบื้องต้น บวก วิศวกรรมความต้องการ ได้หน่วยกิตรวมเท่าไร</t>
+        </is>
+      </c>
+      <c r="E700" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F700" s="39" t="inlineStr">
+        <is>
+          <t>3 + 3</t>
+        </is>
+      </c>
+      <c r="G700" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: รวม 6 หน่วยกิต (3 + 3)
+- 06016411 ระบบคอมพิวเตอร์เบื้องต้น (INTRODUCTION TO COMPUTER SYSTEMS) — 3(2-2-5) | ปีที่ 1 ภาคการศึกษาที่ 1
+- 06016416 วิศวกรรมความต้องการ (REQUIREMENT ENGINEERING) — 3(3-0-6) | ปีที่ 3 ภาคการศึกษาที่ 1</t>
+        </is>
+      </c>
+      <c r="H700" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 84, 24, 25, 31, 35, 38, 328, 330</t>
+        </is>
+      </c>
+      <c r="I700" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวมของสองวิชา) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J700" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K700" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L700" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M700" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N700" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O700" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="701" ht="14.25" customHeight="1" s="36">
+      <c r="A701" s="37" t="inlineStr">
+        <is>
+          <t>SH14</t>
+        </is>
+      </c>
+      <c r="B701" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 3: ยาก</t>
+        </is>
+      </c>
+      <c r="C701" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D701" s="39" t="inlineStr">
+        <is>
+          <t>ถ้าเลื่อนวิชาการพัฒนาเว็บฝั่งเซิร์ฟเวอร์ ไปเรียนปี 4 จะได้หรือเปล่า</t>
+        </is>
+      </c>
+      <c r="E701" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F701" s="39" t="inlineStr">
+        <is>
+          <t>ได้ ตามแผนปี 3 ต้องผ่าน 06016408</t>
+        </is>
+      </c>
+      <c r="G701" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ได้ — ตามแผนวิชานี้อยู่ปีที่ 3 อยู่แล้ว (ต้องผ่านวิชาบังคับก่อนข้างต้นก่อน)
+วิชา 06016418 การพัฒนาเว็บฝั่งเซิร์ฟเวอร์ (SERVER-SIDE WEB DEVELOPMENT) — 3(2-2-5) หน่วยกิต
+ตามแผนการศึกษา: ปีที่ 3 ภาคการศึกษาที่ 1
+วิชาบังคับก่อน (ต้องสอบผ่านก่อนจึงจะลงได้):
+  - 06016408 การสร้างโปรแกรมเชิงวัตถุ (OBJECT-ORIENTED PROGRAMMING) — ปีที่ 1 ภาคการศึกษาที่ 2</t>
+        </is>
+      </c>
+      <c r="H701" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 331, 24, 25, 26, 32, 35, 39, 83</t>
+        </is>
+      </c>
+      <c r="I701" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (ปีตามแผน + วิชาบังคับก่อน → ลงได้/ไม่ได้) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J701" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K701" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L701" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M701" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/IT/IT_academic_plan_no_coop.json)</t>
+        </is>
+      </c>
+      <c r="N701" s="39" t="inlineStr">
+        <is>
+          <t>0.01s</t>
+        </is>
+      </c>
+      <c r="O701" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="702" ht="14.25" customHeight="1" s="36">
+      <c r="A702" s="37" t="inlineStr">
+        <is>
+          <t>SC4</t>
+        </is>
+      </c>
+      <c r="B702" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C702" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D702" s="39" t="inlineStr">
+        <is>
+          <t>เกรดเฉลี่ยตอนจบ 3.49 ได้เกียรตินิยมอันดับไหน</t>
+        </is>
+      </c>
+      <c r="E702" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F702" s="39" t="inlineStr">
+        <is>
+          <t>อันดับ 2 (ไม่ถึง 3.50)</t>
+        </is>
+      </c>
+      <c r="G702" s="39" t="inlineStr">
+        <is>
+          <t>ปริญญาเกียรตินิยม — ข้อ 36 ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 88, 89
+(ข้อบังคับของสถาบัน ใช้กับทุกหลักสูตรปริญญาตรี)
+- เกียรตินิยมอันดับหนึ่งและเหรียญทอง: ค่าระดับคะแนนเฉลี่ยสะสมตามโครงสร้างหลักสูตรสูงสุดในกลุ่มผู้สำเร็จการศึกษาปีเดียวกันของหลักสูตร และค่าระดับคะแนนเฉลี่ยสะสมไม่ต่ำกว่า 3.75 และต้องไม่เทียบโอนผลการเรียนจากสถาบันอื่น
+- เกียรตินิยมอันดับหนึ่ง: ค่าระดับคะแนนเฉลี่ยสะสมไม่ต่ำกว่า 3.50
+- เกียรตินิยมอันดับสอง: ค่าระดับคะแนนเฉลี่ยสะสมไม่ต่ำกว่า 3.25
+- กรณีโอนผลการเรียนจากสถาบันอื่น ทุกรายวิชาต้องได้ไม่ต่ำกว่า B หรือ S และต้องเรียนในหลักสูตรของสถาบันไม่น้อยกว่า 2 ใน 3 ของหน่วยกิตรวม
+- เงื่อนไขทั่วไป (ข้อ 36.1): เรียนไม่เกินระยะเวลาตามแผนการศึกษา · ไม่มีรายวิชาใดได้ F หรือ U · ไม่เคยเรียนซ้ำเพื่อเปลี่ยนเกรด · ไม่เคยลาพักเพราะไม่ลงทะเบียนตามกำหนด และไม่เคยถูกลงโทษทางวินัย</t>
+        </is>
+      </c>
+      <c r="H702" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 88, 89</t>
+        </is>
+      </c>
+      <c r="I702" s="39" t="inlineStr">
+        <is>
+          <t>ข้อบังคับปริญญาตรี (ภาคผนวกเล่ม AIT 2566) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J702" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K702" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L702" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M702" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N702" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O702" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="703" ht="14.25" customHeight="1" s="36">
+      <c r="A703" s="37" t="inlineStr">
+        <is>
+          <t>SC5</t>
+        </is>
+      </c>
+      <c r="B703" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C703" s="39" t="inlineStr">
+        <is>
+          <t>DSBA</t>
+        </is>
+      </c>
+      <c r="D703" s="39" t="inlineStr">
+        <is>
+          <t>ปีสุดท้ายเหลือวิชาอีก 25 หน่วยกิต ลงเทอมเดียวให้จบได้ไหม</t>
+        </is>
+      </c>
+      <c r="E703" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F703" s="39" t="inlineStr">
+        <is>
+          <t>ได้ ข้อยกเว้นปีสุดท้ายไม่เกิน 27</t>
+        </is>
+      </c>
+      <c r="G703" s="39" t="inlineStr">
+        <is>
+          <t>ได้ — นักศึกษาชั้นปีสุดท้ายที่เหลือวิชาไม่ถึง 9 หน่วยกิตหรือต้องลงเกิน 22 หน่วยกิตเพื่อสำเร็จการศึกษา สามารถลงทะเบียนได้ไม่เกิน 27 หน่วยกิตในภาคการศึกษาปกติ (ข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี ภาคผนวก มคอ.2 AIT 2566 หน้า 82) โดยหลักสูตร DSBA 2565 มีหน่วยกิตรวม 132 หน่วยกิต และนักศึกษาปีสุดท้ายสามารถลงวิชาได้สูงสุด 27 หน่วยกิตในภาคเดียว หากจำเป็นต้องสำเร็จการศึกษา.</t>
+        </is>
+      </c>
+      <c r="H703" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 82</t>
+        </is>
+      </c>
+      <c r="I703" s="39" t="inlineStr">
+        <is>
+          <t>ข้อบังคับปริญญาตรี (ภาคผนวกเล่ม AIT 2566) → Typhoon เรียบเรียง</t>
+        </is>
+      </c>
+      <c r="J703" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K703" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L703" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M703" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก ข้อบังคับ ป.ตรี (AIT 2566 ภาคผนวก หน้า 82, 87, 89))</t>
+        </is>
+      </c>
+      <c r="N703" s="39" t="inlineStr">
+        <is>
+          <t>2.44s</t>
+        </is>
+      </c>
+      <c r="O703" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="704" ht="14.25" customHeight="1" s="36">
+      <c r="A704" s="37" t="inlineStr">
+        <is>
+          <t>SC6</t>
+        </is>
+      </c>
+      <c r="B704" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C704" s="39" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="D704" s="39" t="inlineStr">
+        <is>
+          <t>ติดโปรอยู่ ต้องดึงเกรดเฉลี่ยสะสมให้ได้เท่าไรถึงจะหลุดโปร</t>
+        </is>
+      </c>
+      <c r="E704" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F704" s="39" t="inlineStr">
+        <is>
+          <t>ไม่ต่ำกว่า 2.00</t>
+        </is>
+      </c>
+      <c r="G704" s="39" t="inlineStr">
+        <is>
+          <t>การภาคทัณฑ์ — ข้อ 31 ตามข้อบังคับ สจล. ว่าด้วยการศึกษาระดับปริญญาตรี (ภาคผนวกในเล่ม มคอ.2 AIT 2566) หน้า 87
+(ข้อบังคับของสถาบัน ใช้กับทุกหลักสูตรปริญญาตรี)
+- นักศึกษาที่ได้ค่าระดับคะแนนเฉลี่ยสะสมต่ำกว่า 2.00 ต้องถูกภาคทัณฑ์
+- จะพ้นภาคทัณฑ์เมื่อค่าระดับคะแนนเฉลี่ยสะสมไม่ต่ำกว่า 2.00 (นับรวมภาคการศึกษาพิเศษด้วย)
+- ถ้าระหว่างภาคทัณฑ์ได้ค่าระดับคะแนนเฉลี่ยประจำภาคถัดไปต่ำกว่า 2.00 จะพ้นสภาพนักศึกษา (ข้อ 43.10)</t>
+        </is>
+      </c>
+      <c r="H704" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 87</t>
+        </is>
+      </c>
+      <c r="I704" s="39" t="inlineStr">
+        <is>
+          <t>ข้อบังคับปริญญาตรี (ภาคผนวกเล่ม AIT 2566) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J704" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K704" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L704" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M704" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก ข้อบังคับ ป.ตรี (AIT 2566 ภาคผนวก หน้า 82, 87, 89))</t>
+        </is>
+      </c>
+      <c r="N704" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O704" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="705" ht="14.25" customHeight="1" s="36">
+      <c r="A705" s="37" t="inlineStr">
+        <is>
+          <t>SC7</t>
+        </is>
+      </c>
+      <c r="B705" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C705" s="39" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D705" s="39" t="inlineStr">
+        <is>
+          <t>มี 120 หน่วยกิต เกรดเฉลี่ยสะสม 2.10 สำเร็จการศึกษาได้แล้วหรือยัง</t>
+        </is>
+      </c>
+      <c r="E705" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F705" s="39" t="inlineStr">
+        <is>
+          <t>ยัง ขาด 6</t>
+        </is>
+      </c>
+      <c r="G705" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ยังจบไม่ได้
+หลักสูตร BIT 2565 (ปริญญาตรี) ต้องเรียนครบไม่น้อยกว่า 126 หน่วยกิต (หน้า 6)
+- หน่วยกิต: เก็บได้ 120 หน่วยกิต → ยังขาดอีก 6 หน่วยกิต (ต้องครบ 126)
+- เกรดเฉลี่ยสะสม 2.10 → ผ่านเกณฑ์ขั้นต่ำ 2.00 (ข้อ 34)
+- เงื่อนไขอื่นตามข้อ 34: สอบผ่านทุกรายวิชาตามโครงสร้างหลักสูตร และผ่านการสอบภาษาอังกฤษ (English Exit exam)</t>
+        </is>
+      </c>
+      <c r="H705" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 6, 88</t>
+        </is>
+      </c>
+      <c r="I705" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวม + เกรดขั้นต่ำ ข้อ 34) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J705" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K705" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L705" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M705" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N705" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O705" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="706" ht="14.25" customHeight="1" s="36">
+      <c r="A706" s="37" t="inlineStr">
+        <is>
+          <t>SC8</t>
+        </is>
+      </c>
+      <c r="B706" s="38" t="inlineStr">
+        <is>
+          <t>ระดับ 4: ท้าทาย</t>
+        </is>
+      </c>
+      <c r="C706" s="39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D706" s="39" t="inlineStr">
+        <is>
+          <t>AIT กับ BIT หลักสูตรไหนเรียนน้อยกว่า น้อยกว่ากี่หน่วยกิต</t>
+        </is>
+      </c>
+      <c r="E706" s="39" t="inlineStr">
+        <is>
+          <t>ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย) — ชุดที่ระบบไม่เคยเห็น รอบ 9 (ยาก/ท้าทาย)</t>
+        </is>
+      </c>
+      <c r="F706" s="39" t="inlineStr">
+        <is>
+          <t>AIT 120 น้อยกว่า BIT 126 อยู่ 6</t>
+        </is>
+      </c>
+      <c r="G706" s="39" t="inlineStr">
+        <is>
+          <t>คำตอบ: ต่างกัน 6 หน่วยกิต (BIT 2565 (ปริญญาตรี) มากกว่า AIT 2566 (ปริญญาตรี))
+- AIT 2566 (ปริญญาตรี): ไม่น้อยกว่า 120 หน่วยกิต (หน้า 5)
+- BIT 2565 (ปริญญาตรี): ไม่น้อยกว่า 126 หน่วยกิต (หน้า 6)</t>
+        </is>
+      </c>
+      <c r="H706" s="39" t="inlineStr">
+        <is>
+          <t>หน้า 5, 6</t>
+        </is>
+      </c>
+      <c r="I706" s="39" t="inlineStr">
+        <is>
+          <t>Multi-hop SQL (หน่วยกิตรวมข้ามหลักสูตร) — ไม่ผ่าน LLM</t>
+        </is>
+      </c>
+      <c r="J706" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K706" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L706" s="41" t="inlineStr">
+        <is>
+          <t>ถูกครบ</t>
+        </is>
+      </c>
+      <c r="M706" s="39" t="inlineStr">
+        <is>
+          <t>ตรวจอัตโนมัติ: คำตอบมีค่าตามเฉลยครบ (เฉลยจาก teacher_gt/rules_ground_truth.json)</t>
+        </is>
+      </c>
+      <c r="N706" s="39" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+      <c r="O706" s="41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
     <row r="707" ht="14.25" customHeight="1" s="36"/>
     <row r="708" ht="14.25" customHeight="1" s="36"/>
     <row r="709" ht="14.25" customHeight="1" s="36"/>
